--- a/IG/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61968BC0-7399-4A28-AE6C-0836B5E48083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFBEAB3-0E29-4F8E-A1D5-6813AA661763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,11 +20,10 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$120</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -89,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="285">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -503,22 +502,6 @@
     <t>予備</t>
     <rPh sb="0" eb="2">
       <t>ヨビ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>※時間が不足した場合、割愛してください。</t>
-    <rPh sb="1" eb="3">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>フソク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カツアイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1763,13 +1746,7 @@
       <t>ガタ</t>
     </rPh>
     <rPh sb="125" eb="126">
-      <t>ガタ</t>
-    </rPh>
-    <rPh sb="149" eb="151">
-      <t>キサイ</t>
-    </rPh>
-    <rPh sb="152" eb="154">
-      <t>ヒツヨウ</t>
+      <t>ガタキサイヒツヨウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2298,12 +2275,909 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>Gitとは、「ドキュメントやソースコードなどの変更履歴を管理するためのバージョン管理システム」のこと。
+※変更履歴を時系列で管理し、過去の状態の確認や復元ができます。
+■Gitのメリット
+・変更履歴を残せる
+・以前の状態に戻せる
+・安心して変更や実験ができる</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ユーザ登録の手順を説明する。
+1. VS Codeでプロジェクトを開く(File→Open Folderからプロジェクトのルートディレクトリを選択)
+2. 上部のタブからTerminalを選択し、「New Terminal」をクリックする。
+3. 開いたターミナルで以下2つのコマンドを打つ。
+　1. git config --local user.name "任意の名前"
+  2. git config --local user.email “自身のメールアドレス(@jp.nttdata.comのもの)"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。
+※まとめてコマンドを実行しないように注意する。</t>
+    </r>
+    <rPh sb="3" eb="5">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="282" eb="284">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="290" eb="292">
+      <t>チュウイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ローカルリポジトリの作成手順を説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。</t>
+    </r>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">最初のコミットの手順を説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。
+※コメントは必須であることを強調する。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>キョウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">２回目以降のコミットの手順を説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。
+※コメントは必須であることを強調する。</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>キョウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">過去のコミットの確認方法を説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>カコ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>個人がローカル環境（ローカルリポジトリのみの運用）でGitを使う方法を説明する。
+1. ファイルを編集（作業ディレクトリ）
+   ・sample.txt を編集
+2. 変更内容をステージに追加
+   ・git add sample.txt
+   ※コミットしたい変更を選択する
+3. ステージされた変更を履歴として保存
+   ・git commit -m "初回作成"
+   ※ローカルリポジトリに保存する
+4. 履歴を確認
+   ・git log
+5. 必要に応じて以前の状態へ戻す
+   ・git reset
+   ・git revert</t>
+    <rPh sb="32" eb="34">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">戻す方法を説明する。
+revert：履歴を残して変更を取り消す
+reset：履歴を巻き戻す
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <rPh sb="0" eb="1">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ソフトウェア開発ライフサイクル</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>ソフトウェア開発ライフサイクルの種類</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>TERASOLUNA 開発手順</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>プロジェクトごとのテーラリング</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>V字モデル　– 要求定義 –</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>「要求」と「要件」の違い</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t xml:space="preserve">V字モデル　– システムテスト – </t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t xml:space="preserve">V字モデル　– 受入テスト – </t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>参考：TERASOLUNA開発手順　タスクフロー</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>講義の目的</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>システム開発におけるソフトウェア開発ライフサイクル</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>TERASOLUNA 開発手順</t>
+  </si>
+  <si>
+    <t>プロジェクトごとのテーラリング</t>
+  </si>
+  <si>
+    <t>V字モデル　– 要求定義 –</t>
+  </si>
+  <si>
+    <t>TERASOLUNAとは</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>V字モデル</t>
+  </si>
+  <si>
+    <t>V字モデルとは</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「要求」と「要件」の違い</t>
+  </si>
+  <si>
+    <t>V字モデル</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>V字モデル　– 要求分析 –</t>
+  </si>
+  <si>
+    <t>V字モデル　– 要求分析 –</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>V字モデル　– アーキテクチャ設計 –</t>
+  </si>
+  <si>
+    <t>V字モデル　– アーキテクチャ設計 –</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>V字モデル　– 詳細設計 –</t>
+  </si>
+  <si>
+    <t>V字モデル　– 詳細設計 –</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>V字モデル　– 製造 –</t>
+  </si>
+  <si>
+    <t>V字モデル　– 製造 –</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>V字モデル　– 単体テスト –</t>
+  </si>
+  <si>
+    <t>V字モデル　– 単体テスト –</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t>V字モデル　– 結合テスト –</t>
+    <phoneticPr fontId="24"/>
+  </si>
+  <si>
+    <t xml:space="preserve">V字モデル　– システムテスト – </t>
+  </si>
+  <si>
+    <t xml:space="preserve">V字モデル　– 受入テスト – </t>
+  </si>
+  <si>
+    <t>参考：TERASOLUNA開発手順　タスクフロー</t>
+  </si>
+  <si>
+    <t xml:space="preserve">以下を学習することを説明する。
+・システム開発プロセスを理解する
+本研修では以下を中心に学習することを説明する。
+・製造工程（前半「Webアプリケーション開発-Java&amp;Spring&amp;DB」）
+・単体テスト工程（後半「単体テストとJUnit」）
+</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="34" eb="37">
+      <t>ホンケンシュウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>チュウシン</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ソフトウェア開発ライフサイクル（SDLC）とは、「要件定義、設計、製造、テスト、リリースなど、ソフトウェア開発における各工程と、それらの実施順序や関係性を定義したもの」のこと。</t>
+    <rPh sb="33" eb="35">
+      <t>セイゾウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">各ソフトウェア開発モデルの種類を説明する。
+■ウォーターフォール開発
+　ソフトウェア開発の工程を前から順番に進めていく直線的なモデル
+　アジャイルソフトウェア開発：短いサイクルで設計・実装・テストを繰り返しながら、変化に柔軟に対応して進める反復型・適応型のモデル
+　TERASOLUNA開発手順は、ウォーターフォール開発の一つである。
+■スクラム開発
+　アジャイルソフトウェア開発の代表的な手法の一つ。短い期間（スプリント）ごとに、設計・実装・テストを繰り返しながら機能を完成させていく開発手法。
+重視する4つの価値
+　・プロセスやツールよりも、個人と対話を重視する
+　・包括的なドキュメントよりも、動くソフトウェアを重視する
+　・契約交渉よりも、顧客との協調を重視する
+　・計画に従うことよりも、変化への対応を重視する
+スクラムアカウンタビリティ（役割）の種類
+　・スクラムマスター：スクラムの進行を支援し、チームが円滑に活動できるようサポートする
+　・プロダクトオーナー：開発する機能や優先順位を決定し、プロダクトの価値を最大化する
+　・開発者：設計・実装・テストを行い、成果物を作成する
+</t>
+    <rPh sb="0" eb="1">
+      <t>カク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="160" eb="161">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="377" eb="379">
+      <t>ヤクワリ</t>
+    </rPh>
+    <rPh sb="381" eb="383">
+      <t>シュルイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>TERASOLUNAとは、「NTTD社が提供するオープン系システム開発のための総合ソリューションの総称」のこと。
+その一つである「TERASOLUNA開発標準」は、要求定義から受入テストまでを対象としたシステム開発手順を提供しており、品質を確保するためにV字モデルを採用している。
+TERASOLUNAが提供する主な内容
+・開発手順（プロセス）
+　要求定義から受入テストまでの開発プロセスや成果物の作成方法を提供
+・開発環境
+　フレームワーク、ライブラリ、IDEなどの開発基盤を提供
+・サポート
+　技術情報、Q&amp;A、教育・研修などの支援を提供</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>「TERASOLUNA」により開発手順、開発環境、成果物などを標準化している。
+しかし、すべてのプロジェクトに同じ手順やルールを適用すると、プロジェクトの特性によっては開発効率の低下や進行の妨げとなる場合がある。
+↓
+そのため、プロジェクトの規模や特性に応じて標準を調整する「テーラリング」が認められている。
+※テーラリング：標準プロセスをそのまま適用するのではなく、プロジェクトの特性に合わせて最適化することである。
+また、生成AIを活用した「AIネイティブ開発」では、従来の開発プロセスとは異なる考慮が必要となる。
+そのため、TERASOLUNAで定められた開発手順や成果物についても、生成AIの特性を踏まえたテーラリングが求められる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>V字モデルとは、「開発工程とテスト工程の対応関係をV字型で表現した開発モデル」のこと。
+TERASOLUNA開発手順では、要求定義から受入テストまでの8つのフェーズを対象にV字モデルを採用し、各設計工程の成果物を対応するテスト工程で検証することで品質を確保している。
+※品質の作りこみVS製造・テスト
+■メリット
+・各フェーズが明確で、進捗管理がしやすい
+・設計内容とテスト内容の対応関係が明確で、品質を確保しやすい
+・フェーズごとに成果物を確認するため、問題を早期に発見しやすい
+■デメリット
+・各フェーズが順序立てて実施され、途中での開始/終了ができない
+・前のフェーズの成果物をインプットにしているため、複数フェーズを同時進行できない</t>
+    <rPh sb="136" eb="138">
+      <t>ヒンシツ</t>
+    </rPh>
+    <rPh sb="139" eb="140">
+      <t>ツク</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>セイゾウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>要求定義フェーズについて説明する。
+顧客の抱える問題・課題や目指す将来像を踏まえ、システム化の目的や解決方針を明確にするフェーズ。
+顧客や利害関係者との対話を通じて要求を収集・整理し、システムに求められる機能や制約条件を要求仕様として文書化する。
+実施順序
+　情報収集　→　検討　→　提案</t>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="127" eb="129">
+      <t>ジュンジョ</t>
+    </rPh>
+    <rPh sb="131" eb="133">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>シュウシュウ</t>
+    </rPh>
+    <rPh sb="138" eb="140">
+      <t>ケントウ</t>
+    </rPh>
+    <rPh sb="143" eb="145">
+      <t>テイアン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>要求と要件の違いを説明する。
+・要求（Requirement）
+　顧客やユーザーが実現したいこと、解決したい課題、期待する結果。
+　「何を実現したいか」を表す。
+・要件（System Requirement）
+　要求を実現するために、システムが満たすべき具体的な条件や機能。
+　「何を備える必要があるか」を表す。</t>
+    <rPh sb="3" eb="5">
+      <t>ヨウケン</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">要求分析フェーズについて説明する。
+顧客と合意した要求を分析・整理し、システムとして実現すべき要件を明確化するフェーズ。
+要求分析では、要求を機能要求と非機能要求に分類し、システムに必要な要件を定義する。
+・機能要求
+　システムがユーザーに対して提供する機能やサービスに関する要件。
+　例：ユーザ登録機能、商品検索機能など
+・非機能要求
+　機能以外の品質や運用に関する要件。
+　例：可用性、性能・拡張性、運用・保守性、セキュリティなど
+業務フロー定義の概要を説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">※タスクやアクティビティという言葉は触れない。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+成果物の概要を説明する。
+・業務フロー図
+・ユースケース定義書
+・画面遷移図
+・画面定義書
+・外部IF定義書
+・ER図
+・エンティティ定義書</t>
+    </r>
+    <rPh sb="2" eb="4">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="154" eb="156">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="221" eb="223">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="226" eb="228">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="229" eb="231">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="232" eb="234">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="263" eb="266">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="267" eb="269">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="270" eb="272">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="282" eb="283">
+      <t>ズ</t>
+    </rPh>
+    <rPh sb="291" eb="293">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="293" eb="294">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="296" eb="298">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="298" eb="301">
+      <t>センイズ</t>
+    </rPh>
+    <rPh sb="303" eb="305">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="310" eb="312">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="314" eb="316">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="316" eb="317">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="321" eb="322">
+      <t>ズ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アーキテクチャ設計フェーズについて説明する。
+要求分析フェーズで定義した要件を実現するための実現方法（入出力、処理、データ構造など）を決めるフェーズ。
+要求定義の成果物（定義書）→アーキテクチャ設計→XXX設計書
+成果物の概要を説明する。
+・オンライン処理設計書
+・画面設計書
+・画面定義書
+・外部IF設計書
+・テーブル設計書</t>
+    <rPh sb="7" eb="9">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="76" eb="80">
+      <t>ヨウキュウテイギ</t>
+    </rPh>
+    <rPh sb="81" eb="84">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="87" eb="88">
+      <t>ショ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="103" eb="106">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="108" eb="111">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="136" eb="139">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>ガイブ</t>
+    </rPh>
+    <rPh sb="152" eb="155">
+      <t>セッケイショ</t>
+    </rPh>
+    <rPh sb="161" eb="164">
+      <t>セッケイショ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>詳細設計フェーズについて説明する。
+アーキテクチャ設計を元に、そのまま開発できるレベルまで詳細化するフェーズ。
+※独自に設計書を書き起こす必要がないと判断され、省略されることが多い
+成果物の概要を説明する。
+・ユニット設計書</t>
+    <rPh sb="0" eb="2">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="92" eb="95">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="110" eb="113">
+      <t>セッケイショ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>製造フェーズについて説明する。
+詳細設計通りに動作するプログラムコードを作成するフェーズ。
+成果物の概要を説明する。
+・プログラムコード</t>
+    <rPh sb="0" eb="2">
+      <t>セイゾウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="47" eb="50">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>単体テストフェーズについて説明する。
+アプリケーションが詳細設計通りに動作するかを確認するフェーズ。
+成果物の概要を説明する。
+・ユニット計画書
+・ユニットテストケース表
+・ユニットテストコード
+・ユニットテスト手順書</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="70" eb="73">
+      <t>ケイカクショ</t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t>ヒョウ</t>
+    </rPh>
+    <rPh sb="107" eb="110">
+      <t>テジュンショ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>V字モデル　– 結合テスト –</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>結合テストフェーズについて説明する。
+アプリケーションが要件/設計通りに動作するかを確認するフェーズ。
+テストの種類が分かれていることを説明する。
+・処理テスト：処理設計の妥当性を検証する。
+・ユースケーステスト：ユースケース定義の妥当性を検証する。
+・業務テスト：業務定義の妥当性を検証する。
+※システムの詳細な部分からテストを実施し、テスト対象範囲を少しずつ広くしていく</t>
+    <rPh sb="0" eb="2">
+      <t>ケツゴウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="47" eb="50">
+      <t>セイカブツ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="57" eb="59">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>ワ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>ショリ</t>
+    </rPh>
+    <rPh sb="84" eb="86">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="87" eb="90">
+      <t>ダトウセイ</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>ケンショウ</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="136" eb="138">
+      <t>テイギ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">システムテストフェーズについて説明する。
+システム基盤とアプリケーションを結合したシステム全体に対して、機能要求と非機能要求を満たすかどうかを確認するフェーズ。
+機能要求を満たしているかを確認するテストのほかに、性能テスト、負荷テスト、ユーザビリティテストなどの非機能要求に対するテストを実施する。
+</t>
+    <rPh sb="15" eb="17">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>受入テストフェーズについて説明する。
+システム移行準備とシステムテストが完了したシステムに対して、顧客と最終確認を行い、本番移行を実施するフェーズ。
+主要な作業を説明する。
+・移行計画と設計
+・移行支援ツール等の開発
+・移行テストの計画、設計、実施
+・受入テストの計画、設計、実施
+・移行リハーサル実施
+・移行実施</t>
+    <rPh sb="0" eb="2">
+      <t>ウケイレ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="76" eb="78">
+      <t>シュヨウ</t>
+    </rPh>
+    <rPh sb="79" eb="81">
+      <t>サギョウ</t>
+    </rPh>
+    <rPh sb="82" eb="84">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2474,6 +3348,13 @@
       <name val="ＭＳ Ｐゴシック"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="11">
@@ -2736,7 +3617,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3025,6 +3906,33 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -3076,6 +3984,33 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3085,15 +4020,6 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -3103,15 +4029,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -3120,18 +4037,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3505,15 +4410,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="97" t="str">
+      <c r="B2" s="106" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -3526,10 +4431,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="98" t="s">
+      <c r="B4" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="99"/>
+      <c r="C4" s="108"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -3537,18 +4442,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="100"/>
-      <c r="C5" s="101"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="110"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="102"/>
+      <c r="C7" s="111"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="27"/>
@@ -3608,7 +4513,7 @@
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="F14" s="96"/>
+      <c r="F14" s="105"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -3617,7 +4522,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="87"/>
-      <c r="F15" s="96"/>
+      <c r="F15" s="105"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -3626,7 +4531,7 @@
       </c>
       <c r="B16" s="44"/>
       <c r="C16" s="88"/>
-      <c r="F16" s="96"/>
+      <c r="F16" s="105"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
@@ -3638,14 +4543,14 @@
         <f>master!B13</f>
         <v>0</v>
       </c>
-      <c r="F17" s="96"/>
+      <c r="F17" s="105"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="41"/>
       <c r="B18" s="44"/>
       <c r="C18" s="88"/>
-      <c r="F18" s="96"/>
+      <c r="F18" s="105"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -3657,7 +4562,7 @@
         <f>master!B18</f>
         <v>0</v>
       </c>
-      <c r="F19" s="96"/>
+      <c r="F19" s="105"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -3671,14 +4576,14 @@
         <f>master!B23</f>
         <v>0</v>
       </c>
-      <c r="F20" s="96"/>
+      <c r="F20" s="105"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="61"/>
       <c r="B21" s="63"/>
       <c r="C21" s="88"/>
-      <c r="F21" s="96"/>
+      <c r="F21" s="105"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -3731,7 +4636,7 @@
         <v>0.5625</v>
       </c>
       <c r="C26" s="88"/>
-      <c r="F26" s="96"/>
+      <c r="F26" s="105"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -3744,7 +4649,7 @@
         <f>master!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F27" s="96"/>
+      <c r="F27" s="105"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -3754,7 +4659,7 @@
       </c>
       <c r="B28" s="44"/>
       <c r="C28" s="88"/>
-      <c r="F28" s="96"/>
+      <c r="F28" s="105"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -3768,7 +4673,7 @@
       </c>
       <c r="D29" s="60"/>
       <c r="E29" s="57"/>
-      <c r="F29" s="96"/>
+      <c r="F29" s="105"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -3777,7 +4682,7 @@
       <c r="C30" s="64"/>
       <c r="D30" s="60"/>
       <c r="E30" s="57"/>
-      <c r="F30" s="96"/>
+      <c r="F30" s="105"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -3786,7 +4691,7 @@
       <c r="C31" s="64"/>
       <c r="D31" s="60"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="96"/>
+      <c r="F31" s="105"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -3797,7 +4702,7 @@
       <c r="C32" s="64"/>
       <c r="D32" s="60"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="96"/>
+      <c r="F32" s="105"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -3806,7 +4711,7 @@
       <c r="C33" s="64"/>
       <c r="D33" s="60"/>
       <c r="E33" s="57"/>
-      <c r="F33" s="96"/>
+      <c r="F33" s="105"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -3820,7 +4725,7 @@
       </c>
       <c r="D34" s="60"/>
       <c r="E34" s="57"/>
-      <c r="F34" s="96"/>
+      <c r="F34" s="105"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -3829,7 +4734,7 @@
       <c r="C35" s="64"/>
       <c r="D35" s="60"/>
       <c r="E35" s="57"/>
-      <c r="F35" s="96"/>
+      <c r="F35" s="105"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -3840,7 +4745,7 @@
       <c r="C36" s="64"/>
       <c r="D36" s="60"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="96"/>
+      <c r="F36" s="105"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -3849,7 +4754,7 @@
       <c r="C37" s="64"/>
       <c r="D37" s="60"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="96"/>
+      <c r="F37" s="105"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -3858,7 +4763,7 @@
       <c r="C38" s="64"/>
       <c r="D38" s="60"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="96"/>
+      <c r="F38" s="105"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -3867,7 +4772,7 @@
       <c r="C39" s="70"/>
       <c r="D39" s="60"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="96"/>
+      <c r="F39" s="105"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -3878,11 +4783,11 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D40" s="60"/>
       <c r="E40" s="57"/>
-      <c r="F40" s="96"/>
+      <c r="F40" s="105"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -3891,7 +4796,7 @@
       <c r="C41" s="64"/>
       <c r="D41" s="62"/>
       <c r="E41" s="58"/>
-      <c r="F41" s="96"/>
+      <c r="F41" s="105"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -3900,7 +4805,7 @@
       <c r="C42" s="65"/>
       <c r="D42" s="60"/>
       <c r="E42" s="58"/>
-      <c r="F42" s="96"/>
+      <c r="F42" s="105"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
@@ -3987,10 +4892,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="108"/>
+      <c r="C4" s="117"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4001,16 +4906,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4023,10 +4928,10 @@
         <v>16</v>
       </c>
       <c r="C7" s="36"/>
-      <c r="D7" s="110" t="s">
+      <c r="D7" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="110"/>
+      <c r="E7" s="119"/>
       <c r="F7" s="36" t="s">
         <v>11</v>
       </c>
@@ -4066,46 +4971,46 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="104"/>
-      <c r="C11" s="104" t="s">
+      <c r="B11" s="113"/>
+      <c r="C11" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="104" t="s">
+      <c r="D11" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="104"/>
-      <c r="F11" s="104"/>
-      <c r="G11" s="104" t="s">
+      <c r="E11" s="113"/>
+      <c r="F11" s="113"/>
+      <c r="G11" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="111" t="s">
+      <c r="H11" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="103" t="s">
+      <c r="I11" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103" t="s">
+      <c r="J11" s="112"/>
+      <c r="K11" s="112" t="s">
         <v>34</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="112"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="113"/>
+      <c r="H12" s="121"/>
       <c r="I12" s="31" t="s">
         <v>27</v>
       </c>
       <c r="J12" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="104"/>
+      <c r="K12" s="113"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
@@ -4114,11 +5019,11 @@
       <c r="C13" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="105" t="s">
+      <c r="D13" s="114" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="106"/>
-      <c r="F13" s="107"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="116"/>
       <c r="G13" s="66" t="s">
         <v>59</v>
       </c>
@@ -4138,11 +5043,11 @@
       <c r="C14" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="105" t="s">
+      <c r="D14" s="114" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="106"/>
-      <c r="F14" s="107"/>
+      <c r="E14" s="115"/>
+      <c r="F14" s="116"/>
       <c r="G14" s="82" t="s">
         <v>60</v>
       </c>
@@ -4192,7 +5097,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N102"/>
+  <dimension ref="A2:N121"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -4242,12 +5147,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="108" t="s">
+      <c r="B4" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="108"/>
-      <c r="D4" s="108"/>
-      <c r="E4" s="108"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -4258,30 +5163,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="115"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="115"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="115"/>
-      <c r="J5" s="115"/>
-      <c r="K5" s="115"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="133"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="133"/>
+      <c r="F5" s="133"/>
+      <c r="G5" s="133"/>
+      <c r="H5" s="133"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="133"/>
+      <c r="K5" s="133"/>
       <c r="L5" s="32"/>
       <c r="M5" s="33"/>
     </row>
     <row r="6" spans="2:14" ht="32.4" customHeight="1">
-      <c r="B6" s="115"/>
-      <c r="C6" s="115"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="115"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="115"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="115"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="115"/>
+      <c r="B6" s="133"/>
+      <c r="C6" s="133"/>
+      <c r="D6" s="133"/>
+      <c r="E6" s="133"/>
+      <c r="F6" s="133"/>
+      <c r="G6" s="133"/>
+      <c r="H6" s="133"/>
+      <c r="I6" s="133"/>
+      <c r="J6" s="133"/>
+      <c r="K6" s="133"/>
       <c r="L6" s="32"/>
       <c r="M6" s="33"/>
     </row>
@@ -4364,7 +5269,7 @@
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C11" s="39" t="s">
         <v>40</v>
@@ -4386,10 +5291,10 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" s="37" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C12" s="73" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D12" s="39" t="s">
         <v>21</v>
@@ -4408,10 +5313,10 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C13" s="39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D13" s="39" t="s">
         <v>21</v>
@@ -4430,7 +5335,7 @@
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C14" s="73" t="s">
         <v>42</v>
@@ -4452,7 +5357,7 @@
     </row>
     <row r="15" spans="2:14">
       <c r="B15" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" s="73" t="s">
         <v>43</v>
@@ -4474,7 +5379,7 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C16" s="73" t="s">
         <v>46</v>
@@ -4525,28 +5430,28 @@
     </row>
     <row r="20" spans="1:14" ht="24" customHeight="1">
       <c r="A20" s="10"/>
-      <c r="B20" s="104" t="s">
+      <c r="B20" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="104" t="s">
+      <c r="D20" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104" t="s">
+      <c r="E20" s="113"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="103" t="s">
+      <c r="H20" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="113" t="s">
+      <c r="I20" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="J20" s="114"/>
-      <c r="K20" s="103" t="s">
+      <c r="J20" s="132"/>
+      <c r="K20" s="112" t="s">
         <v>36</v>
       </c>
       <c r="L20" s="6"/>
@@ -4555,20 +5460,20 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="10"/>
-      <c r="B21" s="104"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="103"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="113"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="112"/>
       <c r="I21" s="31" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="104"/>
+      <c r="K21" s="113"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
@@ -4583,13 +5488,13 @@
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D22" s="116" t="s">
+      <c r="D22" s="122" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="123"/>
+      <c r="F22" s="124"/>
+      <c r="G22" s="55" t="s">
         <v>107</v>
-      </c>
-      <c r="E22" s="117"/>
-      <c r="F22" s="118"/>
-      <c r="G22" s="55" t="s">
-        <v>108</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="52" t="s">
@@ -4605,7 +5510,7 @@
     </row>
     <row r="23" spans="1:14" ht="138.6" customHeight="1">
       <c r="A23" s="10"/>
-      <c r="B23" s="119" t="str">
+      <c r="B23" s="134" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -4613,11 +5518,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D23" s="116" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="117"/>
-      <c r="F23" s="118"/>
+      <c r="D23" s="122" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="123"/>
+      <c r="F23" s="124"/>
       <c r="G23" s="55" t="s">
         <v>48</v>
       </c>
@@ -4635,16 +5540,16 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="120"/>
+      <c r="B24" s="135"/>
       <c r="C24" s="55" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D24" s="116" t="s">
-        <v>110</v>
-      </c>
-      <c r="E24" s="117"/>
-      <c r="F24" s="118"/>
+      <c r="D24" s="122" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="123"/>
+      <c r="F24" s="124"/>
       <c r="G24" s="55" t="s">
         <v>52</v>
       </c>
@@ -4662,16 +5567,16 @@
     </row>
     <row r="25" spans="1:14" ht="37.799999999999997">
       <c r="A25" s="11"/>
-      <c r="B25" s="120"/>
+      <c r="B25" s="135"/>
       <c r="C25" s="55" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D25" s="116" t="s">
-        <v>111</v>
-      </c>
-      <c r="E25" s="117"/>
-      <c r="F25" s="118"/>
+      <c r="D25" s="122" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="123"/>
+      <c r="F25" s="124"/>
       <c r="G25" s="55" t="s">
         <v>50</v>
       </c>
@@ -4689,16 +5594,16 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="120"/>
+      <c r="B26" s="135"/>
       <c r="C26" s="55" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D26" s="116" t="s">
-        <v>112</v>
-      </c>
-      <c r="E26" s="117"/>
-      <c r="F26" s="118"/>
+      <c r="D26" s="122" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="123"/>
+      <c r="F26" s="124"/>
       <c r="G26" s="55" t="s">
         <v>49</v>
       </c>
@@ -4716,13 +5621,13 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="120"/>
+      <c r="B27" s="135"/>
       <c r="C27" s="55"/>
-      <c r="D27" s="116" t="s">
-        <v>113</v>
-      </c>
-      <c r="E27" s="117"/>
-      <c r="F27" s="118"/>
+      <c r="D27" s="122" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="123"/>
+      <c r="F27" s="124"/>
       <c r="G27" s="55" t="s">
         <v>49</v>
       </c>
@@ -4740,16 +5645,16 @@
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="121"/>
+      <c r="B28" s="136"/>
       <c r="C28" s="55" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D28" s="116" t="s">
-        <v>114</v>
-      </c>
-      <c r="E28" s="117"/>
-      <c r="F28" s="118"/>
+      <c r="D28" s="122" t="s">
+        <v>113</v>
+      </c>
+      <c r="E28" s="123"/>
+      <c r="F28" s="124"/>
       <c r="G28" s="55" t="s">
         <v>53</v>
       </c>
@@ -4767,7 +5672,7 @@
     </row>
     <row r="29" spans="1:14" ht="102" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="119" t="str">
+      <c r="B29" s="134" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -4775,11 +5680,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D29" s="116" t="s">
-        <v>115</v>
-      </c>
-      <c r="E29" s="117"/>
-      <c r="F29" s="118"/>
+      <c r="D29" s="122" t="s">
+        <v>114</v>
+      </c>
+      <c r="E29" s="123"/>
+      <c r="F29" s="124"/>
       <c r="G29" s="55" t="s">
         <v>50</v>
       </c>
@@ -4797,16 +5702,16 @@
     </row>
     <row r="30" spans="1:14" ht="88.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="120"/>
+      <c r="B30" s="135"/>
       <c r="C30" s="55" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D30" s="116" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" s="117"/>
-      <c r="F30" s="118"/>
+      <c r="D30" s="122" t="s">
+        <v>115</v>
+      </c>
+      <c r="E30" s="123"/>
+      <c r="F30" s="124"/>
       <c r="G30" s="55" t="s">
         <v>54</v>
       </c>
@@ -4824,16 +5729,16 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="120"/>
+      <c r="B31" s="135"/>
       <c r="C31" s="55" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D31" s="116" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" s="117"/>
-      <c r="F31" s="118"/>
+      <c r="D31" s="122" t="s">
+        <v>116</v>
+      </c>
+      <c r="E31" s="123"/>
+      <c r="F31" s="124"/>
       <c r="G31" s="55" t="s">
         <v>55</v>
       </c>
@@ -4845,7 +5750,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K31" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
@@ -4853,16 +5758,16 @@
     </row>
     <row r="32" spans="1:14" ht="75.599999999999994">
       <c r="A32" s="11"/>
-      <c r="B32" s="120"/>
+      <c r="B32" s="135"/>
       <c r="C32" s="55" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D32" s="116" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="117"/>
-      <c r="F32" s="118"/>
+      <c r="D32" s="122" t="s">
+        <v>117</v>
+      </c>
+      <c r="E32" s="123"/>
+      <c r="F32" s="124"/>
       <c r="G32" s="55" t="s">
         <v>52</v>
       </c>
@@ -4880,16 +5785,16 @@
     </row>
     <row r="33" spans="1:14" ht="100.8">
       <c r="A33" s="11"/>
-      <c r="B33" s="120"/>
+      <c r="B33" s="135"/>
       <c r="C33" s="55" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D33" s="116" t="s">
-        <v>119</v>
-      </c>
-      <c r="E33" s="117"/>
-      <c r="F33" s="118"/>
+      <c r="D33" s="122" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="123"/>
+      <c r="F33" s="124"/>
       <c r="G33" s="55" t="s">
         <v>56</v>
       </c>
@@ -4907,16 +5812,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="120"/>
+      <c r="B34" s="135"/>
       <c r="C34" s="55" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D34" s="116" t="s">
-        <v>120</v>
-      </c>
-      <c r="E34" s="117"/>
-      <c r="F34" s="118"/>
+      <c r="D34" s="122" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="123"/>
+      <c r="F34" s="124"/>
       <c r="G34" s="55" t="s">
         <v>50</v>
       </c>
@@ -4934,16 +5839,16 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="120"/>
+      <c r="B35" s="135"/>
       <c r="C35" s="55" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D35" s="116" t="s">
-        <v>121</v>
-      </c>
-      <c r="E35" s="117"/>
-      <c r="F35" s="118"/>
+      <c r="D35" s="122" t="s">
+        <v>120</v>
+      </c>
+      <c r="E35" s="123"/>
+      <c r="F35" s="124"/>
       <c r="G35" s="55" t="s">
         <v>50</v>
       </c>
@@ -4961,16 +5866,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="121"/>
+      <c r="B36" s="136"/>
       <c r="C36" s="55" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D36" s="116" t="s">
-        <v>122</v>
-      </c>
-      <c r="E36" s="117"/>
-      <c r="F36" s="118"/>
+      <c r="D36" s="122" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="123"/>
+      <c r="F36" s="124"/>
       <c r="G36" s="55" t="s">
         <v>50</v>
       </c>
@@ -4988,7 +5893,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="119" t="str">
+      <c r="B37" s="134" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -4996,11 +5901,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D37" s="116" t="s">
-        <v>123</v>
-      </c>
-      <c r="E37" s="117"/>
-      <c r="F37" s="118"/>
+      <c r="D37" s="122" t="s">
+        <v>122</v>
+      </c>
+      <c r="E37" s="123"/>
+      <c r="F37" s="124"/>
       <c r="G37" s="55" t="s">
         <v>54</v>
       </c>
@@ -5018,16 +5923,16 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="120"/>
+      <c r="B38" s="135"/>
       <c r="C38" s="55" t="str">
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D38" s="116" t="s">
-        <v>124</v>
-      </c>
-      <c r="E38" s="117"/>
-      <c r="F38" s="118"/>
+      <c r="D38" s="122" t="s">
+        <v>123</v>
+      </c>
+      <c r="E38" s="123"/>
+      <c r="F38" s="124"/>
       <c r="G38" s="55" t="s">
         <v>52</v>
       </c>
@@ -5045,16 +5950,16 @@
     </row>
     <row r="39" spans="1:14" ht="75.599999999999994">
       <c r="A39" s="11"/>
-      <c r="B39" s="120"/>
+      <c r="B39" s="135"/>
       <c r="C39" s="55" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D39" s="116" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="117"/>
-      <c r="F39" s="118"/>
+      <c r="D39" s="122" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="123"/>
+      <c r="F39" s="124"/>
       <c r="G39" s="55" t="s">
         <v>52</v>
       </c>
@@ -5072,16 +5977,16 @@
     </row>
     <row r="40" spans="1:14" ht="50.4">
       <c r="A40" s="11"/>
-      <c r="B40" s="120"/>
+      <c r="B40" s="135"/>
       <c r="C40" s="55" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D40" s="116" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="117"/>
-      <c r="F40" s="118"/>
+      <c r="D40" s="122" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="123"/>
+      <c r="F40" s="124"/>
       <c r="G40" s="55" t="s">
         <v>51</v>
       </c>
@@ -5099,16 +6004,16 @@
     </row>
     <row r="41" spans="1:14" ht="88.2">
       <c r="A41" s="11"/>
-      <c r="B41" s="120"/>
+      <c r="B41" s="135"/>
       <c r="C41" s="55" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D41" s="116" t="s">
-        <v>128</v>
-      </c>
-      <c r="E41" s="117"/>
-      <c r="F41" s="118"/>
+      <c r="D41" s="122" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" s="123"/>
+      <c r="F41" s="124"/>
       <c r="G41" s="55" t="s">
         <v>54</v>
       </c>
@@ -5120,7 +6025,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K41" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -5128,18 +6033,18 @@
     </row>
     <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
-      <c r="B42" s="120"/>
+      <c r="B42" s="135"/>
       <c r="C42" s="55" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D42" s="116" t="s">
+      <c r="D42" s="122" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42" s="123"/>
+      <c r="F42" s="124"/>
+      <c r="G42" s="55" t="s">
         <v>129</v>
-      </c>
-      <c r="E42" s="117"/>
-      <c r="F42" s="118"/>
-      <c r="G42" s="55" t="s">
-        <v>130</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="52" t="s">
@@ -5155,16 +6060,16 @@
     </row>
     <row r="43" spans="1:14" ht="37.799999999999997">
       <c r="A43" s="11"/>
-      <c r="B43" s="120"/>
+      <c r="B43" s="135"/>
       <c r="C43" s="55" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D43" s="116" t="s">
-        <v>131</v>
-      </c>
-      <c r="E43" s="117"/>
-      <c r="F43" s="118"/>
+      <c r="D43" s="122" t="s">
+        <v>130</v>
+      </c>
+      <c r="E43" s="123"/>
+      <c r="F43" s="124"/>
       <c r="G43" s="55" t="s">
         <v>50</v>
       </c>
@@ -5182,18 +6087,18 @@
     </row>
     <row r="44" spans="1:14" ht="163.80000000000001">
       <c r="A44" s="11"/>
-      <c r="B44" s="120"/>
+      <c r="B44" s="135"/>
       <c r="C44" s="55" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D44" s="116" t="s">
+      <c r="D44" s="122" t="s">
+        <v>131</v>
+      </c>
+      <c r="E44" s="123"/>
+      <c r="F44" s="124"/>
+      <c r="G44" s="55" t="s">
         <v>132</v>
-      </c>
-      <c r="E44" s="117"/>
-      <c r="F44" s="118"/>
-      <c r="G44" s="55" t="s">
-        <v>133</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="52" t="s">
@@ -5209,16 +6114,16 @@
     </row>
     <row r="45" spans="1:14" ht="25.2">
       <c r="A45" s="11"/>
-      <c r="B45" s="120"/>
+      <c r="B45" s="135"/>
       <c r="C45" s="55" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D45" s="116" t="s">
-        <v>134</v>
-      </c>
-      <c r="E45" s="117"/>
-      <c r="F45" s="118"/>
+      <c r="D45" s="122" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="123"/>
+      <c r="F45" s="124"/>
       <c r="G45" s="55" t="s">
         <v>55</v>
       </c>
@@ -5236,18 +6141,18 @@
     </row>
     <row r="46" spans="1:14" ht="189">
       <c r="A46" s="11"/>
-      <c r="B46" s="120"/>
+      <c r="B46" s="135"/>
       <c r="C46" s="55" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D46" s="116" t="s">
+      <c r="D46" s="122" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="123"/>
+      <c r="F46" s="124"/>
+      <c r="G46" s="55" t="s">
         <v>135</v>
-      </c>
-      <c r="E46" s="117"/>
-      <c r="F46" s="118"/>
-      <c r="G46" s="55" t="s">
-        <v>136</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="52" t="s">
@@ -5263,16 +6168,16 @@
     </row>
     <row r="47" spans="1:14" ht="88.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="120"/>
+      <c r="B47" s="135"/>
       <c r="C47" s="55" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D47" s="116" t="s">
-        <v>137</v>
-      </c>
-      <c r="E47" s="117"/>
-      <c r="F47" s="118"/>
+      <c r="D47" s="122" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="123"/>
+      <c r="F47" s="124"/>
       <c r="G47" s="55" t="s">
         <v>54</v>
       </c>
@@ -5284,7 +6189,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K47" s="46" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
@@ -5292,16 +6197,16 @@
     </row>
     <row r="48" spans="1:14" ht="63">
       <c r="A48" s="11"/>
-      <c r="B48" s="120"/>
+      <c r="B48" s="135"/>
       <c r="C48" s="55" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D48" s="116" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" s="117"/>
-      <c r="F48" s="118"/>
+      <c r="D48" s="122" t="s">
+        <v>137</v>
+      </c>
+      <c r="E48" s="123"/>
+      <c r="F48" s="124"/>
       <c r="G48" s="55" t="s">
         <v>49</v>
       </c>
@@ -5319,16 +6224,16 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="120"/>
+      <c r="B49" s="135"/>
       <c r="C49" s="55" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D49" s="116" t="s">
-        <v>139</v>
-      </c>
-      <c r="E49" s="117"/>
-      <c r="F49" s="118"/>
+      <c r="D49" s="122" t="s">
+        <v>138</v>
+      </c>
+      <c r="E49" s="123"/>
+      <c r="F49" s="124"/>
       <c r="G49" s="55" t="s">
         <v>56</v>
       </c>
@@ -5346,16 +6251,16 @@
     </row>
     <row r="50" spans="1:14" ht="100.8">
       <c r="A50" s="11"/>
-      <c r="B50" s="120"/>
+      <c r="B50" s="135"/>
       <c r="C50" s="55" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D50" s="116" t="s">
-        <v>140</v>
-      </c>
-      <c r="E50" s="117"/>
-      <c r="F50" s="118"/>
+      <c r="D50" s="122" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="123"/>
+      <c r="F50" s="124"/>
       <c r="G50" s="55" t="s">
         <v>56</v>
       </c>
@@ -5373,16 +6278,16 @@
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="120"/>
+      <c r="B51" s="135"/>
       <c r="C51" s="55" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D51" s="116" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" s="117"/>
-      <c r="F51" s="118"/>
+      <c r="D51" s="122" t="s">
+        <v>140</v>
+      </c>
+      <c r="E51" s="123"/>
+      <c r="F51" s="124"/>
       <c r="G51" s="55" t="s">
         <v>54</v>
       </c>
@@ -5400,16 +6305,16 @@
     </row>
     <row r="52" spans="1:14" ht="63">
       <c r="A52" s="11"/>
-      <c r="B52" s="120"/>
+      <c r="B52" s="135"/>
       <c r="C52" s="55" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D52" s="116" t="s">
-        <v>142</v>
-      </c>
-      <c r="E52" s="117"/>
-      <c r="F52" s="118"/>
+      <c r="D52" s="122" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" s="123"/>
+      <c r="F52" s="124"/>
       <c r="G52" s="55" t="s">
         <v>49</v>
       </c>
@@ -5427,16 +6332,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="120"/>
+      <c r="B53" s="135"/>
       <c r="C53" s="55" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D53" s="116" t="s">
-        <v>143</v>
-      </c>
-      <c r="E53" s="117"/>
-      <c r="F53" s="118"/>
+      <c r="D53" s="122" t="s">
+        <v>142</v>
+      </c>
+      <c r="E53" s="123"/>
+      <c r="F53" s="124"/>
       <c r="G53" s="55" t="s">
         <v>51</v>
       </c>
@@ -5454,16 +6359,16 @@
     </row>
     <row r="54" spans="1:14" ht="88.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="120"/>
+      <c r="B54" s="135"/>
       <c r="C54" s="55" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D54" s="116" t="s">
-        <v>144</v>
-      </c>
-      <c r="E54" s="117"/>
-      <c r="F54" s="118"/>
+      <c r="D54" s="122" t="s">
+        <v>143</v>
+      </c>
+      <c r="E54" s="123"/>
+      <c r="F54" s="124"/>
       <c r="G54" s="55" t="s">
         <v>54</v>
       </c>
@@ -5481,14 +6386,14 @@
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="121"/>
+      <c r="B55" s="136"/>
       <c r="C55" s="55" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D55" s="116"/>
-      <c r="E55" s="117"/>
-      <c r="F55" s="118"/>
+      <c r="D55" s="122"/>
+      <c r="E55" s="123"/>
+      <c r="F55" s="124"/>
       <c r="G55" s="55" t="s">
         <v>55</v>
       </c>
@@ -5506,7 +6411,7 @@
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="125" t="str">
+      <c r="B56" s="137" t="str">
         <f>master!B37</f>
         <v>導入</v>
       </c>
@@ -5514,11 +6419,11 @@
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D56" s="122" t="s">
-        <v>187</v>
-      </c>
-      <c r="E56" s="123"/>
-      <c r="F56" s="124"/>
+      <c r="D56" s="128" t="s">
+        <v>186</v>
+      </c>
+      <c r="E56" s="129"/>
+      <c r="F56" s="130"/>
       <c r="G56" s="77" t="s">
         <v>50</v>
       </c>
@@ -5536,16 +6441,16 @@
     </row>
     <row r="57" spans="1:14" ht="37.799999999999997">
       <c r="A57" s="11"/>
-      <c r="B57" s="126"/>
+      <c r="B57" s="138"/>
       <c r="C57" s="77" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D57" s="122" t="s">
-        <v>188</v>
-      </c>
-      <c r="E57" s="123"/>
-      <c r="F57" s="124"/>
+      <c r="D57" s="128" t="s">
+        <v>187</v>
+      </c>
+      <c r="E57" s="129"/>
+      <c r="F57" s="130"/>
       <c r="G57" s="77" t="s">
         <v>50</v>
       </c>
@@ -5563,16 +6468,16 @@
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="127"/>
+      <c r="B58" s="139"/>
       <c r="C58" s="77" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D58" s="122" t="s">
-        <v>189</v>
-      </c>
-      <c r="E58" s="123"/>
-      <c r="F58" s="124"/>
+      <c r="D58" s="128" t="s">
+        <v>188</v>
+      </c>
+      <c r="E58" s="129"/>
+      <c r="F58" s="130"/>
       <c r="G58" s="77" t="s">
         <v>52</v>
       </c>
@@ -5590,7 +6495,7 @@
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="11"/>
-      <c r="B59" s="125" t="str">
+      <c r="B59" s="137" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -5598,9 +6503,9 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D59" s="122"/>
-      <c r="E59" s="123"/>
-      <c r="F59" s="124"/>
+      <c r="D59" s="128"/>
+      <c r="E59" s="129"/>
+      <c r="F59" s="130"/>
       <c r="G59" s="77" t="s">
         <v>47</v>
       </c>
@@ -5618,16 +6523,16 @@
     </row>
     <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="126"/>
+      <c r="B60" s="138"/>
       <c r="C60" s="77" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="122" t="s">
-        <v>190</v>
-      </c>
-      <c r="E60" s="123"/>
-      <c r="F60" s="124"/>
+      <c r="D60" s="128" t="s">
+        <v>189</v>
+      </c>
+      <c r="E60" s="129"/>
+      <c r="F60" s="130"/>
       <c r="G60" s="77" t="s">
         <v>50</v>
       </c>
@@ -5645,16 +6550,16 @@
     </row>
     <row r="61" spans="1:14" ht="25.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="126"/>
+      <c r="B61" s="138"/>
       <c r="C61" s="77" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D61" s="122" t="s">
-        <v>191</v>
-      </c>
-      <c r="E61" s="123"/>
-      <c r="F61" s="124"/>
+      <c r="D61" s="128" t="s">
+        <v>190</v>
+      </c>
+      <c r="E61" s="129"/>
+      <c r="F61" s="130"/>
       <c r="G61" s="77" t="s">
         <v>55</v>
       </c>
@@ -5672,16 +6577,16 @@
     </row>
     <row r="62" spans="1:14" ht="88.2">
       <c r="A62" s="11"/>
-      <c r="B62" s="126"/>
+      <c r="B62" s="138"/>
       <c r="C62" s="77" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D62" s="122" t="s">
-        <v>214</v>
-      </c>
-      <c r="E62" s="123"/>
-      <c r="F62" s="124"/>
+      <c r="D62" s="128" t="s">
+        <v>213</v>
+      </c>
+      <c r="E62" s="129"/>
+      <c r="F62" s="130"/>
       <c r="G62" s="77" t="s">
         <v>54</v>
       </c>
@@ -5699,16 +6604,16 @@
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="126"/>
+      <c r="B63" s="138"/>
       <c r="C63" s="77" t="str">
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D63" s="122" t="s">
-        <v>192</v>
-      </c>
-      <c r="E63" s="123"/>
-      <c r="F63" s="124"/>
+      <c r="D63" s="128" t="s">
+        <v>191</v>
+      </c>
+      <c r="E63" s="129"/>
+      <c r="F63" s="130"/>
       <c r="G63" s="77" t="s">
         <v>51</v>
       </c>
@@ -5726,18 +6631,18 @@
     </row>
     <row r="64" spans="1:14" ht="151.19999999999999">
       <c r="A64" s="11"/>
-      <c r="B64" s="126"/>
+      <c r="B64" s="138"/>
       <c r="C64" s="77" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D64" s="122" t="s">
-        <v>195</v>
-      </c>
-      <c r="E64" s="123"/>
-      <c r="F64" s="124"/>
+      <c r="D64" s="128" t="s">
+        <v>194</v>
+      </c>
+      <c r="E64" s="129"/>
+      <c r="F64" s="130"/>
       <c r="G64" s="77" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H64" s="78"/>
       <c r="I64" s="79" t="s">
@@ -5753,18 +6658,18 @@
     </row>
     <row r="65" spans="1:14" ht="214.2">
       <c r="A65" s="11"/>
-      <c r="B65" s="126"/>
+      <c r="B65" s="138"/>
       <c r="C65" s="77" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D65" s="122" t="s">
-        <v>196</v>
-      </c>
-      <c r="E65" s="123"/>
-      <c r="F65" s="124"/>
+      <c r="D65" s="128" t="s">
+        <v>195</v>
+      </c>
+      <c r="E65" s="129"/>
+      <c r="F65" s="130"/>
       <c r="G65" s="77" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H65" s="78"/>
       <c r="I65" s="79" t="s">
@@ -5780,16 +6685,16 @@
     </row>
     <row r="66" spans="1:14" ht="63">
       <c r="A66" s="11"/>
-      <c r="B66" s="126"/>
+      <c r="B66" s="138"/>
       <c r="C66" s="77" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D66" s="122" t="s">
-        <v>197</v>
-      </c>
-      <c r="E66" s="123"/>
-      <c r="F66" s="124"/>
+      <c r="D66" s="128" t="s">
+        <v>196</v>
+      </c>
+      <c r="E66" s="129"/>
+      <c r="F66" s="130"/>
       <c r="G66" s="77" t="s">
         <v>49</v>
       </c>
@@ -5807,18 +6712,18 @@
     </row>
     <row r="67" spans="1:14" ht="163.80000000000001">
       <c r="A67" s="11"/>
-      <c r="B67" s="126"/>
+      <c r="B67" s="138"/>
       <c r="C67" s="77" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D67" s="122" t="s">
-        <v>199</v>
-      </c>
-      <c r="E67" s="123"/>
-      <c r="F67" s="124"/>
+      <c r="D67" s="128" t="s">
+        <v>198</v>
+      </c>
+      <c r="E67" s="129"/>
+      <c r="F67" s="130"/>
       <c r="G67" s="77" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H67" s="78"/>
       <c r="I67" s="79" t="s">
@@ -5834,16 +6739,16 @@
     </row>
     <row r="68" spans="1:14" ht="50.4">
       <c r="A68" s="11"/>
-      <c r="B68" s="126"/>
+      <c r="B68" s="138"/>
       <c r="C68" s="77" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D68" s="122" t="s">
-        <v>200</v>
-      </c>
-      <c r="E68" s="123"/>
-      <c r="F68" s="124"/>
+      <c r="D68" s="128" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68" s="129"/>
+      <c r="F68" s="130"/>
       <c r="G68" s="77" t="s">
         <v>51</v>
       </c>
@@ -5861,16 +6766,16 @@
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="126"/>
+      <c r="B69" s="138"/>
       <c r="C69" s="77" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D69" s="122" t="s">
-        <v>201</v>
-      </c>
-      <c r="E69" s="123"/>
-      <c r="F69" s="124"/>
+      <c r="D69" s="128" t="s">
+        <v>200</v>
+      </c>
+      <c r="E69" s="129"/>
+      <c r="F69" s="130"/>
       <c r="G69" s="77" t="s">
         <v>50</v>
       </c>
@@ -5888,16 +6793,16 @@
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="126"/>
+      <c r="B70" s="138"/>
       <c r="C70" s="77" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D70" s="122" t="s">
-        <v>203</v>
-      </c>
-      <c r="E70" s="123"/>
-      <c r="F70" s="124"/>
+      <c r="D70" s="128" t="s">
+        <v>202</v>
+      </c>
+      <c r="E70" s="129"/>
+      <c r="F70" s="130"/>
       <c r="G70" s="77" t="s">
         <v>50</v>
       </c>
@@ -5915,16 +6820,16 @@
     </row>
     <row r="71" spans="1:14" ht="37.799999999999997">
       <c r="A71" s="11"/>
-      <c r="B71" s="126"/>
+      <c r="B71" s="138"/>
       <c r="C71" s="77" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D71" s="122" t="s">
-        <v>202</v>
-      </c>
-      <c r="E71" s="123"/>
-      <c r="F71" s="124"/>
+      <c r="D71" s="128" t="s">
+        <v>201</v>
+      </c>
+      <c r="E71" s="129"/>
+      <c r="F71" s="130"/>
       <c r="G71" s="77" t="s">
         <v>50</v>
       </c>
@@ -5942,7 +6847,7 @@
     </row>
     <row r="72" spans="1:14" ht="25.2" customHeight="1">
       <c r="A72" s="11"/>
-      <c r="B72" s="125" t="str">
+      <c r="B72" s="137" t="str">
         <f>master!B53</f>
         <v>バイブコーディング：ハンズオン</v>
       </c>
@@ -5950,11 +6855,11 @@
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D72" s="122" t="s">
-        <v>204</v>
-      </c>
-      <c r="E72" s="123"/>
-      <c r="F72" s="124"/>
+      <c r="D72" s="128" t="s">
+        <v>203</v>
+      </c>
+      <c r="E72" s="129"/>
+      <c r="F72" s="130"/>
       <c r="G72" s="77" t="s">
         <v>55</v>
       </c>
@@ -5972,16 +6877,16 @@
     </row>
     <row r="73" spans="1:14" ht="138.6">
       <c r="A73" s="11"/>
-      <c r="B73" s="126"/>
+      <c r="B73" s="138"/>
       <c r="C73" s="77" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D73" s="122" t="s">
-        <v>205</v>
-      </c>
-      <c r="E73" s="123"/>
-      <c r="F73" s="124"/>
+      <c r="D73" s="128" t="s">
+        <v>204</v>
+      </c>
+      <c r="E73" s="129"/>
+      <c r="F73" s="130"/>
       <c r="G73" s="77" t="s">
         <v>48</v>
       </c>
@@ -5999,16 +6904,16 @@
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="126"/>
-      <c r="C74" s="130" t="str">
+      <c r="B74" s="138"/>
+      <c r="C74" s="98" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D74" s="122" t="s">
-        <v>215</v>
-      </c>
-      <c r="E74" s="123"/>
-      <c r="F74" s="124"/>
+      <c r="D74" s="128" t="s">
+        <v>214</v>
+      </c>
+      <c r="E74" s="129"/>
+      <c r="F74" s="130"/>
       <c r="G74" s="77" t="s">
         <v>51</v>
       </c>
@@ -6026,13 +6931,13 @@
     </row>
     <row r="75" spans="1:14" ht="88.2" customHeight="1">
       <c r="A75" s="11"/>
-      <c r="B75" s="126"/>
-      <c r="C75" s="131"/>
-      <c r="D75" s="122" t="s">
-        <v>206</v>
-      </c>
-      <c r="E75" s="123"/>
-      <c r="F75" s="124"/>
+      <c r="B75" s="138"/>
+      <c r="C75" s="99"/>
+      <c r="D75" s="128" t="s">
+        <v>205</v>
+      </c>
+      <c r="E75" s="129"/>
+      <c r="F75" s="130"/>
       <c r="G75" s="77" t="s">
         <v>54</v>
       </c>
@@ -6046,16 +6951,16 @@
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="126"/>
-      <c r="C76" s="130" t="str">
+      <c r="B76" s="138"/>
+      <c r="C76" s="98" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D76" s="122" t="s">
-        <v>219</v>
-      </c>
-      <c r="E76" s="123"/>
-      <c r="F76" s="124"/>
+      <c r="D76" s="128" t="s">
+        <v>218</v>
+      </c>
+      <c r="E76" s="129"/>
+      <c r="F76" s="130"/>
       <c r="G76" s="77" t="s">
         <v>51</v>
       </c>
@@ -6073,13 +6978,13 @@
     </row>
     <row r="77" spans="1:14" ht="88.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="126"/>
-      <c r="C77" s="131"/>
-      <c r="D77" s="122" t="s">
-        <v>206</v>
-      </c>
-      <c r="E77" s="123"/>
-      <c r="F77" s="124"/>
+      <c r="B77" s="138"/>
+      <c r="C77" s="99"/>
+      <c r="D77" s="128" t="s">
+        <v>205</v>
+      </c>
+      <c r="E77" s="129"/>
+      <c r="F77" s="130"/>
       <c r="G77" s="77" t="s">
         <v>54</v>
       </c>
@@ -6093,16 +6998,16 @@
     </row>
     <row r="78" spans="1:14" ht="50.4">
       <c r="A78" s="11"/>
-      <c r="B78" s="126"/>
-      <c r="C78" s="130" t="str">
+      <c r="B78" s="138"/>
+      <c r="C78" s="98" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D78" s="122" t="s">
-        <v>218</v>
-      </c>
-      <c r="E78" s="123"/>
-      <c r="F78" s="124"/>
+      <c r="D78" s="128" t="s">
+        <v>217</v>
+      </c>
+      <c r="E78" s="129"/>
+      <c r="F78" s="130"/>
       <c r="G78" s="77" t="s">
         <v>51</v>
       </c>
@@ -6120,13 +7025,13 @@
     </row>
     <row r="79" spans="1:14" ht="88.2">
       <c r="A79" s="11"/>
-      <c r="B79" s="126"/>
-      <c r="C79" s="131"/>
-      <c r="D79" s="122" t="s">
-        <v>206</v>
-      </c>
-      <c r="E79" s="123"/>
-      <c r="F79" s="124"/>
+      <c r="B79" s="138"/>
+      <c r="C79" s="99"/>
+      <c r="D79" s="128" t="s">
+        <v>205</v>
+      </c>
+      <c r="E79" s="129"/>
+      <c r="F79" s="130"/>
       <c r="G79" s="77" t="s">
         <v>54</v>
       </c>
@@ -6140,16 +7045,16 @@
     </row>
     <row r="80" spans="1:14" ht="63">
       <c r="A80" s="11"/>
-      <c r="B80" s="126"/>
-      <c r="C80" s="130" t="str">
+      <c r="B80" s="138"/>
+      <c r="C80" s="98" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D80" s="122" t="s">
-        <v>217</v>
-      </c>
-      <c r="E80" s="123"/>
-      <c r="F80" s="124"/>
+      <c r="D80" s="128" t="s">
+        <v>216</v>
+      </c>
+      <c r="E80" s="129"/>
+      <c r="F80" s="130"/>
       <c r="G80" s="77" t="s">
         <v>49</v>
       </c>
@@ -6167,13 +7072,13 @@
     </row>
     <row r="81" spans="1:14" ht="88.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="126"/>
-      <c r="C81" s="131"/>
-      <c r="D81" s="122" t="s">
-        <v>206</v>
-      </c>
-      <c r="E81" s="123"/>
-      <c r="F81" s="124"/>
+      <c r="B81" s="138"/>
+      <c r="C81" s="99"/>
+      <c r="D81" s="128" t="s">
+        <v>205</v>
+      </c>
+      <c r="E81" s="129"/>
+      <c r="F81" s="130"/>
       <c r="G81" s="77" t="s">
         <v>54</v>
       </c>
@@ -6187,16 +7092,16 @@
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="126"/>
+      <c r="B82" s="138"/>
       <c r="C82" s="77" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D82" s="122" t="s">
-        <v>207</v>
-      </c>
-      <c r="E82" s="123"/>
-      <c r="F82" s="124"/>
+      <c r="D82" s="128" t="s">
+        <v>206</v>
+      </c>
+      <c r="E82" s="129"/>
+      <c r="F82" s="130"/>
       <c r="G82" s="77" t="s">
         <v>51</v>
       </c>
@@ -6214,16 +7119,16 @@
     </row>
     <row r="83" spans="1:14" ht="50.4">
       <c r="A83" s="11"/>
-      <c r="B83" s="126"/>
+      <c r="B83" s="138"/>
       <c r="C83" s="77" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="122" t="s">
-        <v>208</v>
-      </c>
-      <c r="E83" s="123"/>
-      <c r="F83" s="124"/>
+      <c r="D83" s="128" t="s">
+        <v>207</v>
+      </c>
+      <c r="E83" s="129"/>
+      <c r="F83" s="130"/>
       <c r="G83" s="77" t="s">
         <v>51</v>
       </c>
@@ -6241,16 +7146,16 @@
     </row>
     <row r="84" spans="1:14" ht="37.799999999999997">
       <c r="A84" s="11"/>
-      <c r="B84" s="126"/>
+      <c r="B84" s="138"/>
       <c r="C84" s="77" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D84" s="122" t="s">
-        <v>209</v>
-      </c>
-      <c r="E84" s="123"/>
-      <c r="F84" s="124"/>
+      <c r="D84" s="128" t="s">
+        <v>208</v>
+      </c>
+      <c r="E84" s="129"/>
+      <c r="F84" s="130"/>
       <c r="G84" s="77" t="s">
         <v>50</v>
       </c>
@@ -6268,16 +7173,16 @@
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="126"/>
-      <c r="C85" s="130" t="str">
+      <c r="B85" s="138"/>
+      <c r="C85" s="98" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D85" s="122" t="s">
-        <v>216</v>
-      </c>
-      <c r="E85" s="123"/>
-      <c r="F85" s="124"/>
+      <c r="D85" s="128" t="s">
+        <v>215</v>
+      </c>
+      <c r="E85" s="129"/>
+      <c r="F85" s="130"/>
       <c r="G85" s="77" t="s">
         <v>51</v>
       </c>
@@ -6295,13 +7200,13 @@
     </row>
     <row r="86" spans="1:14" ht="88.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="126"/>
-      <c r="C86" s="131"/>
-      <c r="D86" s="122" t="s">
-        <v>206</v>
-      </c>
-      <c r="E86" s="123"/>
-      <c r="F86" s="124"/>
+      <c r="B86" s="138"/>
+      <c r="C86" s="99"/>
+      <c r="D86" s="128" t="s">
+        <v>205</v>
+      </c>
+      <c r="E86" s="129"/>
+      <c r="F86" s="130"/>
       <c r="G86" s="77" t="s">
         <v>54</v>
       </c>
@@ -6315,16 +7220,16 @@
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="126"/>
+      <c r="B87" s="138"/>
       <c r="C87" s="77" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D87" s="122" t="s">
-        <v>210</v>
-      </c>
-      <c r="E87" s="123"/>
-      <c r="F87" s="124"/>
+      <c r="D87" s="128" t="s">
+        <v>209</v>
+      </c>
+      <c r="E87" s="129"/>
+      <c r="F87" s="130"/>
       <c r="G87" s="77" t="s">
         <v>50</v>
       </c>
@@ -6342,16 +7247,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="126"/>
+      <c r="B88" s="138"/>
       <c r="C88" s="77" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D88" s="122" t="s">
-        <v>211</v>
-      </c>
-      <c r="E88" s="123"/>
-      <c r="F88" s="124"/>
+      <c r="D88" s="128" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88" s="129"/>
+      <c r="F88" s="130"/>
       <c r="G88" s="77" t="s">
         <v>50</v>
       </c>
@@ -6369,16 +7274,16 @@
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="126"/>
+      <c r="B89" s="138"/>
       <c r="C89" s="77" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D89" s="122" t="s">
-        <v>212</v>
-      </c>
-      <c r="E89" s="123"/>
-      <c r="F89" s="124"/>
+      <c r="D89" s="128" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" s="129"/>
+      <c r="F89" s="130"/>
       <c r="G89" s="77" t="s">
         <v>50</v>
       </c>
@@ -6396,16 +7301,16 @@
     </row>
     <row r="90" spans="1:14" ht="75.599999999999994">
       <c r="A90" s="11"/>
-      <c r="B90" s="126"/>
-      <c r="C90" s="130" t="str">
+      <c r="B90" s="138"/>
+      <c r="C90" s="98" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D90" s="122" t="s">
-        <v>213</v>
-      </c>
-      <c r="E90" s="123"/>
-      <c r="F90" s="124"/>
+      <c r="D90" s="128" t="s">
+        <v>212</v>
+      </c>
+      <c r="E90" s="129"/>
+      <c r="F90" s="130"/>
       <c r="G90" s="77" t="s">
         <v>52</v>
       </c>
@@ -6423,13 +7328,13 @@
     </row>
     <row r="91" spans="1:14" ht="63">
       <c r="A91" s="11"/>
-      <c r="B91" s="127"/>
-      <c r="C91" s="131"/>
-      <c r="D91" s="122" t="s">
-        <v>220</v>
-      </c>
-      <c r="E91" s="123"/>
-      <c r="F91" s="124"/>
+      <c r="B91" s="139"/>
+      <c r="C91" s="99"/>
+      <c r="D91" s="128" t="s">
+        <v>219</v>
+      </c>
+      <c r="E91" s="129"/>
+      <c r="F91" s="130"/>
       <c r="G91" s="77" t="s">
         <v>49</v>
       </c>
@@ -6445,273 +7350,769 @@
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:14" ht="214.2">
+    <row r="92" spans="1:14" ht="100.8">
       <c r="A92" s="11"/>
-      <c r="B92" s="129" t="str">
-        <f>master!B67</f>
-        <v>バイブコーディング：演習</v>
+      <c r="B92" s="137" t="str">
+        <f>master!B69</f>
+        <v>Gitとは</v>
       </c>
       <c r="C92" s="77" t="str">
-        <f>master!C67</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D92" s="122" t="s">
+        <f>master!C69</f>
+        <v>Gitとは</v>
+      </c>
+      <c r="D92" s="128" t="s">
         <v>223</v>
       </c>
-      <c r="E92" s="123"/>
-      <c r="F92" s="124"/>
+      <c r="E92" s="129"/>
+      <c r="F92" s="130"/>
       <c r="G92" s="77" t="s">
-        <v>194</v>
+        <v>56</v>
       </c>
       <c r="H92" s="78"/>
       <c r="I92" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J92" s="80">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K92" s="81"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
-    <row r="93" spans="1:14" ht="64.2" customHeight="1">
+    <row r="93" spans="1:14" ht="189">
       <c r="A93" s="11"/>
-      <c r="B93" s="125" t="str">
-        <f>master!B69</f>
-        <v>Gitとは</v>
-      </c>
+      <c r="B93" s="139"/>
       <c r="C93" s="77" t="str">
-        <f>master!C69</f>
-        <v>Gitとは</v>
-      </c>
-      <c r="D93" s="122"/>
-      <c r="E93" s="123"/>
-      <c r="F93" s="124"/>
+        <f>master!C70</f>
+        <v>Gitの基本的な流れ</v>
+      </c>
+      <c r="D93" s="128" t="s">
+        <v>230</v>
+      </c>
+      <c r="E93" s="129"/>
+      <c r="F93" s="130"/>
       <c r="G93" s="77" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="H93" s="78"/>
       <c r="I93" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J93" s="80">
-        <v>1.3888888888888889E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K93" s="81"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
-    <row r="94" spans="1:14" ht="113.4">
+    <row r="94" spans="1:14" ht="126">
       <c r="A94" s="11"/>
-      <c r="B94" s="127"/>
+      <c r="B94" s="137" t="str">
+        <f>master!B71</f>
+        <v>VS Code上でGitを使う手順</v>
+      </c>
       <c r="C94" s="77" t="str">
-        <f>master!C70</f>
-        <v>Gitの基本的な流れ</v>
-      </c>
-      <c r="D94" s="122"/>
-      <c r="E94" s="123"/>
-      <c r="F94" s="124"/>
+        <f>master!C71</f>
+        <v>VS Code上でGitを使う手順-1 【ユーザ名等の登録】</v>
+      </c>
+      <c r="D94" s="128" t="s">
+        <v>224</v>
+      </c>
+      <c r="E94" s="129"/>
+      <c r="F94" s="130"/>
       <c r="G94" s="77" t="s">
-        <v>53</v>
+        <v>225</v>
       </c>
       <c r="H94" s="78"/>
       <c r="I94" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J94" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K94" s="81" t="s">
-        <v>62</v>
-      </c>
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K94" s="81"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
-    <row r="95" spans="1:14" ht="215.4" customHeight="1">
+    <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="125" t="str">
-        <f>master!B71</f>
-        <v>VS Code上でGitを使う手順</v>
-      </c>
+      <c r="B95" s="138"/>
       <c r="C95" s="77" t="str">
-        <f>master!C71</f>
-        <v>VS Code上でGitを使う手順-1 【ユーザ名等の登録】</v>
-      </c>
-      <c r="D95" s="122"/>
-      <c r="E95" s="123"/>
-      <c r="F95" s="124"/>
+        <f>master!C72</f>
+        <v>VS Code上でGitを使う手順-2 【リポジトリの初期化】</v>
+      </c>
+      <c r="D95" s="128" t="s">
+        <v>226</v>
+      </c>
+      <c r="E95" s="129"/>
+      <c r="F95" s="130"/>
       <c r="G95" s="77" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H95" s="78"/>
       <c r="I95" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J95" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K95" s="81" t="s">
-        <v>62</v>
-      </c>
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K95" s="81"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
-    <row r="96" spans="1:14" ht="113.4">
+    <row r="96" spans="1:14" ht="50.4">
       <c r="A96" s="11"/>
-      <c r="B96" s="126"/>
+      <c r="B96" s="138"/>
       <c r="C96" s="77" t="str">
-        <f>master!C72</f>
-        <v>VS Code上でGitを使う手順-2 【リポジトリの初期化】</v>
-      </c>
-      <c r="D96" s="122"/>
-      <c r="E96" s="123"/>
-      <c r="F96" s="124"/>
+        <f>master!C73</f>
+        <v>VS Code上でGitを使う手順-3 【最初のcommit】</v>
+      </c>
+      <c r="D96" s="128" t="s">
+        <v>227</v>
+      </c>
+      <c r="E96" s="129"/>
+      <c r="F96" s="130"/>
       <c r="G96" s="77" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H96" s="78"/>
       <c r="I96" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J96" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K96" s="81" t="s">
-        <v>62</v>
-      </c>
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K96" s="81"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
-    <row r="97" spans="1:14" ht="113.4">
+    <row r="97" spans="1:14" ht="50.4">
       <c r="A97" s="11"/>
-      <c r="B97" s="126"/>
+      <c r="B97" s="138"/>
       <c r="C97" s="77" t="str">
-        <f>master!C73</f>
-        <v>VS Code上でGitを使う手順-3 【最初のcommit】</v>
-      </c>
-      <c r="D97" s="122"/>
-      <c r="E97" s="123"/>
-      <c r="F97" s="124"/>
+        <f>master!C74</f>
+        <v>VS Code上でGitを使う手順-4 【2回目以降のコミット】</v>
+      </c>
+      <c r="D97" s="128" t="s">
+        <v>228</v>
+      </c>
+      <c r="E97" s="129"/>
+      <c r="F97" s="130"/>
       <c r="G97" s="77" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H97" s="78"/>
       <c r="I97" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J97" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K97" s="81" t="s">
-        <v>62</v>
-      </c>
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K97" s="81"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
-    <row r="98" spans="1:14" ht="113.4">
+    <row r="98" spans="1:14" ht="37.799999999999997">
       <c r="A98" s="11"/>
-      <c r="B98" s="126"/>
+      <c r="B98" s="138"/>
       <c r="C98" s="77" t="str">
-        <f>master!C74</f>
-        <v>VS Code上でGitを使う手順-4 【2回目以降のコミット】</v>
-      </c>
-      <c r="D98" s="122"/>
-      <c r="E98" s="123"/>
-      <c r="F98" s="124"/>
+        <f>master!C75</f>
+        <v>VS Code上でGitを使う手順-5 【過去のcommitの確認】</v>
+      </c>
+      <c r="D98" s="128" t="s">
+        <v>229</v>
+      </c>
+      <c r="E98" s="129"/>
+      <c r="F98" s="130"/>
       <c r="G98" s="77" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H98" s="78"/>
       <c r="I98" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J98" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K98" s="81" t="s">
-        <v>62</v>
-      </c>
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K98" s="81"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
-    <row r="99" spans="1:14" ht="113.4">
+    <row r="99" spans="1:14" ht="63">
       <c r="A99" s="11"/>
-      <c r="B99" s="126"/>
+      <c r="B99" s="139"/>
       <c r="C99" s="77" t="str">
-        <f>master!C75</f>
-        <v>VS Code上でGitを使う手順-5 【過去のcommitの確認】</v>
-      </c>
-      <c r="D99" s="122"/>
-      <c r="E99" s="123"/>
-      <c r="F99" s="124"/>
+        <f>master!C76</f>
+        <v>VS Code上でGitを使う手順-6 【過去の状態に戻す】</v>
+      </c>
+      <c r="D99" s="128" t="s">
+        <v>231</v>
+      </c>
+      <c r="E99" s="129"/>
+      <c r="F99" s="130"/>
       <c r="G99" s="77" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H99" s="78"/>
       <c r="I99" s="79" t="s">
         <v>26</v>
       </c>
       <c r="J99" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K99" s="81" t="s">
-        <v>62</v>
-      </c>
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K99" s="81"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
       <c r="N99" s="6"/>
     </row>
-    <row r="100" spans="1:14" ht="113.4">
+    <row r="100" spans="1:14" ht="214.2">
       <c r="A100" s="11"/>
-      <c r="B100" s="127"/>
+      <c r="B100" s="97" t="str">
+        <f>master!B67</f>
+        <v>バイブコーディング：演習</v>
+      </c>
       <c r="C100" s="77" t="str">
-        <f>master!C76</f>
-        <v>VS Code上でGitを使う手順-6 【過去の状態に戻す】</v>
-      </c>
-      <c r="D100" s="122"/>
-      <c r="E100" s="123"/>
-      <c r="F100" s="124"/>
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D100" s="128" t="s">
+        <v>222</v>
+      </c>
+      <c r="E100" s="129"/>
+      <c r="F100" s="130"/>
       <c r="G100" s="77" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="H100" s="78"/>
       <c r="I100" s="79" t="s">
         <v>26</v>
       </c>
-      <c r="J100" s="80">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K100" s="81" t="s">
-        <v>62</v>
-      </c>
+      <c r="J100" s="80" t="s">
+        <v>232</v>
+      </c>
+      <c r="K100" s="81"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
       <c r="N100" s="6"/>
     </row>
-    <row r="101" spans="1:14" ht="15" customHeight="1">
-      <c r="J101" s="49"/>
-    </row>
-    <row r="102" spans="1:14" ht="15" customHeight="1"/>
+    <row r="101" spans="1:14" ht="88.2">
+      <c r="A101" s="11"/>
+      <c r="B101" s="104" t="str">
+        <f>master!B78</f>
+        <v>導入</v>
+      </c>
+      <c r="C101" s="103" t="str">
+        <f>master!C78</f>
+        <v>講義の目的</v>
+      </c>
+      <c r="D101" s="122" t="s">
+        <v>266</v>
+      </c>
+      <c r="E101" s="123"/>
+      <c r="F101" s="124"/>
+      <c r="G101" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H101" s="12"/>
+      <c r="I101" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J101" s="50">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K101" s="46"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" ht="37.799999999999997">
+      <c r="A102" s="11"/>
+      <c r="B102" s="125" t="str">
+        <f>master!B79</f>
+        <v>システム開発におけるソフトウェア開発ライフサイクル</v>
+      </c>
+      <c r="C102" s="103" t="str">
+        <f>master!C79</f>
+        <v>ソフトウェア開発ライフサイクル</v>
+      </c>
+      <c r="D102" s="122" t="s">
+        <v>267</v>
+      </c>
+      <c r="E102" s="123"/>
+      <c r="F102" s="124"/>
+      <c r="G102" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H102" s="12"/>
+      <c r="I102" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J102" s="50">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K102" s="46"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" ht="277.2">
+      <c r="A103" s="11"/>
+      <c r="B103" s="126"/>
+      <c r="C103" s="103" t="str">
+        <f>master!C80</f>
+        <v>ソフトウェア開発ライフサイクルの種類</v>
+      </c>
+      <c r="D103" s="122" t="s">
+        <v>269</v>
+      </c>
+      <c r="E103" s="123"/>
+      <c r="F103" s="124"/>
+      <c r="G103" s="55" t="s">
+        <v>268</v>
+      </c>
+      <c r="H103" s="12"/>
+      <c r="I103" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J103" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K103" s="46"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="1:14" ht="151.19999999999999">
+      <c r="A104" s="11"/>
+      <c r="B104" s="125" t="str">
+        <f>master!B81</f>
+        <v>TERASOLUNAとは</v>
+      </c>
+      <c r="C104" s="103" t="s">
+        <v>244</v>
+      </c>
+      <c r="D104" s="122" t="s">
+        <v>270</v>
+      </c>
+      <c r="E104" s="123"/>
+      <c r="F104" s="124"/>
+      <c r="G104" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="H104" s="12"/>
+      <c r="I104" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J104" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K104" s="46"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="1:14" ht="138.6">
+      <c r="A105" s="11"/>
+      <c r="B105" s="126"/>
+      <c r="C105" s="103" t="s">
+        <v>245</v>
+      </c>
+      <c r="D105" s="122" t="s">
+        <v>271</v>
+      </c>
+      <c r="E105" s="123"/>
+      <c r="F105" s="124"/>
+      <c r="G105" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="H105" s="12"/>
+      <c r="I105" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J105" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K105" s="46"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" ht="189">
+      <c r="A106" s="11"/>
+      <c r="B106" s="125" t="str">
+        <f>master!B83</f>
+        <v>V字モデルとは</v>
+      </c>
+      <c r="C106" s="103" t="s">
+        <v>248</v>
+      </c>
+      <c r="D106" s="122" t="s">
+        <v>272</v>
+      </c>
+      <c r="E106" s="123"/>
+      <c r="F106" s="124"/>
+      <c r="G106" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="H106" s="12"/>
+      <c r="I106" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J106" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K106" s="46"/>
+      <c r="L106" s="6"/>
+      <c r="M106" s="6"/>
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="1:14" ht="100.8">
+      <c r="A107" s="11"/>
+      <c r="B107" s="127"/>
+      <c r="C107" s="103" t="s">
+        <v>246</v>
+      </c>
+      <c r="D107" s="122" t="s">
+        <v>273</v>
+      </c>
+      <c r="E107" s="123"/>
+      <c r="F107" s="124"/>
+      <c r="G107" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="H107" s="12"/>
+      <c r="I107" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J107" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K107" s="46"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6"/>
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" ht="113.4">
+      <c r="A108" s="11"/>
+      <c r="B108" s="127"/>
+      <c r="C108" s="103" t="s">
+        <v>250</v>
+      </c>
+      <c r="D108" s="122" t="s">
+        <v>274</v>
+      </c>
+      <c r="E108" s="123"/>
+      <c r="F108" s="124"/>
+      <c r="G108" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K108" s="46"/>
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="1:14" ht="302.39999999999998">
+      <c r="A109" s="11"/>
+      <c r="B109" s="127"/>
+      <c r="C109" s="103" t="s">
+        <v>252</v>
+      </c>
+      <c r="D109" s="122" t="s">
+        <v>276</v>
+      </c>
+      <c r="E109" s="123"/>
+      <c r="F109" s="124"/>
+      <c r="G109" s="55" t="s">
+        <v>275</v>
+      </c>
+      <c r="H109" s="12"/>
+      <c r="I109" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J109" s="50">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K109" s="46"/>
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="1:14" ht="138.6">
+      <c r="A110" s="11"/>
+      <c r="B110" s="127"/>
+      <c r="C110" s="103" t="s">
+        <v>254</v>
+      </c>
+      <c r="D110" s="122" t="s">
+        <v>277</v>
+      </c>
+      <c r="E110" s="123"/>
+      <c r="F110" s="124"/>
+      <c r="G110" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="H110" s="12"/>
+      <c r="I110" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J110" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K110" s="46"/>
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" ht="88.2">
+      <c r="A111" s="11"/>
+      <c r="B111" s="127"/>
+      <c r="C111" s="103" t="s">
+        <v>256</v>
+      </c>
+      <c r="D111" s="122" t="s">
+        <v>278</v>
+      </c>
+      <c r="E111" s="123"/>
+      <c r="F111" s="124"/>
+      <c r="G111" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H111" s="12"/>
+      <c r="I111" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J111" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K111" s="46"/>
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:14" ht="75.599999999999994">
+      <c r="A112" s="11"/>
+      <c r="B112" s="127"/>
+      <c r="C112" s="103" t="s">
+        <v>258</v>
+      </c>
+      <c r="D112" s="122" t="s">
+        <v>279</v>
+      </c>
+      <c r="E112" s="123"/>
+      <c r="F112" s="124"/>
+      <c r="G112" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="H112" s="12"/>
+      <c r="I112" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J112" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K112" s="46"/>
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:14" ht="113.4">
+      <c r="A113" s="11"/>
+      <c r="B113" s="127"/>
+      <c r="C113" s="103" t="s">
+        <v>260</v>
+      </c>
+      <c r="D113" s="122" t="s">
+        <v>280</v>
+      </c>
+      <c r="E113" s="123"/>
+      <c r="F113" s="124"/>
+      <c r="G113" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="H113" s="12"/>
+      <c r="I113" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J113" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K113" s="46"/>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:14" ht="126">
+      <c r="A114" s="11"/>
+      <c r="B114" s="127"/>
+      <c r="C114" s="103" t="s">
+        <v>281</v>
+      </c>
+      <c r="D114" s="122" t="s">
+        <v>282</v>
+      </c>
+      <c r="E114" s="123"/>
+      <c r="F114" s="124"/>
+      <c r="G114" s="55" t="s">
+        <v>225</v>
+      </c>
+      <c r="H114" s="12"/>
+      <c r="I114" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J114" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K114" s="46"/>
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="1:14" ht="88.2">
+      <c r="A115" s="11"/>
+      <c r="B115" s="127"/>
+      <c r="C115" s="103" t="s">
+        <v>263</v>
+      </c>
+      <c r="D115" s="122" t="s">
+        <v>283</v>
+      </c>
+      <c r="E115" s="123"/>
+      <c r="F115" s="124"/>
+      <c r="G115" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H115" s="12"/>
+      <c r="I115" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J115" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K115" s="46"/>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" ht="138.6">
+      <c r="A116" s="11"/>
+      <c r="B116" s="127"/>
+      <c r="C116" s="103" t="s">
+        <v>264</v>
+      </c>
+      <c r="D116" s="122" t="s">
+        <v>284</v>
+      </c>
+      <c r="E116" s="123"/>
+      <c r="F116" s="124"/>
+      <c r="G116" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="H116" s="12"/>
+      <c r="I116" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J116" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K116" s="46"/>
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="1:14" ht="24" customHeight="1">
+      <c r="A117" s="11"/>
+      <c r="B117" s="126"/>
+      <c r="C117" s="103" t="s">
+        <v>265</v>
+      </c>
+      <c r="D117" s="122"/>
+      <c r="E117" s="123"/>
+      <c r="F117" s="124"/>
+      <c r="G117" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H117" s="12"/>
+      <c r="I117" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J117" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K117" s="46"/>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="1:14" ht="24" customHeight="1">
+      <c r="A118" s="11"/>
+      <c r="B118" s="104"/>
+      <c r="C118" s="103"/>
+      <c r="D118" s="122"/>
+      <c r="E118" s="123"/>
+      <c r="F118" s="124"/>
+      <c r="G118" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H118" s="12"/>
+      <c r="I118" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J118" s="50"/>
+      <c r="K118" s="46"/>
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="1:14" ht="24" customHeight="1">
+      <c r="A119" s="11"/>
+      <c r="B119" s="104"/>
+      <c r="C119" s="103"/>
+      <c r="D119" s="122"/>
+      <c r="E119" s="123"/>
+      <c r="F119" s="124"/>
+      <c r="G119" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H119" s="12"/>
+      <c r="I119" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J119" s="50"/>
+      <c r="K119" s="46"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="1:14" ht="15" customHeight="1">
+      <c r="J120" s="49"/>
+    </row>
+    <row r="121" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="96">
-    <mergeCell ref="B72:B91"/>
-    <mergeCell ref="D98:F98"/>
+  <mergeCells count="118">
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="B94:B99"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D93:F93"/>
     <mergeCell ref="D99:F99"/>
-    <mergeCell ref="B95:B100"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="B59:B71"/>
-    <mergeCell ref="B93:B94"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="B92:B93"/>
     <mergeCell ref="D77:F77"/>
     <mergeCell ref="D79:F79"/>
     <mergeCell ref="D81:F81"/>
@@ -6720,24 +8121,22 @@
     <mergeCell ref="D91:F91"/>
     <mergeCell ref="D83:F83"/>
     <mergeCell ref="D84:F84"/>
+    <mergeCell ref="B72:B91"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="B59:B71"/>
     <mergeCell ref="D70:F70"/>
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D100:F100"/>
     <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D82:F82"/>
     <mergeCell ref="D57:F57"/>
     <mergeCell ref="D58:F58"/>
     <mergeCell ref="D59:F59"/>
@@ -6750,6 +8149,8 @@
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D65:F65"/>
     <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D74:F74"/>
     <mergeCell ref="D56:F56"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
@@ -6797,6 +8198,29 @@
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B106:B117"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D102:F102"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6809,7 +8233,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H22:H100</xm:sqref>
+          <xm:sqref>H22:H119</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6819,7 +8243,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C77"/>
+  <dimension ref="B1:C101"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="9.6"/>
   <cols>
     <col min="1" max="1" width="4.6640625" style="75" customWidth="1"/>
@@ -6830,7 +8254,7 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="2:3">
@@ -6843,408 +8267,508 @@
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="75" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="75" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" s="75" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="C5" s="75" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" s="75" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" s="75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" s="75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C9" s="75" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" s="75" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" s="75" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" s="75" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" s="75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" s="75" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" s="75" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="C16" s="75" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="2:3">
       <c r="B17" s="75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C17" s="75" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="C18" s="75" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="2:3">
       <c r="C19" s="75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="2:3">
       <c r="C20" s="75" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="C21" s="75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="2:3">
       <c r="C22" s="75" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:3">
       <c r="C23" s="75" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="2:3">
       <c r="C24" s="75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:3">
       <c r="C25" s="75" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="C26" s="75" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="27" spans="2:3">
       <c r="C27" s="75" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="2:3">
       <c r="C28" s="75" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="C29" s="75" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:3">
       <c r="C30" s="75" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="2:3">
       <c r="C31" s="75" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="2:3">
       <c r="C32" s="75" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="C33" s="75" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="C34" s="75" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="2:3">
       <c r="C35" s="75" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="128"/>
-      <c r="C36" s="128"/>
+      <c r="B36" s="96"/>
+      <c r="C36" s="96"/>
     </row>
     <row r="37" spans="2:3">
       <c r="B37" s="75" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C37" s="75" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" s="75" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" s="75" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="B40" s="75" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C40" s="75" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" s="75" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" s="75" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" s="75" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="B44" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="75" t="s">
         <v>151</v>
-      </c>
-      <c r="C44" s="75" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" s="75" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" s="75" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" s="75" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" s="75" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="C49" s="75" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="C50" s="75" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="C51" s="75" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="C52" s="75" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="B53" s="75" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C53" s="75" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="C54" s="75" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="2:3">
       <c r="C55" s="75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="2:3">
       <c r="C56" s="75" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="2:3">
       <c r="C57" s="75" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" spans="2:3">
       <c r="C58" s="75" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="2:3">
       <c r="C59" s="75" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="60" spans="2:3">
       <c r="C60" s="75" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="2:3">
       <c r="C61" s="75" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="62" spans="2:3">
       <c r="C62" s="75" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="63" spans="2:3">
       <c r="C63" s="75" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="2:3">
       <c r="C64" s="75" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="65" spans="2:3">
       <c r="C65" s="75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="2:3">
       <c r="C66" s="75" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="67" spans="2:3">
       <c r="B67" s="75" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C67" s="75" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="2:3">
-      <c r="B68" s="128"/>
-      <c r="C68" s="128"/>
+      <c r="B68" s="96"/>
+      <c r="C68" s="96"/>
     </row>
     <row r="69" spans="2:3">
       <c r="B69" s="75" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C69" s="75" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="C70" s="75" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="B71" s="75" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C71" s="75" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="C72" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="C73" s="75" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="C74" s="75" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" s="75" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="C76" s="75" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3">
+      <c r="B77" s="96"/>
+      <c r="C77" s="96"/>
+    </row>
+    <row r="78" spans="2:3">
+      <c r="B78" s="75" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="77" spans="2:3">
-      <c r="B77" s="128"/>
-      <c r="C77" s="128"/>
+      <c r="C78" s="100" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3">
+      <c r="B79" s="75" t="s">
+        <v>243</v>
+      </c>
+      <c r="C79" s="100" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3">
+      <c r="C80" s="100" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3">
+      <c r="B81" s="75" t="s">
+        <v>247</v>
+      </c>
+      <c r="C81" s="101" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3">
+      <c r="C82" s="102" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3">
+      <c r="B83" s="75" t="s">
+        <v>249</v>
+      </c>
+      <c r="C83" s="102" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3">
+      <c r="C84" s="102" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="C85" s="102" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="C86" s="102" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="C87" s="102" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="C88" s="102" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="C89" s="102" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="C90" s="102" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="C91" s="102" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="C92" s="102" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="C93" s="102" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3">
+      <c r="C94" s="102" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="101" spans="3:3">
+      <c r="C101" s="102"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/IG/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/AI Native-バイブコーディング_IG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DFBEAB3-0E29-4F8E-A1D5-6813AA661763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FB369A-7BE0-442F-8C01-B60CBD95190A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール（1日）" sheetId="33" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（1日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$120</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$149</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="355">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -2518,43 +2518,43 @@
   </si>
   <si>
     <t>ソフトウェア開発ライフサイクル</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>ソフトウェア開発ライフサイクルの種類</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>TERASOLUNA 開発手順</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>プロジェクトごとのテーラリング</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>V字モデル　– 要求定義 –</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>「要求」と「要件」の違い</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t xml:space="preserve">V字モデル　– システムテスト – </t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t xml:space="preserve">V字モデル　– 受入テスト – </t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>参考：TERASOLUNA開発手順　タスクフロー</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>講義の目的</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>システム開発におけるソフトウェア開発ライフサイクル</t>
@@ -2585,46 +2585,46 @@
   </si>
   <si>
     <t>V字モデル</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>V字モデル　– 要求分析 –</t>
   </si>
   <si>
     <t>V字モデル　– 要求分析 –</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>V字モデル　– アーキテクチャ設計 –</t>
   </si>
   <si>
     <t>V字モデル　– アーキテクチャ設計 –</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>V字モデル　– 詳細設計 –</t>
   </si>
   <si>
     <t>V字モデル　– 詳細設計 –</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>V字モデル　– 製造 –</t>
   </si>
   <si>
     <t>V字モデル　– 製造 –</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>V字モデル　– 単体テスト –</t>
   </si>
   <si>
     <t>V字モデル　– 単体テスト –</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t>V字モデル　– 結合テスト –</t>
-    <phoneticPr fontId="24"/>
+    <phoneticPr fontId="22"/>
   </si>
   <si>
     <t xml:space="preserve">V字モデル　– システムテスト – </t>
@@ -3172,12 +3172,660 @@
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
+  <si>
+    <t>TERASOLUNA 開発手順　 ※再掲</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>V字モデル　 ※再掲</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テストとは</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テストの目的</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テストを実施しなかった場合…</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>コラム：テストとデバッグ</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テスト技法 – ブラックボックステスト技法 –</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>ブラックボックステスト：状態遷移テスト</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テスト技法 – ホワイトボックステスト技法 –</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>ホワイトボックステストの評価基準</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>ホワイトボックステスト：ステートメントテスト</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>ホワイトボックステスト：ブランチテスト</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>ホワイトボックステスト：コンディションテスト</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テスト技法 – 経験ベースの技法 –</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>単体テスト（Unit Test）とは</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>スタブとドライバ</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>スタブとモック</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>JUnitとは</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テストとは</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>単体テストとは</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テスト設計の流れ</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>テスト設計の例</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>単体テスト（Unit Test）とは</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ブラックボックステスト：同値分割法</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>ブラックボックステスト：境界値分析</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>ブラックボックステスト：ディシジョンテーブルテスト</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>Junit</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>参考文献</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>以下を学習することを説明する。
+・テストの目的を理解する
+・単体テストの手法を理解する</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>右側を学習することを説明する。</t>
+    <rPh sb="0" eb="2">
+      <t>ミギガワ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">テストとは、「テストとは、開発したシステムが要件どおりに動作することを確認し、要件との差異や欠陥（バグ）を発見するための作業」のこと。
+※テストは欠陥が存在することは示せるが、欠陥が存在しないことは証明できない。
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JSTQBでは、以下の9つの目的を挙げている。
+・要件、ユーザーストーリー、設計、コードなどの作業成果物を評価する
+　→　成果物の品質や妥当性を確認する。
+・故障を引き起こし、欠陥を発見する
+　→　システムに潜む不具合や問題点を見つける。
+・求められるテスト対象のカバレッジ（網羅率）を確保する
+　→　必要な範囲が十分にテストされていることを確認する。
+・ソフトウェア品質が不十分な場合のリスクレベルを下げる
+　→　本番運用時の障害や損失の発生リスクを軽減する。
+・仕様化した要件が満たされているかどうかを検証する
+　→　システムが要件どおりに実装されていることを確認する。
+・テスト対象が契約、法律、規制の要件に適合していることを検証する
+　→　契約事項や法令・規制を満たしていることを確認する。
+・ステークホルダーに根拠ある判断をしてもらうための情報を提供する
+　→　リリース可否や品質評価の判断材料を提供する。
+・テスト対象の品質に対する信頼を積み上げる
+　→　テスト結果を通じて品質への信頼を高める。
+・テスト対象が完成し、ステークホルダーの期待通りに動作するかどうかの妥当性確認をする
+　→　利用者や関係者の期待に沿ったシステムであることを確認する。
+要約すると以下となる（楕円）。
+開発したシステムを検証・評価して欠陥を発見し、リスクを低減するとともに品質を向上させる。
+また、その結果をステークホルダーに提供し、リリース判断を支援するとともに品質への信頼を高める。</t>
+    <rPh sb="533" eb="535">
+      <t>ヨウヤク</t>
+    </rPh>
+    <rPh sb="538" eb="540">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="544" eb="546">
+      <t>ダエン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-01
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テストの目的をフェーズに対応するように説明する。</t>
+    <rPh sb="4" eb="6">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>タイオウ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テストとデバッグの違いを説明する。
+テスト：テスト対象を実行・評価し、要件との差異や欠陥（バグ）を発見するプロセス
+デバッグ：テストなどで発見された欠陥（バグ）の原因を特定し、修正するプロセス
+※要約は以下
+テスト　=　問題を見つける活動
+デバッグ　=　問題を直す活動</t>
+    <rPh sb="9" eb="10">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="99" eb="101">
+      <t>ヨウヤク</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>単体テストとは、「プログラムの最小単位が正しく動作することを確認するテスト」のこと。
+ユニット＝単体</t>
+    <rPh sb="48" eb="50">
+      <t>タンタイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テスト設計の全体像を説明する。
+手順
+1. テスト観点のテーラリング（カスタマイズ）
+　テスト観点（標準）からテスト観点（カスタマイズ）にテーラリングする。
+　■テスト観点（標準）
+　　テスト対象をどのような視点で確認するかを定義したもの。
+　　※標準的なテスト観点表を用いることで、テストの網羅性を確保する。
+　■テスト観点（カスタマイズ）
+　　テスト観点（標準）をベースに、対象システムの特性や要件に合わせてテーラリング（変更・削除・追加）を行ったテスト観点表のこと。
+　　※テスト観点（標準）は、あらゆるシステムに共通して利用できるよう作成されているため、そのまま適用できるとは限らない。
+2. テスト項目の洗い出し
+　テスト観点（カスタマイズ）とインプットを掛け合わせて、網羅的なテスト項目を洗い出す。
+　■インプット
+　　前段の工程で作成された成果物のこと。
+3. テストケースの作成
+  テスト項目を実際に実施できるレベルまで具体化する。
+　■テストケース
+　　テスト項目に対して、具体的な入力値や期待結果を定義したもの。</t>
+    <rPh sb="3" eb="5">
+      <t>セッケイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ゼンタイゾウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <rPh sb="59" eb="61">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="85" eb="87">
+      <t>カンテン</t>
+    </rPh>
+    <rPh sb="88" eb="90">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <rPh sb="114" eb="116">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="247" eb="249">
+      <t>ヒョウジュン</t>
+    </rPh>
+    <rPh sb="368" eb="370">
+      <t>ゼンダン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ツアー予約アプリケーションを例に全体を説明する。
+※角丸の四角は業務ルール</t>
+    <rPh sb="14" eb="15">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゼンタイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>カド</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>マル</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>シカク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ギョウム</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テスト技法とは、「効率的かつ効果的にテストケースを作成するための手法」のこと。
+・ブラックボックステスト技法
+・ホワイトボックステスト技法
+・経験ベースのテスト技法</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ブラックボックステスト技法とは、「テスト対象の内部構造や実装内容を考慮せず、入力に対する出力や振る舞いを検証するテスト技法」のこと。
+■種類
+　・同値分割法
+　・境界値分析
+　・ディシジョンテーブルテスト
+　・状態遷移テスト</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ディシジョンテーブルテストとは、「ディシジョンテーブル（条件と動作の組み合わせ表）を用いて、複数の条件の組み合わせに対する動作をテストする技法」のこと。
+ツアー予約の例で説明する。
+■条件
+・開始日
+・人数
+・空き数
+■動作
+・予約完了
+・予約不可
+これらの組み合わせを使用した、テストケースを作成する。</t>
+    <rPh sb="81" eb="83">
+      <t>ヨヤク</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>レイ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="97" eb="100">
+      <t>カイシビ</t>
+    </rPh>
+    <rPh sb="102" eb="104">
+      <t>ニンズウ</t>
+    </rPh>
+    <rPh sb="106" eb="107">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="108" eb="109">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>ドウサ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>ヨヤク</t>
+    </rPh>
+    <rPh sb="117" eb="119">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>ヨヤク</t>
+    </rPh>
+    <rPh sb="123" eb="125">
+      <t>フカ</t>
+    </rPh>
+    <rPh sb="131" eb="132">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="133" eb="134">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="137" eb="139">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="149" eb="151">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>境界値分析とは、「同値クラスの境界値（範囲の端にある値）に着目し、テストケースを作成する技法」のこと。
+「開始日」の例で説明する。
+■境界値の選定
+・無効値と有効値A
+・有効値Aと有効値B
+境界値を使用した、テストケースを作成する。</t>
+    <rPh sb="68" eb="71">
+      <t>キョウカイチ</t>
+    </rPh>
+    <rPh sb="72" eb="74">
+      <t>センテイ</t>
+    </rPh>
+    <rPh sb="97" eb="100">
+      <t>キョウカイチ</t>
+    </rPh>
+    <rPh sb="101" eb="103">
+      <t>シヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>同値分割法とは、「同じ結果となる入力値をグループ化し、その代表値を用いて効率的にテストケースを作成する技法」のこと。
+同値クラス：テスト対象において同じように処理される入力値のグループ
+代表値：同値クラスを代表してテストに使用する値
+「開始日」の例で説明する。
+■同値クラスの分割
+・無効値：過去
+・有効値A：未来（早期割なし）
+・有効値B：未来（早期割あり）
+■代表値の選定
+真ん中の日付
+代表値を使用した、テストケースを作成する。</t>
+    <rPh sb="59" eb="61">
+      <t>ドウチ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="95" eb="96">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="97" eb="99">
+      <t>ドウチ</t>
+    </rPh>
+    <rPh sb="126" eb="128">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ドウチ</t>
+    </rPh>
+    <rPh sb="139" eb="141">
+      <t>ブンカツ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>ユウコウ</t>
+    </rPh>
+    <rPh sb="153" eb="154">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>ミライ</t>
+    </rPh>
+    <rPh sb="184" eb="186">
+      <t>ダイヒョウ</t>
+    </rPh>
+    <rPh sb="186" eb="187">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="188" eb="190">
+      <t>センテイ</t>
+    </rPh>
+    <rPh sb="191" eb="192">
+      <t>マ</t>
+    </rPh>
+    <rPh sb="193" eb="194">
+      <t>ナカ</t>
+    </rPh>
+    <rPh sb="195" eb="197">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="199" eb="202">
+      <t>ダイヒョウアタイ</t>
+    </rPh>
+    <rPh sb="203" eb="205">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="215" eb="217">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>状態遷移テスト、「システムの状態と状態間の遷移を基にテストケースを作成する技法」のこと。
+※遷移前状態、イベント、遷移後状態の関係を状態遷移図や状態遷移表で整理し、テスト項目を作成する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ホワイトボックステスト技法とは、「テスト対象の内部構造に基づいてテストケースを作成し、プログラムの処理経路を検証するテスト技法」のこと。
+■種類
+　・ステートメントテスト
+　・ブランチテスト</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>コードカバレッジとは、「テスト対象範囲において、実施したテストによってプログラムコードのどの程度が実行されたかを示す指標」のこと。
+ホワイトボックステストにおいて、テストの網羅性を評価するための基準として利用される。
+■主なカバレッジ基準
+　・命令網羅（C0）
+　　全ての命令を最低1回は実行する
+　・分岐網羅（C1）
+　　全ての分岐の結果（True/False）を最低1回は実行する
+　・条件網羅（C2）
+　　条件式を構成する各条件が、TrueとFalseの両方になるように実行する</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ステートメントテストとは、「命令網羅（C0）の達成を目的として、全てのステートメント（命令文）が少なくとも1回実行されるようにテストケースを作成する技法」のこと。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ブランチテストとは、「分岐網羅（C1）の達成を目的として、全ての分岐の結果（True/False）が少なくとも1回実行されるようにテストケースを作成する技法」のこと。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>コンディションテストとは、「条件網羅（C2）の達成を目的として、条件式を構成する全ての条件がTrueとFalseの両方になるようにテストケースを作成する技法」のこと。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>経験ベースの技法とは、「テスト担当者の知識や経験を基に、テストケースを作成する技法」のこと。
+※過去の障害事例や経験を活用することで、潜在的な欠陥を効率的に発見できる。
+■種類
+　・エラー推測
+　・探索的テスト
+　・チェックリストベースドテスト</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>スタブとドライバの違いを説明する。
+・ドライバ
+　テスト対象（被テストモジュール）を呼び出すために使用する模倣オブジェクト。上位モジュールの代わりとなり、テスト対象を制御する。
+・スタブ
+　テスト対象から呼び出される下位モジュールの代わりに使用する模倣オブジェクト。固定の戻り値などを返してテストを支援する。</t>
+    <rPh sb="9" eb="10">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">スタブとモックの違いを説明する。
+・スタブ
+　テスト対象が依存する下位モジュールの代わりとなり、固定の値を返す模倣オブジェクト。
+・モック
+　テスト対象の振る舞いを検証するために、呼び出し内容や回数などを確認できる模倣オブジェクト。
+</t>
+    <rPh sb="8" eb="9">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JUnitとは、「Javaプログラミング言語向けの標準的な単体テストフレームワーク」のこと。
+テストコードを作成して実行することで、繰り返し実行可能なテストを効率的に行うことができる。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>続き</t>
+    <rPh sb="0" eb="1">
+      <t>ツヅ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>[構造理解] Webアプリケーションで必要なもの  ※再掲</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>テストクラスを作成する単位</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>JUnitで単体テスト</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バイブコーディングで単体テスト – はじめに</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バイブコーディング単体テスト❶ テスト項目表を作る</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バイブコーディング単体テスト➋ Repositoryのテストを作る</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>[解説] Repositoryのテストクラス（抜粋）</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バイブコーディング単体テスト➌ Serviceのテストを作る</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>[解説] Serviceのテストクラス（抜粋）</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バイブコーディング単体テスト❹ Controllerのテストを作る</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>[解説] Controllerのテストクラス（抜粋）</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バイブコーディングで単体テスト(JUnit)</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ここから各自で演習を始めましょう。</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>バイブコーディングで単体テスト(JUnit)：演習</t>
+    <rPh sb="23" eb="25">
+      <t>エンシュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3337,24 +3985,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="11">
@@ -3617,7 +4259,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3843,200 +4485,203 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4410,15 +5055,15 @@
   <sheetData>
     <row r="2" spans="1:8" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="106" t="str">
+      <c r="B2" s="100" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
     </row>
     <row r="3" spans="1:8" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -4431,10 +5076,10 @@
     </row>
     <row r="4" spans="1:8" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="107" t="s">
+      <c r="B4" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="108"/>
+      <c r="C4" s="102"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -4442,18 +5087,18 @@
     </row>
     <row r="5" spans="1:8" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="109"/>
-      <c r="C5" s="110"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="104"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:8" ht="16.2">
-      <c r="B7" s="111" t="s">
+      <c r="B7" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="111"/>
+      <c r="C7" s="105"/>
     </row>
     <row r="9" spans="1:8">
       <c r="B9" s="27"/>
@@ -4469,7 +5114,7 @@
       <c r="B10" s="17">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="89" t="s">
+      <c r="C10" s="87" t="s">
         <v>3</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -4481,7 +5126,7 @@
       <c r="B11" s="72">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="86" t="str">
+      <c r="C11" s="84" t="str">
         <f>master!B3</f>
         <v>講義の目的</v>
       </c>
@@ -4491,16 +5136,16 @@
       <c r="A12" s="40">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="83"/>
-      <c r="C12" s="87"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="85"/>
       <c r="G12" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="41"/>
-      <c r="B13" s="84"/>
-      <c r="C13" s="88"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="86"/>
       <c r="F13" s="26"/>
       <c r="H13" s="6"/>
     </row>
@@ -4509,11 +5154,11 @@
       <c r="B14" s="40">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="86" t="str">
+      <c r="C14" s="84" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="F14" s="105"/>
+      <c r="F14" s="99"/>
       <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8">
@@ -4521,8 +5166,8 @@
       <c r="B15" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="87"/>
-      <c r="F15" s="105"/>
+      <c r="C15" s="85"/>
+      <c r="F15" s="99"/>
       <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8">
@@ -4530,8 +5175,8 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="B16" s="44"/>
-      <c r="C16" s="88"/>
-      <c r="F16" s="105"/>
+      <c r="C16" s="86"/>
+      <c r="F16" s="99"/>
       <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8">
@@ -4539,18 +5184,18 @@
       <c r="B17" s="43">
         <v>0.46875</v>
       </c>
-      <c r="C17" s="86">
+      <c r="C17" s="84">
         <f>master!B13</f>
         <v>0</v>
       </c>
-      <c r="F17" s="105"/>
+      <c r="F17" s="99"/>
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="41"/>
       <c r="B18" s="44"/>
-      <c r="C18" s="88"/>
-      <c r="F18" s="105"/>
+      <c r="C18" s="86"/>
+      <c r="F18" s="99"/>
       <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8">
@@ -4558,11 +5203,11 @@
       <c r="B19" s="45">
         <v>0.48958333333333331</v>
       </c>
-      <c r="C19" s="85">
+      <c r="C19" s="83">
         <f>master!B18</f>
         <v>0</v>
       </c>
-      <c r="F19" s="105"/>
+      <c r="F19" s="99"/>
       <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8">
@@ -4572,18 +5217,18 @@
       <c r="B20" s="69">
         <v>0.5</v>
       </c>
-      <c r="C20" s="86">
+      <c r="C20" s="84">
         <f>master!B23</f>
         <v>0</v>
       </c>
-      <c r="F20" s="105"/>
+      <c r="F20" s="99"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="61"/>
       <c r="B21" s="63"/>
-      <c r="C21" s="88"/>
-      <c r="F21" s="105"/>
+      <c r="C21" s="86"/>
+      <c r="F21" s="99"/>
       <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8">
@@ -4591,7 +5236,7 @@
       <c r="B22" s="41">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="90" t="s">
+      <c r="C22" s="88" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="25"/>
@@ -4603,7 +5248,7 @@
       <c r="B23" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C23" s="91"/>
+      <c r="C23" s="89"/>
       <c r="F23" s="25"/>
       <c r="G23" s="10"/>
       <c r="H23" s="6"/>
@@ -4615,7 +5260,7 @@
       <c r="B24" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="91"/>
+      <c r="C24" s="89"/>
       <c r="F24" s="25"/>
       <c r="G24" s="10"/>
       <c r="H24" s="6"/>
@@ -4625,7 +5270,7 @@
       <c r="B25" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="C25" s="92"/>
+      <c r="C25" s="90"/>
       <c r="F25" s="25"/>
       <c r="G25" s="10"/>
       <c r="H25" s="6"/>
@@ -4635,8 +5280,8 @@
       <c r="B26" s="45">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="88"/>
-      <c r="F26" s="105"/>
+      <c r="C26" s="86"/>
+      <c r="F26" s="99"/>
       <c r="G26" s="14"/>
       <c r="H26" s="6"/>
     </row>
@@ -4645,11 +5290,11 @@
       <c r="B27" s="43">
         <v>0.57291666666666663</v>
       </c>
-      <c r="C27" s="86" t="e">
+      <c r="C27" s="84" t="e">
         <f>master!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="F27" s="105"/>
+      <c r="F27" s="99"/>
       <c r="G27" s="14"/>
       <c r="H27" s="6"/>
     </row>
@@ -4658,8 +5303,8 @@
         <v>0.58333333333333337</v>
       </c>
       <c r="B28" s="44"/>
-      <c r="C28" s="88"/>
-      <c r="F28" s="105"/>
+      <c r="C28" s="86"/>
+      <c r="F28" s="99"/>
       <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8">
@@ -4673,7 +5318,7 @@
       </c>
       <c r="D29" s="60"/>
       <c r="E29" s="57"/>
-      <c r="F29" s="105"/>
+      <c r="F29" s="99"/>
       <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8">
@@ -4682,7 +5327,7 @@
       <c r="C30" s="64"/>
       <c r="D30" s="60"/>
       <c r="E30" s="57"/>
-      <c r="F30" s="105"/>
+      <c r="F30" s="99"/>
       <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8">
@@ -4691,7 +5336,7 @@
       <c r="C31" s="64"/>
       <c r="D31" s="60"/>
       <c r="E31" s="11"/>
-      <c r="F31" s="105"/>
+      <c r="F31" s="99"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8">
@@ -4702,7 +5347,7 @@
       <c r="C32" s="64"/>
       <c r="D32" s="60"/>
       <c r="E32" s="11"/>
-      <c r="F32" s="105"/>
+      <c r="F32" s="99"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8">
@@ -4711,7 +5356,7 @@
       <c r="C33" s="64"/>
       <c r="D33" s="60"/>
       <c r="E33" s="57"/>
-      <c r="F33" s="105"/>
+      <c r="F33" s="99"/>
       <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8">
@@ -4725,7 +5370,7 @@
       </c>
       <c r="D34" s="60"/>
       <c r="E34" s="57"/>
-      <c r="F34" s="105"/>
+      <c r="F34" s="99"/>
       <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8">
@@ -4734,7 +5379,7 @@
       <c r="C35" s="64"/>
       <c r="D35" s="60"/>
       <c r="E35" s="57"/>
-      <c r="F35" s="105"/>
+      <c r="F35" s="99"/>
       <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8">
@@ -4745,7 +5390,7 @@
       <c r="C36" s="64"/>
       <c r="D36" s="60"/>
       <c r="E36" s="11"/>
-      <c r="F36" s="105"/>
+      <c r="F36" s="99"/>
       <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8">
@@ -4754,7 +5399,7 @@
       <c r="C37" s="64"/>
       <c r="D37" s="60"/>
       <c r="E37" s="11"/>
-      <c r="F37" s="105"/>
+      <c r="F37" s="99"/>
       <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8">
@@ -4763,7 +5408,7 @@
       <c r="C38" s="64"/>
       <c r="D38" s="60"/>
       <c r="E38" s="11"/>
-      <c r="F38" s="105"/>
+      <c r="F38" s="99"/>
       <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8">
@@ -4772,7 +5417,7 @@
       <c r="C39" s="70"/>
       <c r="D39" s="60"/>
       <c r="E39" s="11"/>
-      <c r="F39" s="105"/>
+      <c r="F39" s="99"/>
       <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8">
@@ -4787,7 +5432,7 @@
       </c>
       <c r="D40" s="60"/>
       <c r="E40" s="57"/>
-      <c r="F40" s="105"/>
+      <c r="F40" s="99"/>
       <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8">
@@ -4796,7 +5441,7 @@
       <c r="C41" s="64"/>
       <c r="D41" s="62"/>
       <c r="E41" s="58"/>
-      <c r="F41" s="105"/>
+      <c r="F41" s="99"/>
       <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8">
@@ -4805,15 +5450,15 @@
       <c r="C42" s="65"/>
       <c r="D42" s="60"/>
       <c r="E42" s="58"/>
-      <c r="F42" s="105"/>
+      <c r="F42" s="99"/>
       <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
       <c r="A43" s="44"/>
-      <c r="B43" s="94">
+      <c r="B43" s="92">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="93" t="s">
+      <c r="C43" s="91" t="s">
         <v>61</v>
       </c>
       <c r="D43" s="61"/>
@@ -4892,10 +5537,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="117"/>
+      <c r="C4" s="111"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -4906,16 +5551,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+      <c r="F5" s="112"/>
+      <c r="G5" s="112"/>
+      <c r="H5" s="112"/>
+      <c r="I5" s="112"/>
+      <c r="J5" s="112"/>
+      <c r="K5" s="112"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -4928,10 +5573,10 @@
         <v>16</v>
       </c>
       <c r="C7" s="36"/>
-      <c r="D7" s="119" t="s">
+      <c r="D7" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="119"/>
+      <c r="E7" s="113"/>
       <c r="F7" s="36" t="s">
         <v>11</v>
       </c>
@@ -4971,46 +5616,46 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="113" t="s">
+      <c r="B11" s="107"/>
+      <c r="C11" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="113" t="s">
+      <c r="D11" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="113"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113" t="s">
+      <c r="E11" s="107"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="120" t="s">
+      <c r="H11" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="I11" s="112" t="s">
+      <c r="I11" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="112"/>
-      <c r="K11" s="112" t="s">
+      <c r="J11" s="106"/>
+      <c r="K11" s="106" t="s">
         <v>34</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="113"/>
-      <c r="C12" s="113"/>
-      <c r="D12" s="113"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="113"/>
-      <c r="G12" s="113"/>
-      <c r="H12" s="121"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="115"/>
       <c r="I12" s="31" t="s">
         <v>27</v>
       </c>
       <c r="J12" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="113"/>
+      <c r="K12" s="107"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
@@ -5019,11 +5664,11 @@
       <c r="C13" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="114" t="s">
+      <c r="D13" s="108" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="115"/>
-      <c r="F13" s="116"/>
+      <c r="E13" s="109"/>
+      <c r="F13" s="110"/>
       <c r="G13" s="66" t="s">
         <v>59</v>
       </c>
@@ -5043,12 +5688,12 @@
       <c r="C14" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="114" t="s">
+      <c r="D14" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="115"/>
-      <c r="F14" s="116"/>
-      <c r="G14" s="82" t="s">
+      <c r="E14" s="109"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="80" t="s">
         <v>60</v>
       </c>
       <c r="H14" s="20"/>
@@ -5097,7 +5742,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N121"/>
+  <dimension ref="A2:N150"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -5147,12 +5792,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
+      <c r="C4" s="111"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="111"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -5163,30 +5808,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="133"/>
-      <c r="C5" s="133"/>
-      <c r="D5" s="133"/>
-      <c r="E5" s="133"/>
-      <c r="F5" s="133"/>
-      <c r="G5" s="133"/>
-      <c r="H5" s="133"/>
-      <c r="I5" s="133"/>
-      <c r="J5" s="133"/>
-      <c r="K5" s="133"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="127"/>
+      <c r="J5" s="127"/>
+      <c r="K5" s="127"/>
       <c r="L5" s="32"/>
       <c r="M5" s="33"/>
     </row>
     <row r="6" spans="2:14" ht="32.4" customHeight="1">
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="133"/>
-      <c r="K6" s="133"/>
+      <c r="B6" s="127"/>
+      <c r="C6" s="127"/>
+      <c r="D6" s="127"/>
+      <c r="E6" s="127"/>
+      <c r="F6" s="127"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="127"/>
+      <c r="I6" s="127"/>
+      <c r="J6" s="127"/>
+      <c r="K6" s="127"/>
       <c r="L6" s="32"/>
       <c r="M6" s="33"/>
     </row>
@@ -5430,28 +6075,28 @@
     </row>
     <row r="20" spans="1:14" ht="24" customHeight="1">
       <c r="A20" s="10"/>
-      <c r="B20" s="113" t="s">
+      <c r="B20" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="113" t="s">
+      <c r="D20" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="113"/>
-      <c r="F20" s="113"/>
-      <c r="G20" s="113" t="s">
+      <c r="E20" s="107"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="112" t="s">
+      <c r="H20" s="106" t="s">
         <v>25</v>
       </c>
-      <c r="I20" s="131" t="s">
+      <c r="I20" s="125" t="s">
         <v>35</v>
       </c>
-      <c r="J20" s="132"/>
-      <c r="K20" s="112" t="s">
+      <c r="J20" s="126"/>
+      <c r="K20" s="106" t="s">
         <v>36</v>
       </c>
       <c r="L20" s="6"/>
@@ -5460,27 +6105,27 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="10"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="113"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="112"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="107"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="107"/>
+      <c r="H21" s="106"/>
       <c r="I21" s="31" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="K21" s="113"/>
+      <c r="K21" s="107"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" ht="151.19999999999999">
       <c r="A22" s="10"/>
-      <c r="B22" s="95" t="str">
+      <c r="B22" s="93" t="str">
         <f>master!B3</f>
         <v>講義の目的</v>
       </c>
@@ -5488,11 +6133,11 @@
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D22" s="122" t="s">
+      <c r="D22" s="116" t="s">
         <v>106</v>
       </c>
-      <c r="E22" s="123"/>
-      <c r="F22" s="124"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
       <c r="G22" s="55" t="s">
         <v>107</v>
       </c>
@@ -5510,7 +6155,7 @@
     </row>
     <row r="23" spans="1:14" ht="138.6" customHeight="1">
       <c r="A23" s="10"/>
-      <c r="B23" s="134" t="str">
+      <c r="B23" s="128" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -5518,11 +6163,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D23" s="122" t="s">
+      <c r="D23" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="E23" s="123"/>
-      <c r="F23" s="124"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="55" t="s">
         <v>48</v>
       </c>
@@ -5540,16 +6185,16 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="135"/>
+      <c r="B24" s="129"/>
       <c r="C24" s="55" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D24" s="122" t="s">
+      <c r="D24" s="116" t="s">
         <v>109</v>
       </c>
-      <c r="E24" s="123"/>
-      <c r="F24" s="124"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="118"/>
       <c r="G24" s="55" t="s">
         <v>52</v>
       </c>
@@ -5567,16 +6212,16 @@
     </row>
     <row r="25" spans="1:14" ht="37.799999999999997">
       <c r="A25" s="11"/>
-      <c r="B25" s="135"/>
+      <c r="B25" s="129"/>
       <c r="C25" s="55" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D25" s="122" t="s">
+      <c r="D25" s="116" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="123"/>
-      <c r="F25" s="124"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="118"/>
       <c r="G25" s="55" t="s">
         <v>50</v>
       </c>
@@ -5594,16 +6239,16 @@
     </row>
     <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
-      <c r="B26" s="135"/>
+      <c r="B26" s="129"/>
       <c r="C26" s="55" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D26" s="122" t="s">
+      <c r="D26" s="116" t="s">
         <v>111</v>
       </c>
-      <c r="E26" s="123"/>
-      <c r="F26" s="124"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="118"/>
       <c r="G26" s="55" t="s">
         <v>49</v>
       </c>
@@ -5621,13 +6266,13 @@
     </row>
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
-      <c r="B27" s="135"/>
+      <c r="B27" s="129"/>
       <c r="C27" s="55"/>
-      <c r="D27" s="122" t="s">
+      <c r="D27" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="E27" s="123"/>
-      <c r="F27" s="124"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="55" t="s">
         <v>49</v>
       </c>
@@ -5645,16 +6290,16 @@
     </row>
     <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="136"/>
+      <c r="B28" s="130"/>
       <c r="C28" s="55" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D28" s="122" t="s">
+      <c r="D28" s="116" t="s">
         <v>113</v>
       </c>
-      <c r="E28" s="123"/>
-      <c r="F28" s="124"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
       <c r="G28" s="55" t="s">
         <v>53</v>
       </c>
@@ -5672,7 +6317,7 @@
     </row>
     <row r="29" spans="1:14" ht="102" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="134" t="str">
+      <c r="B29" s="128" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -5680,11 +6325,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D29" s="122" t="s">
+      <c r="D29" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="E29" s="123"/>
-      <c r="F29" s="124"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="118"/>
       <c r="G29" s="55" t="s">
         <v>50</v>
       </c>
@@ -5702,16 +6347,16 @@
     </row>
     <row r="30" spans="1:14" ht="88.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="135"/>
+      <c r="B30" s="129"/>
       <c r="C30" s="55" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D30" s="122" t="s">
+      <c r="D30" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="E30" s="123"/>
-      <c r="F30" s="124"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="118"/>
       <c r="G30" s="55" t="s">
         <v>54</v>
       </c>
@@ -5729,16 +6374,16 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="135"/>
+      <c r="B31" s="129"/>
       <c r="C31" s="55" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D31" s="122" t="s">
+      <c r="D31" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="E31" s="123"/>
-      <c r="F31" s="124"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="55" t="s">
         <v>55</v>
       </c>
@@ -5758,16 +6403,16 @@
     </row>
     <row r="32" spans="1:14" ht="75.599999999999994">
       <c r="A32" s="11"/>
-      <c r="B32" s="135"/>
+      <c r="B32" s="129"/>
       <c r="C32" s="55" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D32" s="122" t="s">
+      <c r="D32" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="E32" s="123"/>
-      <c r="F32" s="124"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
       <c r="G32" s="55" t="s">
         <v>52</v>
       </c>
@@ -5785,16 +6430,16 @@
     </row>
     <row r="33" spans="1:14" ht="100.8">
       <c r="A33" s="11"/>
-      <c r="B33" s="135"/>
+      <c r="B33" s="129"/>
       <c r="C33" s="55" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D33" s="122" t="s">
+      <c r="D33" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="123"/>
-      <c r="F33" s="124"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="118"/>
       <c r="G33" s="55" t="s">
         <v>56</v>
       </c>
@@ -5812,16 +6457,16 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="135"/>
+      <c r="B34" s="129"/>
       <c r="C34" s="55" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D34" s="122" t="s">
+      <c r="D34" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="123"/>
-      <c r="F34" s="124"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="118"/>
       <c r="G34" s="55" t="s">
         <v>50</v>
       </c>
@@ -5839,16 +6484,16 @@
     </row>
     <row r="35" spans="1:14" ht="37.799999999999997">
       <c r="A35" s="11"/>
-      <c r="B35" s="135"/>
+      <c r="B35" s="129"/>
       <c r="C35" s="55" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D35" s="122" t="s">
+      <c r="D35" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="E35" s="123"/>
-      <c r="F35" s="124"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="55" t="s">
         <v>50</v>
       </c>
@@ -5866,16 +6511,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="136"/>
+      <c r="B36" s="130"/>
       <c r="C36" s="55" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D36" s="122" t="s">
+      <c r="D36" s="116" t="s">
         <v>121</v>
       </c>
-      <c r="E36" s="123"/>
-      <c r="F36" s="124"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="118"/>
       <c r="G36" s="55" t="s">
         <v>50</v>
       </c>
@@ -5893,7 +6538,7 @@
     </row>
     <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="134" t="str">
+      <c r="B37" s="128" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -5901,11 +6546,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D37" s="122" t="s">
+      <c r="D37" s="116" t="s">
         <v>122</v>
       </c>
-      <c r="E37" s="123"/>
-      <c r="F37" s="124"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="118"/>
       <c r="G37" s="55" t="s">
         <v>54</v>
       </c>
@@ -5923,16 +6568,16 @@
     </row>
     <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="135"/>
+      <c r="B38" s="129"/>
       <c r="C38" s="55" t="str">
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D38" s="122" t="s">
+      <c r="D38" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="E38" s="123"/>
-      <c r="F38" s="124"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="118"/>
       <c r="G38" s="55" t="s">
         <v>52</v>
       </c>
@@ -5950,16 +6595,16 @@
     </row>
     <row r="39" spans="1:14" ht="75.599999999999994">
       <c r="A39" s="11"/>
-      <c r="B39" s="135"/>
+      <c r="B39" s="129"/>
       <c r="C39" s="55" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D39" s="122" t="s">
+      <c r="D39" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="123"/>
-      <c r="F39" s="124"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="55" t="s">
         <v>52</v>
       </c>
@@ -5977,16 +6622,16 @@
     </row>
     <row r="40" spans="1:14" ht="50.4">
       <c r="A40" s="11"/>
-      <c r="B40" s="135"/>
+      <c r="B40" s="129"/>
       <c r="C40" s="55" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D40" s="122" t="s">
+      <c r="D40" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="123"/>
-      <c r="F40" s="124"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="118"/>
       <c r="G40" s="55" t="s">
         <v>51</v>
       </c>
@@ -6004,16 +6649,16 @@
     </row>
     <row r="41" spans="1:14" ht="88.2">
       <c r="A41" s="11"/>
-      <c r="B41" s="135"/>
+      <c r="B41" s="129"/>
       <c r="C41" s="55" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D41" s="122" t="s">
+      <c r="D41" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="123"/>
-      <c r="F41" s="124"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="118"/>
       <c r="G41" s="55" t="s">
         <v>54</v>
       </c>
@@ -6033,16 +6678,16 @@
     </row>
     <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
-      <c r="B42" s="135"/>
+      <c r="B42" s="129"/>
       <c r="C42" s="55" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D42" s="122" t="s">
+      <c r="D42" s="116" t="s">
         <v>128</v>
       </c>
-      <c r="E42" s="123"/>
-      <c r="F42" s="124"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="118"/>
       <c r="G42" s="55" t="s">
         <v>129</v>
       </c>
@@ -6060,16 +6705,16 @@
     </row>
     <row r="43" spans="1:14" ht="37.799999999999997">
       <c r="A43" s="11"/>
-      <c r="B43" s="135"/>
+      <c r="B43" s="129"/>
       <c r="C43" s="55" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D43" s="122" t="s">
+      <c r="D43" s="116" t="s">
         <v>130</v>
       </c>
-      <c r="E43" s="123"/>
-      <c r="F43" s="124"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="55" t="s">
         <v>50</v>
       </c>
@@ -6087,16 +6732,16 @@
     </row>
     <row r="44" spans="1:14" ht="163.80000000000001">
       <c r="A44" s="11"/>
-      <c r="B44" s="135"/>
+      <c r="B44" s="129"/>
       <c r="C44" s="55" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D44" s="122" t="s">
+      <c r="D44" s="116" t="s">
         <v>131</v>
       </c>
-      <c r="E44" s="123"/>
-      <c r="F44" s="124"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="118"/>
       <c r="G44" s="55" t="s">
         <v>132</v>
       </c>
@@ -6114,16 +6759,16 @@
     </row>
     <row r="45" spans="1:14" ht="25.2">
       <c r="A45" s="11"/>
-      <c r="B45" s="135"/>
+      <c r="B45" s="129"/>
       <c r="C45" s="55" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D45" s="122" t="s">
+      <c r="D45" s="116" t="s">
         <v>133</v>
       </c>
-      <c r="E45" s="123"/>
-      <c r="F45" s="124"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="118"/>
       <c r="G45" s="55" t="s">
         <v>55</v>
       </c>
@@ -6141,16 +6786,16 @@
     </row>
     <row r="46" spans="1:14" ht="189">
       <c r="A46" s="11"/>
-      <c r="B46" s="135"/>
+      <c r="B46" s="129"/>
       <c r="C46" s="55" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D46" s="122" t="s">
+      <c r="D46" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="E46" s="123"/>
-      <c r="F46" s="124"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="118"/>
       <c r="G46" s="55" t="s">
         <v>135</v>
       </c>
@@ -6168,16 +6813,16 @@
     </row>
     <row r="47" spans="1:14" ht="88.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="135"/>
+      <c r="B47" s="129"/>
       <c r="C47" s="55" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D47" s="122" t="s">
+      <c r="D47" s="116" t="s">
         <v>136</v>
       </c>
-      <c r="E47" s="123"/>
-      <c r="F47" s="124"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="55" t="s">
         <v>54</v>
       </c>
@@ -6197,16 +6842,16 @@
     </row>
     <row r="48" spans="1:14" ht="63">
       <c r="A48" s="11"/>
-      <c r="B48" s="135"/>
+      <c r="B48" s="129"/>
       <c r="C48" s="55" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D48" s="122" t="s">
+      <c r="D48" s="116" t="s">
         <v>137</v>
       </c>
-      <c r="E48" s="123"/>
-      <c r="F48" s="124"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="118"/>
       <c r="G48" s="55" t="s">
         <v>49</v>
       </c>
@@ -6224,16 +6869,16 @@
     </row>
     <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
-      <c r="B49" s="135"/>
+      <c r="B49" s="129"/>
       <c r="C49" s="55" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D49" s="122" t="s">
+      <c r="D49" s="116" t="s">
         <v>138</v>
       </c>
-      <c r="E49" s="123"/>
-      <c r="F49" s="124"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="118"/>
       <c r="G49" s="55" t="s">
         <v>56</v>
       </c>
@@ -6251,16 +6896,16 @@
     </row>
     <row r="50" spans="1:14" ht="100.8">
       <c r="A50" s="11"/>
-      <c r="B50" s="135"/>
+      <c r="B50" s="129"/>
       <c r="C50" s="55" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D50" s="122" t="s">
+      <c r="D50" s="116" t="s">
         <v>139</v>
       </c>
-      <c r="E50" s="123"/>
-      <c r="F50" s="124"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="118"/>
       <c r="G50" s="55" t="s">
         <v>56</v>
       </c>
@@ -6278,16 +6923,16 @@
     </row>
     <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="135"/>
+      <c r="B51" s="129"/>
       <c r="C51" s="55" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D51" s="122" t="s">
+      <c r="D51" s="116" t="s">
         <v>140</v>
       </c>
-      <c r="E51" s="123"/>
-      <c r="F51" s="124"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="55" t="s">
         <v>54</v>
       </c>
@@ -6305,16 +6950,16 @@
     </row>
     <row r="52" spans="1:14" ht="63">
       <c r="A52" s="11"/>
-      <c r="B52" s="135"/>
+      <c r="B52" s="129"/>
       <c r="C52" s="55" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D52" s="122" t="s">
+      <c r="D52" s="116" t="s">
         <v>141</v>
       </c>
-      <c r="E52" s="123"/>
-      <c r="F52" s="124"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="118"/>
       <c r="G52" s="55" t="s">
         <v>49</v>
       </c>
@@ -6332,16 +6977,16 @@
     </row>
     <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
-      <c r="B53" s="135"/>
+      <c r="B53" s="129"/>
       <c r="C53" s="55" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D53" s="122" t="s">
+      <c r="D53" s="116" t="s">
         <v>142</v>
       </c>
-      <c r="E53" s="123"/>
-      <c r="F53" s="124"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="118"/>
       <c r="G53" s="55" t="s">
         <v>51</v>
       </c>
@@ -6359,16 +7004,16 @@
     </row>
     <row r="54" spans="1:14" ht="88.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="135"/>
+      <c r="B54" s="129"/>
       <c r="C54" s="55" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D54" s="122" t="s">
+      <c r="D54" s="116" t="s">
         <v>143</v>
       </c>
-      <c r="E54" s="123"/>
-      <c r="F54" s="124"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="118"/>
       <c r="G54" s="55" t="s">
         <v>54</v>
       </c>
@@ -6386,14 +7031,14 @@
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="136"/>
+      <c r="B55" s="130"/>
       <c r="C55" s="55" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D55" s="122"/>
-      <c r="E55" s="123"/>
-      <c r="F55" s="124"/>
+      <c r="D55" s="116"/>
+      <c r="E55" s="117"/>
+      <c r="F55" s="118"/>
       <c r="G55" s="55" t="s">
         <v>55</v>
       </c>
@@ -6411,1212 +7056,1212 @@
     </row>
     <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="137" t="str">
+      <c r="B56" s="131" t="str">
         <f>master!B37</f>
         <v>導入</v>
       </c>
-      <c r="C56" s="77" t="str">
+      <c r="C56" s="75" t="str">
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D56" s="128" t="s">
+      <c r="D56" s="122" t="s">
         <v>186</v>
       </c>
-      <c r="E56" s="129"/>
-      <c r="F56" s="130"/>
-      <c r="G56" s="77" t="s">
+      <c r="E56" s="123"/>
+      <c r="F56" s="124"/>
+      <c r="G56" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H56" s="78"/>
-      <c r="I56" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J56" s="80">
+      <c r="H56" s="76"/>
+      <c r="I56" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J56" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K56" s="81"/>
+      <c r="K56" s="79"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="37.799999999999997">
       <c r="A57" s="11"/>
-      <c r="B57" s="138"/>
-      <c r="C57" s="77" t="str">
+      <c r="B57" s="132"/>
+      <c r="C57" s="75" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D57" s="128" t="s">
+      <c r="D57" s="122" t="s">
         <v>187</v>
       </c>
-      <c r="E57" s="129"/>
-      <c r="F57" s="130"/>
-      <c r="G57" s="77" t="s">
+      <c r="E57" s="123"/>
+      <c r="F57" s="124"/>
+      <c r="G57" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H57" s="78"/>
-      <c r="I57" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J57" s="80">
+      <c r="H57" s="76"/>
+      <c r="I57" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J57" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K57" s="81"/>
+      <c r="K57" s="79"/>
       <c r="L57" s="6"/>
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
     <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="139"/>
-      <c r="C58" s="77" t="str">
+      <c r="B58" s="133"/>
+      <c r="C58" s="75" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D58" s="128" t="s">
+      <c r="D58" s="122" t="s">
         <v>188</v>
       </c>
-      <c r="E58" s="129"/>
-      <c r="F58" s="130"/>
-      <c r="G58" s="77" t="s">
+      <c r="E58" s="123"/>
+      <c r="F58" s="124"/>
+      <c r="G58" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="H58" s="78"/>
-      <c r="I58" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J58" s="80">
+      <c r="H58" s="76"/>
+      <c r="I58" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J58" s="78">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K58" s="81"/>
+      <c r="K58" s="79"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="11"/>
-      <c r="B59" s="137" t="str">
+      <c r="B59" s="131" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
-      <c r="C59" s="77" t="str">
+      <c r="C59" s="75" t="str">
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D59" s="128"/>
-      <c r="E59" s="129"/>
-      <c r="F59" s="130"/>
-      <c r="G59" s="77" t="s">
+      <c r="D59" s="122"/>
+      <c r="E59" s="123"/>
+      <c r="F59" s="124"/>
+      <c r="G59" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="H59" s="78"/>
-      <c r="I59" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J59" s="80">
+      <c r="H59" s="76"/>
+      <c r="I59" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K59" s="81"/>
+      <c r="K59" s="79"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="138"/>
-      <c r="C60" s="77" t="str">
+      <c r="B60" s="132"/>
+      <c r="C60" s="75" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D60" s="128" t="s">
+      <c r="D60" s="122" t="s">
         <v>189</v>
       </c>
-      <c r="E60" s="129"/>
-      <c r="F60" s="130"/>
-      <c r="G60" s="77" t="s">
+      <c r="E60" s="123"/>
+      <c r="F60" s="124"/>
+      <c r="G60" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H60" s="78"/>
-      <c r="I60" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J60" s="80">
+      <c r="H60" s="76"/>
+      <c r="I60" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J60" s="78">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K60" s="81"/>
+      <c r="K60" s="79"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" ht="25.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="138"/>
-      <c r="C61" s="77" t="str">
+      <c r="B61" s="132"/>
+      <c r="C61" s="75" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D61" s="128" t="s">
+      <c r="D61" s="122" t="s">
         <v>190</v>
       </c>
-      <c r="E61" s="129"/>
-      <c r="F61" s="130"/>
-      <c r="G61" s="77" t="s">
+      <c r="E61" s="123"/>
+      <c r="F61" s="124"/>
+      <c r="G61" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="H61" s="78"/>
-      <c r="I61" s="79" t="s">
+      <c r="H61" s="76"/>
+      <c r="I61" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="J61" s="80">
+      <c r="J61" s="78">
         <v>0</v>
       </c>
-      <c r="K61" s="81"/>
+      <c r="K61" s="79"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
     <row r="62" spans="1:14" ht="88.2">
       <c r="A62" s="11"/>
-      <c r="B62" s="138"/>
-      <c r="C62" s="77" t="str">
+      <c r="B62" s="132"/>
+      <c r="C62" s="75" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D62" s="128" t="s">
+      <c r="D62" s="122" t="s">
         <v>213</v>
       </c>
-      <c r="E62" s="129"/>
-      <c r="F62" s="130"/>
-      <c r="G62" s="77" t="s">
+      <c r="E62" s="123"/>
+      <c r="F62" s="124"/>
+      <c r="G62" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="H62" s="78"/>
-      <c r="I62" s="79" t="s">
+      <c r="H62" s="76"/>
+      <c r="I62" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="J62" s="80">
+      <c r="J62" s="78">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K62" s="81"/>
+      <c r="K62" s="79"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14" ht="50.4">
       <c r="A63" s="11"/>
-      <c r="B63" s="138"/>
-      <c r="C63" s="77" t="str">
+      <c r="B63" s="132"/>
+      <c r="C63" s="75" t="str">
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D63" s="128" t="s">
+      <c r="D63" s="122" t="s">
         <v>191</v>
       </c>
-      <c r="E63" s="129"/>
-      <c r="F63" s="130"/>
-      <c r="G63" s="77" t="s">
+      <c r="E63" s="123"/>
+      <c r="F63" s="124"/>
+      <c r="G63" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H63" s="78"/>
-      <c r="I63" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J63" s="80">
+      <c r="H63" s="76"/>
+      <c r="I63" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J63" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K63" s="81"/>
+      <c r="K63" s="79"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14" ht="151.19999999999999">
       <c r="A64" s="11"/>
-      <c r="B64" s="138"/>
-      <c r="C64" s="77" t="str">
+      <c r="B64" s="132"/>
+      <c r="C64" s="75" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D64" s="128" t="s">
+      <c r="D64" s="122" t="s">
         <v>194</v>
       </c>
-      <c r="E64" s="129"/>
-      <c r="F64" s="130"/>
-      <c r="G64" s="77" t="s">
+      <c r="E64" s="123"/>
+      <c r="F64" s="124"/>
+      <c r="G64" s="75" t="s">
         <v>107</v>
       </c>
-      <c r="H64" s="78"/>
-      <c r="I64" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J64" s="80">
+      <c r="H64" s="76"/>
+      <c r="I64" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J64" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K64" s="81"/>
+      <c r="K64" s="79"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" ht="214.2">
       <c r="A65" s="11"/>
-      <c r="B65" s="138"/>
-      <c r="C65" s="77" t="str">
+      <c r="B65" s="132"/>
+      <c r="C65" s="75" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D65" s="128" t="s">
+      <c r="D65" s="122" t="s">
         <v>195</v>
       </c>
-      <c r="E65" s="129"/>
-      <c r="F65" s="130"/>
-      <c r="G65" s="77" t="s">
+      <c r="E65" s="123"/>
+      <c r="F65" s="124"/>
+      <c r="G65" s="75" t="s">
         <v>193</v>
       </c>
-      <c r="H65" s="78"/>
-      <c r="I65" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J65" s="80">
+      <c r="H65" s="76"/>
+      <c r="I65" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J65" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K65" s="81"/>
+      <c r="K65" s="79"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
     <row r="66" spans="1:14" ht="63">
       <c r="A66" s="11"/>
-      <c r="B66" s="138"/>
-      <c r="C66" s="77" t="str">
+      <c r="B66" s="132"/>
+      <c r="C66" s="75" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D66" s="128" t="s">
+      <c r="D66" s="122" t="s">
         <v>196</v>
       </c>
-      <c r="E66" s="129"/>
-      <c r="F66" s="130"/>
-      <c r="G66" s="77" t="s">
+      <c r="E66" s="123"/>
+      <c r="F66" s="124"/>
+      <c r="G66" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="H66" s="78"/>
-      <c r="I66" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J66" s="80">
+      <c r="H66" s="76"/>
+      <c r="I66" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K66" s="81"/>
+      <c r="K66" s="79"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" ht="163.80000000000001">
       <c r="A67" s="11"/>
-      <c r="B67" s="138"/>
-      <c r="C67" s="77" t="str">
+      <c r="B67" s="132"/>
+      <c r="C67" s="75" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D67" s="128" t="s">
+      <c r="D67" s="122" t="s">
         <v>198</v>
       </c>
-      <c r="E67" s="129"/>
-      <c r="F67" s="130"/>
-      <c r="G67" s="77" t="s">
+      <c r="E67" s="123"/>
+      <c r="F67" s="124"/>
+      <c r="G67" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="H67" s="78"/>
-      <c r="I67" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J67" s="80">
+      <c r="H67" s="76"/>
+      <c r="I67" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J67" s="78">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K67" s="81"/>
+      <c r="K67" s="79"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" ht="50.4">
       <c r="A68" s="11"/>
-      <c r="B68" s="138"/>
-      <c r="C68" s="77" t="str">
+      <c r="B68" s="132"/>
+      <c r="C68" s="75" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D68" s="128" t="s">
+      <c r="D68" s="122" t="s">
         <v>199</v>
       </c>
-      <c r="E68" s="129"/>
-      <c r="F68" s="130"/>
-      <c r="G68" s="77" t="s">
+      <c r="E68" s="123"/>
+      <c r="F68" s="124"/>
+      <c r="G68" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H68" s="78"/>
-      <c r="I68" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J68" s="80">
+      <c r="H68" s="76"/>
+      <c r="I68" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J68" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K68" s="81"/>
+      <c r="K68" s="79"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="138"/>
-      <c r="C69" s="77" t="str">
+      <c r="B69" s="132"/>
+      <c r="C69" s="75" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D69" s="128" t="s">
+      <c r="D69" s="122" t="s">
         <v>200</v>
       </c>
-      <c r="E69" s="129"/>
-      <c r="F69" s="130"/>
-      <c r="G69" s="77" t="s">
+      <c r="E69" s="123"/>
+      <c r="F69" s="124"/>
+      <c r="G69" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H69" s="78"/>
-      <c r="I69" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J69" s="80">
+      <c r="H69" s="76"/>
+      <c r="I69" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J69" s="78">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K69" s="81"/>
+      <c r="K69" s="79"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="138"/>
-      <c r="C70" s="77" t="str">
+      <c r="B70" s="132"/>
+      <c r="C70" s="75" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D70" s="128" t="s">
+      <c r="D70" s="122" t="s">
         <v>202</v>
       </c>
-      <c r="E70" s="129"/>
-      <c r="F70" s="130"/>
-      <c r="G70" s="77" t="s">
+      <c r="E70" s="123"/>
+      <c r="F70" s="124"/>
+      <c r="G70" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H70" s="78"/>
-      <c r="I70" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J70" s="80">
+      <c r="H70" s="76"/>
+      <c r="I70" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J70" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K70" s="81"/>
+      <c r="K70" s="79"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
     <row r="71" spans="1:14" ht="37.799999999999997">
       <c r="A71" s="11"/>
-      <c r="B71" s="138"/>
-      <c r="C71" s="77" t="str">
+      <c r="B71" s="132"/>
+      <c r="C71" s="75" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D71" s="128" t="s">
+      <c r="D71" s="122" t="s">
         <v>201</v>
       </c>
-      <c r="E71" s="129"/>
-      <c r="F71" s="130"/>
-      <c r="G71" s="77" t="s">
+      <c r="E71" s="123"/>
+      <c r="F71" s="124"/>
+      <c r="G71" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H71" s="78"/>
-      <c r="I71" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J71" s="80">
+      <c r="H71" s="76"/>
+      <c r="I71" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J71" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K71" s="81"/>
+      <c r="K71" s="79"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
     <row r="72" spans="1:14" ht="25.2" customHeight="1">
       <c r="A72" s="11"/>
-      <c r="B72" s="137" t="str">
+      <c r="B72" s="131" t="str">
         <f>master!B53</f>
         <v>バイブコーディング：ハンズオン</v>
       </c>
-      <c r="C72" s="77" t="str">
+      <c r="C72" s="75" t="str">
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D72" s="128" t="s">
+      <c r="D72" s="122" t="s">
         <v>203</v>
       </c>
-      <c r="E72" s="129"/>
-      <c r="F72" s="130"/>
-      <c r="G72" s="77" t="s">
+      <c r="E72" s="123"/>
+      <c r="F72" s="124"/>
+      <c r="G72" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="H72" s="78"/>
-      <c r="I72" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J72" s="80">
+      <c r="H72" s="76"/>
+      <c r="I72" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J72" s="78">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K72" s="81"/>
+      <c r="K72" s="79"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" ht="138.6">
       <c r="A73" s="11"/>
-      <c r="B73" s="138"/>
-      <c r="C73" s="77" t="str">
+      <c r="B73" s="132"/>
+      <c r="C73" s="75" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D73" s="128" t="s">
+      <c r="D73" s="122" t="s">
         <v>204</v>
       </c>
-      <c r="E73" s="129"/>
-      <c r="F73" s="130"/>
-      <c r="G73" s="77" t="s">
+      <c r="E73" s="123"/>
+      <c r="F73" s="124"/>
+      <c r="G73" s="75" t="s">
         <v>48</v>
       </c>
-      <c r="H73" s="78"/>
-      <c r="I73" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J73" s="80">
+      <c r="H73" s="76"/>
+      <c r="I73" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J73" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K73" s="81"/>
+      <c r="K73" s="79"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
     <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="138"/>
-      <c r="C74" s="98" t="str">
+      <c r="B74" s="132"/>
+      <c r="C74" s="95" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D74" s="128" t="s">
+      <c r="D74" s="122" t="s">
         <v>214</v>
       </c>
-      <c r="E74" s="129"/>
-      <c r="F74" s="130"/>
-      <c r="G74" s="77" t="s">
+      <c r="E74" s="123"/>
+      <c r="F74" s="124"/>
+      <c r="G74" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H74" s="78"/>
-      <c r="I74" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J74" s="80">
+      <c r="H74" s="76"/>
+      <c r="I74" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J74" s="78">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K74" s="81"/>
+      <c r="K74" s="79"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
     <row r="75" spans="1:14" ht="88.2" customHeight="1">
       <c r="A75" s="11"/>
-      <c r="B75" s="138"/>
-      <c r="C75" s="99"/>
-      <c r="D75" s="128" t="s">
+      <c r="B75" s="132"/>
+      <c r="C75" s="96"/>
+      <c r="D75" s="122" t="s">
         <v>205</v>
       </c>
-      <c r="E75" s="129"/>
-      <c r="F75" s="130"/>
-      <c r="G75" s="77" t="s">
+      <c r="E75" s="123"/>
+      <c r="F75" s="124"/>
+      <c r="G75" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="H75" s="78"/>
-      <c r="I75" s="79"/>
-      <c r="J75" s="80"/>
-      <c r="K75" s="81"/>
+      <c r="H75" s="76"/>
+      <c r="I75" s="77"/>
+      <c r="J75" s="78"/>
+      <c r="K75" s="79"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="138"/>
-      <c r="C76" s="98" t="str">
+      <c r="B76" s="132"/>
+      <c r="C76" s="95" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D76" s="128" t="s">
+      <c r="D76" s="122" t="s">
         <v>218</v>
       </c>
-      <c r="E76" s="129"/>
-      <c r="F76" s="130"/>
-      <c r="G76" s="77" t="s">
+      <c r="E76" s="123"/>
+      <c r="F76" s="124"/>
+      <c r="G76" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H76" s="78"/>
-      <c r="I76" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J76" s="80">
+      <c r="H76" s="76"/>
+      <c r="I76" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K76" s="81"/>
+      <c r="K76" s="79"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" ht="88.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="138"/>
-      <c r="C77" s="99"/>
-      <c r="D77" s="128" t="s">
+      <c r="B77" s="132"/>
+      <c r="C77" s="96"/>
+      <c r="D77" s="122" t="s">
         <v>205</v>
       </c>
-      <c r="E77" s="129"/>
-      <c r="F77" s="130"/>
-      <c r="G77" s="77" t="s">
+      <c r="E77" s="123"/>
+      <c r="F77" s="124"/>
+      <c r="G77" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="H77" s="78"/>
-      <c r="I77" s="79"/>
-      <c r="J77" s="80"/>
-      <c r="K77" s="81"/>
+      <c r="H77" s="76"/>
+      <c r="I77" s="77"/>
+      <c r="J77" s="78"/>
+      <c r="K77" s="79"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" ht="50.4">
       <c r="A78" s="11"/>
-      <c r="B78" s="138"/>
-      <c r="C78" s="98" t="str">
+      <c r="B78" s="132"/>
+      <c r="C78" s="95" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D78" s="128" t="s">
+      <c r="D78" s="122" t="s">
         <v>217</v>
       </c>
-      <c r="E78" s="129"/>
-      <c r="F78" s="130"/>
-      <c r="G78" s="77" t="s">
+      <c r="E78" s="123"/>
+      <c r="F78" s="124"/>
+      <c r="G78" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H78" s="78"/>
-      <c r="I78" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J78" s="80">
+      <c r="H78" s="76"/>
+      <c r="I78" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J78" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K78" s="81"/>
+      <c r="K78" s="79"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" ht="88.2">
       <c r="A79" s="11"/>
-      <c r="B79" s="138"/>
-      <c r="C79" s="99"/>
-      <c r="D79" s="128" t="s">
+      <c r="B79" s="132"/>
+      <c r="C79" s="96"/>
+      <c r="D79" s="122" t="s">
         <v>205</v>
       </c>
-      <c r="E79" s="129"/>
-      <c r="F79" s="130"/>
-      <c r="G79" s="77" t="s">
+      <c r="E79" s="123"/>
+      <c r="F79" s="124"/>
+      <c r="G79" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="H79" s="78"/>
-      <c r="I79" s="79"/>
-      <c r="J79" s="80"/>
-      <c r="K79" s="81"/>
+      <c r="H79" s="76"/>
+      <c r="I79" s="77"/>
+      <c r="J79" s="78"/>
+      <c r="K79" s="79"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
     <row r="80" spans="1:14" ht="63">
       <c r="A80" s="11"/>
-      <c r="B80" s="138"/>
-      <c r="C80" s="98" t="str">
+      <c r="B80" s="132"/>
+      <c r="C80" s="95" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D80" s="128" t="s">
+      <c r="D80" s="122" t="s">
         <v>216</v>
       </c>
-      <c r="E80" s="129"/>
-      <c r="F80" s="130"/>
-      <c r="G80" s="77" t="s">
+      <c r="E80" s="123"/>
+      <c r="F80" s="124"/>
+      <c r="G80" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="H80" s="78"/>
-      <c r="I80" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J80" s="80">
+      <c r="H80" s="76"/>
+      <c r="I80" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J80" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K80" s="81"/>
+      <c r="K80" s="79"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="88.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="138"/>
-      <c r="C81" s="99"/>
-      <c r="D81" s="128" t="s">
+      <c r="B81" s="132"/>
+      <c r="C81" s="96"/>
+      <c r="D81" s="122" t="s">
         <v>205</v>
       </c>
-      <c r="E81" s="129"/>
-      <c r="F81" s="130"/>
-      <c r="G81" s="77" t="s">
+      <c r="E81" s="123"/>
+      <c r="F81" s="124"/>
+      <c r="G81" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="H81" s="78"/>
-      <c r="I81" s="79"/>
-      <c r="J81" s="80"/>
-      <c r="K81" s="81"/>
+      <c r="H81" s="76"/>
+      <c r="I81" s="77"/>
+      <c r="J81" s="78"/>
+      <c r="K81" s="79"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
     </row>
     <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="138"/>
-      <c r="C82" s="77" t="str">
+      <c r="B82" s="132"/>
+      <c r="C82" s="75" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D82" s="128" t="s">
+      <c r="D82" s="122" t="s">
         <v>206</v>
       </c>
-      <c r="E82" s="129"/>
-      <c r="F82" s="130"/>
-      <c r="G82" s="77" t="s">
+      <c r="E82" s="123"/>
+      <c r="F82" s="124"/>
+      <c r="G82" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H82" s="78"/>
-      <c r="I82" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J82" s="80">
+      <c r="H82" s="76"/>
+      <c r="I82" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J82" s="78">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K82" s="81"/>
+      <c r="K82" s="79"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
     <row r="83" spans="1:14" ht="50.4">
       <c r="A83" s="11"/>
-      <c r="B83" s="138"/>
-      <c r="C83" s="77" t="str">
+      <c r="B83" s="132"/>
+      <c r="C83" s="75" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D83" s="128" t="s">
+      <c r="D83" s="122" t="s">
         <v>207</v>
       </c>
-      <c r="E83" s="129"/>
-      <c r="F83" s="130"/>
-      <c r="G83" s="77" t="s">
+      <c r="E83" s="123"/>
+      <c r="F83" s="124"/>
+      <c r="G83" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H83" s="78"/>
-      <c r="I83" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J83" s="80">
+      <c r="H83" s="76"/>
+      <c r="I83" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J83" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K83" s="81"/>
+      <c r="K83" s="79"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
     <row r="84" spans="1:14" ht="37.799999999999997">
       <c r="A84" s="11"/>
-      <c r="B84" s="138"/>
-      <c r="C84" s="77" t="str">
+      <c r="B84" s="132"/>
+      <c r="C84" s="75" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D84" s="128" t="s">
+      <c r="D84" s="122" t="s">
         <v>208</v>
       </c>
-      <c r="E84" s="129"/>
-      <c r="F84" s="130"/>
-      <c r="G84" s="77" t="s">
+      <c r="E84" s="123"/>
+      <c r="F84" s="124"/>
+      <c r="G84" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H84" s="78"/>
-      <c r="I84" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J84" s="80">
+      <c r="H84" s="76"/>
+      <c r="I84" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J84" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K84" s="81"/>
+      <c r="K84" s="79"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="138"/>
-      <c r="C85" s="98" t="str">
+      <c r="B85" s="132"/>
+      <c r="C85" s="95" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D85" s="128" t="s">
+      <c r="D85" s="122" t="s">
         <v>215</v>
       </c>
-      <c r="E85" s="129"/>
-      <c r="F85" s="130"/>
-      <c r="G85" s="77" t="s">
+      <c r="E85" s="123"/>
+      <c r="F85" s="124"/>
+      <c r="G85" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H85" s="78"/>
-      <c r="I85" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J85" s="80">
+      <c r="H85" s="76"/>
+      <c r="I85" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J85" s="78">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K85" s="81"/>
+      <c r="K85" s="79"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
     <row r="86" spans="1:14" ht="88.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="138"/>
-      <c r="C86" s="99"/>
-      <c r="D86" s="128" t="s">
+      <c r="B86" s="132"/>
+      <c r="C86" s="96"/>
+      <c r="D86" s="122" t="s">
         <v>205</v>
       </c>
-      <c r="E86" s="129"/>
-      <c r="F86" s="130"/>
-      <c r="G86" s="77" t="s">
+      <c r="E86" s="123"/>
+      <c r="F86" s="124"/>
+      <c r="G86" s="75" t="s">
         <v>54</v>
       </c>
-      <c r="H86" s="78"/>
-      <c r="I86" s="79"/>
-      <c r="J86" s="80"/>
-      <c r="K86" s="81"/>
+      <c r="H86" s="76"/>
+      <c r="I86" s="77"/>
+      <c r="J86" s="78"/>
+      <c r="K86" s="79"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
     <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="138"/>
-      <c r="C87" s="77" t="str">
+      <c r="B87" s="132"/>
+      <c r="C87" s="75" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D87" s="128" t="s">
+      <c r="D87" s="122" t="s">
         <v>209</v>
       </c>
-      <c r="E87" s="129"/>
-      <c r="F87" s="130"/>
-      <c r="G87" s="77" t="s">
+      <c r="E87" s="123"/>
+      <c r="F87" s="124"/>
+      <c r="G87" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H87" s="78"/>
-      <c r="I87" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J87" s="80">
+      <c r="H87" s="76"/>
+      <c r="I87" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J87" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K87" s="81"/>
+      <c r="K87" s="79"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="138"/>
-      <c r="C88" s="77" t="str">
+      <c r="B88" s="132"/>
+      <c r="C88" s="75" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D88" s="128" t="s">
+      <c r="D88" s="122" t="s">
         <v>210</v>
       </c>
-      <c r="E88" s="129"/>
-      <c r="F88" s="130"/>
-      <c r="G88" s="77" t="s">
+      <c r="E88" s="123"/>
+      <c r="F88" s="124"/>
+      <c r="G88" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H88" s="78"/>
-      <c r="I88" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J88" s="80">
+      <c r="H88" s="76"/>
+      <c r="I88" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J88" s="78">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K88" s="81"/>
+      <c r="K88" s="79"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="138"/>
-      <c r="C89" s="77" t="str">
+      <c r="B89" s="132"/>
+      <c r="C89" s="75" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D89" s="128" t="s">
+      <c r="D89" s="122" t="s">
         <v>211</v>
       </c>
-      <c r="E89" s="129"/>
-      <c r="F89" s="130"/>
-      <c r="G89" s="77" t="s">
+      <c r="E89" s="123"/>
+      <c r="F89" s="124"/>
+      <c r="G89" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H89" s="78"/>
-      <c r="I89" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J89" s="80">
+      <c r="H89" s="76"/>
+      <c r="I89" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J89" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K89" s="81"/>
+      <c r="K89" s="79"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" ht="75.599999999999994">
       <c r="A90" s="11"/>
-      <c r="B90" s="138"/>
-      <c r="C90" s="98" t="str">
+      <c r="B90" s="132"/>
+      <c r="C90" s="95" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D90" s="128" t="s">
+      <c r="D90" s="122" t="s">
         <v>212</v>
       </c>
-      <c r="E90" s="129"/>
-      <c r="F90" s="130"/>
-      <c r="G90" s="77" t="s">
+      <c r="E90" s="123"/>
+      <c r="F90" s="124"/>
+      <c r="G90" s="75" t="s">
         <v>52</v>
       </c>
-      <c r="H90" s="78"/>
-      <c r="I90" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J90" s="80">
+      <c r="H90" s="76"/>
+      <c r="I90" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J90" s="78">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K90" s="81"/>
+      <c r="K90" s="79"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" ht="63">
       <c r="A91" s="11"/>
-      <c r="B91" s="139"/>
-      <c r="C91" s="99"/>
-      <c r="D91" s="128" t="s">
+      <c r="B91" s="133"/>
+      <c r="C91" s="96"/>
+      <c r="D91" s="122" t="s">
         <v>219</v>
       </c>
-      <c r="E91" s="129"/>
-      <c r="F91" s="130"/>
-      <c r="G91" s="77" t="s">
+      <c r="E91" s="123"/>
+      <c r="F91" s="124"/>
+      <c r="G91" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="H91" s="78"/>
-      <c r="I91" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J91" s="80">
+      <c r="H91" s="76"/>
+      <c r="I91" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J91" s="78">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K91" s="81"/>
+      <c r="K91" s="79"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
     <row r="92" spans="1:14" ht="100.8">
       <c r="A92" s="11"/>
-      <c r="B92" s="137" t="str">
+      <c r="B92" s="131" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
-      <c r="C92" s="77" t="str">
+      <c r="C92" s="75" t="str">
         <f>master!C69</f>
         <v>Gitとは</v>
       </c>
-      <c r="D92" s="128" t="s">
+      <c r="D92" s="122" t="s">
         <v>223</v>
       </c>
-      <c r="E92" s="129"/>
-      <c r="F92" s="130"/>
-      <c r="G92" s="77" t="s">
+      <c r="E92" s="123"/>
+      <c r="F92" s="124"/>
+      <c r="G92" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="H92" s="78"/>
-      <c r="I92" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J92" s="80">
+      <c r="H92" s="76"/>
+      <c r="I92" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J92" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K92" s="81"/>
+      <c r="K92" s="79"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
     <row r="93" spans="1:14" ht="189">
       <c r="A93" s="11"/>
-      <c r="B93" s="139"/>
-      <c r="C93" s="77" t="str">
+      <c r="B93" s="133"/>
+      <c r="C93" s="75" t="str">
         <f>master!C70</f>
         <v>Gitの基本的な流れ</v>
       </c>
-      <c r="D93" s="128" t="s">
+      <c r="D93" s="122" t="s">
         <v>230</v>
       </c>
-      <c r="E93" s="129"/>
-      <c r="F93" s="130"/>
-      <c r="G93" s="77" t="s">
+      <c r="E93" s="123"/>
+      <c r="F93" s="124"/>
+      <c r="G93" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="H93" s="78"/>
-      <c r="I93" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J93" s="80">
+      <c r="H93" s="76"/>
+      <c r="I93" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J93" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K93" s="81"/>
+      <c r="K93" s="79"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
     <row r="94" spans="1:14" ht="126">
       <c r="A94" s="11"/>
-      <c r="B94" s="137" t="str">
+      <c r="B94" s="131" t="str">
         <f>master!B71</f>
         <v>VS Code上でGitを使う手順</v>
       </c>
-      <c r="C94" s="77" t="str">
+      <c r="C94" s="75" t="str">
         <f>master!C71</f>
         <v>VS Code上でGitを使う手順-1 【ユーザ名等の登録】</v>
       </c>
-      <c r="D94" s="128" t="s">
+      <c r="D94" s="122" t="s">
         <v>224</v>
       </c>
-      <c r="E94" s="129"/>
-      <c r="F94" s="130"/>
-      <c r="G94" s="77" t="s">
+      <c r="E94" s="123"/>
+      <c r="F94" s="124"/>
+      <c r="G94" s="75" t="s">
         <v>225</v>
       </c>
-      <c r="H94" s="78"/>
-      <c r="I94" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J94" s="80">
+      <c r="H94" s="76"/>
+      <c r="I94" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J94" s="78">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K94" s="81"/>
+      <c r="K94" s="79"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
     <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="138"/>
-      <c r="C95" s="77" t="str">
+      <c r="B95" s="132"/>
+      <c r="C95" s="75" t="str">
         <f>master!C72</f>
         <v>VS Code上でGitを使う手順-2 【リポジトリの初期化】</v>
       </c>
-      <c r="D95" s="128" t="s">
+      <c r="D95" s="122" t="s">
         <v>226</v>
       </c>
-      <c r="E95" s="129"/>
-      <c r="F95" s="130"/>
-      <c r="G95" s="77" t="s">
+      <c r="E95" s="123"/>
+      <c r="F95" s="124"/>
+      <c r="G95" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H95" s="78"/>
-      <c r="I95" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J95" s="80">
+      <c r="H95" s="76"/>
+      <c r="I95" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J95" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K95" s="81"/>
+      <c r="K95" s="79"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
     <row r="96" spans="1:14" ht="50.4">
       <c r="A96" s="11"/>
-      <c r="B96" s="138"/>
-      <c r="C96" s="77" t="str">
+      <c r="B96" s="132"/>
+      <c r="C96" s="75" t="str">
         <f>master!C73</f>
         <v>VS Code上でGitを使う手順-3 【最初のcommit】</v>
       </c>
-      <c r="D96" s="128" t="s">
+      <c r="D96" s="122" t="s">
         <v>227</v>
       </c>
-      <c r="E96" s="129"/>
-      <c r="F96" s="130"/>
-      <c r="G96" s="77" t="s">
+      <c r="E96" s="123"/>
+      <c r="F96" s="124"/>
+      <c r="G96" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H96" s="78"/>
-      <c r="I96" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J96" s="80">
+      <c r="H96" s="76"/>
+      <c r="I96" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J96" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K96" s="81"/>
+      <c r="K96" s="79"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
     <row r="97" spans="1:14" ht="50.4">
       <c r="A97" s="11"/>
-      <c r="B97" s="138"/>
-      <c r="C97" s="77" t="str">
+      <c r="B97" s="132"/>
+      <c r="C97" s="75" t="str">
         <f>master!C74</f>
         <v>VS Code上でGitを使う手順-4 【2回目以降のコミット】</v>
       </c>
-      <c r="D97" s="128" t="s">
+      <c r="D97" s="122" t="s">
         <v>228</v>
       </c>
-      <c r="E97" s="129"/>
-      <c r="F97" s="130"/>
-      <c r="G97" s="77" t="s">
+      <c r="E97" s="123"/>
+      <c r="F97" s="124"/>
+      <c r="G97" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="H97" s="78"/>
-      <c r="I97" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J97" s="80">
+      <c r="H97" s="76"/>
+      <c r="I97" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J97" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K97" s="81"/>
+      <c r="K97" s="79"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
     <row r="98" spans="1:14" ht="37.799999999999997">
       <c r="A98" s="11"/>
-      <c r="B98" s="138"/>
-      <c r="C98" s="77" t="str">
+      <c r="B98" s="132"/>
+      <c r="C98" s="75" t="str">
         <f>master!C75</f>
         <v>VS Code上でGitを使う手順-5 【過去のcommitの確認】</v>
       </c>
-      <c r="D98" s="128" t="s">
+      <c r="D98" s="122" t="s">
         <v>229</v>
       </c>
-      <c r="E98" s="129"/>
-      <c r="F98" s="130"/>
-      <c r="G98" s="77" t="s">
+      <c r="E98" s="123"/>
+      <c r="F98" s="124"/>
+      <c r="G98" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H98" s="78"/>
-      <c r="I98" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J98" s="80">
+      <c r="H98" s="76"/>
+      <c r="I98" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J98" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K98" s="81"/>
+      <c r="K98" s="79"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
     <row r="99" spans="1:14" ht="63">
       <c r="A99" s="11"/>
-      <c r="B99" s="139"/>
-      <c r="C99" s="77" t="str">
+      <c r="B99" s="133"/>
+      <c r="C99" s="75" t="str">
         <f>master!C76</f>
         <v>VS Code上でGitを使う手順-6 【過去の状態に戻す】</v>
       </c>
-      <c r="D99" s="128" t="s">
+      <c r="D99" s="122" t="s">
         <v>231</v>
       </c>
-      <c r="E99" s="129"/>
-      <c r="F99" s="130"/>
-      <c r="G99" s="77" t="s">
+      <c r="E99" s="123"/>
+      <c r="F99" s="124"/>
+      <c r="G99" s="75" t="s">
         <v>49</v>
       </c>
-      <c r="H99" s="78"/>
-      <c r="I99" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J99" s="80">
+      <c r="H99" s="76"/>
+      <c r="I99" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J99" s="78">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K99" s="81"/>
+      <c r="K99" s="79"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
       <c r="N99" s="6"/>
     </row>
     <row r="100" spans="1:14" ht="214.2">
       <c r="A100" s="11"/>
-      <c r="B100" s="97" t="str">
+      <c r="B100" s="94" t="str">
         <f>master!B67</f>
         <v>バイブコーディング：演習</v>
       </c>
-      <c r="C100" s="77" t="str">
+      <c r="C100" s="75" t="str">
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D100" s="128" t="s">
+      <c r="D100" s="122" t="s">
         <v>222</v>
       </c>
-      <c r="E100" s="129"/>
-      <c r="F100" s="130"/>
-      <c r="G100" s="77" t="s">
+      <c r="E100" s="123"/>
+      <c r="F100" s="124"/>
+      <c r="G100" s="75" t="s">
         <v>193</v>
       </c>
-      <c r="H100" s="78"/>
-      <c r="I100" s="79" t="s">
-        <v>26</v>
-      </c>
-      <c r="J100" s="80" t="s">
+      <c r="H100" s="76"/>
+      <c r="I100" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J100" s="78" t="s">
         <v>232</v>
       </c>
-      <c r="K100" s="81"/>
+      <c r="K100" s="79"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
       <c r="N100" s="6"/>
     </row>
     <row r="101" spans="1:14" ht="88.2">
       <c r="A101" s="11"/>
-      <c r="B101" s="104" t="str">
+      <c r="B101" s="98" t="str">
         <f>master!B78</f>
         <v>導入</v>
       </c>
-      <c r="C101" s="103" t="str">
+      <c r="C101" s="97" t="str">
         <f>master!C78</f>
         <v>講義の目的</v>
       </c>
-      <c r="D101" s="122" t="s">
+      <c r="D101" s="116" t="s">
         <v>266</v>
       </c>
-      <c r="E101" s="123"/>
-      <c r="F101" s="124"/>
+      <c r="E101" s="117"/>
+      <c r="F101" s="118"/>
       <c r="G101" s="55" t="s">
         <v>54</v>
       </c>
@@ -7634,19 +8279,19 @@
     </row>
     <row r="102" spans="1:14" ht="37.799999999999997">
       <c r="A102" s="11"/>
-      <c r="B102" s="125" t="str">
+      <c r="B102" s="119" t="str">
         <f>master!B79</f>
         <v>システム開発におけるソフトウェア開発ライフサイクル</v>
       </c>
-      <c r="C102" s="103" t="str">
+      <c r="C102" s="97" t="str">
         <f>master!C79</f>
         <v>ソフトウェア開発ライフサイクル</v>
       </c>
-      <c r="D102" s="122" t="s">
+      <c r="D102" s="116" t="s">
         <v>267</v>
       </c>
-      <c r="E102" s="123"/>
-      <c r="F102" s="124"/>
+      <c r="E102" s="117"/>
+      <c r="F102" s="118"/>
       <c r="G102" s="55" t="s">
         <v>50</v>
       </c>
@@ -7664,16 +8309,16 @@
     </row>
     <row r="103" spans="1:14" ht="277.2">
       <c r="A103" s="11"/>
-      <c r="B103" s="126"/>
-      <c r="C103" s="103" t="str">
+      <c r="B103" s="120"/>
+      <c r="C103" s="97" t="str">
         <f>master!C80</f>
         <v>ソフトウェア開発ライフサイクルの種類</v>
       </c>
-      <c r="D103" s="122" t="s">
+      <c r="D103" s="116" t="s">
         <v>269</v>
       </c>
-      <c r="E103" s="123"/>
-      <c r="F103" s="124"/>
+      <c r="E103" s="117"/>
+      <c r="F103" s="118"/>
       <c r="G103" s="55" t="s">
         <v>268</v>
       </c>
@@ -7691,18 +8336,18 @@
     </row>
     <row r="104" spans="1:14" ht="151.19999999999999">
       <c r="A104" s="11"/>
-      <c r="B104" s="125" t="str">
+      <c r="B104" s="119" t="str">
         <f>master!B81</f>
         <v>TERASOLUNAとは</v>
       </c>
-      <c r="C104" s="103" t="s">
+      <c r="C104" s="97" t="s">
         <v>244</v>
       </c>
-      <c r="D104" s="122" t="s">
+      <c r="D104" s="116" t="s">
         <v>270</v>
       </c>
-      <c r="E104" s="123"/>
-      <c r="F104" s="124"/>
+      <c r="E104" s="117"/>
+      <c r="F104" s="118"/>
       <c r="G104" s="55" t="s">
         <v>107</v>
       </c>
@@ -7720,15 +8365,15 @@
     </row>
     <row r="105" spans="1:14" ht="138.6">
       <c r="A105" s="11"/>
-      <c r="B105" s="126"/>
-      <c r="C105" s="103" t="s">
+      <c r="B105" s="120"/>
+      <c r="C105" s="97" t="s">
         <v>245</v>
       </c>
-      <c r="D105" s="122" t="s">
+      <c r="D105" s="116" t="s">
         <v>271</v>
       </c>
-      <c r="E105" s="123"/>
-      <c r="F105" s="124"/>
+      <c r="E105" s="117"/>
+      <c r="F105" s="118"/>
       <c r="G105" s="55" t="s">
         <v>48</v>
       </c>
@@ -7746,18 +8391,18 @@
     </row>
     <row r="106" spans="1:14" ht="189">
       <c r="A106" s="11"/>
-      <c r="B106" s="125" t="str">
+      <c r="B106" s="119" t="str">
         <f>master!B83</f>
         <v>V字モデルとは</v>
       </c>
-      <c r="C106" s="103" t="s">
+      <c r="C106" s="97" t="s">
         <v>248</v>
       </c>
-      <c r="D106" s="122" t="s">
+      <c r="D106" s="116" t="s">
         <v>272</v>
       </c>
-      <c r="E106" s="123"/>
-      <c r="F106" s="124"/>
+      <c r="E106" s="117"/>
+      <c r="F106" s="118"/>
       <c r="G106" s="55" t="s">
         <v>135</v>
       </c>
@@ -7775,15 +8420,15 @@
     </row>
     <row r="107" spans="1:14" ht="100.8">
       <c r="A107" s="11"/>
-      <c r="B107" s="127"/>
-      <c r="C107" s="103" t="s">
+      <c r="B107" s="121"/>
+      <c r="C107" s="97" t="s">
         <v>246</v>
       </c>
-      <c r="D107" s="122" t="s">
+      <c r="D107" s="116" t="s">
         <v>273</v>
       </c>
-      <c r="E107" s="123"/>
-      <c r="F107" s="124"/>
+      <c r="E107" s="117"/>
+      <c r="F107" s="118"/>
       <c r="G107" s="55" t="s">
         <v>56</v>
       </c>
@@ -7801,15 +8446,15 @@
     </row>
     <row r="108" spans="1:14" ht="113.4">
       <c r="A108" s="11"/>
-      <c r="B108" s="127"/>
-      <c r="C108" s="103" t="s">
+      <c r="B108" s="121"/>
+      <c r="C108" s="97" t="s">
         <v>250</v>
       </c>
-      <c r="D108" s="122" t="s">
+      <c r="D108" s="116" t="s">
         <v>274</v>
       </c>
-      <c r="E108" s="123"/>
-      <c r="F108" s="124"/>
+      <c r="E108" s="117"/>
+      <c r="F108" s="118"/>
       <c r="G108" s="55" t="s">
         <v>53</v>
       </c>
@@ -7827,15 +8472,15 @@
     </row>
     <row r="109" spans="1:14" ht="302.39999999999998">
       <c r="A109" s="11"/>
-      <c r="B109" s="127"/>
-      <c r="C109" s="103" t="s">
+      <c r="B109" s="121"/>
+      <c r="C109" s="97" t="s">
         <v>252</v>
       </c>
-      <c r="D109" s="122" t="s">
+      <c r="D109" s="116" t="s">
         <v>276</v>
       </c>
-      <c r="E109" s="123"/>
-      <c r="F109" s="124"/>
+      <c r="E109" s="117"/>
+      <c r="F109" s="118"/>
       <c r="G109" s="55" t="s">
         <v>275</v>
       </c>
@@ -7853,15 +8498,15 @@
     </row>
     <row r="110" spans="1:14" ht="138.6">
       <c r="A110" s="11"/>
-      <c r="B110" s="127"/>
-      <c r="C110" s="103" t="s">
+      <c r="B110" s="121"/>
+      <c r="C110" s="97" t="s">
         <v>254</v>
       </c>
-      <c r="D110" s="122" t="s">
+      <c r="D110" s="116" t="s">
         <v>277</v>
       </c>
-      <c r="E110" s="123"/>
-      <c r="F110" s="124"/>
+      <c r="E110" s="117"/>
+      <c r="F110" s="118"/>
       <c r="G110" s="55" t="s">
         <v>48</v>
       </c>
@@ -7879,15 +8524,15 @@
     </row>
     <row r="111" spans="1:14" ht="88.2">
       <c r="A111" s="11"/>
-      <c r="B111" s="127"/>
-      <c r="C111" s="103" t="s">
+      <c r="B111" s="121"/>
+      <c r="C111" s="97" t="s">
         <v>256</v>
       </c>
-      <c r="D111" s="122" t="s">
+      <c r="D111" s="116" t="s">
         <v>278</v>
       </c>
-      <c r="E111" s="123"/>
-      <c r="F111" s="124"/>
+      <c r="E111" s="117"/>
+      <c r="F111" s="118"/>
       <c r="G111" s="55" t="s">
         <v>54</v>
       </c>
@@ -7905,15 +8550,15 @@
     </row>
     <row r="112" spans="1:14" ht="75.599999999999994">
       <c r="A112" s="11"/>
-      <c r="B112" s="127"/>
-      <c r="C112" s="103" t="s">
+      <c r="B112" s="121"/>
+      <c r="C112" s="97" t="s">
         <v>258</v>
       </c>
-      <c r="D112" s="122" t="s">
+      <c r="D112" s="116" t="s">
         <v>279</v>
       </c>
-      <c r="E112" s="123"/>
-      <c r="F112" s="124"/>
+      <c r="E112" s="117"/>
+      <c r="F112" s="118"/>
       <c r="G112" s="55" t="s">
         <v>52</v>
       </c>
@@ -7931,15 +8576,15 @@
     </row>
     <row r="113" spans="1:14" ht="113.4">
       <c r="A113" s="11"/>
-      <c r="B113" s="127"/>
-      <c r="C113" s="103" t="s">
+      <c r="B113" s="121"/>
+      <c r="C113" s="97" t="s">
         <v>260</v>
       </c>
-      <c r="D113" s="122" t="s">
+      <c r="D113" s="116" t="s">
         <v>280</v>
       </c>
-      <c r="E113" s="123"/>
-      <c r="F113" s="124"/>
+      <c r="E113" s="117"/>
+      <c r="F113" s="118"/>
       <c r="G113" s="55" t="s">
         <v>53</v>
       </c>
@@ -7957,15 +8602,15 @@
     </row>
     <row r="114" spans="1:14" ht="126">
       <c r="A114" s="11"/>
-      <c r="B114" s="127"/>
-      <c r="C114" s="103" t="s">
+      <c r="B114" s="121"/>
+      <c r="C114" s="97" t="s">
         <v>281</v>
       </c>
-      <c r="D114" s="122" t="s">
+      <c r="D114" s="116" t="s">
         <v>282</v>
       </c>
-      <c r="E114" s="123"/>
-      <c r="F114" s="124"/>
+      <c r="E114" s="117"/>
+      <c r="F114" s="118"/>
       <c r="G114" s="55" t="s">
         <v>225</v>
       </c>
@@ -7983,15 +8628,15 @@
     </row>
     <row r="115" spans="1:14" ht="88.2">
       <c r="A115" s="11"/>
-      <c r="B115" s="127"/>
-      <c r="C115" s="103" t="s">
+      <c r="B115" s="121"/>
+      <c r="C115" s="97" t="s">
         <v>263</v>
       </c>
-      <c r="D115" s="122" t="s">
+      <c r="D115" s="116" t="s">
         <v>283</v>
       </c>
-      <c r="E115" s="123"/>
-      <c r="F115" s="124"/>
+      <c r="E115" s="117"/>
+      <c r="F115" s="118"/>
       <c r="G115" s="55" t="s">
         <v>54</v>
       </c>
@@ -8009,15 +8654,15 @@
     </row>
     <row r="116" spans="1:14" ht="138.6">
       <c r="A116" s="11"/>
-      <c r="B116" s="127"/>
-      <c r="C116" s="103" t="s">
+      <c r="B116" s="121"/>
+      <c r="C116" s="97" t="s">
         <v>264</v>
       </c>
-      <c r="D116" s="122" t="s">
+      <c r="D116" s="116" t="s">
         <v>284</v>
       </c>
-      <c r="E116" s="123"/>
-      <c r="F116" s="124"/>
+      <c r="E116" s="117"/>
+      <c r="F116" s="118"/>
       <c r="G116" s="55" t="s">
         <v>48</v>
       </c>
@@ -8035,13 +8680,13 @@
     </row>
     <row r="117" spans="1:14" ht="24" customHeight="1">
       <c r="A117" s="11"/>
-      <c r="B117" s="126"/>
-      <c r="C117" s="103" t="s">
+      <c r="B117" s="120"/>
+      <c r="C117" s="97" t="s">
         <v>265</v>
       </c>
-      <c r="D117" s="122"/>
-      <c r="E117" s="123"/>
-      <c r="F117" s="124"/>
+      <c r="D117" s="116"/>
+      <c r="E117" s="117"/>
+      <c r="F117" s="118"/>
       <c r="G117" s="55" t="s">
         <v>55</v>
       </c>
@@ -8057,52 +8702,868 @@
       <c r="M117" s="6"/>
       <c r="N117" s="6"/>
     </row>
-    <row r="118" spans="1:14" ht="24" customHeight="1">
+    <row r="118" spans="1:14" ht="37.799999999999997">
       <c r="A118" s="11"/>
-      <c r="B118" s="104"/>
-      <c r="C118" s="103"/>
-      <c r="D118" s="122"/>
+      <c r="B118" s="75" t="str">
+        <f>master!B67</f>
+        <v>バイブコーディング：演習</v>
+      </c>
+      <c r="C118" s="75" t="str">
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D118" s="122" t="s">
+        <v>340</v>
+      </c>
       <c r="E118" s="123"/>
       <c r="F118" s="124"/>
-      <c r="G118" s="55" t="s">
-        <v>55</v>
-      </c>
-      <c r="H118" s="12"/>
-      <c r="I118" s="52" t="s">
-        <v>26</v>
-      </c>
-      <c r="J118" s="50"/>
-      <c r="K118" s="46"/>
+      <c r="G118" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="H118" s="76"/>
+      <c r="I118" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J118" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="K118" s="79"/>
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
       <c r="N118" s="6"/>
     </row>
-    <row r="119" spans="1:14" ht="24" customHeight="1">
+    <row r="119" spans="1:14" ht="50.4">
       <c r="A119" s="11"/>
-      <c r="B119" s="104"/>
-      <c r="C119" s="103"/>
-      <c r="D119" s="122"/>
-      <c r="E119" s="123"/>
-      <c r="F119" s="124"/>
+      <c r="B119" s="119" t="str">
+        <f>master!B96</f>
+        <v>導入</v>
+      </c>
+      <c r="C119" s="97" t="str">
+        <f>master!C96</f>
+        <v>講義の目的</v>
+      </c>
+      <c r="D119" s="116" t="s">
+        <v>314</v>
+      </c>
+      <c r="E119" s="117"/>
+      <c r="F119" s="118"/>
       <c r="G119" s="55" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="52" t="s">
         <v>26</v>
       </c>
-      <c r="J119" s="50"/>
+      <c r="J119" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
       <c r="K119" s="46"/>
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
       <c r="N119" s="6"/>
     </row>
-    <row r="120" spans="1:14" ht="15" customHeight="1">
-      <c r="J120" s="49"/>
-    </row>
-    <row r="121" spans="1:14" ht="15" customHeight="1"/>
+    <row r="120" spans="1:14" ht="25.2">
+      <c r="A120" s="11"/>
+      <c r="B120" s="121"/>
+      <c r="C120" s="97" t="str">
+        <f>master!C97</f>
+        <v>TERASOLUNA 開発手順　 ※再掲</v>
+      </c>
+      <c r="D120" s="116"/>
+      <c r="E120" s="117"/>
+      <c r="F120" s="118"/>
+      <c r="G120" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H120" s="12"/>
+      <c r="I120" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J120" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K120" s="46"/>
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="6"/>
+    </row>
+    <row r="121" spans="1:14" ht="25.2">
+      <c r="A121" s="11"/>
+      <c r="B121" s="120"/>
+      <c r="C121" s="97" t="str">
+        <f>master!C98</f>
+        <v>V字モデル　 ※再掲</v>
+      </c>
+      <c r="D121" s="116" t="s">
+        <v>315</v>
+      </c>
+      <c r="E121" s="117"/>
+      <c r="F121" s="118"/>
+      <c r="G121" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H121" s="12"/>
+      <c r="I121" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J121" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K121" s="46"/>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
+      <c r="N121" s="6"/>
+    </row>
+    <row r="122" spans="1:14" ht="50.4">
+      <c r="A122" s="11"/>
+      <c r="B122" s="119" t="str">
+        <f>master!B99</f>
+        <v>テストとは</v>
+      </c>
+      <c r="C122" s="97" t="str">
+        <f>master!C99</f>
+        <v>テストとは</v>
+      </c>
+      <c r="D122" s="116" t="s">
+        <v>316</v>
+      </c>
+      <c r="E122" s="117"/>
+      <c r="F122" s="118"/>
+      <c r="G122" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H122" s="12"/>
+      <c r="I122" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J122" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K122" s="46"/>
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="6"/>
+    </row>
+    <row r="123" spans="1:14" ht="315">
+      <c r="A123" s="11"/>
+      <c r="B123" s="121"/>
+      <c r="C123" s="97" t="str">
+        <f>master!C100</f>
+        <v>テストの目的</v>
+      </c>
+      <c r="D123" s="116" t="s">
+        <v>318</v>
+      </c>
+      <c r="E123" s="117"/>
+      <c r="F123" s="118"/>
+      <c r="G123" s="55" t="s">
+        <v>319</v>
+      </c>
+      <c r="H123" s="12"/>
+      <c r="I123" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J123" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K123" s="46"/>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
+      <c r="N123" s="6"/>
+    </row>
+    <row r="124" spans="1:14" ht="25.2">
+      <c r="A124" s="11"/>
+      <c r="B124" s="121"/>
+      <c r="C124" s="97" t="str">
+        <f>master!C101</f>
+        <v>テストを実施しなかった場合…</v>
+      </c>
+      <c r="D124" s="116" t="s">
+        <v>320</v>
+      </c>
+      <c r="E124" s="117"/>
+      <c r="F124" s="118"/>
+      <c r="G124" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H124" s="12"/>
+      <c r="I124" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J124" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K124" s="46"/>
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="N124" s="6"/>
+    </row>
+    <row r="125" spans="1:14" ht="100.8">
+      <c r="A125" s="11"/>
+      <c r="B125" s="120"/>
+      <c r="C125" s="97" t="str">
+        <f>master!C102</f>
+        <v>コラム：テストとデバッグ</v>
+      </c>
+      <c r="D125" s="116" t="s">
+        <v>321</v>
+      </c>
+      <c r="E125" s="117"/>
+      <c r="F125" s="118"/>
+      <c r="G125" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="H125" s="12"/>
+      <c r="I125" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J125" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K125" s="46"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+      <c r="N125" s="6"/>
+    </row>
+    <row r="126" spans="1:14" ht="50.4">
+      <c r="A126" s="11"/>
+      <c r="B126" s="119" t="str">
+        <f>master!B103</f>
+        <v>単体テストとは</v>
+      </c>
+      <c r="C126" s="97" t="str">
+        <f>master!C103</f>
+        <v>単体テスト（Unit Test）とは</v>
+      </c>
+      <c r="D126" s="116" t="s">
+        <v>322</v>
+      </c>
+      <c r="E126" s="117"/>
+      <c r="F126" s="118"/>
+      <c r="G126" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H126" s="12"/>
+      <c r="I126" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J126" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K126" s="46"/>
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
+      <c r="N126" s="6"/>
+    </row>
+    <row r="127" spans="1:14" ht="25.2">
+      <c r="A127" s="11"/>
+      <c r="B127" s="121"/>
+      <c r="C127" s="97" t="str">
+        <f>master!C104</f>
+        <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
+      </c>
+      <c r="D127" s="116"/>
+      <c r="E127" s="117"/>
+      <c r="F127" s="118"/>
+      <c r="G127" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H127" s="12"/>
+      <c r="I127" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J127" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K127" s="46"/>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
+      <c r="N127" s="6"/>
+    </row>
+    <row r="128" spans="1:14" ht="302.39999999999998">
+      <c r="A128" s="11"/>
+      <c r="B128" s="121"/>
+      <c r="C128" s="97" t="str">
+        <f>master!C105</f>
+        <v>テスト設計の流れ</v>
+      </c>
+      <c r="D128" s="116" t="s">
+        <v>323</v>
+      </c>
+      <c r="E128" s="117"/>
+      <c r="F128" s="118"/>
+      <c r="G128" s="55" t="s">
+        <v>275</v>
+      </c>
+      <c r="H128" s="12"/>
+      <c r="I128" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J128" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K128" s="46"/>
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
+      <c r="N128" s="6"/>
+    </row>
+    <row r="129" spans="1:14" ht="37.799999999999997">
+      <c r="A129" s="11"/>
+      <c r="B129" s="121"/>
+      <c r="C129" s="97" t="str">
+        <f>master!C106</f>
+        <v>テスト設計の例</v>
+      </c>
+      <c r="D129" s="116" t="s">
+        <v>324</v>
+      </c>
+      <c r="E129" s="117"/>
+      <c r="F129" s="118"/>
+      <c r="G129" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H129" s="12"/>
+      <c r="I129" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J129" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K129" s="46"/>
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
+      <c r="N129" s="6"/>
+    </row>
+    <row r="130" spans="1:14" ht="75.599999999999994">
+      <c r="A130" s="11"/>
+      <c r="B130" s="121"/>
+      <c r="C130" s="97" t="str">
+        <f>master!C107</f>
+        <v>単体テスト（Unit Test）とは</v>
+      </c>
+      <c r="D130" s="116" t="s">
+        <v>325</v>
+      </c>
+      <c r="E130" s="117"/>
+      <c r="F130" s="118"/>
+      <c r="G130" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="H130" s="12"/>
+      <c r="I130" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J130" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K130" s="46"/>
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+      <c r="N130" s="6"/>
+    </row>
+    <row r="131" spans="1:14" ht="113.4">
+      <c r="A131" s="11"/>
+      <c r="B131" s="121"/>
+      <c r="C131" s="97" t="str">
+        <f>master!C108</f>
+        <v>テスト技法 – ブラックボックステスト技法 –</v>
+      </c>
+      <c r="D131" s="116" t="s">
+        <v>326</v>
+      </c>
+      <c r="E131" s="117"/>
+      <c r="F131" s="118"/>
+      <c r="G131" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="H131" s="12"/>
+      <c r="I131" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J131" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K131" s="46"/>
+      <c r="L131" s="6"/>
+      <c r="M131" s="6"/>
+      <c r="N131" s="6"/>
+    </row>
+    <row r="132" spans="1:14" ht="201.6">
+      <c r="A132" s="11"/>
+      <c r="B132" s="121"/>
+      <c r="C132" s="97" t="str">
+        <f>master!C109</f>
+        <v>ブラックボックステスト：同値分割法</v>
+      </c>
+      <c r="D132" s="116" t="s">
+        <v>329</v>
+      </c>
+      <c r="E132" s="117"/>
+      <c r="F132" s="118"/>
+      <c r="G132" s="55" t="s">
+        <v>129</v>
+      </c>
+      <c r="H132" s="12"/>
+      <c r="I132" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J132" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K132" s="46"/>
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
+      <c r="N132" s="6"/>
+    </row>
+    <row r="133" spans="1:14" ht="113.4">
+      <c r="A133" s="11"/>
+      <c r="B133" s="121"/>
+      <c r="C133" s="97" t="str">
+        <f>master!C110</f>
+        <v>ブラックボックステスト：境界値分析</v>
+      </c>
+      <c r="D133" s="116" t="s">
+        <v>328</v>
+      </c>
+      <c r="E133" s="117"/>
+      <c r="F133" s="118"/>
+      <c r="G133" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="H133" s="12"/>
+      <c r="I133" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J133" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K133" s="46"/>
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
+      <c r="N133" s="6"/>
+    </row>
+    <row r="134" spans="1:14" ht="176.4">
+      <c r="A134" s="11"/>
+      <c r="B134" s="121"/>
+      <c r="C134" s="97" t="str">
+        <f>master!C111</f>
+        <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
+      </c>
+      <c r="D134" s="116" t="s">
+        <v>327</v>
+      </c>
+      <c r="E134" s="117"/>
+      <c r="F134" s="118"/>
+      <c r="G134" s="55" t="s">
+        <v>317</v>
+      </c>
+      <c r="H134" s="12"/>
+      <c r="I134" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J134" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K134" s="46"/>
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
+      <c r="N134" s="6"/>
+    </row>
+    <row r="135" spans="1:14" ht="37.799999999999997">
+      <c r="A135" s="11"/>
+      <c r="B135" s="121"/>
+      <c r="C135" s="97" t="str">
+        <f>master!C112</f>
+        <v>ブラックボックステスト：状態遷移テスト</v>
+      </c>
+      <c r="D135" s="116" t="s">
+        <v>330</v>
+      </c>
+      <c r="E135" s="117"/>
+      <c r="F135" s="118"/>
+      <c r="G135" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H135" s="12"/>
+      <c r="I135" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J135" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K135" s="46"/>
+      <c r="L135" s="6"/>
+      <c r="M135" s="6"/>
+      <c r="N135" s="6"/>
+    </row>
+    <row r="136" spans="1:14" ht="88.2">
+      <c r="A136" s="11"/>
+      <c r="B136" s="121"/>
+      <c r="C136" s="97" t="str">
+        <f>master!C113</f>
+        <v>テスト技法 – ホワイトボックステスト技法 –</v>
+      </c>
+      <c r="D136" s="116" t="s">
+        <v>331</v>
+      </c>
+      <c r="E136" s="117"/>
+      <c r="F136" s="118"/>
+      <c r="G136" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="H136" s="12"/>
+      <c r="I136" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J136" s="50">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K136" s="46"/>
+      <c r="L136" s="6"/>
+      <c r="M136" s="6"/>
+      <c r="N136" s="6"/>
+    </row>
+    <row r="137" spans="1:14" ht="151.19999999999999">
+      <c r="A137" s="11"/>
+      <c r="B137" s="121"/>
+      <c r="C137" s="97" t="str">
+        <f>master!C114</f>
+        <v>ホワイトボックステストの評価基準</v>
+      </c>
+      <c r="D137" s="116" t="s">
+        <v>332</v>
+      </c>
+      <c r="E137" s="117"/>
+      <c r="F137" s="118"/>
+      <c r="G137" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="H137" s="12"/>
+      <c r="I137" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J137" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K137" s="46"/>
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
+      <c r="N137" s="6"/>
+    </row>
+    <row r="138" spans="1:14" ht="37.799999999999997">
+      <c r="A138" s="11"/>
+      <c r="B138" s="121"/>
+      <c r="C138" s="97" t="str">
+        <f>master!C115</f>
+        <v>ホワイトボックステスト：ステートメントテスト</v>
+      </c>
+      <c r="D138" s="116" t="s">
+        <v>333</v>
+      </c>
+      <c r="E138" s="117"/>
+      <c r="F138" s="118"/>
+      <c r="G138" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H138" s="12"/>
+      <c r="I138" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J138" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K138" s="46"/>
+      <c r="L138" s="6"/>
+      <c r="M138" s="6"/>
+      <c r="N138" s="6"/>
+    </row>
+    <row r="139" spans="1:14" ht="37.799999999999997">
+      <c r="A139" s="11"/>
+      <c r="B139" s="121"/>
+      <c r="C139" s="97" t="str">
+        <f>master!C116</f>
+        <v>ホワイトボックステスト：ブランチテスト</v>
+      </c>
+      <c r="D139" s="116" t="s">
+        <v>334</v>
+      </c>
+      <c r="E139" s="117"/>
+      <c r="F139" s="118"/>
+      <c r="G139" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H139" s="12"/>
+      <c r="I139" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J139" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K139" s="46"/>
+      <c r="L139" s="6"/>
+      <c r="M139" s="6"/>
+      <c r="N139" s="6"/>
+    </row>
+    <row r="140" spans="1:14" ht="37.799999999999997">
+      <c r="A140" s="11"/>
+      <c r="B140" s="121"/>
+      <c r="C140" s="97" t="str">
+        <f>master!C117</f>
+        <v>ホワイトボックステスト：コンディションテスト</v>
+      </c>
+      <c r="D140" s="116" t="s">
+        <v>335</v>
+      </c>
+      <c r="E140" s="117"/>
+      <c r="F140" s="118"/>
+      <c r="G140" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H140" s="12"/>
+      <c r="I140" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J140" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K140" s="46"/>
+      <c r="L140" s="6"/>
+      <c r="M140" s="6"/>
+      <c r="N140" s="6"/>
+    </row>
+    <row r="141" spans="1:14" ht="100.8">
+      <c r="A141" s="11"/>
+      <c r="B141" s="121"/>
+      <c r="C141" s="97" t="str">
+        <f>master!C118</f>
+        <v>テスト技法 – 経験ベースの技法 –</v>
+      </c>
+      <c r="D141" s="116" t="s">
+        <v>336</v>
+      </c>
+      <c r="E141" s="117"/>
+      <c r="F141" s="118"/>
+      <c r="G141" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="H141" s="12"/>
+      <c r="I141" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J141" s="50">
+        <v>6.9444444444444441E-3</v>
+      </c>
+      <c r="K141" s="46"/>
+      <c r="L141" s="6"/>
+      <c r="M141" s="6"/>
+      <c r="N141" s="6"/>
+    </row>
+    <row r="142" spans="1:14" ht="100.8">
+      <c r="A142" s="11"/>
+      <c r="B142" s="121"/>
+      <c r="C142" s="97" t="str">
+        <f>master!C119</f>
+        <v>スタブとドライバ</v>
+      </c>
+      <c r="D142" s="116" t="s">
+        <v>337</v>
+      </c>
+      <c r="E142" s="117"/>
+      <c r="F142" s="118"/>
+      <c r="G142" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="H142" s="12"/>
+      <c r="I142" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J142" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K142" s="46"/>
+      <c r="L142" s="6"/>
+      <c r="M142" s="6"/>
+      <c r="N142" s="6"/>
+    </row>
+    <row r="143" spans="1:14" ht="75.599999999999994">
+      <c r="A143" s="11"/>
+      <c r="B143" s="120"/>
+      <c r="C143" s="97" t="str">
+        <f>master!C120</f>
+        <v>スタブとモック</v>
+      </c>
+      <c r="D143" s="116" t="s">
+        <v>338</v>
+      </c>
+      <c r="E143" s="117"/>
+      <c r="F143" s="118"/>
+      <c r="G143" s="55" t="s">
+        <v>52</v>
+      </c>
+      <c r="H143" s="12"/>
+      <c r="I143" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J143" s="50">
+        <v>3.472222222222222E-3</v>
+      </c>
+      <c r="K143" s="46"/>
+      <c r="L143" s="6"/>
+      <c r="M143" s="6"/>
+      <c r="N143" s="6"/>
+    </row>
+    <row r="144" spans="1:14" ht="37.799999999999997">
+      <c r="A144" s="11"/>
+      <c r="B144" s="119" t="str">
+        <f>master!B121</f>
+        <v>Junit</v>
+      </c>
+      <c r="C144" s="97" t="str">
+        <f>master!C121</f>
+        <v>JUnitとは</v>
+      </c>
+      <c r="D144" s="116" t="s">
+        <v>339</v>
+      </c>
+      <c r="E144" s="117"/>
+      <c r="F144" s="118"/>
+      <c r="G144" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="H144" s="12"/>
+      <c r="I144" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J144" s="50">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K144" s="46"/>
+      <c r="L144" s="6"/>
+      <c r="M144" s="6"/>
+      <c r="N144" s="6"/>
+    </row>
+    <row r="145" spans="1:14" ht="25.2">
+      <c r="A145" s="11"/>
+      <c r="B145" s="120"/>
+      <c r="C145" s="97" t="str">
+        <f>master!C122</f>
+        <v>参考文献</v>
+      </c>
+      <c r="D145" s="116"/>
+      <c r="E145" s="117"/>
+      <c r="F145" s="118"/>
+      <c r="G145" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H145" s="12"/>
+      <c r="I145" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J145" s="50">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K145" s="46"/>
+      <c r="L145" s="6"/>
+      <c r="M145" s="6"/>
+      <c r="N145" s="6"/>
+    </row>
+    <row r="146" spans="1:14" ht="37.799999999999997">
+      <c r="A146" s="11"/>
+      <c r="B146" s="75" t="str">
+        <f>master!B67</f>
+        <v>バイブコーディング：演習</v>
+      </c>
+      <c r="C146" s="75" t="str">
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D146" s="122" t="s">
+        <v>340</v>
+      </c>
+      <c r="E146" s="123"/>
+      <c r="F146" s="124"/>
+      <c r="G146" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="H146" s="76"/>
+      <c r="I146" s="77" t="s">
+        <v>26</v>
+      </c>
+      <c r="J146" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="K146" s="79"/>
+      <c r="L146" s="6"/>
+      <c r="M146" s="6"/>
+      <c r="N146" s="6"/>
+    </row>
+    <row r="147" spans="1:14" ht="24" customHeight="1">
+      <c r="A147" s="11"/>
+      <c r="B147" s="98"/>
+      <c r="C147" s="97"/>
+      <c r="D147" s="116"/>
+      <c r="E147" s="117"/>
+      <c r="F147" s="118"/>
+      <c r="G147" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H147" s="12"/>
+      <c r="I147" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J147" s="50"/>
+      <c r="K147" s="46"/>
+      <c r="L147" s="6"/>
+      <c r="M147" s="6"/>
+      <c r="N147" s="6"/>
+    </row>
+    <row r="148" spans="1:14" ht="24" customHeight="1">
+      <c r="A148" s="11"/>
+      <c r="B148" s="98"/>
+      <c r="C148" s="97"/>
+      <c r="D148" s="116"/>
+      <c r="E148" s="117"/>
+      <c r="F148" s="118"/>
+      <c r="G148" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="H148" s="12"/>
+      <c r="I148" s="52" t="s">
+        <v>26</v>
+      </c>
+      <c r="J148" s="50"/>
+      <c r="K148" s="46"/>
+      <c r="L148" s="6"/>
+      <c r="M148" s="6"/>
+      <c r="N148" s="6"/>
+    </row>
+    <row r="149" spans="1:14" ht="15" customHeight="1">
+      <c r="J149" s="49"/>
+    </row>
+    <row r="150" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="118">
+  <mergeCells count="151">
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="B126:B143"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
     <mergeCell ref="D97:F97"/>
     <mergeCell ref="D96:F96"/>
     <mergeCell ref="D95:F95"/>
@@ -8198,10 +9659,10 @@
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D116:F116"/>
     <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D117:F117"/>
     <mergeCell ref="D114:F114"/>
     <mergeCell ref="D115:F115"/>
     <mergeCell ref="D112:F112"/>
@@ -8210,6 +9671,18 @@
     <mergeCell ref="D105:F105"/>
     <mergeCell ref="D106:F106"/>
     <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D120:F120"/>
     <mergeCell ref="D108:F108"/>
     <mergeCell ref="D109:F109"/>
     <mergeCell ref="D110:F110"/>
@@ -8233,7 +9706,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H22:H119</xm:sqref>
+          <xm:sqref>H22:H148</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8243,532 +9716,758 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C101"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="9.6"/>
+  <dimension ref="B1:C136"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="75" customWidth="1"/>
-    <col min="2" max="2" width="40.109375" style="75" customWidth="1"/>
-    <col min="3" max="3" width="44" style="75" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="75"/>
+    <col min="1" max="1" width="4.6640625" style="135" customWidth="1"/>
+    <col min="2" max="2" width="40.109375" style="135" customWidth="1"/>
+    <col min="3" max="3" width="44" style="135" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="8.88671875" style="135"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:3">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="135" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="136" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="136" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="135" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="135" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:3">
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="135" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="135" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:3">
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="135" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="2:3">
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="135" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="2:3">
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="135" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="8" spans="2:3">
-      <c r="C8" s="75" t="s">
+      <c r="C8" s="135" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="9" spans="2:3">
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="135" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="135" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:3">
-      <c r="C10" s="75" t="s">
+      <c r="C10" s="135" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:3">
-      <c r="C11" s="75" t="s">
+      <c r="C11" s="135" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="12" spans="2:3">
-      <c r="C12" s="75" t="s">
+      <c r="C12" s="135" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="13" spans="2:3">
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="135" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="14" spans="2:3">
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="135" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="15" spans="2:3">
-      <c r="C15" s="75" t="s">
+      <c r="C15" s="135" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="16" spans="2:3">
-      <c r="C16" s="75" t="s">
+      <c r="C16" s="135" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="135" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="135" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="C18" s="75" t="s">
+      <c r="C18" s="135" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="C19" s="75" t="s">
+      <c r="C19" s="135" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="C20" s="75" t="s">
+      <c r="C20" s="135" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="C21" s="75" t="s">
+      <c r="C21" s="135" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="C22" s="75" t="s">
+      <c r="C22" s="135" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="C23" s="75" t="s">
+      <c r="C23" s="135" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="C24" s="75" t="s">
+      <c r="C24" s="135" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="25" spans="2:3">
-      <c r="C25" s="75" t="s">
+      <c r="C25" s="135" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26" spans="2:3">
-      <c r="C26" s="75" t="s">
+      <c r="C26" s="135" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="27" spans="2:3">
-      <c r="C27" s="75" t="s">
+      <c r="C27" s="135" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="C28" s="75" t="s">
+      <c r="C28" s="135" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="29" spans="2:3">
-      <c r="C29" s="75" t="s">
+      <c r="C29" s="135" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:3">
-      <c r="C30" s="75" t="s">
+      <c r="C30" s="135" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="31" spans="2:3">
-      <c r="C31" s="75" t="s">
+      <c r="C31" s="135" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="32" spans="2:3">
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="135" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="C33" s="75" t="s">
+      <c r="C33" s="135" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="C34" s="75" t="s">
+      <c r="C34" s="135" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="C35" s="75" t="s">
+      <c r="C35" s="135" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="96"/>
-      <c r="C36" s="96"/>
+      <c r="B36" s="137"/>
+      <c r="C36" s="137"/>
     </row>
     <row r="37" spans="2:3">
-      <c r="B37" s="75" t="s">
+      <c r="B37" s="135" t="s">
         <v>180</v>
       </c>
-      <c r="C37" s="75" t="s">
+      <c r="C37" s="135" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="38" spans="2:3">
-      <c r="C38" s="75" t="s">
+      <c r="C38" s="135" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="39" spans="2:3">
-      <c r="C39" s="75" t="s">
+      <c r="C39" s="135" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="40" spans="2:3">
-      <c r="B40" s="75" t="s">
+      <c r="B40" s="135" t="s">
         <v>181</v>
       </c>
-      <c r="C40" s="75" t="s">
+      <c r="C40" s="135" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="41" spans="2:3">
-      <c r="C41" s="75" t="s">
+      <c r="C41" s="135" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="42" spans="2:3">
-      <c r="C42" s="75" t="s">
+      <c r="C42" s="135" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="C43" s="75" t="s">
+      <c r="C43" s="135" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="44" spans="2:3">
-      <c r="B44" s="75" t="s">
+      <c r="B44" s="135" t="s">
         <v>150</v>
       </c>
-      <c r="C44" s="75" t="s">
+      <c r="C44" s="135" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="45" spans="2:3">
-      <c r="C45" s="75" t="s">
+      <c r="C45" s="135" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="46" spans="2:3">
-      <c r="C46" s="75" t="s">
+      <c r="C46" s="135" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="47" spans="2:3">
-      <c r="C47" s="75" t="s">
+      <c r="C47" s="135" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="48" spans="2:3">
-      <c r="C48" s="75" t="s">
+      <c r="C48" s="135" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="49" spans="2:3">
-      <c r="C49" s="75" t="s">
+      <c r="C49" s="135" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="50" spans="2:3">
-      <c r="C50" s="75" t="s">
+      <c r="C50" s="135" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="51" spans="2:3">
-      <c r="C51" s="75" t="s">
+      <c r="C51" s="135" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="52" spans="2:3">
-      <c r="C52" s="75" t="s">
+      <c r="C52" s="135" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="53" spans="2:3">
-      <c r="B53" s="75" t="s">
+      <c r="B53" s="135" t="s">
         <v>220</v>
       </c>
-      <c r="C53" s="75" t="s">
+      <c r="C53" s="135" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="54" spans="2:3">
-      <c r="C54" s="75" t="s">
+      <c r="C54" s="135" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="55" spans="2:3">
-      <c r="C55" s="75" t="s">
+      <c r="C55" s="135" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="56" spans="2:3">
-      <c r="C56" s="75" t="s">
+      <c r="C56" s="135" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="57" spans="2:3">
-      <c r="C57" s="75" t="s">
+      <c r="C57" s="135" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="58" spans="2:3">
-      <c r="C58" s="75" t="s">
+      <c r="C58" s="135" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="59" spans="2:3">
-      <c r="C59" s="75" t="s">
+      <c r="C59" s="135" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="60" spans="2:3">
-      <c r="C60" s="75" t="s">
+      <c r="C60" s="135" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="61" spans="2:3">
-      <c r="C61" s="75" t="s">
+      <c r="C61" s="135" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="62" spans="2:3">
-      <c r="C62" s="75" t="s">
+      <c r="C62" s="135" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="63" spans="2:3">
-      <c r="C63" s="75" t="s">
+      <c r="C63" s="135" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="64" spans="2:3">
-      <c r="C64" s="75" t="s">
+      <c r="C64" s="135" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="65" spans="2:3">
-      <c r="C65" s="75" t="s">
+      <c r="C65" s="135" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="66" spans="2:3">
-      <c r="C66" s="75" t="s">
+      <c r="C66" s="135" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="67" spans="2:3">
-      <c r="B67" s="75" t="s">
+      <c r="B67" s="135" t="s">
         <v>221</v>
       </c>
-      <c r="C67" s="75" t="s">
+      <c r="C67" s="135" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="68" spans="2:3">
-      <c r="B68" s="96"/>
-      <c r="C68" s="96"/>
+      <c r="B68" s="137"/>
+      <c r="C68" s="137"/>
     </row>
     <row r="69" spans="2:3">
-      <c r="B69" s="75" t="s">
+      <c r="B69" s="135" t="s">
         <v>182</v>
       </c>
-      <c r="C69" s="75" t="s">
+      <c r="C69" s="135" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="70" spans="2:3">
-      <c r="C70" s="75" t="s">
+      <c r="C70" s="135" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="71" spans="2:3">
-      <c r="B71" s="75" t="s">
+      <c r="B71" s="135" t="s">
         <v>184</v>
       </c>
-      <c r="C71" s="75" t="s">
+      <c r="C71" s="135" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="72" spans="2:3">
-      <c r="C72" s="75" t="s">
+      <c r="C72" s="135" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="73" spans="2:3">
-      <c r="C73" s="75" t="s">
+      <c r="C73" s="135" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="74" spans="2:3">
-      <c r="C74" s="75" t="s">
+      <c r="C74" s="135" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="75" spans="2:3">
-      <c r="C75" s="75" t="s">
+      <c r="C75" s="135" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="76" spans="2:3">
-      <c r="C76" s="75" t="s">
+      <c r="C76" s="135" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="77" spans="2:3">
-      <c r="B77" s="96"/>
-      <c r="C77" s="96"/>
+      <c r="B77" s="137"/>
+      <c r="C77" s="137"/>
     </row>
     <row r="78" spans="2:3">
-      <c r="B78" s="75" t="s">
+      <c r="B78" s="135" t="s">
         <v>180</v>
       </c>
-      <c r="C78" s="100" t="s">
+      <c r="C78" s="138" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="79" spans="2:3">
-      <c r="B79" s="75" t="s">
+      <c r="B79" s="135" t="s">
         <v>243</v>
       </c>
-      <c r="C79" s="100" t="s">
+      <c r="C79" s="138" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="80" spans="2:3">
-      <c r="C80" s="100" t="s">
+      <c r="C80" s="138" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="81" spans="2:3">
-      <c r="B81" s="75" t="s">
+      <c r="B81" s="135" t="s">
         <v>247</v>
       </c>
-      <c r="C81" s="101" t="s">
+      <c r="C81" s="139" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="82" spans="2:3">
-      <c r="C82" s="102" t="s">
+      <c r="C82" s="140" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="83" spans="2:3">
-      <c r="B83" s="75" t="s">
+      <c r="B83" s="135" t="s">
         <v>249</v>
       </c>
-      <c r="C83" s="102" t="s">
+      <c r="C83" s="140" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="84" spans="2:3">
-      <c r="C84" s="102" t="s">
+      <c r="C84" s="140" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="85" spans="2:3">
-      <c r="C85" s="102" t="s">
+      <c r="C85" s="140" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="86" spans="2:3">
-      <c r="C86" s="102" t="s">
+      <c r="C86" s="140" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="87" spans="2:3">
-      <c r="C87" s="102" t="s">
+      <c r="C87" s="140" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="88" spans="2:3">
-      <c r="C88" s="102" t="s">
+      <c r="C88" s="140" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="89" spans="2:3">
-      <c r="C89" s="102" t="s">
+      <c r="C89" s="140" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="90" spans="2:3">
-      <c r="C90" s="102" t="s">
+      <c r="C90" s="140" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="91" spans="2:3">
-      <c r="C91" s="102" t="s">
+      <c r="C91" s="140" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="92" spans="2:3">
-      <c r="C92" s="102" t="s">
+      <c r="C92" s="140" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="93" spans="2:3">
-      <c r="C93" s="102" t="s">
+      <c r="C93" s="140" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="94" spans="2:3">
-      <c r="C94" s="102" t="s">
+      <c r="C94" s="140" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="101" spans="3:3">
-      <c r="C101" s="102"/>
+    <row r="95" spans="2:3">
+      <c r="B95" s="137"/>
+      <c r="C95" s="137"/>
+    </row>
+    <row r="96" spans="2:3">
+      <c r="B96" s="135" t="s">
+        <v>180</v>
+      </c>
+      <c r="C96" s="140" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3">
+      <c r="C97" s="138" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3">
+      <c r="C98" s="138" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3">
+      <c r="B99" s="135" t="s">
+        <v>304</v>
+      </c>
+      <c r="C99" s="138" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3">
+      <c r="C100" s="138" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="C101" s="139" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3">
+      <c r="C102" s="140" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3">
+      <c r="B103" s="135" t="s">
+        <v>305</v>
+      </c>
+      <c r="C103" s="140" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3">
+      <c r="C104" s="140" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="105" spans="2:3">
+      <c r="C105" s="140" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="106" spans="2:3">
+      <c r="C106" s="140" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="107" spans="2:3">
+      <c r="C107" s="135" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="C108" s="140" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3">
+      <c r="C109" s="140" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3">
+      <c r="C110" s="140" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3">
+      <c r="C111" s="140" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="112" spans="2:3">
+      <c r="C112" s="140" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="C113" s="140" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="C114" s="140" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="115" spans="2:3">
+      <c r="C115" s="140" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3">
+      <c r="C116" s="140" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="C117" s="140" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3">
+      <c r="C118" s="140" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3">
+      <c r="C119" s="140" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3">
+      <c r="C120" s="140" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3">
+      <c r="B121" s="140" t="s">
+        <v>312</v>
+      </c>
+      <c r="C121" s="140" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3">
+      <c r="C122" s="140" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="123" spans="2:3">
+      <c r="B123" s="137"/>
+      <c r="C123" s="137"/>
+    </row>
+    <row r="124" spans="2:3">
+      <c r="B124" s="135" t="s">
+        <v>180</v>
+      </c>
+      <c r="C124" s="135" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="125" spans="2:3">
+      <c r="C125" s="135" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="126" spans="2:3">
+      <c r="C126" s="134" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="127" spans="2:3">
+      <c r="C127" s="134" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="128" spans="2:3">
+      <c r="B128" s="135" t="s">
+        <v>352</v>
+      </c>
+      <c r="C128" s="134" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3">
+      <c r="C129" s="134" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3">
+      <c r="C130" s="134" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3">
+      <c r="C131" s="134" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3">
+      <c r="C132" s="134" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="C133" s="134" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3">
+      <c r="C134" s="134" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3">
+      <c r="C135" s="134" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="136" spans="2:3">
+      <c r="B136" s="135" t="s">
+        <v>354</v>
+      </c>
+      <c r="C136" s="134" t="s">
+        <v>353</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/IG/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41962563-FE89-4ECD-8F4B-8618CEF65EC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA83E724-F89A-4102-BBE8-9E58F6D24E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -89,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="431">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -1386,13 +1385,6 @@
   </si>
   <si>
     <t>VS Code上でGitを使う手順-6 【過去の状態に戻す】</t>
-  </si>
-  <si>
-    <t>導入</t>
-    <rPh sb="0" eb="2">
-      <t>ドウニュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>Spring Bootプロジェクトの_x000B_準備、起動確認</t>
@@ -2151,17 +2143,6 @@
 ※アプリケーションを二重に起動するとポートが競合し、正常に起動できない場合があることを説明する。
 ※起動エラーが発生した場合、既存のアプリケーションを実行しているターミナルを停止し、再度起動することを伝える。</t>
     </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>バイブコーディング：ハンズオン</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>バイブコーディング：演習</t>
-    <rPh sb="10" eb="12">
-      <t>エンシュウ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -3722,19 +3703,8 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>バイブコーディングで単体テスト(JUnit)</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>ここから各自で演習を始めましょう。</t>
     <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>バイブコーディングで単体テスト(JUnit)：演習</t>
-    <rPh sb="23" eb="25">
-      <t>エンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>追加課題②：クーポン機能</t>
@@ -4590,16 +4560,103 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>AWS</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>振り返り</t>
-    <rPh sb="0" eb="1">
+    <t>AWS講義</t>
+    <rPh sb="3" eb="5">
+      <t>コウギ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題2の実施</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題1の実施</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題の振り返り</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
       <t>フ</t>
     </rPh>
+    <rPh sb="5" eb="6">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ハンズオン</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バイブコーディングの導入</t>
+    <rPh sb="10" eb="12">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題1の導入</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>システム開発プロセスの導入</t>
+    <rPh sb="4" eb="6">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>単体テストとJunitの導入</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題2の導入</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>その他の導入</t>
     <rPh sb="2" eb="3">
-      <t>カエ</t>
+      <t>タ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウニュウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -5302,6 +5359,18 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5350,42 +5419,60 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
@@ -5394,36 +5481,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5799,17 +5856,17 @@
   <sheetData>
     <row r="2" spans="1:10" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="90" t="str">
+      <c r="B2" s="94" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="90"/>
-      <c r="D2" s="90"/>
-      <c r="E2" s="90"/>
-      <c r="F2" s="90"/>
-      <c r="G2" s="90"/>
-      <c r="H2" s="90"/>
-      <c r="I2" s="90"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
     </row>
     <row r="3" spans="1:10" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -5824,10 +5881,10 @@
     </row>
     <row r="4" spans="1:10" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="91" t="s">
+      <c r="B4" s="95" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="92"/>
+      <c r="C4" s="96"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -5837,8 +5894,8 @@
     </row>
     <row r="5" spans="1:10" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="93"/>
-      <c r="C5" s="94"/>
+      <c r="B5" s="97"/>
+      <c r="C5" s="98"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -5847,10 +5904,10 @@
       <c r="I5" s="13"/>
     </row>
     <row r="7" spans="1:10" ht="16.2">
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="99" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="95"/>
+      <c r="C7" s="99"/>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" s="15"/>
@@ -5864,15 +5921,15 @@
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="24" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="H9" s="24"/>
       <c r="I9" s="24" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1">
@@ -5911,27 +5968,27 @@
       </c>
       <c r="C11" s="70" t="str">
         <f>master!B3</f>
-        <v>導入</v>
+        <v>バイブコーディングの導入</v>
       </c>
       <c r="D11" s="60">
         <v>0.40625</v>
       </c>
       <c r="E11" s="70" t="str">
         <f>master!B78</f>
-        <v>導入</v>
+        <v>システム開発プロセスの導入</v>
       </c>
       <c r="F11" s="60">
         <v>0.40625</v>
       </c>
       <c r="G11" s="70" t="str">
         <f>master!B96</f>
-        <v>導入</v>
+        <v>単体テストとJunitの導入</v>
       </c>
       <c r="H11" s="60">
         <v>0.40625</v>
       </c>
       <c r="I11" s="70" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5965,7 +6022,7 @@
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D13" s="128">
+      <c r="D13" s="91">
         <v>0.42708333333333331</v>
       </c>
       <c r="E13" s="70" t="str">
@@ -6051,8 +6108,8 @@
         <v>0.47916666666666669</v>
       </c>
       <c r="E18" s="59" t="str">
-        <f>master!B53</f>
-        <v>バイブコーディング：ハンズオン</v>
+        <f>master!B67</f>
+        <v>課題1の実施</v>
       </c>
       <c r="F18" s="68"/>
       <c r="G18" s="72"/>
@@ -6093,8 +6150,8 @@
         <v>0.5</v>
       </c>
       <c r="G20" s="59" t="str">
-        <f>master!B53</f>
-        <v>バイブコーディング：ハンズオン</v>
+        <f>master!B67</f>
+        <v>課題1の実施</v>
       </c>
       <c r="H20" s="67"/>
       <c r="I20" s="71"/>
@@ -6209,23 +6266,26 @@
       </c>
       <c r="C26" s="59" t="str">
         <f>master!B37</f>
-        <v>導入</v>
+        <v>課題1の導入</v>
       </c>
       <c r="D26" s="40">
         <v>0.5625</v>
       </c>
       <c r="E26" s="59"/>
-      <c r="F26" s="129">
+      <c r="F26" s="92">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="130" t="str">
+      <c r="G26" s="93" t="str">
         <f>master!B124</f>
-        <v>導入</v>
+        <v>課題2の導入</v>
       </c>
       <c r="H26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="I26" s="59"/>
+      <c r="I26" s="59" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
       <c r="J26" s="6"/>
     </row>
     <row r="27" spans="1:10">
@@ -6239,10 +6299,13 @@
       </c>
       <c r="G27" s="59" t="str">
         <f>master!B128</f>
-        <v>バイブコーディングで単体テスト(JUnit)</v>
+        <v>ハンズオン</v>
       </c>
       <c r="H27" s="42"/>
-      <c r="I27" s="54"/>
+      <c r="I27" s="54" t="str">
+        <f>master!B136</f>
+        <v>課題2の実施</v>
+      </c>
       <c r="J27" s="6"/>
     </row>
     <row r="28" spans="1:10">
@@ -6314,7 +6377,7 @@
       </c>
       <c r="C32" s="59" t="str">
         <f>master!B53</f>
-        <v>バイブコーディング：ハンズオン</v>
+        <v>ハンズオン</v>
       </c>
       <c r="D32" s="42"/>
       <c r="E32" s="54"/>
@@ -6335,7 +6398,7 @@
       </c>
       <c r="G33" s="54" t="str">
         <f>master!B136</f>
-        <v>バイブコーディングで単体テスト(JUnit)：演習</v>
+        <v>課題2の実施</v>
       </c>
       <c r="H33" s="42"/>
       <c r="I33" s="54"/>
@@ -6393,7 +6456,7 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="38"/>
-      <c r="B38" s="128">
+      <c r="B38" s="91">
         <v>0.6875</v>
       </c>
       <c r="C38" s="69" t="str">
@@ -6426,7 +6489,7 @@
       </c>
       <c r="I39" s="54" t="str">
         <f>master!B143</f>
-        <v>振り返り</v>
+        <v>課題の振り返り</v>
       </c>
       <c r="J39" s="6"/>
     </row>
@@ -6451,7 +6514,7 @@
       </c>
       <c r="C41" s="59" t="str">
         <f>master!B67</f>
-        <v>バイブコーディング：演習</v>
+        <v>課題1の実施</v>
       </c>
       <c r="D41" s="42"/>
       <c r="E41" s="54"/>
@@ -6565,10 +6628,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="101"/>
+      <c r="C4" s="105"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -6579,16 +6642,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -6601,10 +6664,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="33"/>
-      <c r="D7" s="103" t="s">
+      <c r="D7" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="103"/>
+      <c r="E7" s="107"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -6644,46 +6707,46 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97" t="s">
+      <c r="B11" s="101"/>
+      <c r="C11" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="97" t="s">
+      <c r="D11" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97" t="s">
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="104" t="s">
+      <c r="H11" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="96" t="s">
+      <c r="I11" s="100" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96" t="s">
+      <c r="J11" s="100"/>
+      <c r="K11" s="100" t="s">
         <v>32</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="97"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="97"/>
-      <c r="E12" s="97"/>
-      <c r="F12" s="97"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="105"/>
+      <c r="B12" s="101"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101"/>
+      <c r="H12" s="109"/>
       <c r="I12" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="97"/>
+      <c r="K12" s="101"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
@@ -6692,11 +6755,11 @@
       <c r="C13" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D13" s="98" t="s">
+      <c r="D13" s="102" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="99"/>
-      <c r="F13" s="100"/>
+      <c r="E13" s="103"/>
+      <c r="F13" s="104"/>
       <c r="G13" s="56" t="s">
         <v>54</v>
       </c>
@@ -6795,12 +6858,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -6811,30 +6874,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="126"/>
-      <c r="C5" s="126"/>
-      <c r="D5" s="126"/>
-      <c r="E5" s="126"/>
-      <c r="F5" s="126"/>
-      <c r="G5" s="126"/>
-      <c r="H5" s="126"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="124"/>
+      <c r="J5" s="124"/>
+      <c r="K5" s="124"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="2:14" ht="32.4" customHeight="1">
-      <c r="B6" s="126"/>
-      <c r="C6" s="126"/>
-      <c r="D6" s="126"/>
-      <c r="E6" s="126"/>
-      <c r="F6" s="126"/>
-      <c r="G6" s="126"/>
-      <c r="H6" s="126"/>
-      <c r="I6" s="126"/>
-      <c r="J6" s="126"/>
-      <c r="K6" s="126"/>
+      <c r="B6" s="124"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="124"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="124"/>
+      <c r="K6" s="124"/>
       <c r="L6" s="29"/>
       <c r="M6" s="30"/>
     </row>
@@ -7030,7 +7093,7 @@
         <v>98</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>19</v>
@@ -7049,10 +7112,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="34" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>19</v>
@@ -7071,10 +7134,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="B18" s="34" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="C18" s="61" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>19</v>
@@ -7093,10 +7156,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="34" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C19" s="61" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>19</v>
@@ -7126,28 +7189,28 @@
     </row>
     <row r="22" spans="1:14" ht="24" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="97" t="s">
+      <c r="B22" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="97" t="s">
+      <c r="C22" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="97" t="s">
+      <c r="D22" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="97"/>
-      <c r="F22" s="97"/>
-      <c r="G22" s="97" t="s">
+      <c r="E22" s="101"/>
+      <c r="F22" s="101"/>
+      <c r="G22" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="96" t="s">
+      <c r="H22" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="124" t="s">
+      <c r="I22" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="125"/>
-      <c r="K22" s="96" t="s">
+      <c r="J22" s="123"/>
+      <c r="K22" s="100" t="s">
         <v>34</v>
       </c>
       <c r="L22" s="6"/>
@@ -7156,20 +7219,20 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="10"/>
-      <c r="B23" s="97"/>
-      <c r="C23" s="97"/>
-      <c r="D23" s="97"/>
-      <c r="E23" s="97"/>
-      <c r="F23" s="97"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="96"/>
+      <c r="B23" s="101"/>
+      <c r="C23" s="101"/>
+      <c r="D23" s="101"/>
+      <c r="E23" s="101"/>
+      <c r="F23" s="101"/>
+      <c r="G23" s="101"/>
+      <c r="H23" s="100"/>
       <c r="I23" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J23" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K23" s="97"/>
+      <c r="K23" s="101"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
@@ -7178,17 +7241,17 @@
       <c r="A24" s="10"/>
       <c r="B24" s="79" t="str">
         <f>master!B3</f>
-        <v>導入</v>
+        <v>バイブコーディングの導入</v>
       </c>
       <c r="C24" s="51" t="str">
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D24" s="108" t="s">
+      <c r="D24" s="116" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="109"/>
-      <c r="F24" s="110"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="118"/>
       <c r="G24" s="51" t="s">
         <v>100</v>
       </c>
@@ -7206,7 +7269,7 @@
     </row>
     <row r="25" spans="1:14" ht="138.6" customHeight="1">
       <c r="A25" s="10"/>
-      <c r="B25" s="121" t="str">
+      <c r="B25" s="125" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -7214,11 +7277,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D25" s="108" t="s">
+      <c r="D25" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E25" s="109"/>
-      <c r="F25" s="110"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="118"/>
       <c r="G25" s="51" t="s">
         <v>43</v>
       </c>
@@ -7236,16 +7299,16 @@
     </row>
     <row r="26" spans="1:14" ht="75.599999999999994">
       <c r="A26" s="11"/>
-      <c r="B26" s="122"/>
+      <c r="B26" s="126"/>
       <c r="C26" s="51" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D26" s="108" t="s">
+      <c r="D26" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="E26" s="109"/>
-      <c r="F26" s="110"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="118"/>
       <c r="G26" s="51" t="s">
         <v>47</v>
       </c>
@@ -7263,16 +7326,16 @@
     </row>
     <row r="27" spans="1:14" ht="37.799999999999997">
       <c r="A27" s="11"/>
-      <c r="B27" s="122"/>
+      <c r="B27" s="126"/>
       <c r="C27" s="51" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D27" s="108" t="s">
+      <c r="D27" s="116" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="109"/>
-      <c r="F27" s="110"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="51" t="s">
         <v>45</v>
       </c>
@@ -7290,16 +7353,16 @@
     </row>
     <row r="28" spans="1:14" ht="63">
       <c r="A28" s="11"/>
-      <c r="B28" s="122"/>
+      <c r="B28" s="126"/>
       <c r="C28" s="51" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D28" s="108" t="s">
+      <c r="D28" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="E28" s="109"/>
-      <c r="F28" s="110"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
       <c r="G28" s="51" t="s">
         <v>44</v>
       </c>
@@ -7317,13 +7380,13 @@
     </row>
     <row r="29" spans="1:14" ht="63">
       <c r="A29" s="11"/>
-      <c r="B29" s="122"/>
+      <c r="B29" s="126"/>
       <c r="C29" s="51"/>
-      <c r="D29" s="108" t="s">
+      <c r="D29" s="116" t="s">
         <v>105</v>
       </c>
-      <c r="E29" s="109"/>
-      <c r="F29" s="110"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="118"/>
       <c r="G29" s="51" t="s">
         <v>44</v>
       </c>
@@ -7341,16 +7404,16 @@
     </row>
     <row r="30" spans="1:14" ht="113.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="123"/>
+      <c r="B30" s="127"/>
       <c r="C30" s="51" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D30" s="108" t="s">
+      <c r="D30" s="116" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="109"/>
-      <c r="F30" s="110"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="118"/>
       <c r="G30" s="51" t="s">
         <v>48</v>
       </c>
@@ -7368,7 +7431,7 @@
     </row>
     <row r="31" spans="1:14" ht="102" customHeight="1">
       <c r="A31" s="11"/>
-      <c r="B31" s="121" t="str">
+      <c r="B31" s="125" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -7376,11 +7439,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D31" s="108" t="s">
+      <c r="D31" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="109"/>
-      <c r="F31" s="110"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="51" t="s">
         <v>45</v>
       </c>
@@ -7398,16 +7461,16 @@
     </row>
     <row r="32" spans="1:14" ht="88.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="122"/>
+      <c r="B32" s="126"/>
       <c r="C32" s="51" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D32" s="108" t="s">
+      <c r="D32" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="E32" s="109"/>
-      <c r="F32" s="110"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
       <c r="G32" s="51" t="s">
         <v>49</v>
       </c>
@@ -7425,16 +7488,16 @@
     </row>
     <row r="33" spans="1:14" ht="25.2">
       <c r="A33" s="11"/>
-      <c r="B33" s="122"/>
+      <c r="B33" s="126"/>
       <c r="C33" s="51" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D33" s="108" t="s">
+      <c r="D33" s="116" t="s">
         <v>109</v>
       </c>
-      <c r="E33" s="109"/>
-      <c r="F33" s="110"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="118"/>
       <c r="G33" s="51" t="s">
         <v>50</v>
       </c>
@@ -7454,16 +7517,16 @@
     </row>
     <row r="34" spans="1:14" ht="75.599999999999994">
       <c r="A34" s="11"/>
-      <c r="B34" s="122"/>
+      <c r="B34" s="126"/>
       <c r="C34" s="51" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D34" s="108" t="s">
+      <c r="D34" s="116" t="s">
         <v>110</v>
       </c>
-      <c r="E34" s="109"/>
-      <c r="F34" s="110"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="118"/>
       <c r="G34" s="51" t="s">
         <v>47</v>
       </c>
@@ -7481,16 +7544,16 @@
     </row>
     <row r="35" spans="1:14" ht="100.8">
       <c r="A35" s="11"/>
-      <c r="B35" s="122"/>
+      <c r="B35" s="126"/>
       <c r="C35" s="51" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D35" s="108" t="s">
+      <c r="D35" s="116" t="s">
         <v>111</v>
       </c>
-      <c r="E35" s="109"/>
-      <c r="F35" s="110"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="51" t="s">
         <v>51</v>
       </c>
@@ -7508,16 +7571,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="122"/>
+      <c r="B36" s="126"/>
       <c r="C36" s="51" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D36" s="108" t="s">
+      <c r="D36" s="116" t="s">
         <v>112</v>
       </c>
-      <c r="E36" s="109"/>
-      <c r="F36" s="110"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="118"/>
       <c r="G36" s="51" t="s">
         <v>45</v>
       </c>
@@ -7535,16 +7598,16 @@
     </row>
     <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="122"/>
+      <c r="B37" s="126"/>
       <c r="C37" s="51" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D37" s="108" t="s">
+      <c r="D37" s="116" t="s">
         <v>113</v>
       </c>
-      <c r="E37" s="109"/>
-      <c r="F37" s="110"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="118"/>
       <c r="G37" s="51" t="s">
         <v>45</v>
       </c>
@@ -7562,16 +7625,16 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="123"/>
+      <c r="B38" s="127"/>
       <c r="C38" s="51" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D38" s="108" t="s">
+      <c r="D38" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="E38" s="109"/>
-      <c r="F38" s="110"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="118"/>
       <c r="G38" s="51" t="s">
         <v>45</v>
       </c>
@@ -7589,7 +7652,7 @@
     </row>
     <row r="39" spans="1:14" ht="88.2">
       <c r="A39" s="11"/>
-      <c r="B39" s="121" t="str">
+      <c r="B39" s="125" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -7597,11 +7660,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D39" s="108" t="s">
+      <c r="D39" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="E39" s="109"/>
-      <c r="F39" s="110"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="51" t="s">
         <v>49</v>
       </c>
@@ -7619,16 +7682,16 @@
     </row>
     <row r="40" spans="1:14" ht="75.599999999999994">
       <c r="A40" s="11"/>
-      <c r="B40" s="122"/>
+      <c r="B40" s="126"/>
       <c r="C40" s="51" t="str">
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D40" s="108" t="s">
+      <c r="D40" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="E40" s="109"/>
-      <c r="F40" s="110"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="118"/>
       <c r="G40" s="51" t="s">
         <v>47</v>
       </c>
@@ -7646,16 +7709,16 @@
     </row>
     <row r="41" spans="1:14" ht="75.599999999999994">
       <c r="A41" s="11"/>
-      <c r="B41" s="122"/>
+      <c r="B41" s="126"/>
       <c r="C41" s="51" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D41" s="108" t="s">
+      <c r="D41" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="E41" s="109"/>
-      <c r="F41" s="110"/>
+      <c r="E41" s="117"/>
+      <c r="F41" s="118"/>
       <c r="G41" s="51" t="s">
         <v>47</v>
       </c>
@@ -7673,16 +7736,16 @@
     </row>
     <row r="42" spans="1:14" ht="50.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="122"/>
+      <c r="B42" s="126"/>
       <c r="C42" s="51" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D42" s="108" t="s">
+      <c r="D42" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="E42" s="109"/>
-      <c r="F42" s="110"/>
+      <c r="E42" s="117"/>
+      <c r="F42" s="118"/>
       <c r="G42" s="51" t="s">
         <v>46</v>
       </c>
@@ -7700,16 +7763,16 @@
     </row>
     <row r="43" spans="1:14" ht="88.2">
       <c r="A43" s="11"/>
-      <c r="B43" s="122"/>
+      <c r="B43" s="126"/>
       <c r="C43" s="51" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D43" s="108" t="s">
+      <c r="D43" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="E43" s="109"/>
-      <c r="F43" s="110"/>
+      <c r="E43" s="117"/>
+      <c r="F43" s="118"/>
       <c r="G43" s="51" t="s">
         <v>49</v>
       </c>
@@ -7729,16 +7792,16 @@
     </row>
     <row r="44" spans="1:14" ht="201.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="122"/>
+      <c r="B44" s="126"/>
       <c r="C44" s="51" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D44" s="108" t="s">
+      <c r="D44" s="116" t="s">
         <v>121</v>
       </c>
-      <c r="E44" s="109"/>
-      <c r="F44" s="110"/>
+      <c r="E44" s="117"/>
+      <c r="F44" s="118"/>
       <c r="G44" s="51" t="s">
         <v>122</v>
       </c>
@@ -7756,16 +7819,16 @@
     </row>
     <row r="45" spans="1:14" ht="37.799999999999997">
       <c r="A45" s="11"/>
-      <c r="B45" s="122"/>
+      <c r="B45" s="126"/>
       <c r="C45" s="51" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D45" s="108" t="s">
+      <c r="D45" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="E45" s="109"/>
-      <c r="F45" s="110"/>
+      <c r="E45" s="117"/>
+      <c r="F45" s="118"/>
       <c r="G45" s="51" t="s">
         <v>45</v>
       </c>
@@ -7783,16 +7846,16 @@
     </row>
     <row r="46" spans="1:14" ht="163.80000000000001">
       <c r="A46" s="11"/>
-      <c r="B46" s="122"/>
+      <c r="B46" s="126"/>
       <c r="C46" s="51" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D46" s="108" t="s">
+      <c r="D46" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="E46" s="109"/>
-      <c r="F46" s="110"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="118"/>
       <c r="G46" s="51" t="s">
         <v>125</v>
       </c>
@@ -7810,16 +7873,16 @@
     </row>
     <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="122"/>
+      <c r="B47" s="126"/>
       <c r="C47" s="51" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D47" s="108" t="s">
+      <c r="D47" s="116" t="s">
         <v>126</v>
       </c>
-      <c r="E47" s="109"/>
-      <c r="F47" s="110"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="118"/>
       <c r="G47" s="51" t="s">
         <v>50</v>
       </c>
@@ -7837,16 +7900,16 @@
     </row>
     <row r="48" spans="1:14" ht="189">
       <c r="A48" s="11"/>
-      <c r="B48" s="122"/>
+      <c r="B48" s="126"/>
       <c r="C48" s="51" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D48" s="108" t="s">
+      <c r="D48" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="109"/>
-      <c r="F48" s="110"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="118"/>
       <c r="G48" s="51" t="s">
         <v>128</v>
       </c>
@@ -7864,16 +7927,16 @@
     </row>
     <row r="49" spans="1:14" ht="88.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="122"/>
+      <c r="B49" s="126"/>
       <c r="C49" s="51" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D49" s="108" t="s">
+      <c r="D49" s="116" t="s">
         <v>129</v>
       </c>
-      <c r="E49" s="109"/>
-      <c r="F49" s="110"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="118"/>
       <c r="G49" s="51" t="s">
         <v>49</v>
       </c>
@@ -7893,16 +7956,16 @@
     </row>
     <row r="50" spans="1:14" ht="63">
       <c r="A50" s="11"/>
-      <c r="B50" s="122"/>
+      <c r="B50" s="126"/>
       <c r="C50" s="51" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D50" s="108" t="s">
+      <c r="D50" s="116" t="s">
         <v>130</v>
       </c>
-      <c r="E50" s="109"/>
-      <c r="F50" s="110"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="118"/>
       <c r="G50" s="51" t="s">
         <v>44</v>
       </c>
@@ -7920,16 +7983,16 @@
     </row>
     <row r="51" spans="1:14" ht="100.8">
       <c r="A51" s="11"/>
-      <c r="B51" s="122"/>
+      <c r="B51" s="126"/>
       <c r="C51" s="51" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D51" s="108" t="s">
+      <c r="D51" s="116" t="s">
         <v>131</v>
       </c>
-      <c r="E51" s="109"/>
-      <c r="F51" s="110"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="118"/>
       <c r="G51" s="51" t="s">
         <v>51</v>
       </c>
@@ -7947,16 +8010,16 @@
     </row>
     <row r="52" spans="1:14" ht="100.8">
       <c r="A52" s="11"/>
-      <c r="B52" s="122"/>
+      <c r="B52" s="126"/>
       <c r="C52" s="51" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D52" s="108" t="s">
+      <c r="D52" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="E52" s="109"/>
-      <c r="F52" s="110"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="118"/>
       <c r="G52" s="51" t="s">
         <v>51</v>
       </c>
@@ -7974,16 +8037,16 @@
     </row>
     <row r="53" spans="1:14" ht="88.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="122"/>
+      <c r="B53" s="126"/>
       <c r="C53" s="51" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D53" s="108" t="s">
+      <c r="D53" s="116" t="s">
         <v>133</v>
       </c>
-      <c r="E53" s="109"/>
-      <c r="F53" s="110"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="118"/>
       <c r="G53" s="51" t="s">
         <v>49</v>
       </c>
@@ -8001,16 +8064,16 @@
     </row>
     <row r="54" spans="1:14" ht="63">
       <c r="A54" s="11"/>
-      <c r="B54" s="122"/>
+      <c r="B54" s="126"/>
       <c r="C54" s="51" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D54" s="108" t="s">
+      <c r="D54" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="E54" s="109"/>
-      <c r="F54" s="110"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="118"/>
       <c r="G54" s="51" t="s">
         <v>44</v>
       </c>
@@ -8028,16 +8091,16 @@
     </row>
     <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="122"/>
+      <c r="B55" s="126"/>
       <c r="C55" s="51" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D55" s="108" t="s">
+      <c r="D55" s="116" t="s">
         <v>135</v>
       </c>
-      <c r="E55" s="109"/>
-      <c r="F55" s="110"/>
+      <c r="E55" s="117"/>
+      <c r="F55" s="118"/>
       <c r="G55" s="51" t="s">
         <v>46</v>
       </c>
@@ -8055,16 +8118,16 @@
     </row>
     <row r="56" spans="1:14" ht="88.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="122"/>
+      <c r="B56" s="126"/>
       <c r="C56" s="51" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D56" s="108" t="s">
+      <c r="D56" s="116" t="s">
         <v>136</v>
       </c>
-      <c r="E56" s="109"/>
-      <c r="F56" s="110"/>
+      <c r="E56" s="117"/>
+      <c r="F56" s="118"/>
       <c r="G56" s="51" t="s">
         <v>49</v>
       </c>
@@ -8082,14 +8145,14 @@
     </row>
     <row r="57" spans="1:14" ht="25.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="123"/>
+      <c r="B57" s="127"/>
       <c r="C57" s="51" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D57" s="108"/>
-      <c r="E57" s="109"/>
-      <c r="F57" s="110"/>
+      <c r="D57" s="116"/>
+      <c r="E57" s="117"/>
+      <c r="F57" s="118"/>
       <c r="G57" s="51" t="s">
         <v>50</v>
       </c>
@@ -8107,21 +8170,21 @@
     </row>
     <row r="58" spans="1:14" ht="37.799999999999997">
       <c r="A58" s="11"/>
-      <c r="B58" s="118" t="str">
+      <c r="B58" s="128" t="str">
         <f>master!B37</f>
-        <v>導入</v>
+        <v>課題1の導入</v>
       </c>
       <c r="C58" s="62" t="str">
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D58" s="111" t="s">
-        <v>179</v>
-      </c>
-      <c r="E58" s="112"/>
-      <c r="F58" s="113"/>
+      <c r="D58" s="112" t="s">
+        <v>178</v>
+      </c>
+      <c r="E58" s="113"/>
+      <c r="F58" s="114"/>
       <c r="G58" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H58" s="63"/>
       <c r="I58" s="64" t="s">
@@ -8137,18 +8200,18 @@
     </row>
     <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="119"/>
+      <c r="B59" s="129"/>
       <c r="C59" s="62" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D59" s="111" t="s">
-        <v>180</v>
-      </c>
-      <c r="E59" s="112"/>
-      <c r="F59" s="113"/>
+      <c r="D59" s="112" t="s">
+        <v>179</v>
+      </c>
+      <c r="E59" s="113"/>
+      <c r="F59" s="114"/>
       <c r="G59" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H59" s="63"/>
       <c r="I59" s="64" t="s">
@@ -8164,18 +8227,18 @@
     </row>
     <row r="60" spans="1:14" ht="75.599999999999994">
       <c r="A60" s="11"/>
-      <c r="B60" s="120"/>
+      <c r="B60" s="130"/>
       <c r="C60" s="62" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D60" s="111" t="s">
-        <v>181</v>
-      </c>
-      <c r="E60" s="112"/>
-      <c r="F60" s="113"/>
+      <c r="D60" s="112" t="s">
+        <v>180</v>
+      </c>
+      <c r="E60" s="113"/>
+      <c r="F60" s="114"/>
       <c r="G60" s="62" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="H60" s="63"/>
       <c r="I60" s="64" t="s">
@@ -8191,7 +8254,7 @@
     </row>
     <row r="61" spans="1:14" ht="15" customHeight="1">
       <c r="A61" s="11"/>
-      <c r="B61" s="118" t="str">
+      <c r="B61" s="128" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -8199,11 +8262,11 @@
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D61" s="111"/>
-      <c r="E61" s="112"/>
-      <c r="F61" s="113"/>
+      <c r="D61" s="112"/>
+      <c r="E61" s="113"/>
+      <c r="F61" s="114"/>
       <c r="G61" s="62" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H61" s="63"/>
       <c r="I61" s="64" t="s">
@@ -8219,18 +8282,18 @@
     </row>
     <row r="62" spans="1:14" ht="37.799999999999997">
       <c r="A62" s="11"/>
-      <c r="B62" s="119"/>
+      <c r="B62" s="129"/>
       <c r="C62" s="62" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D62" s="111" t="s">
-        <v>182</v>
-      </c>
-      <c r="E62" s="112"/>
-      <c r="F62" s="113"/>
+      <c r="D62" s="112" t="s">
+        <v>181</v>
+      </c>
+      <c r="E62" s="113"/>
+      <c r="F62" s="114"/>
       <c r="G62" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H62" s="63"/>
       <c r="I62" s="64" t="s">
@@ -8246,18 +8309,18 @@
     </row>
     <row r="63" spans="1:14" ht="25.2">
       <c r="A63" s="11"/>
-      <c r="B63" s="119"/>
+      <c r="B63" s="129"/>
       <c r="C63" s="62" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D63" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="E63" s="112"/>
-      <c r="F63" s="113"/>
+      <c r="D63" s="112" t="s">
+        <v>182</v>
+      </c>
+      <c r="E63" s="113"/>
+      <c r="F63" s="114"/>
       <c r="G63" s="62" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H63" s="63"/>
       <c r="I63" s="64" t="s">
@@ -8273,18 +8336,18 @@
     </row>
     <row r="64" spans="1:14" ht="88.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="120"/>
+      <c r="B64" s="130"/>
       <c r="C64" s="62" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D64" s="111" t="s">
-        <v>205</v>
-      </c>
-      <c r="E64" s="112"/>
-      <c r="F64" s="113"/>
+      <c r="D64" s="112" t="s">
+        <v>204</v>
+      </c>
+      <c r="E64" s="113"/>
+      <c r="F64" s="114"/>
       <c r="G64" s="62" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="H64" s="63"/>
       <c r="I64" s="64" t="s">
@@ -8300,7 +8363,7 @@
     </row>
     <row r="65" spans="1:14" ht="190.2" customHeight="1">
       <c r="A65" s="11"/>
-      <c r="B65" s="118" t="str">
+      <c r="B65" s="128" t="str">
         <f>master!B44</f>
         <v>ECサイト Webアプリの要件</v>
       </c>
@@ -8308,13 +8371,13 @@
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D65" s="111" t="s">
-        <v>184</v>
-      </c>
-      <c r="E65" s="112"/>
-      <c r="F65" s="113"/>
+      <c r="D65" s="112" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" s="113"/>
+      <c r="F65" s="114"/>
       <c r="G65" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H65" s="63"/>
       <c r="I65" s="64" t="s">
@@ -8330,18 +8393,18 @@
     </row>
     <row r="66" spans="1:14" ht="151.19999999999999">
       <c r="A66" s="11"/>
-      <c r="B66" s="119"/>
+      <c r="B66" s="129"/>
       <c r="C66" s="62" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D66" s="111" t="s">
-        <v>186</v>
-      </c>
-      <c r="E66" s="112"/>
-      <c r="F66" s="113"/>
+      <c r="D66" s="112" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" s="113"/>
+      <c r="F66" s="114"/>
       <c r="G66" s="62" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="H66" s="63"/>
       <c r="I66" s="64" t="s">
@@ -8357,18 +8420,18 @@
     </row>
     <row r="67" spans="1:14" ht="214.2">
       <c r="A67" s="11"/>
-      <c r="B67" s="119"/>
+      <c r="B67" s="129"/>
       <c r="C67" s="62" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D67" s="111" t="s">
-        <v>187</v>
-      </c>
-      <c r="E67" s="112"/>
-      <c r="F67" s="113"/>
+      <c r="D67" s="112" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67" s="113"/>
+      <c r="F67" s="114"/>
       <c r="G67" s="62" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="H67" s="63"/>
       <c r="I67" s="64" t="s">
@@ -8384,18 +8447,18 @@
     </row>
     <row r="68" spans="1:14" ht="63">
       <c r="A68" s="11"/>
-      <c r="B68" s="119"/>
+      <c r="B68" s="129"/>
       <c r="C68" s="62" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D68" s="111" t="s">
-        <v>188</v>
-      </c>
-      <c r="E68" s="112"/>
-      <c r="F68" s="113"/>
+      <c r="D68" s="112" t="s">
+        <v>187</v>
+      </c>
+      <c r="E68" s="113"/>
+      <c r="F68" s="114"/>
       <c r="G68" s="62" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="H68" s="63"/>
       <c r="I68" s="64" t="s">
@@ -8411,18 +8474,18 @@
     </row>
     <row r="69" spans="1:14" ht="163.80000000000001">
       <c r="A69" s="11"/>
-      <c r="B69" s="119"/>
+      <c r="B69" s="129"/>
       <c r="C69" s="62" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D69" s="111" t="s">
-        <v>190</v>
-      </c>
-      <c r="E69" s="112"/>
-      <c r="F69" s="113"/>
+      <c r="D69" s="112" t="s">
+        <v>189</v>
+      </c>
+      <c r="E69" s="113"/>
+      <c r="F69" s="114"/>
       <c r="G69" s="62" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="H69" s="63"/>
       <c r="I69" s="64" t="s">
@@ -8438,18 +8501,18 @@
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="119"/>
+      <c r="B70" s="129"/>
       <c r="C70" s="62" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D70" s="111" t="s">
-        <v>191</v>
-      </c>
-      <c r="E70" s="112"/>
-      <c r="F70" s="113"/>
+      <c r="D70" s="112" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="113"/>
+      <c r="F70" s="114"/>
       <c r="G70" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H70" s="63"/>
       <c r="I70" s="64" t="s">
@@ -8465,18 +8528,18 @@
     </row>
     <row r="71" spans="1:14" ht="37.799999999999997">
       <c r="A71" s="11"/>
-      <c r="B71" s="119"/>
+      <c r="B71" s="129"/>
       <c r="C71" s="62" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D71" s="111" t="s">
-        <v>192</v>
-      </c>
-      <c r="E71" s="112"/>
-      <c r="F71" s="113"/>
+      <c r="D71" s="112" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" s="113"/>
+      <c r="F71" s="114"/>
       <c r="G71" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H71" s="63"/>
       <c r="I71" s="64" t="s">
@@ -8492,18 +8555,18 @@
     </row>
     <row r="72" spans="1:14" ht="37.799999999999997">
       <c r="A72" s="11"/>
-      <c r="B72" s="119"/>
+      <c r="B72" s="129"/>
       <c r="C72" s="62" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D72" s="111" t="s">
-        <v>194</v>
-      </c>
-      <c r="E72" s="112"/>
-      <c r="F72" s="113"/>
+      <c r="D72" s="112" t="s">
+        <v>193</v>
+      </c>
+      <c r="E72" s="113"/>
+      <c r="F72" s="114"/>
       <c r="G72" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H72" s="63"/>
       <c r="I72" s="64" t="s">
@@ -8519,18 +8582,18 @@
     </row>
     <row r="73" spans="1:14" ht="37.799999999999997">
       <c r="A73" s="11"/>
-      <c r="B73" s="120"/>
+      <c r="B73" s="130"/>
       <c r="C73" s="62" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D73" s="111" t="s">
-        <v>193</v>
-      </c>
-      <c r="E73" s="112"/>
-      <c r="F73" s="113"/>
+      <c r="D73" s="112" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" s="113"/>
+      <c r="F73" s="114"/>
       <c r="G73" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H73" s="63"/>
       <c r="I73" s="64" t="s">
@@ -8546,21 +8609,21 @@
     </row>
     <row r="74" spans="1:14" ht="25.2">
       <c r="A74" s="11"/>
-      <c r="B74" s="118" t="str">
+      <c r="B74" s="128" t="str">
         <f>master!B53</f>
-        <v>バイブコーディング：ハンズオン</v>
+        <v>ハンズオン</v>
       </c>
       <c r="C74" s="62" t="str">
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D74" s="111" t="s">
-        <v>195</v>
-      </c>
-      <c r="E74" s="112"/>
-      <c r="F74" s="113"/>
+      <c r="D74" s="112" t="s">
+        <v>194</v>
+      </c>
+      <c r="E74" s="113"/>
+      <c r="F74" s="114"/>
       <c r="G74" s="62" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="H74" s="63"/>
       <c r="I74" s="64" t="s">
@@ -8576,18 +8639,18 @@
     </row>
     <row r="75" spans="1:14" ht="138.6">
       <c r="A75" s="11"/>
-      <c r="B75" s="119"/>
+      <c r="B75" s="129"/>
       <c r="C75" s="62" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D75" s="111" t="s">
-        <v>196</v>
-      </c>
-      <c r="E75" s="112"/>
-      <c r="F75" s="113"/>
+      <c r="D75" s="112" t="s">
+        <v>195</v>
+      </c>
+      <c r="E75" s="113"/>
+      <c r="F75" s="114"/>
       <c r="G75" s="62" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="H75" s="63"/>
       <c r="I75" s="64" t="s">
@@ -8603,18 +8666,18 @@
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="119"/>
+      <c r="B76" s="129"/>
       <c r="C76" s="81" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D76" s="111" t="s">
-        <v>206</v>
-      </c>
-      <c r="E76" s="112"/>
-      <c r="F76" s="113"/>
+      <c r="D76" s="112" t="s">
+        <v>205</v>
+      </c>
+      <c r="E76" s="113"/>
+      <c r="F76" s="114"/>
       <c r="G76" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H76" s="63"/>
       <c r="I76" s="64" t="s">
@@ -8630,15 +8693,15 @@
     </row>
     <row r="77" spans="1:14" ht="88.2" customHeight="1">
       <c r="A77" s="11"/>
-      <c r="B77" s="119"/>
+      <c r="B77" s="129"/>
       <c r="C77" s="82"/>
-      <c r="D77" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E77" s="112"/>
-      <c r="F77" s="113"/>
+      <c r="D77" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E77" s="113"/>
+      <c r="F77" s="114"/>
       <c r="G77" s="62" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="H77" s="63"/>
       <c r="I77" s="64"/>
@@ -8650,18 +8713,18 @@
     </row>
     <row r="78" spans="1:14" ht="50.4">
       <c r="A78" s="11"/>
-      <c r="B78" s="119"/>
+      <c r="B78" s="129"/>
       <c r="C78" s="81" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D78" s="111" t="s">
-        <v>210</v>
-      </c>
-      <c r="E78" s="112"/>
-      <c r="F78" s="113"/>
+      <c r="D78" s="112" t="s">
+        <v>209</v>
+      </c>
+      <c r="E78" s="113"/>
+      <c r="F78" s="114"/>
       <c r="G78" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H78" s="63"/>
       <c r="I78" s="64" t="s">
@@ -8677,15 +8740,15 @@
     </row>
     <row r="79" spans="1:14" ht="88.2">
       <c r="A79" s="11"/>
-      <c r="B79" s="119"/>
+      <c r="B79" s="129"/>
       <c r="C79" s="82"/>
-      <c r="D79" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E79" s="112"/>
-      <c r="F79" s="113"/>
+      <c r="D79" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E79" s="113"/>
+      <c r="F79" s="114"/>
       <c r="G79" s="62" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="H79" s="63"/>
       <c r="I79" s="64"/>
@@ -8697,18 +8760,18 @@
     </row>
     <row r="80" spans="1:14" ht="50.4">
       <c r="A80" s="11"/>
-      <c r="B80" s="119"/>
+      <c r="B80" s="129"/>
       <c r="C80" s="81" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D80" s="111" t="s">
-        <v>209</v>
-      </c>
-      <c r="E80" s="112"/>
-      <c r="F80" s="113"/>
+      <c r="D80" s="112" t="s">
+        <v>208</v>
+      </c>
+      <c r="E80" s="113"/>
+      <c r="F80" s="114"/>
       <c r="G80" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H80" s="63"/>
       <c r="I80" s="64" t="s">
@@ -8724,15 +8787,15 @@
     </row>
     <row r="81" spans="1:14" ht="88.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="119"/>
+      <c r="B81" s="129"/>
       <c r="C81" s="82"/>
-      <c r="D81" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E81" s="112"/>
-      <c r="F81" s="113"/>
+      <c r="D81" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E81" s="113"/>
+      <c r="F81" s="114"/>
       <c r="G81" s="62" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="H81" s="63"/>
       <c r="I81" s="64"/>
@@ -8744,18 +8807,18 @@
     </row>
     <row r="82" spans="1:14" ht="63">
       <c r="A82" s="11"/>
-      <c r="B82" s="119"/>
+      <c r="B82" s="129"/>
       <c r="C82" s="81" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D82" s="111" t="s">
-        <v>208</v>
-      </c>
-      <c r="E82" s="112"/>
-      <c r="F82" s="113"/>
+      <c r="D82" s="112" t="s">
+        <v>207</v>
+      </c>
+      <c r="E82" s="113"/>
+      <c r="F82" s="114"/>
       <c r="G82" s="62" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="H82" s="63"/>
       <c r="I82" s="64" t="s">
@@ -8771,15 +8834,15 @@
     </row>
     <row r="83" spans="1:14" ht="88.2">
       <c r="A83" s="11"/>
-      <c r="B83" s="119"/>
+      <c r="B83" s="129"/>
       <c r="C83" s="82"/>
-      <c r="D83" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E83" s="112"/>
-      <c r="F83" s="113"/>
+      <c r="D83" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E83" s="113"/>
+      <c r="F83" s="114"/>
       <c r="G83" s="62" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="H83" s="63"/>
       <c r="I83" s="64"/>
@@ -8791,18 +8854,18 @@
     </row>
     <row r="84" spans="1:14" ht="50.4">
       <c r="A84" s="11"/>
-      <c r="B84" s="119"/>
+      <c r="B84" s="129"/>
       <c r="C84" s="62" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D84" s="111" t="s">
-        <v>198</v>
-      </c>
-      <c r="E84" s="112"/>
-      <c r="F84" s="113"/>
+      <c r="D84" s="112" t="s">
+        <v>197</v>
+      </c>
+      <c r="E84" s="113"/>
+      <c r="F84" s="114"/>
       <c r="G84" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H84" s="63"/>
       <c r="I84" s="64" t="s">
@@ -8818,18 +8881,18 @@
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="119"/>
+      <c r="B85" s="129"/>
       <c r="C85" s="62" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D85" s="111" t="s">
-        <v>199</v>
-      </c>
-      <c r="E85" s="112"/>
-      <c r="F85" s="113"/>
+      <c r="D85" s="112" t="s">
+        <v>198</v>
+      </c>
+      <c r="E85" s="113"/>
+      <c r="F85" s="114"/>
       <c r="G85" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H85" s="63"/>
       <c r="I85" s="64" t="s">
@@ -8845,18 +8908,18 @@
     </row>
     <row r="86" spans="1:14" ht="37.799999999999997">
       <c r="A86" s="11"/>
-      <c r="B86" s="119"/>
+      <c r="B86" s="129"/>
       <c r="C86" s="62" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D86" s="111" t="s">
-        <v>200</v>
-      </c>
-      <c r="E86" s="112"/>
-      <c r="F86" s="113"/>
+      <c r="D86" s="112" t="s">
+        <v>199</v>
+      </c>
+      <c r="E86" s="113"/>
+      <c r="F86" s="114"/>
       <c r="G86" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H86" s="63"/>
       <c r="I86" s="64" t="s">
@@ -8872,18 +8935,18 @@
     </row>
     <row r="87" spans="1:14" ht="50.4">
       <c r="A87" s="11"/>
-      <c r="B87" s="119"/>
+      <c r="B87" s="129"/>
       <c r="C87" s="81" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D87" s="111" t="s">
-        <v>207</v>
-      </c>
-      <c r="E87" s="112"/>
-      <c r="F87" s="113"/>
+      <c r="D87" s="112" t="s">
+        <v>206</v>
+      </c>
+      <c r="E87" s="113"/>
+      <c r="F87" s="114"/>
       <c r="G87" s="62" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="H87" s="63"/>
       <c r="I87" s="64" t="s">
@@ -8899,15 +8962,15 @@
     </row>
     <row r="88" spans="1:14" ht="88.2">
       <c r="A88" s="11"/>
-      <c r="B88" s="119"/>
+      <c r="B88" s="129"/>
       <c r="C88" s="82"/>
-      <c r="D88" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E88" s="112"/>
-      <c r="F88" s="113"/>
+      <c r="D88" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E88" s="113"/>
+      <c r="F88" s="114"/>
       <c r="G88" s="62" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="H88" s="63"/>
       <c r="I88" s="64"/>
@@ -8919,18 +8982,18 @@
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="119"/>
+      <c r="B89" s="129"/>
       <c r="C89" s="62" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D89" s="111" t="s">
-        <v>201</v>
-      </c>
-      <c r="E89" s="112"/>
-      <c r="F89" s="113"/>
+      <c r="D89" s="112" t="s">
+        <v>200</v>
+      </c>
+      <c r="E89" s="113"/>
+      <c r="F89" s="114"/>
       <c r="G89" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H89" s="63"/>
       <c r="I89" s="64" t="s">
@@ -8946,18 +9009,18 @@
     </row>
     <row r="90" spans="1:14" ht="37.799999999999997">
       <c r="A90" s="11"/>
-      <c r="B90" s="119"/>
+      <c r="B90" s="129"/>
       <c r="C90" s="62" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D90" s="111" t="s">
-        <v>202</v>
-      </c>
-      <c r="E90" s="112"/>
-      <c r="F90" s="113"/>
+      <c r="D90" s="112" t="s">
+        <v>201</v>
+      </c>
+      <c r="E90" s="113"/>
+      <c r="F90" s="114"/>
       <c r="G90" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H90" s="63"/>
       <c r="I90" s="64" t="s">
@@ -8973,18 +9036,18 @@
     </row>
     <row r="91" spans="1:14" ht="37.799999999999997">
       <c r="A91" s="11"/>
-      <c r="B91" s="119"/>
+      <c r="B91" s="129"/>
       <c r="C91" s="62" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D91" s="111" t="s">
-        <v>203</v>
-      </c>
-      <c r="E91" s="112"/>
-      <c r="F91" s="113"/>
+      <c r="D91" s="112" t="s">
+        <v>202</v>
+      </c>
+      <c r="E91" s="113"/>
+      <c r="F91" s="114"/>
       <c r="G91" s="62" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="H91" s="63"/>
       <c r="I91" s="64" t="s">
@@ -9000,18 +9063,18 @@
     </row>
     <row r="92" spans="1:14" ht="75.599999999999994">
       <c r="A92" s="11"/>
-      <c r="B92" s="119"/>
+      <c r="B92" s="129"/>
       <c r="C92" s="81" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D92" s="111" t="s">
-        <v>204</v>
-      </c>
-      <c r="E92" s="112"/>
-      <c r="F92" s="113"/>
+      <c r="D92" s="112" t="s">
+        <v>203</v>
+      </c>
+      <c r="E92" s="113"/>
+      <c r="F92" s="114"/>
       <c r="G92" s="62" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="H92" s="63"/>
       <c r="I92" s="64" t="s">
@@ -9027,15 +9090,15 @@
     </row>
     <row r="93" spans="1:14" ht="63">
       <c r="A93" s="11"/>
-      <c r="B93" s="120"/>
+      <c r="B93" s="130"/>
       <c r="C93" s="82"/>
-      <c r="D93" s="111" t="s">
-        <v>211</v>
-      </c>
-      <c r="E93" s="112"/>
-      <c r="F93" s="113"/>
+      <c r="D93" s="112" t="s">
+        <v>210</v>
+      </c>
+      <c r="E93" s="113"/>
+      <c r="F93" s="114"/>
       <c r="G93" s="62" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="H93" s="63"/>
       <c r="I93" s="64" t="s">
@@ -9051,7 +9114,7 @@
     </row>
     <row r="94" spans="1:14" ht="100.8">
       <c r="A94" s="11"/>
-      <c r="B94" s="118" t="str">
+      <c r="B94" s="128" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
@@ -9059,13 +9122,13 @@
         <f>master!C69</f>
         <v>Gitとは</v>
       </c>
-      <c r="D94" s="111" t="s">
-        <v>215</v>
-      </c>
-      <c r="E94" s="112"/>
-      <c r="F94" s="113"/>
+      <c r="D94" s="112" t="s">
+        <v>212</v>
+      </c>
+      <c r="E94" s="113"/>
+      <c r="F94" s="114"/>
       <c r="G94" s="62" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="H94" s="63"/>
       <c r="I94" s="64" t="s">
@@ -9081,18 +9144,18 @@
     </row>
     <row r="95" spans="1:14" ht="189">
       <c r="A95" s="11"/>
-      <c r="B95" s="120"/>
+      <c r="B95" s="130"/>
       <c r="C95" s="62" t="str">
         <f>master!C70</f>
         <v>Gitの基本的な流れ</v>
       </c>
-      <c r="D95" s="111" t="s">
-        <v>221</v>
-      </c>
-      <c r="E95" s="112"/>
-      <c r="F95" s="113"/>
+      <c r="D95" s="112" t="s">
+        <v>218</v>
+      </c>
+      <c r="E95" s="113"/>
+      <c r="F95" s="114"/>
       <c r="G95" s="62" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="H95" s="63"/>
       <c r="I95" s="64" t="s">
@@ -9108,7 +9171,7 @@
     </row>
     <row r="96" spans="1:14" ht="126">
       <c r="A96" s="11"/>
-      <c r="B96" s="118" t="str">
+      <c r="B96" s="128" t="str">
         <f>master!B71</f>
         <v>VS Code上でGitを使う手順</v>
       </c>
@@ -9116,13 +9179,13 @@
         <f>master!C71</f>
         <v>VS Code上でGitを使う手順-1 【ユーザ名等の登録】</v>
       </c>
-      <c r="D96" s="111" t="s">
-        <v>216</v>
-      </c>
-      <c r="E96" s="112"/>
-      <c r="F96" s="113"/>
+      <c r="D96" s="112" t="s">
+        <v>213</v>
+      </c>
+      <c r="E96" s="113"/>
+      <c r="F96" s="114"/>
       <c r="G96" s="62" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="H96" s="63"/>
       <c r="I96" s="64" t="s">
@@ -9138,18 +9201,18 @@
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="119"/>
+      <c r="B97" s="129"/>
       <c r="C97" s="62" t="str">
         <f>master!C72</f>
         <v>VS Code上でGitを使う手順-2 【リポジトリの初期化】</v>
       </c>
-      <c r="D97" s="111" t="s">
-        <v>217</v>
-      </c>
-      <c r="E97" s="112"/>
-      <c r="F97" s="113"/>
+      <c r="D97" s="112" t="s">
+        <v>214</v>
+      </c>
+      <c r="E97" s="113"/>
+      <c r="F97" s="114"/>
       <c r="G97" s="62" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H97" s="63"/>
       <c r="I97" s="64" t="s">
@@ -9165,18 +9228,18 @@
     </row>
     <row r="98" spans="1:14" ht="50.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="119"/>
+      <c r="B98" s="129"/>
       <c r="C98" s="62" t="str">
         <f>master!C73</f>
         <v>VS Code上でGitを使う手順-3 【最初のcommit】</v>
       </c>
-      <c r="D98" s="111" t="s">
-        <v>218</v>
-      </c>
-      <c r="E98" s="112"/>
-      <c r="F98" s="113"/>
+      <c r="D98" s="112" t="s">
+        <v>215</v>
+      </c>
+      <c r="E98" s="113"/>
+      <c r="F98" s="114"/>
       <c r="G98" s="62" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H98" s="63"/>
       <c r="I98" s="64" t="s">
@@ -9192,18 +9255,18 @@
     </row>
     <row r="99" spans="1:14" ht="50.4">
       <c r="A99" s="11"/>
-      <c r="B99" s="119"/>
+      <c r="B99" s="129"/>
       <c r="C99" s="62" t="str">
         <f>master!C74</f>
         <v>VS Code上でGitを使う手順-4 【2回目以降のコミット】</v>
       </c>
-      <c r="D99" s="111" t="s">
-        <v>219</v>
-      </c>
-      <c r="E99" s="112"/>
-      <c r="F99" s="113"/>
+      <c r="D99" s="112" t="s">
+        <v>216</v>
+      </c>
+      <c r="E99" s="113"/>
+      <c r="F99" s="114"/>
       <c r="G99" s="62" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="H99" s="63"/>
       <c r="I99" s="64" t="s">
@@ -9219,18 +9282,18 @@
     </row>
     <row r="100" spans="1:14" ht="37.799999999999997">
       <c r="A100" s="11"/>
-      <c r="B100" s="119"/>
+      <c r="B100" s="129"/>
       <c r="C100" s="62" t="str">
         <f>master!C75</f>
         <v>VS Code上でGitを使う手順-5 【過去のcommitの確認】</v>
       </c>
-      <c r="D100" s="111" t="s">
-        <v>220</v>
-      </c>
-      <c r="E100" s="112"/>
-      <c r="F100" s="113"/>
+      <c r="D100" s="112" t="s">
+        <v>217</v>
+      </c>
+      <c r="E100" s="113"/>
+      <c r="F100" s="114"/>
       <c r="G100" s="62" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H100" s="63"/>
       <c r="I100" s="64" t="s">
@@ -9246,18 +9309,18 @@
     </row>
     <row r="101" spans="1:14" ht="63">
       <c r="A101" s="11"/>
-      <c r="B101" s="120"/>
+      <c r="B101" s="130"/>
       <c r="C101" s="62" t="str">
         <f>master!C76</f>
         <v>VS Code上でGitを使う手順-6 【過去の状態に戻す】</v>
       </c>
-      <c r="D101" s="111" t="s">
-        <v>222</v>
-      </c>
-      <c r="E101" s="112"/>
-      <c r="F101" s="113"/>
+      <c r="D101" s="112" t="s">
+        <v>219</v>
+      </c>
+      <c r="E101" s="113"/>
+      <c r="F101" s="114"/>
       <c r="G101" s="62" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H101" s="63"/>
       <c r="I101" s="64" t="s">
@@ -9275,26 +9338,26 @@
       <c r="A102" s="11"/>
       <c r="B102" s="80" t="str">
         <f>master!B67</f>
-        <v>バイブコーディング：演習</v>
+        <v>課題1の実施</v>
       </c>
       <c r="C102" s="62" t="str">
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D102" s="111" t="s">
-        <v>214</v>
-      </c>
-      <c r="E102" s="112"/>
-      <c r="F102" s="113"/>
+      <c r="D102" s="112" t="s">
+        <v>211</v>
+      </c>
+      <c r="E102" s="113"/>
+      <c r="F102" s="114"/>
       <c r="G102" s="62" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="H102" s="63"/>
       <c r="I102" s="64" t="s">
         <v>24</v>
       </c>
       <c r="J102" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K102" s="66"/>
       <c r="L102" s="6"/>
@@ -9305,19 +9368,19 @@
       <c r="A103" s="11"/>
       <c r="B103" s="84" t="str">
         <f>master!B78</f>
-        <v>導入</v>
+        <v>システム開発プロセスの導入</v>
       </c>
       <c r="C103" s="83" t="str">
         <f>master!C78</f>
         <v>講義の目的</v>
       </c>
-      <c r="D103" s="108" t="s">
-        <v>257</v>
-      </c>
-      <c r="E103" s="109"/>
-      <c r="F103" s="110"/>
+      <c r="D103" s="116" t="s">
+        <v>254</v>
+      </c>
+      <c r="E103" s="117"/>
+      <c r="F103" s="118"/>
       <c r="G103" s="51" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="49" t="s">
@@ -9333,7 +9396,7 @@
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="106" t="str">
+      <c r="B104" s="119" t="str">
         <f>master!B79</f>
         <v>システム開発におけるソフトウェア開発ライフサイクル</v>
       </c>
@@ -9341,13 +9404,13 @@
         <f>master!C79</f>
         <v>ソフトウェア開発ライフサイクル</v>
       </c>
-      <c r="D104" s="108" t="s">
-        <v>258</v>
-      </c>
-      <c r="E104" s="109"/>
-      <c r="F104" s="110"/>
+      <c r="D104" s="116" t="s">
+        <v>255</v>
+      </c>
+      <c r="E104" s="117"/>
+      <c r="F104" s="118"/>
       <c r="G104" s="51" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="49" t="s">
@@ -9363,18 +9426,18 @@
     </row>
     <row r="105" spans="1:14" ht="277.2">
       <c r="A105" s="11"/>
-      <c r="B105" s="107"/>
+      <c r="B105" s="120"/>
       <c r="C105" s="83" t="str">
         <f>master!C80</f>
         <v>ソフトウェア開発ライフサイクルの種類</v>
       </c>
-      <c r="D105" s="108" t="s">
-        <v>259</v>
-      </c>
-      <c r="E105" s="109"/>
-      <c r="F105" s="110"/>
+      <c r="D105" s="116" t="s">
+        <v>256</v>
+      </c>
+      <c r="E105" s="117"/>
+      <c r="F105" s="118"/>
       <c r="G105" s="51" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="49" t="s">
@@ -9390,20 +9453,20 @@
     </row>
     <row r="106" spans="1:14" ht="151.19999999999999">
       <c r="A106" s="11"/>
-      <c r="B106" s="106" t="str">
+      <c r="B106" s="119" t="str">
         <f>master!B81</f>
         <v>TERASOLUNAとは</v>
       </c>
       <c r="C106" s="83" t="s">
-        <v>235</v>
-      </c>
-      <c r="D106" s="108" t="s">
-        <v>260</v>
-      </c>
-      <c r="E106" s="109"/>
-      <c r="F106" s="110"/>
+        <v>232</v>
+      </c>
+      <c r="D106" s="116" t="s">
+        <v>257</v>
+      </c>
+      <c r="E106" s="117"/>
+      <c r="F106" s="118"/>
       <c r="G106" s="51" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="49" t="s">
@@ -9419,17 +9482,17 @@
     </row>
     <row r="107" spans="1:14" ht="138.6">
       <c r="A107" s="11"/>
-      <c r="B107" s="107"/>
+      <c r="B107" s="120"/>
       <c r="C107" s="83" t="s">
-        <v>236</v>
-      </c>
-      <c r="D107" s="108" t="s">
-        <v>261</v>
-      </c>
-      <c r="E107" s="109"/>
-      <c r="F107" s="110"/>
+        <v>233</v>
+      </c>
+      <c r="D107" s="116" t="s">
+        <v>258</v>
+      </c>
+      <c r="E107" s="117"/>
+      <c r="F107" s="118"/>
       <c r="G107" s="51" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="49" t="s">
@@ -9445,20 +9508,20 @@
     </row>
     <row r="108" spans="1:14" ht="189">
       <c r="A108" s="11"/>
-      <c r="B108" s="106" t="str">
+      <c r="B108" s="119" t="str">
         <f>master!B83</f>
         <v>V字モデルとは</v>
       </c>
       <c r="C108" s="83" t="s">
-        <v>239</v>
-      </c>
-      <c r="D108" s="108" t="s">
-        <v>262</v>
-      </c>
-      <c r="E108" s="109"/>
-      <c r="F108" s="110"/>
+        <v>236</v>
+      </c>
+      <c r="D108" s="116" t="s">
+        <v>259</v>
+      </c>
+      <c r="E108" s="117"/>
+      <c r="F108" s="118"/>
       <c r="G108" s="51" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="49" t="s">
@@ -9474,17 +9537,17 @@
     </row>
     <row r="109" spans="1:14" ht="100.8">
       <c r="A109" s="11"/>
-      <c r="B109" s="117"/>
+      <c r="B109" s="121"/>
       <c r="C109" s="83" t="s">
-        <v>237</v>
-      </c>
-      <c r="D109" s="108" t="s">
-        <v>263</v>
-      </c>
-      <c r="E109" s="109"/>
-      <c r="F109" s="110"/>
+        <v>234</v>
+      </c>
+      <c r="D109" s="116" t="s">
+        <v>260</v>
+      </c>
+      <c r="E109" s="117"/>
+      <c r="F109" s="118"/>
       <c r="G109" s="51" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="49" t="s">
@@ -9500,17 +9563,17 @@
     </row>
     <row r="110" spans="1:14" ht="113.4">
       <c r="A110" s="11"/>
-      <c r="B110" s="117"/>
+      <c r="B110" s="121"/>
       <c r="C110" s="83" t="s">
-        <v>241</v>
-      </c>
-      <c r="D110" s="108" t="s">
-        <v>264</v>
-      </c>
-      <c r="E110" s="109"/>
-      <c r="F110" s="110"/>
+        <v>238</v>
+      </c>
+      <c r="D110" s="116" t="s">
+        <v>261</v>
+      </c>
+      <c r="E110" s="117"/>
+      <c r="F110" s="118"/>
       <c r="G110" s="51" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="49" t="s">
@@ -9526,17 +9589,17 @@
     </row>
     <row r="111" spans="1:14" ht="302.39999999999998">
       <c r="A111" s="11"/>
-      <c r="B111" s="117"/>
+      <c r="B111" s="121"/>
       <c r="C111" s="83" t="s">
-        <v>243</v>
-      </c>
-      <c r="D111" s="108" t="s">
-        <v>265</v>
-      </c>
-      <c r="E111" s="109"/>
-      <c r="F111" s="110"/>
+        <v>240</v>
+      </c>
+      <c r="D111" s="116" t="s">
+        <v>262</v>
+      </c>
+      <c r="E111" s="117"/>
+      <c r="F111" s="118"/>
       <c r="G111" s="51" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="49" t="s">
@@ -9552,17 +9615,17 @@
     </row>
     <row r="112" spans="1:14" ht="138.6">
       <c r="A112" s="11"/>
-      <c r="B112" s="117"/>
+      <c r="B112" s="121"/>
       <c r="C112" s="83" t="s">
-        <v>245</v>
-      </c>
-      <c r="D112" s="108" t="s">
-        <v>266</v>
-      </c>
-      <c r="E112" s="109"/>
-      <c r="F112" s="110"/>
+        <v>242</v>
+      </c>
+      <c r="D112" s="116" t="s">
+        <v>263</v>
+      </c>
+      <c r="E112" s="117"/>
+      <c r="F112" s="118"/>
       <c r="G112" s="51" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="49" t="s">
@@ -9578,17 +9641,17 @@
     </row>
     <row r="113" spans="1:14" ht="88.2">
       <c r="A113" s="11"/>
-      <c r="B113" s="117"/>
+      <c r="B113" s="121"/>
       <c r="C113" s="83" t="s">
-        <v>247</v>
-      </c>
-      <c r="D113" s="108" t="s">
-        <v>267</v>
-      </c>
-      <c r="E113" s="109"/>
-      <c r="F113" s="110"/>
+        <v>244</v>
+      </c>
+      <c r="D113" s="116" t="s">
+        <v>264</v>
+      </c>
+      <c r="E113" s="117"/>
+      <c r="F113" s="118"/>
       <c r="G113" s="51" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="49" t="s">
@@ -9604,17 +9667,17 @@
     </row>
     <row r="114" spans="1:14" ht="75.599999999999994">
       <c r="A114" s="11"/>
-      <c r="B114" s="117"/>
+      <c r="B114" s="121"/>
       <c r="C114" s="83" t="s">
-        <v>249</v>
-      </c>
-      <c r="D114" s="108" t="s">
-        <v>268</v>
-      </c>
-      <c r="E114" s="109"/>
-      <c r="F114" s="110"/>
+        <v>246</v>
+      </c>
+      <c r="D114" s="116" t="s">
+        <v>265</v>
+      </c>
+      <c r="E114" s="117"/>
+      <c r="F114" s="118"/>
       <c r="G114" s="51" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="49" t="s">
@@ -9630,17 +9693,17 @@
     </row>
     <row r="115" spans="1:14" ht="113.4">
       <c r="A115" s="11"/>
-      <c r="B115" s="117"/>
+      <c r="B115" s="121"/>
       <c r="C115" s="83" t="s">
-        <v>251</v>
-      </c>
-      <c r="D115" s="108" t="s">
-        <v>269</v>
-      </c>
-      <c r="E115" s="109"/>
-      <c r="F115" s="110"/>
+        <v>248</v>
+      </c>
+      <c r="D115" s="116" t="s">
+        <v>266</v>
+      </c>
+      <c r="E115" s="117"/>
+      <c r="F115" s="118"/>
       <c r="G115" s="51" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="49" t="s">
@@ -9656,17 +9719,17 @@
     </row>
     <row r="116" spans="1:14" ht="126">
       <c r="A116" s="11"/>
-      <c r="B116" s="117"/>
+      <c r="B116" s="121"/>
       <c r="C116" s="83" t="s">
-        <v>270</v>
-      </c>
-      <c r="D116" s="108" t="s">
-        <v>271</v>
-      </c>
-      <c r="E116" s="109"/>
-      <c r="F116" s="110"/>
+        <v>267</v>
+      </c>
+      <c r="D116" s="116" t="s">
+        <v>268</v>
+      </c>
+      <c r="E116" s="117"/>
+      <c r="F116" s="118"/>
       <c r="G116" s="51" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="49" t="s">
@@ -9682,17 +9745,17 @@
     </row>
     <row r="117" spans="1:14" ht="88.2">
       <c r="A117" s="11"/>
-      <c r="B117" s="117"/>
+      <c r="B117" s="121"/>
       <c r="C117" s="83" t="s">
-        <v>254</v>
-      </c>
-      <c r="D117" s="108" t="s">
-        <v>272</v>
-      </c>
-      <c r="E117" s="109"/>
-      <c r="F117" s="110"/>
+        <v>251</v>
+      </c>
+      <c r="D117" s="116" t="s">
+        <v>269</v>
+      </c>
+      <c r="E117" s="117"/>
+      <c r="F117" s="118"/>
       <c r="G117" s="51" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="H117" s="12"/>
       <c r="I117" s="49" t="s">
@@ -9708,17 +9771,17 @@
     </row>
     <row r="118" spans="1:14" ht="138.6">
       <c r="A118" s="11"/>
-      <c r="B118" s="117"/>
+      <c r="B118" s="121"/>
       <c r="C118" s="83" t="s">
-        <v>255</v>
-      </c>
-      <c r="D118" s="108" t="s">
-        <v>273</v>
-      </c>
-      <c r="E118" s="109"/>
-      <c r="F118" s="110"/>
+        <v>252</v>
+      </c>
+      <c r="D118" s="116" t="s">
+        <v>270</v>
+      </c>
+      <c r="E118" s="117"/>
+      <c r="F118" s="118"/>
       <c r="G118" s="51" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="H118" s="12"/>
       <c r="I118" s="49" t="s">
@@ -9734,15 +9797,15 @@
     </row>
     <row r="119" spans="1:14" ht="24" customHeight="1">
       <c r="A119" s="11"/>
-      <c r="B119" s="107"/>
+      <c r="B119" s="120"/>
       <c r="C119" s="83" t="s">
-        <v>256</v>
-      </c>
-      <c r="D119" s="108"/>
-      <c r="E119" s="109"/>
-      <c r="F119" s="110"/>
+        <v>253</v>
+      </c>
+      <c r="D119" s="116"/>
+      <c r="E119" s="117"/>
+      <c r="F119" s="118"/>
       <c r="G119" s="51" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="49" t="s">
@@ -9760,17 +9823,17 @@
       <c r="A120" s="11"/>
       <c r="B120" s="62" t="str">
         <f>master!B67</f>
-        <v>バイブコーディング：演習</v>
+        <v>課題1の実施</v>
       </c>
       <c r="C120" s="62" t="str">
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D120" s="111" t="s">
-        <v>326</v>
-      </c>
-      <c r="E120" s="112"/>
-      <c r="F120" s="113"/>
+      <c r="D120" s="112" t="s">
+        <v>323</v>
+      </c>
+      <c r="E120" s="113"/>
+      <c r="F120" s="114"/>
       <c r="G120" s="62" t="s">
         <v>45</v>
       </c>
@@ -9779,7 +9842,7 @@
         <v>24</v>
       </c>
       <c r="J120" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K120" s="66"/>
       <c r="L120" s="6"/>
@@ -9788,21 +9851,21 @@
     </row>
     <row r="121" spans="1:14" ht="50.4">
       <c r="A121" s="11"/>
-      <c r="B121" s="106" t="str">
+      <c r="B121" s="119" t="str">
         <f>master!B96</f>
-        <v>導入</v>
+        <v>単体テストとJunitの導入</v>
       </c>
       <c r="C121" s="83" t="str">
         <f>master!C96</f>
         <v>講義の目的</v>
       </c>
-      <c r="D121" s="108" t="s">
-        <v>302</v>
-      </c>
-      <c r="E121" s="109"/>
-      <c r="F121" s="110"/>
+      <c r="D121" s="116" t="s">
+        <v>299</v>
+      </c>
+      <c r="E121" s="117"/>
+      <c r="F121" s="118"/>
       <c r="G121" s="51" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="49" t="s">
@@ -9818,16 +9881,16 @@
     </row>
     <row r="122" spans="1:14" ht="25.2">
       <c r="A122" s="11"/>
-      <c r="B122" s="117"/>
+      <c r="B122" s="121"/>
       <c r="C122" s="83" t="str">
         <f>master!C97</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
       </c>
-      <c r="D122" s="108"/>
-      <c r="E122" s="109"/>
-      <c r="F122" s="110"/>
+      <c r="D122" s="116"/>
+      <c r="E122" s="117"/>
+      <c r="F122" s="118"/>
       <c r="G122" s="51" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H122" s="12"/>
       <c r="I122" s="49" t="s">
@@ -9843,18 +9906,18 @@
     </row>
     <row r="123" spans="1:14" ht="25.2">
       <c r="A123" s="11"/>
-      <c r="B123" s="107"/>
+      <c r="B123" s="120"/>
       <c r="C123" s="83" t="str">
         <f>master!C98</f>
         <v>V字モデル　 ※再掲</v>
       </c>
-      <c r="D123" s="108" t="s">
-        <v>303</v>
-      </c>
-      <c r="E123" s="109"/>
-      <c r="F123" s="110"/>
+      <c r="D123" s="116" t="s">
+        <v>300</v>
+      </c>
+      <c r="E123" s="117"/>
+      <c r="F123" s="118"/>
       <c r="G123" s="51" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="49" t="s">
@@ -9870,7 +9933,7 @@
     </row>
     <row r="124" spans="1:14" ht="50.4">
       <c r="A124" s="11"/>
-      <c r="B124" s="106" t="str">
+      <c r="B124" s="119" t="str">
         <f>master!B99</f>
         <v>テストとは</v>
       </c>
@@ -9878,13 +9941,13 @@
         <f>master!C99</f>
         <v>テストとは</v>
       </c>
-      <c r="D124" s="108" t="s">
-        <v>304</v>
-      </c>
-      <c r="E124" s="109"/>
-      <c r="F124" s="110"/>
+      <c r="D124" s="116" t="s">
+        <v>301</v>
+      </c>
+      <c r="E124" s="117"/>
+      <c r="F124" s="118"/>
       <c r="G124" s="51" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H124" s="12"/>
       <c r="I124" s="49" t="s">
@@ -9900,18 +9963,18 @@
     </row>
     <row r="125" spans="1:14" ht="315">
       <c r="A125" s="11"/>
-      <c r="B125" s="117"/>
+      <c r="B125" s="121"/>
       <c r="C125" s="83" t="str">
         <f>master!C100</f>
         <v>テストの目的</v>
       </c>
-      <c r="D125" s="108" t="s">
-        <v>305</v>
-      </c>
-      <c r="E125" s="109"/>
-      <c r="F125" s="110"/>
+      <c r="D125" s="116" t="s">
+        <v>302</v>
+      </c>
+      <c r="E125" s="117"/>
+      <c r="F125" s="118"/>
       <c r="G125" s="51" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="H125" s="12"/>
       <c r="I125" s="49" t="s">
@@ -9927,18 +9990,18 @@
     </row>
     <row r="126" spans="1:14" ht="25.2">
       <c r="A126" s="11"/>
-      <c r="B126" s="117"/>
+      <c r="B126" s="121"/>
       <c r="C126" s="83" t="str">
         <f>master!C101</f>
         <v>テストを実施しなかった場合…</v>
       </c>
-      <c r="D126" s="108" t="s">
-        <v>306</v>
-      </c>
-      <c r="E126" s="109"/>
-      <c r="F126" s="110"/>
+      <c r="D126" s="116" t="s">
+        <v>303</v>
+      </c>
+      <c r="E126" s="117"/>
+      <c r="F126" s="118"/>
       <c r="G126" s="51" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H126" s="12"/>
       <c r="I126" s="49" t="s">
@@ -9954,18 +10017,18 @@
     </row>
     <row r="127" spans="1:14" ht="100.8">
       <c r="A127" s="11"/>
-      <c r="B127" s="107"/>
+      <c r="B127" s="120"/>
       <c r="C127" s="83" t="str">
         <f>master!C102</f>
         <v>コラム：テストとデバッグ</v>
       </c>
-      <c r="D127" s="108" t="s">
-        <v>307</v>
-      </c>
-      <c r="E127" s="109"/>
-      <c r="F127" s="110"/>
+      <c r="D127" s="116" t="s">
+        <v>304</v>
+      </c>
+      <c r="E127" s="117"/>
+      <c r="F127" s="118"/>
       <c r="G127" s="51" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="H127" s="12"/>
       <c r="I127" s="49" t="s">
@@ -9981,7 +10044,7 @@
     </row>
     <row r="128" spans="1:14" ht="50.4">
       <c r="A128" s="11"/>
-      <c r="B128" s="106" t="str">
+      <c r="B128" s="119" t="str">
         <f>master!B103</f>
         <v>単体テストとは</v>
       </c>
@@ -9989,13 +10052,13 @@
         <f>master!C103</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D128" s="108" t="s">
-        <v>308</v>
-      </c>
-      <c r="E128" s="109"/>
-      <c r="F128" s="110"/>
+      <c r="D128" s="116" t="s">
+        <v>305</v>
+      </c>
+      <c r="E128" s="117"/>
+      <c r="F128" s="118"/>
       <c r="G128" s="51" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="H128" s="12"/>
       <c r="I128" s="49" t="s">
@@ -10011,16 +10074,16 @@
     </row>
     <row r="129" spans="1:14" ht="25.2">
       <c r="A129" s="11"/>
-      <c r="B129" s="117"/>
+      <c r="B129" s="121"/>
       <c r="C129" s="83" t="str">
         <f>master!C104</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
       </c>
-      <c r="D129" s="108"/>
-      <c r="E129" s="109"/>
-      <c r="F129" s="110"/>
+      <c r="D129" s="116"/>
+      <c r="E129" s="117"/>
+      <c r="F129" s="118"/>
       <c r="G129" s="51" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H129" s="12"/>
       <c r="I129" s="49" t="s">
@@ -10036,18 +10099,18 @@
     </row>
     <row r="130" spans="1:14" ht="302.39999999999998">
       <c r="A130" s="11"/>
-      <c r="B130" s="117"/>
+      <c r="B130" s="121"/>
       <c r="C130" s="83" t="str">
         <f>master!C105</f>
         <v>テスト設計の流れ</v>
       </c>
-      <c r="D130" s="108" t="s">
-        <v>309</v>
-      </c>
-      <c r="E130" s="109"/>
-      <c r="F130" s="110"/>
+      <c r="D130" s="116" t="s">
+        <v>306</v>
+      </c>
+      <c r="E130" s="117"/>
+      <c r="F130" s="118"/>
       <c r="G130" s="51" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="H130" s="12"/>
       <c r="I130" s="49" t="s">
@@ -10063,18 +10126,18 @@
     </row>
     <row r="131" spans="1:14" ht="37.799999999999997">
       <c r="A131" s="11"/>
-      <c r="B131" s="117"/>
+      <c r="B131" s="121"/>
       <c r="C131" s="83" t="str">
         <f>master!C106</f>
         <v>テスト設計の例</v>
       </c>
-      <c r="D131" s="108" t="s">
-        <v>310</v>
-      </c>
-      <c r="E131" s="109"/>
-      <c r="F131" s="110"/>
+      <c r="D131" s="116" t="s">
+        <v>307</v>
+      </c>
+      <c r="E131" s="117"/>
+      <c r="F131" s="118"/>
       <c r="G131" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H131" s="12"/>
       <c r="I131" s="49" t="s">
@@ -10090,18 +10153,18 @@
     </row>
     <row r="132" spans="1:14" ht="75.599999999999994">
       <c r="A132" s="11"/>
-      <c r="B132" s="117"/>
+      <c r="B132" s="121"/>
       <c r="C132" s="83" t="str">
         <f>master!C107</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D132" s="108" t="s">
-        <v>311</v>
-      </c>
-      <c r="E132" s="109"/>
-      <c r="F132" s="110"/>
+      <c r="D132" s="116" t="s">
+        <v>308</v>
+      </c>
+      <c r="E132" s="117"/>
+      <c r="F132" s="118"/>
       <c r="G132" s="51" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H132" s="12"/>
       <c r="I132" s="49" t="s">
@@ -10117,18 +10180,18 @@
     </row>
     <row r="133" spans="1:14" ht="113.4">
       <c r="A133" s="11"/>
-      <c r="B133" s="117"/>
+      <c r="B133" s="121"/>
       <c r="C133" s="83" t="str">
         <f>master!C108</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
       </c>
-      <c r="D133" s="108" t="s">
-        <v>312</v>
-      </c>
-      <c r="E133" s="109"/>
-      <c r="F133" s="110"/>
+      <c r="D133" s="116" t="s">
+        <v>309</v>
+      </c>
+      <c r="E133" s="117"/>
+      <c r="F133" s="118"/>
       <c r="G133" s="51" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H133" s="12"/>
       <c r="I133" s="49" t="s">
@@ -10144,18 +10207,18 @@
     </row>
     <row r="134" spans="1:14" ht="201.6">
       <c r="A134" s="11"/>
-      <c r="B134" s="117"/>
+      <c r="B134" s="121"/>
       <c r="C134" s="83" t="str">
         <f>master!C109</f>
         <v>ブラックボックステスト：同値分割法</v>
       </c>
-      <c r="D134" s="108" t="s">
-        <v>315</v>
-      </c>
-      <c r="E134" s="109"/>
-      <c r="F134" s="110"/>
+      <c r="D134" s="116" t="s">
+        <v>312</v>
+      </c>
+      <c r="E134" s="117"/>
+      <c r="F134" s="118"/>
       <c r="G134" s="51" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="H134" s="12"/>
       <c r="I134" s="49" t="s">
@@ -10171,18 +10234,18 @@
     </row>
     <row r="135" spans="1:14" ht="113.4">
       <c r="A135" s="11"/>
-      <c r="B135" s="117"/>
+      <c r="B135" s="121"/>
       <c r="C135" s="83" t="str">
         <f>master!C110</f>
         <v>ブラックボックステスト：境界値分析</v>
       </c>
-      <c r="D135" s="108" t="s">
-        <v>314</v>
-      </c>
-      <c r="E135" s="109"/>
-      <c r="F135" s="110"/>
+      <c r="D135" s="116" t="s">
+        <v>311</v>
+      </c>
+      <c r="E135" s="117"/>
+      <c r="F135" s="118"/>
       <c r="G135" s="51" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="H135" s="12"/>
       <c r="I135" s="49" t="s">
@@ -10198,18 +10261,18 @@
     </row>
     <row r="136" spans="1:14" ht="176.4">
       <c r="A136" s="11"/>
-      <c r="B136" s="117"/>
+      <c r="B136" s="121"/>
       <c r="C136" s="83" t="str">
         <f>master!C111</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
       </c>
-      <c r="D136" s="108" t="s">
-        <v>313</v>
-      </c>
-      <c r="E136" s="109"/>
-      <c r="F136" s="110"/>
+      <c r="D136" s="116" t="s">
+        <v>310</v>
+      </c>
+      <c r="E136" s="117"/>
+      <c r="F136" s="118"/>
       <c r="G136" s="51" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="H136" s="12"/>
       <c r="I136" s="49" t="s">
@@ -10225,18 +10288,18 @@
     </row>
     <row r="137" spans="1:14" ht="37.799999999999997">
       <c r="A137" s="11"/>
-      <c r="B137" s="117"/>
+      <c r="B137" s="121"/>
       <c r="C137" s="83" t="str">
         <f>master!C112</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
       </c>
-      <c r="D137" s="108" t="s">
-        <v>316</v>
-      </c>
-      <c r="E137" s="109"/>
-      <c r="F137" s="110"/>
+      <c r="D137" s="116" t="s">
+        <v>313</v>
+      </c>
+      <c r="E137" s="117"/>
+      <c r="F137" s="118"/>
       <c r="G137" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H137" s="12"/>
       <c r="I137" s="49" t="s">
@@ -10252,18 +10315,18 @@
     </row>
     <row r="138" spans="1:14" ht="88.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="117"/>
+      <c r="B138" s="121"/>
       <c r="C138" s="83" t="str">
         <f>master!C113</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
       </c>
-      <c r="D138" s="108" t="s">
-        <v>317</v>
-      </c>
-      <c r="E138" s="109"/>
-      <c r="F138" s="110"/>
+      <c r="D138" s="116" t="s">
+        <v>314</v>
+      </c>
+      <c r="E138" s="117"/>
+      <c r="F138" s="118"/>
       <c r="G138" s="51" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="H138" s="12"/>
       <c r="I138" s="49" t="s">
@@ -10279,18 +10342,18 @@
     </row>
     <row r="139" spans="1:14" ht="151.19999999999999">
       <c r="A139" s="11"/>
-      <c r="B139" s="117"/>
+      <c r="B139" s="121"/>
       <c r="C139" s="83" t="str">
         <f>master!C114</f>
         <v>ホワイトボックステストの評価基準</v>
       </c>
-      <c r="D139" s="108" t="s">
-        <v>318</v>
-      </c>
-      <c r="E139" s="109"/>
-      <c r="F139" s="110"/>
+      <c r="D139" s="116" t="s">
+        <v>315</v>
+      </c>
+      <c r="E139" s="117"/>
+      <c r="F139" s="118"/>
       <c r="G139" s="51" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="H139" s="12"/>
       <c r="I139" s="49" t="s">
@@ -10306,18 +10369,18 @@
     </row>
     <row r="140" spans="1:14" ht="37.799999999999997">
       <c r="A140" s="11"/>
-      <c r="B140" s="117"/>
+      <c r="B140" s="121"/>
       <c r="C140" s="83" t="str">
         <f>master!C115</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
       </c>
-      <c r="D140" s="108" t="s">
-        <v>319</v>
-      </c>
-      <c r="E140" s="109"/>
-      <c r="F140" s="110"/>
+      <c r="D140" s="116" t="s">
+        <v>316</v>
+      </c>
+      <c r="E140" s="117"/>
+      <c r="F140" s="118"/>
       <c r="G140" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H140" s="12"/>
       <c r="I140" s="49" t="s">
@@ -10333,18 +10396,18 @@
     </row>
     <row r="141" spans="1:14" ht="37.799999999999997">
       <c r="A141" s="11"/>
-      <c r="B141" s="117"/>
+      <c r="B141" s="121"/>
       <c r="C141" s="83" t="str">
         <f>master!C116</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
       </c>
-      <c r="D141" s="108" t="s">
-        <v>320</v>
-      </c>
-      <c r="E141" s="109"/>
-      <c r="F141" s="110"/>
+      <c r="D141" s="116" t="s">
+        <v>317</v>
+      </c>
+      <c r="E141" s="117"/>
+      <c r="F141" s="118"/>
       <c r="G141" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H141" s="12"/>
       <c r="I141" s="49" t="s">
@@ -10360,18 +10423,18 @@
     </row>
     <row r="142" spans="1:14" ht="37.799999999999997">
       <c r="A142" s="11"/>
-      <c r="B142" s="117"/>
+      <c r="B142" s="121"/>
       <c r="C142" s="83" t="str">
         <f>master!C117</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
       </c>
-      <c r="D142" s="108" t="s">
-        <v>321</v>
-      </c>
-      <c r="E142" s="109"/>
-      <c r="F142" s="110"/>
+      <c r="D142" s="116" t="s">
+        <v>318</v>
+      </c>
+      <c r="E142" s="117"/>
+      <c r="F142" s="118"/>
       <c r="G142" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H142" s="12"/>
       <c r="I142" s="49" t="s">
@@ -10387,18 +10450,18 @@
     </row>
     <row r="143" spans="1:14" ht="37.799999999999997">
       <c r="A143" s="11"/>
-      <c r="B143" s="117"/>
+      <c r="B143" s="121"/>
       <c r="C143" s="83" t="str">
         <f>master!C118</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
       </c>
-      <c r="D143" s="108" t="s">
-        <v>322</v>
-      </c>
-      <c r="E143" s="109"/>
-      <c r="F143" s="110"/>
+      <c r="D143" s="116" t="s">
+        <v>319</v>
+      </c>
+      <c r="E143" s="117"/>
+      <c r="F143" s="118"/>
       <c r="G143" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H143" s="12"/>
       <c r="I143" s="49" t="s">
@@ -10414,18 +10477,18 @@
     </row>
     <row r="144" spans="1:14" ht="100.8">
       <c r="A144" s="11"/>
-      <c r="B144" s="117"/>
+      <c r="B144" s="121"/>
       <c r="C144" s="83" t="str">
         <f>master!C119</f>
         <v>スタブとドライバ</v>
       </c>
-      <c r="D144" s="108" t="s">
-        <v>323</v>
-      </c>
-      <c r="E144" s="109"/>
-      <c r="F144" s="110"/>
+      <c r="D144" s="116" t="s">
+        <v>320</v>
+      </c>
+      <c r="E144" s="117"/>
+      <c r="F144" s="118"/>
       <c r="G144" s="51" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="H144" s="12"/>
       <c r="I144" s="49" t="s">
@@ -10441,18 +10504,18 @@
     </row>
     <row r="145" spans="1:14" ht="75.599999999999994">
       <c r="A145" s="11"/>
-      <c r="B145" s="107"/>
+      <c r="B145" s="120"/>
       <c r="C145" s="83" t="str">
         <f>master!C120</f>
         <v>スタブとモック</v>
       </c>
-      <c r="D145" s="108" t="s">
-        <v>324</v>
-      </c>
-      <c r="E145" s="109"/>
-      <c r="F145" s="110"/>
+      <c r="D145" s="116" t="s">
+        <v>321</v>
+      </c>
+      <c r="E145" s="117"/>
+      <c r="F145" s="118"/>
       <c r="G145" s="51" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="H145" s="12"/>
       <c r="I145" s="49" t="s">
@@ -10468,7 +10531,7 @@
     </row>
     <row r="146" spans="1:14" ht="37.799999999999997">
       <c r="A146" s="11"/>
-      <c r="B146" s="106" t="str">
+      <c r="B146" s="119" t="str">
         <f>master!B121</f>
         <v>JUnit</v>
       </c>
@@ -10476,13 +10539,13 @@
         <f>master!C121</f>
         <v>JUnitとは</v>
       </c>
-      <c r="D146" s="108" t="s">
-        <v>325</v>
-      </c>
-      <c r="E146" s="109"/>
-      <c r="F146" s="110"/>
+      <c r="D146" s="116" t="s">
+        <v>322</v>
+      </c>
+      <c r="E146" s="117"/>
+      <c r="F146" s="118"/>
       <c r="G146" s="51" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="H146" s="12"/>
       <c r="I146" s="49" t="s">
@@ -10498,16 +10561,16 @@
     </row>
     <row r="147" spans="1:14" ht="25.2">
       <c r="A147" s="11"/>
-      <c r="B147" s="107"/>
+      <c r="B147" s="120"/>
       <c r="C147" s="83" t="str">
         <f>master!C122</f>
         <v>参考文献</v>
       </c>
-      <c r="D147" s="108"/>
-      <c r="E147" s="109"/>
-      <c r="F147" s="110"/>
+      <c r="D147" s="116"/>
+      <c r="E147" s="117"/>
+      <c r="F147" s="118"/>
       <c r="G147" s="51" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="H147" s="12"/>
       <c r="I147" s="49" t="s">
@@ -10525,17 +10588,17 @@
       <c r="A148" s="11"/>
       <c r="B148" s="62" t="str">
         <f>master!B67</f>
-        <v>バイブコーディング：演習</v>
+        <v>課題1の実施</v>
       </c>
       <c r="C148" s="62" t="str">
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D148" s="111" t="s">
-        <v>326</v>
-      </c>
-      <c r="E148" s="112"/>
-      <c r="F148" s="113"/>
+      <c r="D148" s="112" t="s">
+        <v>323</v>
+      </c>
+      <c r="E148" s="113"/>
+      <c r="F148" s="114"/>
       <c r="G148" s="62" t="s">
         <v>45</v>
       </c>
@@ -10544,7 +10607,7 @@
         <v>24</v>
       </c>
       <c r="J148" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K148" s="66"/>
       <c r="L148" s="6"/>
@@ -10553,21 +10616,21 @@
     </row>
     <row r="149" spans="1:14" ht="25.2">
       <c r="A149" s="11"/>
-      <c r="B149" s="114" t="str">
+      <c r="B149" s="110" t="str">
         <f>master!B124</f>
-        <v>導入</v>
+        <v>課題2の導入</v>
       </c>
       <c r="C149" s="62" t="str">
         <f>master!C124</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D149" s="111" t="s">
-        <v>344</v>
-      </c>
-      <c r="E149" s="112"/>
-      <c r="F149" s="113"/>
+      <c r="D149" s="112" t="s">
+        <v>339</v>
+      </c>
+      <c r="E149" s="113"/>
+      <c r="F149" s="114"/>
       <c r="G149" s="62" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H149" s="63"/>
       <c r="I149" s="64" t="s">
@@ -10588,13 +10651,13 @@
         <f>master!C125</f>
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
-      <c r="D150" s="111" t="s">
-        <v>345</v>
-      </c>
-      <c r="E150" s="112"/>
-      <c r="F150" s="113"/>
+      <c r="D150" s="112" t="s">
+        <v>340</v>
+      </c>
+      <c r="E150" s="113"/>
+      <c r="F150" s="114"/>
       <c r="G150" s="62" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H150" s="63"/>
       <c r="I150" s="64" t="s">
@@ -10615,13 +10678,13 @@
         <f>master!C126</f>
         <v>テストクラスを作成する単位</v>
       </c>
-      <c r="D151" s="111" t="s">
-        <v>346</v>
-      </c>
-      <c r="E151" s="112"/>
-      <c r="F151" s="113"/>
+      <c r="D151" s="112" t="s">
+        <v>341</v>
+      </c>
+      <c r="E151" s="113"/>
+      <c r="F151" s="114"/>
       <c r="G151" s="62" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H151" s="63"/>
       <c r="I151" s="64" t="s">
@@ -10637,18 +10700,18 @@
     </row>
     <row r="152" spans="1:14" ht="113.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="116"/>
+      <c r="B152" s="111"/>
       <c r="C152" s="62" t="str">
         <f>master!C127</f>
         <v>JUnitで単体テスト</v>
       </c>
-      <c r="D152" s="111" t="s">
-        <v>347</v>
-      </c>
-      <c r="E152" s="112"/>
-      <c r="F152" s="113"/>
+      <c r="D152" s="112" t="s">
+        <v>342</v>
+      </c>
+      <c r="E152" s="113"/>
+      <c r="F152" s="114"/>
       <c r="G152" s="62" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="H152" s="63"/>
       <c r="I152" s="64" t="s">
@@ -10664,21 +10727,21 @@
     </row>
     <row r="153" spans="1:14" ht="25.2">
       <c r="A153" s="11"/>
-      <c r="B153" s="114" t="str">
+      <c r="B153" s="110" t="str">
         <f>master!B128</f>
-        <v>バイブコーディングで単体テスト(JUnit)</v>
+        <v>ハンズオン</v>
       </c>
       <c r="C153" s="62" t="str">
         <f>master!C128</f>
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
-      <c r="D153" s="111" t="s">
-        <v>348</v>
-      </c>
-      <c r="E153" s="112"/>
-      <c r="F153" s="113"/>
+      <c r="D153" s="112" t="s">
+        <v>343</v>
+      </c>
+      <c r="E153" s="113"/>
+      <c r="F153" s="114"/>
       <c r="G153" s="62" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H153" s="63"/>
       <c r="I153" s="64" t="s">
@@ -10699,13 +10762,13 @@
         <f>master!C129</f>
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
-      <c r="D154" s="111" t="s">
-        <v>349</v>
-      </c>
-      <c r="E154" s="112"/>
-      <c r="F154" s="113"/>
+      <c r="D154" s="112" t="s">
+        <v>344</v>
+      </c>
+      <c r="E154" s="113"/>
+      <c r="F154" s="114"/>
       <c r="G154" s="62" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H154" s="63"/>
       <c r="I154" s="64" t="s">
@@ -10723,13 +10786,13 @@
       <c r="A155" s="11"/>
       <c r="B155" s="115"/>
       <c r="C155" s="62"/>
-      <c r="D155" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E155" s="112"/>
-      <c r="F155" s="113"/>
+      <c r="D155" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E155" s="113"/>
+      <c r="F155" s="114"/>
       <c r="G155" s="62" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H155" s="63"/>
       <c r="I155" s="64" t="s">
@@ -10750,13 +10813,13 @@
         <f>master!C130</f>
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
-      <c r="D156" s="111" t="s">
-        <v>350</v>
-      </c>
-      <c r="E156" s="112"/>
-      <c r="F156" s="113"/>
+      <c r="D156" s="112" t="s">
+        <v>345</v>
+      </c>
+      <c r="E156" s="113"/>
+      <c r="F156" s="114"/>
       <c r="G156" s="62" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H156" s="63"/>
       <c r="I156" s="64" t="s">
@@ -10774,13 +10837,13 @@
       <c r="A157" s="11"/>
       <c r="B157" s="115"/>
       <c r="C157" s="82"/>
-      <c r="D157" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E157" s="112"/>
-      <c r="F157" s="113"/>
+      <c r="D157" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E157" s="113"/>
+      <c r="F157" s="114"/>
       <c r="G157" s="62" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H157" s="63"/>
       <c r="I157" s="64" t="s">
@@ -10801,13 +10864,13 @@
         <f>master!C131</f>
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
-      <c r="D158" s="111" t="s">
-        <v>352</v>
-      </c>
-      <c r="E158" s="112"/>
-      <c r="F158" s="113"/>
+      <c r="D158" s="112" t="s">
+        <v>347</v>
+      </c>
+      <c r="E158" s="113"/>
+      <c r="F158" s="114"/>
       <c r="G158" s="62" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H158" s="63"/>
       <c r="I158" s="64" t="s">
@@ -10828,13 +10891,13 @@
         <f>master!C132</f>
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
-      <c r="D159" s="111" t="s">
-        <v>350</v>
-      </c>
-      <c r="E159" s="112"/>
-      <c r="F159" s="113"/>
+      <c r="D159" s="112" t="s">
+        <v>345</v>
+      </c>
+      <c r="E159" s="113"/>
+      <c r="F159" s="114"/>
       <c r="G159" s="62" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H159" s="63"/>
       <c r="I159" s="64" t="s">
@@ -10852,13 +10915,13 @@
       <c r="A160" s="11"/>
       <c r="B160" s="115"/>
       <c r="C160" s="82"/>
-      <c r="D160" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E160" s="112"/>
-      <c r="F160" s="113"/>
+      <c r="D160" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E160" s="113"/>
+      <c r="F160" s="114"/>
       <c r="G160" s="62" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H160" s="63"/>
       <c r="I160" s="64" t="s">
@@ -10879,13 +10942,13 @@
         <f>master!C133</f>
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
-      <c r="D161" s="111" t="s">
-        <v>351</v>
-      </c>
-      <c r="E161" s="112"/>
-      <c r="F161" s="113"/>
+      <c r="D161" s="112" t="s">
+        <v>346</v>
+      </c>
+      <c r="E161" s="113"/>
+      <c r="F161" s="114"/>
       <c r="G161" s="62" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="H161" s="63"/>
       <c r="I161" s="64" t="s">
@@ -10906,13 +10969,13 @@
         <f>master!C134</f>
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
-      <c r="D162" s="111" t="s">
-        <v>350</v>
-      </c>
-      <c r="E162" s="112"/>
-      <c r="F162" s="113"/>
+      <c r="D162" s="112" t="s">
+        <v>345</v>
+      </c>
+      <c r="E162" s="113"/>
+      <c r="F162" s="114"/>
       <c r="G162" s="62" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="H162" s="63"/>
       <c r="I162" s="64" t="s">
@@ -10930,13 +10993,13 @@
       <c r="A163" s="11"/>
       <c r="B163" s="115"/>
       <c r="C163" s="82"/>
-      <c r="D163" s="111" t="s">
-        <v>197</v>
-      </c>
-      <c r="E163" s="112"/>
-      <c r="F163" s="113"/>
+      <c r="D163" s="112" t="s">
+        <v>196</v>
+      </c>
+      <c r="E163" s="113"/>
+      <c r="F163" s="114"/>
       <c r="G163" s="62" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="H163" s="63"/>
       <c r="I163" s="64" t="s">
@@ -10952,18 +11015,18 @@
     </row>
     <row r="164" spans="1:14" ht="163.80000000000001">
       <c r="A164" s="11"/>
-      <c r="B164" s="116"/>
+      <c r="B164" s="111"/>
       <c r="C164" s="62" t="str">
         <f>master!C135</f>
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
-      <c r="D164" s="111" t="s">
-        <v>353</v>
-      </c>
-      <c r="E164" s="112"/>
-      <c r="F164" s="113"/>
+      <c r="D164" s="112" t="s">
+        <v>348</v>
+      </c>
+      <c r="E164" s="113"/>
+      <c r="F164" s="114"/>
       <c r="G164" s="62" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H164" s="63"/>
       <c r="I164" s="64" t="s">
@@ -10979,28 +11042,28 @@
     </row>
     <row r="165" spans="1:14" ht="165" customHeight="1">
       <c r="A165" s="11"/>
-      <c r="B165" s="114" t="str">
+      <c r="B165" s="110" t="str">
         <f>master!B136</f>
-        <v>バイブコーディングで単体テスト(JUnit)：演習</v>
+        <v>課題2の実施</v>
       </c>
       <c r="C165" s="62" t="str">
         <f>master!C136</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D165" s="111" t="s">
-        <v>354</v>
-      </c>
-      <c r="E165" s="112"/>
-      <c r="F165" s="113"/>
+      <c r="D165" s="112" t="s">
+        <v>349</v>
+      </c>
+      <c r="E165" s="113"/>
+      <c r="F165" s="114"/>
       <c r="G165" s="62" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H165" s="63"/>
       <c r="I165" s="64" t="s">
         <v>24</v>
       </c>
       <c r="J165" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K165" s="66"/>
       <c r="L165" s="6"/>
@@ -11009,18 +11072,18 @@
     </row>
     <row r="166" spans="1:14" ht="151.19999999999999">
       <c r="A166" s="11"/>
-      <c r="B166" s="116"/>
+      <c r="B166" s="111"/>
       <c r="C166" s="62" t="str">
         <f>master!C137</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D166" s="111" t="s">
-        <v>356</v>
-      </c>
-      <c r="E166" s="112"/>
-      <c r="F166" s="113"/>
+      <c r="D166" s="112" t="s">
+        <v>351</v>
+      </c>
+      <c r="E166" s="113"/>
+      <c r="F166" s="114"/>
       <c r="G166" s="62" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="H166" s="63"/>
       <c r="I166" s="64" t="s">
@@ -11036,28 +11099,28 @@
     </row>
     <row r="167" spans="1:14" ht="163.80000000000001">
       <c r="A167" s="11"/>
-      <c r="B167" s="127" t="str">
+      <c r="B167" s="90" t="str">
         <f>master!B139</f>
-        <v>導入</v>
+        <v>その他の導入</v>
       </c>
       <c r="C167" s="62" t="str">
         <f>master!C139</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D167" s="111" t="s">
-        <v>357</v>
-      </c>
-      <c r="E167" s="112"/>
-      <c r="F167" s="113"/>
+      <c r="D167" s="112" t="s">
+        <v>352</v>
+      </c>
+      <c r="E167" s="113"/>
+      <c r="F167" s="114"/>
       <c r="G167" s="62" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="H167" s="63"/>
       <c r="I167" s="64" t="s">
         <v>24</v>
       </c>
       <c r="J167" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K167" s="66"/>
       <c r="L167" s="6"/>
@@ -11066,7 +11129,7 @@
     </row>
     <row r="168" spans="1:14" ht="25.2">
       <c r="A168" s="11"/>
-      <c r="B168" s="114" t="str">
+      <c r="B168" s="110" t="str">
         <f>master!B140</f>
         <v>追加課題</v>
       </c>
@@ -11074,20 +11137,20 @@
         <f>master!C140</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D168" s="111" t="s">
-        <v>359</v>
-      </c>
-      <c r="E168" s="112"/>
-      <c r="F168" s="113"/>
+      <c r="D168" s="112" t="s">
+        <v>354</v>
+      </c>
+      <c r="E168" s="113"/>
+      <c r="F168" s="114"/>
       <c r="G168" s="62" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H168" s="63"/>
       <c r="I168" s="64" t="s">
         <v>24</v>
       </c>
       <c r="J168" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K168" s="66"/>
       <c r="L168" s="6"/>
@@ -11101,20 +11164,20 @@
         <f>master!C141</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D169" s="111" t="s">
-        <v>359</v>
-      </c>
-      <c r="E169" s="112"/>
-      <c r="F169" s="113"/>
+      <c r="D169" s="112" t="s">
+        <v>354</v>
+      </c>
+      <c r="E169" s="113"/>
+      <c r="F169" s="114"/>
       <c r="G169" s="62" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H169" s="63"/>
       <c r="I169" s="64" t="s">
         <v>24</v>
       </c>
       <c r="J169" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K169" s="66"/>
       <c r="L169" s="6"/>
@@ -11123,25 +11186,25 @@
     </row>
     <row r="170" spans="1:14" ht="25.2">
       <c r="A170" s="11"/>
-      <c r="B170" s="116"/>
+      <c r="B170" s="111"/>
       <c r="C170" s="62" t="str">
         <f>master!C142</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D170" s="111" t="s">
-        <v>359</v>
-      </c>
-      <c r="E170" s="112"/>
-      <c r="F170" s="113"/>
+      <c r="D170" s="112" t="s">
+        <v>354</v>
+      </c>
+      <c r="E170" s="113"/>
+      <c r="F170" s="114"/>
       <c r="G170" s="62" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="H170" s="63"/>
       <c r="I170" s="64" t="s">
         <v>24</v>
       </c>
       <c r="J170" s="65" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="K170" s="66"/>
       <c r="L170" s="6"/>
@@ -11150,21 +11213,21 @@
     </row>
     <row r="171" spans="1:14" ht="176.4">
       <c r="A171" s="11"/>
-      <c r="B171" s="114" t="str">
+      <c r="B171" s="110" t="str">
         <f>master!B143</f>
-        <v>振り返り</v>
+        <v>課題の振り返り</v>
       </c>
       <c r="C171" s="62" t="str">
         <f>master!C143</f>
         <v>サンプルのAPとの自分のAPとの比較</v>
       </c>
-      <c r="D171" s="111" t="s">
-        <v>363</v>
-      </c>
-      <c r="E171" s="112"/>
-      <c r="F171" s="113"/>
+      <c r="D171" s="112" t="s">
+        <v>358</v>
+      </c>
+      <c r="E171" s="113"/>
+      <c r="F171" s="114"/>
       <c r="G171" s="62" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="H171" s="63"/>
       <c r="I171" s="64" t="s">
@@ -11180,18 +11243,18 @@
     </row>
     <row r="172" spans="1:14" ht="63">
       <c r="A172" s="11"/>
-      <c r="B172" s="116"/>
+      <c r="B172" s="111"/>
       <c r="C172" s="62" t="str">
         <f>master!C144</f>
         <v>レポートの作成</v>
       </c>
-      <c r="D172" s="111" t="s">
-        <v>361</v>
-      </c>
-      <c r="E172" s="112"/>
-      <c r="F172" s="113"/>
+      <c r="D172" s="112" t="s">
+        <v>356</v>
+      </c>
+      <c r="E172" s="113"/>
+      <c r="F172" s="114"/>
       <c r="G172" s="62" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="H172" s="63"/>
       <c r="I172" s="64" t="s">
@@ -11209,9 +11272,9 @@
       <c r="A173" s="11"/>
       <c r="B173" s="84"/>
       <c r="C173" s="83"/>
-      <c r="D173" s="108"/>
-      <c r="E173" s="109"/>
-      <c r="F173" s="110"/>
+      <c r="D173" s="116"/>
+      <c r="E173" s="117"/>
+      <c r="F173" s="118"/>
       <c r="G173" s="51" t="s">
         <v>50</v>
       </c>
@@ -11229,9 +11292,9 @@
       <c r="A174" s="11"/>
       <c r="B174" s="84"/>
       <c r="C174" s="83"/>
-      <c r="D174" s="108"/>
-      <c r="E174" s="109"/>
-      <c r="F174" s="110"/>
+      <c r="D174" s="116"/>
+      <c r="E174" s="117"/>
+      <c r="F174" s="118"/>
       <c r="G174" s="51" t="s">
         <v>50</v>
       </c>
@@ -11251,30 +11314,139 @@
     <row r="176" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="181">
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="B168:B170"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="B108:B119"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="B153:B164"/>
+    <mergeCell ref="B149:B152"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="B124:B127"/>
+    <mergeCell ref="B128:B145"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="B96:B101"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="B74:B93"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="B65:B73"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="B31:B38"/>
+    <mergeCell ref="B39:B57"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="K22:K23"/>
     <mergeCell ref="D174:F174"/>
     <mergeCell ref="D166:F166"/>
     <mergeCell ref="D118:F118"/>
@@ -11299,139 +11471,30 @@
     <mergeCell ref="D143:F143"/>
     <mergeCell ref="D120:F120"/>
     <mergeCell ref="D122:F122"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="B31:B38"/>
-    <mergeCell ref="B39:B57"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="B65:B73"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="B74:B93"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="B96:B101"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="B124:B127"/>
-    <mergeCell ref="B128:B145"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="B153:B164"/>
-    <mergeCell ref="B149:B152"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B108:B119"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="B168:B170"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11477,7 +11540,7 @@
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>173</v>
+        <v>425</v>
       </c>
       <c r="C3" t="s">
         <v>57</v>
@@ -11658,10 +11721,10 @@
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>173</v>
+        <v>426</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="2:3">
@@ -11676,7 +11739,7 @@
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C40" t="s">
         <v>139</v>
@@ -11722,7 +11785,7 @@
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="2:3">
@@ -11747,7 +11810,7 @@
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>212</v>
+        <v>424</v>
       </c>
       <c r="C53" t="s">
         <v>152</v>
@@ -11805,7 +11868,7 @@
     </row>
     <row r="64" spans="2:3">
       <c r="C64" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="2:3">
@@ -11820,7 +11883,7 @@
     </row>
     <row r="67" spans="2:3">
       <c r="B67" t="s">
-        <v>213</v>
+        <v>422</v>
       </c>
       <c r="C67" t="s">
         <v>165</v>
@@ -11832,7 +11895,7 @@
     </row>
     <row r="69" spans="2:3">
       <c r="B69" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C69" t="s">
         <v>166</v>
@@ -11845,10 +11908,10 @@
     </row>
     <row r="71" spans="2:3">
       <c r="B71" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="2:3">
@@ -11882,99 +11945,99 @@
     </row>
     <row r="78" spans="2:3">
       <c r="B78" t="s">
-        <v>173</v>
+        <v>427</v>
       </c>
       <c r="C78" s="88" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="B79" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C79" s="88" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="80" spans="2:3">
       <c r="C80" s="88" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="B81" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C81" s="89" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="2:3">
       <c r="C82" s="85" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="B83" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C83" s="85" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="2:3">
       <c r="C84" s="85" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="85" spans="2:3">
       <c r="C85" s="85" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="2:3">
       <c r="C86" s="85" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" spans="2:3">
       <c r="C87" s="85" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="88" spans="2:3">
       <c r="C88" s="85" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="2:3">
       <c r="C89" s="85" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="90" spans="2:3">
       <c r="C90" s="85" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91" spans="2:3">
       <c r="C91" s="85" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="92" spans="2:3">
       <c r="C92" s="85" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="93" spans="2:3">
       <c r="C93" s="85" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="94" spans="2:3">
       <c r="C94" s="85" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="95" spans="2:3">
@@ -11983,7 +12046,7 @@
     </row>
     <row r="96" spans="2:3">
       <c r="B96" t="s">
-        <v>173</v>
+        <v>428</v>
       </c>
       <c r="C96" s="85" t="s">
         <v>57</v>
@@ -11991,141 +12054,141 @@
     </row>
     <row r="97" spans="2:3">
       <c r="C97" s="88" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="2:3">
       <c r="C98" s="88" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="B99" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C99" s="88" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="2:3">
       <c r="C100" s="88" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="101" spans="2:3">
       <c r="C101" s="89" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="102" spans="2:3">
       <c r="C102" s="85" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C103" s="85" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="104" spans="2:3">
       <c r="C104" s="85" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="105" spans="2:3">
       <c r="C105" s="85" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="106" spans="2:3">
       <c r="C106" s="85" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="108" spans="2:3">
       <c r="C108" s="85" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="109" spans="2:3">
       <c r="C109" s="85" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="110" spans="2:3">
       <c r="C110" s="85" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="111" spans="2:3">
       <c r="C111" s="85" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="112" spans="2:3">
       <c r="C112" s="85" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="113" spans="2:3">
       <c r="C113" s="85" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="2:3">
       <c r="C114" s="85" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="115" spans="2:3">
       <c r="C115" s="85" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="116" spans="2:3">
       <c r="C116" s="85" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="117" spans="2:3">
       <c r="C117" s="85" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="118" spans="2:3">
       <c r="C118" s="85" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="119" spans="2:3">
       <c r="C119" s="85" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="120" spans="2:3">
       <c r="C120" s="85" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="121" spans="2:3">
       <c r="B121" s="85" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C121" s="85" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="122" spans="2:3">
       <c r="C122" s="85" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="123" spans="2:3">
@@ -12134,81 +12197,81 @@
     </row>
     <row r="124" spans="2:3">
       <c r="B124" t="s">
-        <v>173</v>
+        <v>429</v>
       </c>
       <c r="C124" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="125" spans="2:3">
       <c r="C125" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="126" spans="2:3">
       <c r="C126" s="85" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="127" spans="2:3">
       <c r="C127" s="85" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="128" spans="2:3">
       <c r="B128" t="s">
-        <v>334</v>
+        <v>424</v>
       </c>
       <c r="C128" s="85" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="129" spans="2:3">
       <c r="C129" s="85" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="130" spans="2:3">
       <c r="C130" s="85" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" spans="2:3">
       <c r="C131" s="85" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="132" spans="2:3">
       <c r="C132" s="85" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="133" spans="2:3">
       <c r="C133" s="85" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="134" spans="2:3">
       <c r="C134" s="85" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="135" spans="2:3">
       <c r="C135" s="85" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="136" spans="2:3">
       <c r="B136" t="s">
-        <v>336</v>
+        <v>421</v>
       </c>
       <c r="C136" s="85" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="137" spans="2:3">
       <c r="C137" s="85" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="138" spans="2:3">
@@ -12217,41 +12280,41 @@
     </row>
     <row r="139" spans="2:3">
       <c r="B139" t="s">
-        <v>173</v>
+        <v>430</v>
       </c>
       <c r="C139" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="140" spans="2:3">
       <c r="B140" s="85" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C140" s="85" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="141" spans="2:3">
       <c r="C141" s="85" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="142" spans="2:3">
       <c r="C142" s="85" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="143" spans="2:3">
       <c r="B143" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C143" s="85" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="144" spans="2:3">
       <c r="C144" s="85" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="145" spans="2:3">

--- a/IG/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA83E724-F89A-4102-BBE8-9E58F6D24E4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257680DF-4140-4C5C-A7D3-DC6E3E6CB287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（4日）'!$A$1:$J$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$175</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$173</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="436">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -601,9 +601,6 @@
   </si>
   <si>
     <t>AI-05</t>
-  </si>
-  <si>
-    <t>AI-06</t>
   </si>
   <si>
     <t>AI-07</t>
@@ -2325,42 +2322,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">２回目以降のコミットの手順を説明する。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※ハンズオンとして実施する。
-※コメントは必須であることを強調する。</t>
-    </r>
-    <rPh sb="1" eb="3">
-      <t>カイメ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>イコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>テジュン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="41" eb="43">
-      <t>ヒッス</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>キョウチョウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">過去のコミットの確認方法を説明する。
 </t>
     </r>
@@ -2447,10 +2408,6 @@
     <rPh sb="5" eb="7">
       <t>セツメイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>-</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -3966,130 +3923,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">講師配布のテストプログラムが成功するようにプログラムを修正する。
-■環境構築
-1. zipを解凍する。
-2. 解凍したフォルダに移動し、コマンドプロンプトを開く。
-3. 以下のコマンドを実行する。
-　「mvnw.cmd test -Dtest=WebSpecificationTest」
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">　※VSコード上で実施する場合（PSの場合）、先頭に「.\」を付与する必要がある。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>4. 実施結果を確認する。
-　「BUILD SUCCESS」 で終了し、FailuresとErrorsが0件であることを確認する。
-　※失敗した場合、生成AIを利用してアプリケーションを修正し、再度3から実行する。</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>コウシ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハイフ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>セイコウ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>カンキョウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>コウチク</t>
-    </rPh>
-    <rPh sb="47" eb="49">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>カイトウ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="79" eb="80">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="86" eb="88">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="94" eb="96">
-      <t>ジッコウ</t>
-    </rPh>
-    <rPh sb="152" eb="153">
-      <t>ジョウ</t>
-    </rPh>
-    <rPh sb="154" eb="156">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="158" eb="160">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="164" eb="166">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="173" eb="175">
-      <t>セントウ</t>
-    </rPh>
-    <rPh sb="181" eb="183">
-      <t>フヨ</t>
-    </rPh>
-    <rPh sb="185" eb="187">
-      <t>ヒツヨウ</t>
-    </rPh>
-    <rPh sb="195" eb="197">
-      <t>ジッシ</t>
-    </rPh>
-    <rPh sb="197" eb="199">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="200" eb="202">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="247" eb="249">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="255" eb="257">
-      <t>シッパイ</t>
-    </rPh>
-    <rPh sb="259" eb="261">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="262" eb="264">
-      <t>セイセイ</t>
-    </rPh>
-    <rPh sb="267" eb="269">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="280" eb="282">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="284" eb="286">
-      <t>サイド</t>
-    </rPh>
-    <rPh sb="289" eb="291">
-      <t>ジッコウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">課題1・2を早く完了した受講者は、追加課題に取り組むことを指示する。
 </t>
     </r>
@@ -4155,19 +3988,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>「振り返りレポート」を作成することを説明する。
-①自身のAPとサンプルAPの違い
-②自身のAPをどのように改善できるか
-③気づいたこと・学んだこと</t>
-    <rPh sb="11" eb="13">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>サンプルのAPとの自分のAPとの比較</t>
     <rPh sb="9" eb="11">
       <t>ジブン</t>
@@ -4175,6 +3995,485 @@
     <rPh sb="16" eb="18">
       <t>ヒカク</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>AI-09</t>
+  </si>
+  <si>
+    <t>【AI Native研修-バイブコーディング】演習振り返り.pptx</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>サンプルAP</t>
+  </si>
+  <si>
+    <t>講師配布のテストプログラム</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native研修-バイブコーディング】演習追加課題.pptx</t>
+  </si>
+  <si>
+    <t>AI-10</t>
+  </si>
+  <si>
+    <t>AI-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・AI-04</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-02
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-05
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-05
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-05
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-05
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-05
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-05
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>2 日目</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>3 日目</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>4 日目</t>
+    <rPh sb="2" eb="3">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>メ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>JUnit</t>
+    <phoneticPr fontId="22"/>
+  </si>
+  <si>
+    <t>課題2の実施</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題1の実施</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題の振り返り</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カエ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ハンズオン</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>バイブコーディングの導入</t>
+    <rPh sb="10" eb="12">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題1の導入</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>システム開発プロセスの導入</t>
+    <rPh sb="4" eb="6">
+      <t>カイハツ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>単体テストとJunitの導入</t>
+    <rPh sb="0" eb="2">
+      <t>タンタイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>課題2の導入</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウニュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・本日のスケジュールの説明</t>
+    <rPh sb="1" eb="3">
+      <t>ホンジツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・共通1
+</t>
+    <rPh sb="1" eb="3">
+      <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>オリエンテーション（初日）</t>
+    <rPh sb="10" eb="12">
+      <t>ショニチ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>オリエンテーション（2日目以降）</t>
+    <rPh sb="11" eb="12">
+      <t>ニチ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>メ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>AWS講義（詳細は別紙に記載）</t>
+    <rPh sb="3" eb="5">
+      <t>コウギ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ベッシ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>AI-06</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2回目以降のコミットの手順を説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※ハンズオンとして実施する。
+※コメントは必須であることを強調する。</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>カイメ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="41" eb="43">
+      <t>ヒッス</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>キョウチョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-07
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-08
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-08
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-10
+・AI-11
+</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -4184,9 +4483,7 @@
 1. zipを解凍する。
 2. 解凍したフォルダをVSコードで開く。
 3. アプリケーションを実行する。
-4. アプリケーションを確認する。
-　画面操作
-　ソースコード
+4. アプリケーションやソースコードを確認し、違いを確認する。
 </t>
     </r>
     <r>
@@ -4218,8 +4515,9 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>※ソースコードの比較は「Compare Folders」を使った方がよい。
-違いについては、生成AIを活用して内容を確認すること。</t>
+      <t xml:space="preserve">
+※ソースコードの比較は「Compare Folders」を使った方がよい。
+※ソースコードの違いについては、生成AIを活用して内容を確認すること。</t>
     </r>
     <rPh sb="7" eb="9">
       <t>ジブン</t>
@@ -4236,428 +4534,181 @@
     <rPh sb="80" eb="82">
       <t>ジッコウ</t>
     </rPh>
-    <rPh sb="105" eb="107">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="107" eb="109">
-      <t>ソウサ</t>
-    </rPh>
-    <rPh sb="231" eb="233">
+    <rPh sb="109" eb="110">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="232" eb="234">
       <t>ヒカク</t>
     </rPh>
-    <rPh sb="252" eb="253">
+    <rPh sb="253" eb="254">
       <t>ツカ</t>
     </rPh>
-    <rPh sb="255" eb="256">
+    <rPh sb="256" eb="257">
       <t>ホウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>AI-09</t>
-  </si>
-  <si>
-    <t>【AI Native研修-バイブコーディング】演習振り返り.pptx</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>サンプルAP</t>
-  </si>
-  <si>
-    <t>講師配布のテストプログラム</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>【AI Native研修-バイブコーディング】演習追加課題.pptx</t>
-  </si>
-  <si>
-    <t>AI-10</t>
-  </si>
-  <si>
-    <t>AI-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
+    <t xml:space="preserve">・AI-10
+・AI-11
 </t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・AI-04
+    <t>振り返りレポートを作成することを説明する。
+①自身のAPとサンプルAPの違い
+②自身のAPをどのように改善できるか
+③気づいたこと・学んだこと</t>
+    <rPh sb="9" eb="11">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-05
+・AI-09
 </t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>・AI-04</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
+    <r>
+      <t xml:space="preserve">講師配布のテストプログラムが成功するようにプログラムを修正する。
+■環境構築
+1. zipを解凍する。
+2. 解凍したフォルダに移動し、コマンドプロンプトを開く。
+3. 以下のコマンドを実行する。
+　「mvnw.cmd test -Dtest=WebSpecificationTest」
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">　※VSコード上で実施する場合（PSの場合）、先頭に「.\」を付与する必要がある。
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">4. 実施結果を確認する。
+　「BUILD SUCCESS」 で終了し、FailuresとErrorsが0件であることを確認する。
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-02
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-05
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-06
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-06
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-06
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-06
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-06
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-06
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>2 日目</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>3 日目</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>4 日目</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>JUnit</t>
-    <phoneticPr fontId="22"/>
-  </si>
-  <si>
-    <t>AWS講義</t>
-    <rPh sb="3" eb="5">
-      <t>コウギ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>課題2の実施</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>　※失敗した場合、アプリケーションを修正後、再度3から実行する。</t>
+    </r>
     <rPh sb="0" eb="2">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
+      <t>コウシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハイフ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セイコウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>カンキョウ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>コウチク</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="65" eb="67">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="79" eb="80">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>ジッコウ</t>
+    </rPh>
+    <rPh sb="152" eb="153">
+      <t>ジョウ</t>
+    </rPh>
+    <rPh sb="154" eb="156">
       <t>ジッシ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>課題1の実施</t>
-    <rPh sb="0" eb="2">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
+    <rPh sb="158" eb="160">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="164" eb="166">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="173" eb="175">
+      <t>セントウ</t>
+    </rPh>
+    <rPh sb="181" eb="183">
+      <t>フヨ</t>
+    </rPh>
+    <rPh sb="185" eb="187">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <rPh sb="195" eb="197">
       <t>ジッシ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>課題の振り返り</t>
-    <rPh sb="0" eb="2">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>フ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>カエ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ハンズオン</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>バイブコーディングの導入</t>
-    <rPh sb="10" eb="12">
-      <t>ドウニュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>課題1の導入</t>
-    <rPh sb="0" eb="2">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ドウニュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>システム開発プロセスの導入</t>
-    <rPh sb="4" eb="6">
-      <t>カイハツ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ドウニュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>単体テストとJunitの導入</t>
-    <rPh sb="0" eb="2">
-      <t>タンタイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ドウニュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>課題2の導入</t>
-    <rPh sb="0" eb="2">
-      <t>カダイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ドウニュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>その他の導入</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ドウニュウ</t>
-    </rPh>
+    <rPh sb="197" eb="199">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="200" eb="202">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="247" eb="249">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="255" eb="257">
+      <t>シッパイ</t>
+    </rPh>
+    <rPh sb="259" eb="261">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="271" eb="273">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="273" eb="274">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="275" eb="277">
+      <t>サイド</t>
+    </rPh>
+    <rPh sb="280" eb="282">
+      <t>ジッコウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ー</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -5088,7 +5139,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5257,9 +5308,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -5329,9 +5377,6 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5341,9 +5386,6 @@
     <xf numFmtId="20" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5359,9 +5401,6 @@
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -5371,6 +5410,9 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5395,15 +5437,6 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5419,11 +5452,14 @@
     <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5434,26 +5470,23 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5464,23 +5497,35 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -5856,17 +5901,17 @@
   <sheetData>
     <row r="2" spans="1:10" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="94" t="str">
+      <c r="B2" s="91" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-バイブコーディング_IG」</v>
       </c>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
     </row>
     <row r="3" spans="1:10" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -5881,10 +5926,10 @@
     </row>
     <row r="4" spans="1:10" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="96"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -5894,8 +5939,8 @@
     </row>
     <row r="5" spans="1:10" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="97"/>
-      <c r="C5" s="98"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="95"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -5904,10 +5949,10 @@
       <c r="I5" s="13"/>
     </row>
     <row r="7" spans="1:10" ht="16.2">
-      <c r="B7" s="99" t="s">
+      <c r="B7" s="96" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="99"/>
+      <c r="C7" s="96"/>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" s="15"/>
@@ -5921,15 +5966,15 @@
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="24" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="H9" s="24"/>
       <c r="I9" s="24" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="14.25" customHeight="1">
@@ -5939,234 +5984,234 @@
       <c r="B10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="72" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="37">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E10" s="73" t="s">
+      <c r="E10" s="72" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="37">
         <v>0.39583333333333331</v>
       </c>
-      <c r="G10" s="73" t="s">
+      <c r="G10" s="72" t="s">
         <v>3</v>
       </c>
       <c r="H10" s="37">
         <v>0.39583333333333331</v>
       </c>
-      <c r="I10" s="73" t="s">
+      <c r="I10" s="72" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="39"/>
-      <c r="B11" s="60">
+      <c r="B11" s="59">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="70" t="str">
+      <c r="C11" s="69" t="str">
         <f>master!B3</f>
         <v>バイブコーディングの導入</v>
       </c>
-      <c r="D11" s="60">
+      <c r="D11" s="59">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="70" t="str">
+      <c r="E11" s="69" t="str">
         <f>master!B78</f>
         <v>システム開発プロセスの導入</v>
       </c>
-      <c r="F11" s="60">
+      <c r="F11" s="59">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="70" t="str">
+      <c r="G11" s="69" t="str">
         <f>master!B96</f>
         <v>単体テストとJunitの導入</v>
       </c>
-      <c r="H11" s="60">
+      <c r="H11" s="59">
         <v>0.40625</v>
       </c>
-      <c r="I11" s="70" t="s">
-        <v>420</v>
+      <c r="I11" s="69" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="37">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="69" t="str">
+      <c r="B12" s="67"/>
+      <c r="C12" s="68" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D12" s="68"/>
-      <c r="E12" s="70" t="str">
+      <c r="D12" s="67"/>
+      <c r="E12" s="69" t="str">
         <f>master!B79</f>
         <v>システム開発におけるソフトウェア開発ライフサイクル</v>
       </c>
-      <c r="F12" s="67"/>
-      <c r="G12" s="70" t="str">
+      <c r="F12" s="66"/>
+      <c r="G12" s="69" t="str">
         <f>master!B99</f>
         <v>テストとは</v>
       </c>
-      <c r="H12" s="67"/>
-      <c r="I12" s="71"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="70"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="38"/>
-      <c r="B13" s="60">
+      <c r="B13" s="59">
         <v>0.42708333333333331</v>
       </c>
-      <c r="C13" s="70" t="str">
+      <c r="C13" s="69" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D13" s="91">
+      <c r="D13" s="87">
         <v>0.42708333333333331</v>
       </c>
-      <c r="E13" s="70" t="str">
+      <c r="E13" s="69" t="str">
         <f>master!B81</f>
         <v>TERASOLUNAとは</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="59">
         <v>0.42708333333333331</v>
       </c>
-      <c r="G13" s="70" t="str">
+      <c r="G13" s="69" t="str">
         <f>master!B103</f>
         <v>単体テストとは</v>
       </c>
-      <c r="H13" s="67"/>
-      <c r="I13" s="71"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="70"/>
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="38"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="72"/>
-      <c r="D14" s="67">
+      <c r="B14" s="67"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="66">
         <v>0.43402777777777779</v>
       </c>
-      <c r="E14" s="70" t="str">
+      <c r="E14" s="69" t="str">
         <f>master!B83</f>
         <v>V字モデルとは</v>
       </c>
-      <c r="F14" s="67"/>
-      <c r="G14" s="71"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="71"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="70"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="70"/>
       <c r="J14" s="6"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="39"/>
-      <c r="B15" s="60">
+      <c r="B15" s="59">
         <v>0.44791666666666669</v>
       </c>
-      <c r="C15" s="70" t="str">
+      <c r="C15" s="69" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
-      <c r="D15" s="67"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="71"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="70"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="70"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="70"/>
       <c r="J15" s="6"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="37">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="71"/>
-      <c r="H16" s="67"/>
-      <c r="I16" s="71"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="70"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="70"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="70"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="70"/>
       <c r="J16" s="6"/>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="38"/>
-      <c r="B17" s="67"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="67"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="67"/>
-      <c r="I17" s="71"/>
+      <c r="B17" s="66"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="70"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="70"/>
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="38"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="60">
+      <c r="B18" s="66"/>
+      <c r="C18" s="70"/>
+      <c r="D18" s="59">
         <v>0.47916666666666669</v>
       </c>
-      <c r="E18" s="59" t="str">
+      <c r="E18" s="58" t="str">
         <f>master!B67</f>
         <v>課題1の実施</v>
       </c>
-      <c r="F18" s="68"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="71"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="66"/>
+      <c r="I18" s="70"/>
       <c r="J18" s="6"/>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="39"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="67"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="66"/>
       <c r="E19" s="54"/>
-      <c r="F19" s="60">
+      <c r="F19" s="59">
         <v>0.48958333333333331</v>
       </c>
-      <c r="G19" s="70" t="str">
+      <c r="G19" s="69" t="str">
         <f>master!B121</f>
         <v>JUnit</v>
       </c>
-      <c r="H19" s="67"/>
-      <c r="I19" s="71"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="70"/>
       <c r="J19" s="6"/>
     </row>
     <row r="20" spans="1:10">
-      <c r="A20" s="58">
+      <c r="A20" s="57">
         <v>0.5</v>
       </c>
-      <c r="B20" s="58">
+      <c r="B20" s="57">
         <v>0.5</v>
       </c>
       <c r="C20" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="67"/>
+      <c r="D20" s="66"/>
       <c r="E20" s="54"/>
-      <c r="F20" s="58">
+      <c r="F20" s="57">
         <v>0.5</v>
       </c>
-      <c r="G20" s="59" t="str">
+      <c r="G20" s="58" t="str">
         <f>master!B67</f>
         <v>課題1の実施</v>
       </c>
-      <c r="H20" s="67"/>
-      <c r="I20" s="71"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="70"/>
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="52"/>
       <c r="B21" s="53"/>
       <c r="C21" s="41"/>
-      <c r="D21" s="68"/>
+      <c r="D21" s="67"/>
       <c r="E21" s="55"/>
       <c r="F21" s="39"/>
       <c r="G21" s="55"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="72"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="71"/>
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10">
@@ -6174,25 +6219,25 @@
       <c r="B22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="74" t="s">
+      <c r="C22" s="73" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="E22" s="74" t="s">
+      <c r="E22" s="73" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="G22" s="75" t="s">
+      <c r="G22" s="74" t="s">
         <v>1</v>
       </c>
       <c r="H22" s="38">
         <v>0.52083333333333337</v>
       </c>
-      <c r="I22" s="75" t="s">
+      <c r="I22" s="74" t="s">
         <v>1</v>
       </c>
       <c r="J22" s="6"/>
@@ -6202,19 +6247,19 @@
       <c r="B23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="75"/>
+      <c r="C23" s="74"/>
       <c r="D23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="75"/>
+      <c r="E23" s="74"/>
       <c r="F23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="75"/>
+      <c r="G23" s="74"/>
       <c r="H23" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I23" s="75"/>
+      <c r="I23" s="74"/>
       <c r="J23" s="6"/>
     </row>
     <row r="24" spans="1:10">
@@ -6224,19 +6269,19 @@
       <c r="B24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="75"/>
+      <c r="C24" s="74"/>
       <c r="D24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="75"/>
+      <c r="E24" s="74"/>
       <c r="F24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="75"/>
+      <c r="G24" s="74"/>
       <c r="H24" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="75"/>
+      <c r="I24" s="74"/>
       <c r="J24" s="6"/>
     </row>
     <row r="25" spans="1:10">
@@ -6244,19 +6289,19 @@
       <c r="B25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="76"/>
+      <c r="C25" s="75"/>
       <c r="D25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="76"/>
+      <c r="E25" s="75"/>
       <c r="F25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="76"/>
+      <c r="G25" s="75"/>
       <c r="H25" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="I25" s="76"/>
+      <c r="I25" s="75"/>
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10">
@@ -6264,25 +6309,25 @@
       <c r="B26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="59" t="str">
+      <c r="C26" s="58" t="str">
         <f>master!B37</f>
         <v>課題1の導入</v>
       </c>
       <c r="D26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="92">
+      <c r="E26" s="58"/>
+      <c r="F26" s="88">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="93" t="str">
+      <c r="G26" s="89" t="str">
         <f>master!B124</f>
         <v>課題2の導入</v>
       </c>
       <c r="H26" s="40">
         <v>0.5625</v>
       </c>
-      <c r="I26" s="59" t="str">
+      <c r="I26" s="58" t="str">
         <f>master!B67</f>
         <v>課題1の実施</v>
       </c>
@@ -6297,7 +6342,7 @@
       <c r="F27" s="42">
         <v>0.57291666666666663</v>
       </c>
-      <c r="G27" s="59" t="str">
+      <c r="G27" s="58" t="str">
         <f>master!B128</f>
         <v>ハンズオン</v>
       </c>
@@ -6315,7 +6360,7 @@
       <c r="B28" s="40">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C28" s="59" t="str">
+      <c r="C28" s="58" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
@@ -6369,13 +6414,13 @@
       <c r="J31" s="6"/>
     </row>
     <row r="32" spans="1:10">
-      <c r="A32" s="58">
+      <c r="A32" s="57">
         <v>0.625</v>
       </c>
-      <c r="B32" s="58">
+      <c r="B32" s="57">
         <v>0.625</v>
       </c>
-      <c r="C32" s="59" t="str">
+      <c r="C32" s="58" t="str">
         <f>master!B53</f>
         <v>ハンズオン</v>
       </c>
@@ -6393,7 +6438,7 @@
       <c r="C33" s="54"/>
       <c r="D33" s="42"/>
       <c r="E33" s="54"/>
-      <c r="F33" s="58">
+      <c r="F33" s="57">
         <v>0.63541666666666663</v>
       </c>
       <c r="G33" s="54" t="str">
@@ -6456,10 +6501,10 @@
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="38"/>
-      <c r="B38" s="91">
+      <c r="B38" s="87">
         <v>0.6875</v>
       </c>
-      <c r="C38" s="69" t="str">
+      <c r="C38" s="68" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
@@ -6473,10 +6518,10 @@
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="38"/>
-      <c r="B39" s="67">
+      <c r="B39" s="66">
         <v>0.69791666666666663</v>
       </c>
-      <c r="C39" s="71" t="str">
+      <c r="C39" s="70" t="str">
         <f>master!B71</f>
         <v>VS Code上でGitを使う手順</v>
       </c>
@@ -6484,11 +6529,11 @@
       <c r="E39" s="54"/>
       <c r="F39" s="42"/>
       <c r="G39" s="54"/>
-      <c r="H39" s="60">
+      <c r="H39" s="59">
         <v>0.69791666666666663</v>
       </c>
       <c r="I39" s="54" t="str">
-        <f>master!B143</f>
+        <f>master!B144</f>
         <v>課題の振り返り</v>
       </c>
       <c r="J39" s="6"/>
@@ -6497,13 +6542,13 @@
       <c r="A40" s="40">
         <v>0.70833333333333337</v>
       </c>
-      <c r="B40" s="67"/>
-      <c r="C40" s="72"/>
+      <c r="B40" s="66"/>
+      <c r="C40" s="71"/>
       <c r="D40" s="42"/>
       <c r="E40" s="54"/>
       <c r="F40" s="42"/>
       <c r="G40" s="54"/>
-      <c r="H40" s="67"/>
+      <c r="H40" s="66"/>
       <c r="I40" s="54"/>
       <c r="J40" s="6"/>
     </row>
@@ -6512,7 +6557,7 @@
       <c r="B41" s="40">
         <v>0.71875</v>
       </c>
-      <c r="C41" s="59" t="str">
+      <c r="C41" s="58" t="str">
         <f>master!B67</f>
         <v>課題1の実施</v>
       </c>
@@ -6526,7 +6571,7 @@
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="42"/>
-      <c r="B42" s="68"/>
+      <c r="B42" s="67"/>
       <c r="C42" s="55"/>
       <c r="D42" s="42"/>
       <c r="E42" s="55"/>
@@ -6538,28 +6583,28 @@
     </row>
     <row r="43" spans="1:10" ht="14.25" customHeight="1">
       <c r="A43" s="41"/>
-      <c r="B43" s="78">
+      <c r="B43" s="77">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="77" t="s">
+      <c r="C43" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="78">
+      <c r="D43" s="77">
         <v>0.73958333333333337</v>
       </c>
-      <c r="E43" s="77" t="s">
+      <c r="E43" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="78">
+      <c r="F43" s="77">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G43" s="77" t="s">
+      <c r="G43" s="76" t="s">
         <v>55</v>
       </c>
-      <c r="H43" s="78">
+      <c r="H43" s="77">
         <v>0.73958333333333337</v>
       </c>
-      <c r="I43" s="77" t="s">
+      <c r="I43" s="76" t="s">
         <v>55</v>
       </c>
     </row>
@@ -6585,7 +6630,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L13"/>
+  <dimension ref="A2:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -6628,10 +6673,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="105"/>
+      <c r="C4" s="99"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -6642,16 +6687,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -6664,10 +6709,10 @@
         <v>14</v>
       </c>
       <c r="C7" s="33"/>
-      <c r="D7" s="107" t="s">
+      <c r="D7" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="107"/>
+      <c r="E7" s="101"/>
       <c r="F7" s="33" t="s">
         <v>10</v>
       </c>
@@ -6707,76 +6752,100 @@
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101" t="s">
+      <c r="B11" s="98"/>
+      <c r="C11" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="101" t="s">
+      <c r="D11" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101" t="s">
+      <c r="E11" s="98"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="108" t="s">
+      <c r="H11" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="100" t="s">
+      <c r="I11" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="100"/>
-      <c r="K11" s="100" t="s">
+      <c r="J11" s="97"/>
+      <c r="K11" s="97" t="s">
         <v>32</v>
       </c>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="10"/>
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="109"/>
+      <c r="B12" s="98"/>
+      <c r="C12" s="98"/>
+      <c r="D12" s="98"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="98"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="103"/>
       <c r="I12" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K12" s="101"/>
+      <c r="K12" s="98"/>
       <c r="L12" s="10"/>
     </row>
     <row r="13" spans="1:12" ht="63">
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="102" t="s">
+        <v>416</v>
+      </c>
+      <c r="D13" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="103"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="56" t="s">
+      <c r="E13" s="119"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="120" t="s">
         <v>54</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="50" t="s">
-        <v>28</v>
-      </c>
-      <c r="J13" s="57">
+        <v>24</v>
+      </c>
+      <c r="J13" s="56">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="10"/>
     </row>
+    <row r="14" spans="1:12" ht="25.2">
+      <c r="A14" s="10"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="D14" s="119" t="s">
+        <v>414</v>
+      </c>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="120" t="s">
+        <v>415</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="56">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="K11:K12"/>
-    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="D7:E7"/>
@@ -6786,6 +6855,7 @@
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="D13:F13"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6798,7 +6868,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
+          <xm:sqref>H13:H14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6808,7 +6878,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N176"/>
+  <dimension ref="A2:N174"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -6858,12 +6928,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="2:14" ht="16.2">
-      <c r="B4" s="105" t="s">
+      <c r="B4" s="99" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -6874,30 +6944,30 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="124"/>
-      <c r="C5" s="124"/>
-      <c r="D5" s="124"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="124"/>
-      <c r="G5" s="124"/>
-      <c r="H5" s="124"/>
-      <c r="I5" s="124"/>
-      <c r="J5" s="124"/>
-      <c r="K5" s="124"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="118"/>
       <c r="L5" s="29"/>
       <c r="M5" s="30"/>
     </row>
     <row r="6" spans="2:14" ht="32.4" customHeight="1">
-      <c r="B6" s="124"/>
-      <c r="C6" s="124"/>
-      <c r="D6" s="124"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="124"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="124"/>
-      <c r="K6" s="124"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="118"/>
       <c r="L6" s="29"/>
       <c r="M6" s="30"/>
     </row>
@@ -6938,7 +7008,7 @@
       <c r="B9" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="61" t="s">
+      <c r="C9" s="60" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="36" t="s">
@@ -6960,7 +7030,7 @@
       <c r="B10" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="61" t="s">
+      <c r="C10" s="60" t="s">
         <v>38</v>
       </c>
       <c r="D10" s="36" t="s">
@@ -7004,7 +7074,7 @@
       <c r="B12" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C12" s="61" t="s">
+      <c r="C12" s="60" t="s">
         <v>91</v>
       </c>
       <c r="D12" s="36" t="s">
@@ -7046,9 +7116,9 @@
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="C14" s="61" t="s">
+        <v>419</v>
+      </c>
+      <c r="C14" s="60" t="s">
         <v>39</v>
       </c>
       <c r="D14" s="36" t="s">
@@ -7068,9 +7138,9 @@
     </row>
     <row r="15" spans="2:14">
       <c r="B15" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="60" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="36" t="s">
@@ -7090,10 +7160,10 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="61" t="s">
-        <v>363</v>
+        <v>97</v>
+      </c>
+      <c r="C16" s="60" t="s">
+        <v>357</v>
       </c>
       <c r="D16" s="36" t="s">
         <v>19</v>
@@ -7112,10 +7182,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="34" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D17" s="36" t="s">
         <v>19</v>
@@ -7134,10 +7204,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="B18" s="34" t="s">
-        <v>364</v>
-      </c>
-      <c r="C18" s="61" t="s">
-        <v>360</v>
+        <v>358</v>
+      </c>
+      <c r="C18" s="60" t="s">
+        <v>354</v>
       </c>
       <c r="D18" s="36" t="s">
         <v>19</v>
@@ -7156,10 +7226,10 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="34" t="s">
-        <v>365</v>
-      </c>
-      <c r="C19" s="61" t="s">
-        <v>361</v>
+        <v>359</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>355</v>
       </c>
       <c r="D19" s="36" t="s">
         <v>19</v>
@@ -7189,28 +7259,28 @@
     </row>
     <row r="22" spans="1:14" ht="24" customHeight="1">
       <c r="A22" s="10"/>
-      <c r="B22" s="101" t="s">
+      <c r="B22" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="C22" s="101" t="s">
+      <c r="C22" s="98" t="s">
         <v>7</v>
       </c>
-      <c r="D22" s="101" t="s">
+      <c r="D22" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="101"/>
-      <c r="F22" s="101"/>
-      <c r="G22" s="101" t="s">
+      <c r="E22" s="98"/>
+      <c r="F22" s="98"/>
+      <c r="G22" s="98" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="100" t="s">
+      <c r="H22" s="97" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="122" t="s">
+      <c r="I22" s="116" t="s">
         <v>33</v>
       </c>
-      <c r="J22" s="123"/>
-      <c r="K22" s="100" t="s">
+      <c r="J22" s="117"/>
+      <c r="K22" s="97" t="s">
         <v>34</v>
       </c>
       <c r="L22" s="6"/>
@@ -7219,27 +7289,27 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="10"/>
-      <c r="B23" s="101"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="101"/>
-      <c r="H23" s="100"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="98"/>
+      <c r="D23" s="98"/>
+      <c r="E23" s="98"/>
+      <c r="F23" s="98"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="97"/>
       <c r="I23" s="28" t="s">
         <v>25</v>
       </c>
       <c r="J23" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="K23" s="101"/>
+      <c r="K23" s="98"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" ht="151.19999999999999">
       <c r="A24" s="10"/>
-      <c r="B24" s="79" t="str">
+      <c r="B24" s="78" t="str">
         <f>master!B3</f>
         <v>バイブコーディングの導入</v>
       </c>
@@ -7247,13 +7317,13 @@
         <f>master!C3</f>
         <v>講義の目的</v>
       </c>
-      <c r="D24" s="116" t="s">
+      <c r="D24" s="104" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="105"/>
+      <c r="F24" s="106"/>
+      <c r="G24" s="51" t="s">
         <v>99</v>
-      </c>
-      <c r="E24" s="117"/>
-      <c r="F24" s="118"/>
-      <c r="G24" s="51" t="s">
-        <v>100</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="49" t="s">
@@ -7269,7 +7339,7 @@
     </row>
     <row r="25" spans="1:14" ht="138.6" customHeight="1">
       <c r="A25" s="10"/>
-      <c r="B25" s="125" t="str">
+      <c r="B25" s="113" t="str">
         <f>master!B4</f>
         <v>Webアプリケーションとは</v>
       </c>
@@ -7277,11 +7347,11 @@
         <f>master!C4</f>
         <v>Webアプリケーションとは</v>
       </c>
-      <c r="D25" s="116" t="s">
-        <v>101</v>
-      </c>
-      <c r="E25" s="117"/>
-      <c r="F25" s="118"/>
+      <c r="D25" s="104" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="105"/>
+      <c r="F25" s="106"/>
       <c r="G25" s="51" t="s">
         <v>43</v>
       </c>
@@ -7299,16 +7369,16 @@
     </row>
     <row r="26" spans="1:14" ht="75.599999999999994">
       <c r="A26" s="11"/>
-      <c r="B26" s="126"/>
+      <c r="B26" s="114"/>
       <c r="C26" s="51" t="str">
         <f>master!C5</f>
         <v>Webアプリケーションの種類</v>
       </c>
-      <c r="D26" s="116" t="s">
-        <v>102</v>
-      </c>
-      <c r="E26" s="117"/>
-      <c r="F26" s="118"/>
+      <c r="D26" s="104" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="105"/>
+      <c r="F26" s="106"/>
       <c r="G26" s="51" t="s">
         <v>47</v>
       </c>
@@ -7326,16 +7396,16 @@
     </row>
     <row r="27" spans="1:14" ht="37.799999999999997">
       <c r="A27" s="11"/>
-      <c r="B27" s="126"/>
+      <c r="B27" s="114"/>
       <c r="C27" s="51" t="str">
         <f>master!C6</f>
         <v>アプリケーションとは</v>
       </c>
-      <c r="D27" s="116" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="117"/>
-      <c r="F27" s="118"/>
+      <c r="D27" s="104" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="105"/>
+      <c r="F27" s="106"/>
       <c r="G27" s="51" t="s">
         <v>45</v>
       </c>
@@ -7353,16 +7423,16 @@
     </row>
     <row r="28" spans="1:14" ht="63">
       <c r="A28" s="11"/>
-      <c r="B28" s="126"/>
+      <c r="B28" s="114"/>
       <c r="C28" s="51" t="str">
         <f>master!C7</f>
         <v>Web画面アプリケーション</v>
       </c>
-      <c r="D28" s="116" t="s">
-        <v>104</v>
-      </c>
-      <c r="E28" s="117"/>
-      <c r="F28" s="118"/>
+      <c r="D28" s="104" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="105"/>
+      <c r="F28" s="106"/>
       <c r="G28" s="51" t="s">
         <v>44</v>
       </c>
@@ -7380,13 +7450,13 @@
     </row>
     <row r="29" spans="1:14" ht="63">
       <c r="A29" s="11"/>
-      <c r="B29" s="126"/>
+      <c r="B29" s="114"/>
       <c r="C29" s="51"/>
-      <c r="D29" s="116" t="s">
-        <v>105</v>
-      </c>
-      <c r="E29" s="117"/>
-      <c r="F29" s="118"/>
+      <c r="D29" s="104" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="105"/>
+      <c r="F29" s="106"/>
       <c r="G29" s="51" t="s">
         <v>44</v>
       </c>
@@ -7404,16 +7474,16 @@
     </row>
     <row r="30" spans="1:14" ht="113.4">
       <c r="A30" s="11"/>
-      <c r="B30" s="127"/>
+      <c r="B30" s="115"/>
       <c r="C30" s="51" t="str">
         <f>master!C8</f>
         <v>ブラウザからのリクエスト種類</v>
       </c>
-      <c r="D30" s="116" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="117"/>
-      <c r="F30" s="118"/>
+      <c r="D30" s="104" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="105"/>
+      <c r="F30" s="106"/>
       <c r="G30" s="51" t="s">
         <v>48</v>
       </c>
@@ -7431,7 +7501,7 @@
     </row>
     <row r="31" spans="1:14" ht="102" customHeight="1">
       <c r="A31" s="11"/>
-      <c r="B31" s="125" t="str">
+      <c r="B31" s="113" t="str">
         <f>master!B9</f>
         <v>データベースとは</v>
       </c>
@@ -7439,11 +7509,11 @@
         <f>master!C9</f>
         <v>データベースとは</v>
       </c>
-      <c r="D31" s="116" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" s="117"/>
-      <c r="F31" s="118"/>
+      <c r="D31" s="104" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="105"/>
+      <c r="F31" s="106"/>
       <c r="G31" s="51" t="s">
         <v>45</v>
       </c>
@@ -7461,16 +7531,16 @@
     </row>
     <row r="32" spans="1:14" ht="88.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="126"/>
+      <c r="B32" s="114"/>
       <c r="C32" s="51" t="str">
         <f>master!C10</f>
         <v>リレーショナルデータベース</v>
       </c>
-      <c r="D32" s="116" t="s">
-        <v>108</v>
-      </c>
-      <c r="E32" s="117"/>
-      <c r="F32" s="118"/>
+      <c r="D32" s="104" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="105"/>
+      <c r="F32" s="106"/>
       <c r="G32" s="51" t="s">
         <v>49</v>
       </c>
@@ -7488,16 +7558,16 @@
     </row>
     <row r="33" spans="1:14" ht="25.2">
       <c r="A33" s="11"/>
-      <c r="B33" s="126"/>
+      <c r="B33" s="114"/>
       <c r="C33" s="51" t="str">
         <f>master!C11</f>
         <v>データベースの役割</v>
       </c>
-      <c r="D33" s="116" t="s">
-        <v>109</v>
-      </c>
-      <c r="E33" s="117"/>
-      <c r="F33" s="118"/>
+      <c r="D33" s="104" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="105"/>
+      <c r="F33" s="106"/>
       <c r="G33" s="51" t="s">
         <v>50</v>
       </c>
@@ -7509,7 +7579,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K33" s="43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
@@ -7517,16 +7587,16 @@
     </row>
     <row r="34" spans="1:14" ht="75.599999999999994">
       <c r="A34" s="11"/>
-      <c r="B34" s="126"/>
+      <c r="B34" s="114"/>
       <c r="C34" s="51" t="str">
         <f>master!C12</f>
         <v>2.1.テーブル</v>
       </c>
-      <c r="D34" s="116" t="s">
-        <v>110</v>
-      </c>
-      <c r="E34" s="117"/>
-      <c r="F34" s="118"/>
+      <c r="D34" s="104" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="105"/>
+      <c r="F34" s="106"/>
       <c r="G34" s="51" t="s">
         <v>47</v>
       </c>
@@ -7544,16 +7614,16 @@
     </row>
     <row r="35" spans="1:14" ht="100.8">
       <c r="A35" s="11"/>
-      <c r="B35" s="126"/>
+      <c r="B35" s="114"/>
       <c r="C35" s="51" t="str">
         <f>master!C13</f>
         <v>2.2.データ型１</v>
       </c>
-      <c r="D35" s="116" t="s">
-        <v>111</v>
-      </c>
-      <c r="E35" s="117"/>
-      <c r="F35" s="118"/>
+      <c r="D35" s="104" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="105"/>
+      <c r="F35" s="106"/>
       <c r="G35" s="51" t="s">
         <v>51</v>
       </c>
@@ -7571,16 +7641,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="126"/>
+      <c r="B36" s="114"/>
       <c r="C36" s="51" t="str">
         <f>master!C14</f>
         <v>2.2.データ型２</v>
       </c>
-      <c r="D36" s="116" t="s">
-        <v>112</v>
-      </c>
-      <c r="E36" s="117"/>
-      <c r="F36" s="118"/>
+      <c r="D36" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="105"/>
+      <c r="F36" s="106"/>
       <c r="G36" s="51" t="s">
         <v>45</v>
       </c>
@@ -7598,16 +7668,16 @@
     </row>
     <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="126"/>
+      <c r="B37" s="114"/>
       <c r="C37" s="51" t="str">
         <f>master!C15</f>
         <v>2.3.リレーション</v>
       </c>
-      <c r="D37" s="116" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="117"/>
-      <c r="F37" s="118"/>
+      <c r="D37" s="104" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="105"/>
+      <c r="F37" s="106"/>
       <c r="G37" s="51" t="s">
         <v>45</v>
       </c>
@@ -7625,16 +7695,16 @@
     </row>
     <row r="38" spans="1:14" ht="37.799999999999997">
       <c r="A38" s="11"/>
-      <c r="B38" s="127"/>
+      <c r="B38" s="115"/>
       <c r="C38" s="51" t="str">
         <f>master!C16</f>
         <v>2.4.データを結合して取得（Join）</v>
       </c>
-      <c r="D38" s="116" t="s">
-        <v>114</v>
-      </c>
-      <c r="E38" s="117"/>
-      <c r="F38" s="118"/>
+      <c r="D38" s="104" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="105"/>
+      <c r="F38" s="106"/>
       <c r="G38" s="51" t="s">
         <v>45</v>
       </c>
@@ -7652,7 +7722,7 @@
     </row>
     <row r="39" spans="1:14" ht="88.2">
       <c r="A39" s="11"/>
-      <c r="B39" s="125" t="str">
+      <c r="B39" s="113" t="str">
         <f>master!B17</f>
         <v>Java言語、Springフレームワークとは</v>
       </c>
@@ -7660,11 +7730,11 @@
         <f>master!C17</f>
         <v>Webアプリケーションを作成するためのプログラミング言語</v>
       </c>
-      <c r="D39" s="116" t="s">
-        <v>115</v>
-      </c>
-      <c r="E39" s="117"/>
-      <c r="F39" s="118"/>
+      <c r="D39" s="104" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="105"/>
+      <c r="F39" s="106"/>
       <c r="G39" s="51" t="s">
         <v>49</v>
       </c>
@@ -7682,16 +7752,16 @@
     </row>
     <row r="40" spans="1:14" ht="75.599999999999994">
       <c r="A40" s="11"/>
-      <c r="B40" s="126"/>
+      <c r="B40" s="114"/>
       <c r="C40" s="51" t="str">
         <f>master!C18</f>
         <v>Java</v>
       </c>
-      <c r="D40" s="116" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="117"/>
-      <c r="F40" s="118"/>
+      <c r="D40" s="104" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="105"/>
+      <c r="F40" s="106"/>
       <c r="G40" s="51" t="s">
         <v>47</v>
       </c>
@@ -7709,16 +7779,16 @@
     </row>
     <row r="41" spans="1:14" ht="75.599999999999994">
       <c r="A41" s="11"/>
-      <c r="B41" s="126"/>
+      <c r="B41" s="114"/>
       <c r="C41" s="51" t="str">
         <f>master!C19</f>
         <v>Java言語の構成要素</v>
       </c>
-      <c r="D41" s="116" t="s">
-        <v>117</v>
-      </c>
-      <c r="E41" s="117"/>
-      <c r="F41" s="118"/>
+      <c r="D41" s="104" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="105"/>
+      <c r="F41" s="106"/>
       <c r="G41" s="51" t="s">
         <v>47</v>
       </c>
@@ -7736,16 +7806,16 @@
     </row>
     <row r="42" spans="1:14" ht="50.4">
       <c r="A42" s="11"/>
-      <c r="B42" s="126"/>
+      <c r="B42" s="114"/>
       <c r="C42" s="51" t="str">
         <f>master!C20</f>
         <v>Webアプリケーションを構成するクラス</v>
       </c>
-      <c r="D42" s="116" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="117"/>
-      <c r="F42" s="118"/>
+      <c r="D42" s="104" t="s">
+        <v>117</v>
+      </c>
+      <c r="E42" s="105"/>
+      <c r="F42" s="106"/>
       <c r="G42" s="51" t="s">
         <v>46</v>
       </c>
@@ -7763,16 +7833,16 @@
     </row>
     <row r="43" spans="1:14" ht="88.2">
       <c r="A43" s="11"/>
-      <c r="B43" s="126"/>
+      <c r="B43" s="114"/>
       <c r="C43" s="51" t="str">
         <f>master!C21</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D43" s="116" t="s">
-        <v>120</v>
-      </c>
-      <c r="E43" s="117"/>
-      <c r="F43" s="118"/>
+      <c r="D43" s="104" t="s">
+        <v>119</v>
+      </c>
+      <c r="E43" s="105"/>
+      <c r="F43" s="106"/>
       <c r="G43" s="51" t="s">
         <v>49</v>
       </c>
@@ -7784,7 +7854,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K43" s="43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -7792,18 +7862,18 @@
     </row>
     <row r="44" spans="1:14" ht="201.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="126"/>
+      <c r="B44" s="114"/>
       <c r="C44" s="51" t="str">
         <f>master!C22</f>
         <v>View と Controller と Service と Repository</v>
       </c>
-      <c r="D44" s="116" t="s">
+      <c r="D44" s="104" t="s">
+        <v>120</v>
+      </c>
+      <c r="E44" s="105"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="51" t="s">
         <v>121</v>
-      </c>
-      <c r="E44" s="117"/>
-      <c r="F44" s="118"/>
-      <c r="G44" s="51" t="s">
-        <v>122</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="49" t="s">
@@ -7819,16 +7889,16 @@
     </row>
     <row r="45" spans="1:14" ht="37.799999999999997">
       <c r="A45" s="11"/>
-      <c r="B45" s="126"/>
+      <c r="B45" s="114"/>
       <c r="C45" s="51" t="str">
         <f>master!C23</f>
         <v>Nレイヤーアーキテクチャ</v>
       </c>
-      <c r="D45" s="116" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" s="117"/>
-      <c r="F45" s="118"/>
+      <c r="D45" s="104" t="s">
+        <v>122</v>
+      </c>
+      <c r="E45" s="105"/>
+      <c r="F45" s="106"/>
       <c r="G45" s="51" t="s">
         <v>45</v>
       </c>
@@ -7846,18 +7916,18 @@
     </row>
     <row r="46" spans="1:14" ht="163.80000000000001">
       <c r="A46" s="11"/>
-      <c r="B46" s="126"/>
+      <c r="B46" s="114"/>
       <c r="C46" s="51" t="str">
         <f>master!C24</f>
         <v>Webアプリケーション フレームワーク</v>
       </c>
-      <c r="D46" s="116" t="s">
+      <c r="D46" s="104" t="s">
+        <v>123</v>
+      </c>
+      <c r="E46" s="105"/>
+      <c r="F46" s="106"/>
+      <c r="G46" s="51" t="s">
         <v>124</v>
-      </c>
-      <c r="E46" s="117"/>
-      <c r="F46" s="118"/>
-      <c r="G46" s="51" t="s">
-        <v>125</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="49" t="s">
@@ -7873,16 +7943,16 @@
     </row>
     <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="126"/>
+      <c r="B47" s="114"/>
       <c r="C47" s="51" t="str">
         <f>master!C25</f>
         <v>Java向けWebアプリケーションフレームワーク</v>
       </c>
-      <c r="D47" s="116" t="s">
-        <v>126</v>
-      </c>
-      <c r="E47" s="117"/>
-      <c r="F47" s="118"/>
+      <c r="D47" s="104" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" s="105"/>
+      <c r="F47" s="106"/>
       <c r="G47" s="51" t="s">
         <v>50</v>
       </c>
@@ -7900,18 +7970,18 @@
     </row>
     <row r="48" spans="1:14" ht="189">
       <c r="A48" s="11"/>
-      <c r="B48" s="126"/>
+      <c r="B48" s="114"/>
       <c r="C48" s="51" t="str">
         <f>master!C26</f>
         <v>Springフレームワーク</v>
       </c>
-      <c r="D48" s="116" t="s">
+      <c r="D48" s="104" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" s="105"/>
+      <c r="F48" s="106"/>
+      <c r="G48" s="51" t="s">
         <v>127</v>
-      </c>
-      <c r="E48" s="117"/>
-      <c r="F48" s="118"/>
-      <c r="G48" s="51" t="s">
-        <v>128</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="49" t="s">
@@ -7927,16 +7997,16 @@
     </row>
     <row r="49" spans="1:14" ht="88.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="126"/>
+      <c r="B49" s="114"/>
       <c r="C49" s="51" t="str">
         <f>master!C27</f>
         <v>Springフレームワーク：DIコンテナとは</v>
       </c>
-      <c r="D49" s="116" t="s">
-        <v>129</v>
-      </c>
-      <c r="E49" s="117"/>
-      <c r="F49" s="118"/>
+      <c r="D49" s="104" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="105"/>
+      <c r="F49" s="106"/>
       <c r="G49" s="51" t="s">
         <v>49</v>
       </c>
@@ -7948,7 +8018,7 @@
         <v>3.472222222222222E-3</v>
       </c>
       <c r="K49" s="43" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
@@ -7956,16 +8026,16 @@
     </row>
     <row r="50" spans="1:14" ht="63">
       <c r="A50" s="11"/>
-      <c r="B50" s="126"/>
+      <c r="B50" s="114"/>
       <c r="C50" s="51" t="str">
         <f>master!C28</f>
         <v>DIコンテナ：DIコンテナが部品を注入する</v>
       </c>
-      <c r="D50" s="116" t="s">
-        <v>130</v>
-      </c>
-      <c r="E50" s="117"/>
-      <c r="F50" s="118"/>
+      <c r="D50" s="104" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" s="105"/>
+      <c r="F50" s="106"/>
       <c r="G50" s="51" t="s">
         <v>44</v>
       </c>
@@ -7983,16 +8053,16 @@
     </row>
     <row r="51" spans="1:14" ht="100.8">
       <c r="A51" s="11"/>
-      <c r="B51" s="126"/>
+      <c r="B51" s="114"/>
       <c r="C51" s="51" t="str">
         <f>master!C29</f>
         <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
       </c>
-      <c r="D51" s="116" t="s">
-        <v>131</v>
-      </c>
-      <c r="E51" s="117"/>
-      <c r="F51" s="118"/>
+      <c r="D51" s="104" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="105"/>
+      <c r="F51" s="106"/>
       <c r="G51" s="51" t="s">
         <v>51</v>
       </c>
@@ -8010,16 +8080,16 @@
     </row>
     <row r="52" spans="1:14" ht="100.8">
       <c r="A52" s="11"/>
-      <c r="B52" s="126"/>
+      <c r="B52" s="114"/>
       <c r="C52" s="51" t="str">
         <f>master!C30</f>
         <v>Springフレームワークにおける部品の設定</v>
       </c>
-      <c r="D52" s="116" t="s">
-        <v>132</v>
-      </c>
-      <c r="E52" s="117"/>
-      <c r="F52" s="118"/>
+      <c r="D52" s="104" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="105"/>
+      <c r="F52" s="106"/>
       <c r="G52" s="51" t="s">
         <v>51</v>
       </c>
@@ -8037,16 +8107,16 @@
     </row>
     <row r="53" spans="1:14" ht="88.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="126"/>
+      <c r="B53" s="114"/>
       <c r="C53" s="51" t="str">
         <f>master!C31</f>
         <v>Spring Boot</v>
       </c>
-      <c r="D53" s="116" t="s">
-        <v>133</v>
-      </c>
-      <c r="E53" s="117"/>
-      <c r="F53" s="118"/>
+      <c r="D53" s="104" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="105"/>
+      <c r="F53" s="106"/>
       <c r="G53" s="51" t="s">
         <v>49</v>
       </c>
@@ -8064,16 +8134,16 @@
     </row>
     <row r="54" spans="1:14" ht="63">
       <c r="A54" s="11"/>
-      <c r="B54" s="126"/>
+      <c r="B54" s="114"/>
       <c r="C54" s="51" t="str">
         <f>master!C32</f>
         <v>Spring Boot：オートコンフィグレーション</v>
       </c>
-      <c r="D54" s="116" t="s">
-        <v>134</v>
-      </c>
-      <c r="E54" s="117"/>
-      <c r="F54" s="118"/>
+      <c r="D54" s="104" t="s">
+        <v>133</v>
+      </c>
+      <c r="E54" s="105"/>
+      <c r="F54" s="106"/>
       <c r="G54" s="51" t="s">
         <v>44</v>
       </c>
@@ -8091,16 +8161,16 @@
     </row>
     <row r="55" spans="1:14" ht="50.4">
       <c r="A55" s="11"/>
-      <c r="B55" s="126"/>
+      <c r="B55" s="114"/>
       <c r="C55" s="51" t="str">
         <f>master!C33</f>
         <v>Spring Boot：Starters</v>
       </c>
-      <c r="D55" s="116" t="s">
-        <v>135</v>
-      </c>
-      <c r="E55" s="117"/>
-      <c r="F55" s="118"/>
+      <c r="D55" s="104" t="s">
+        <v>134</v>
+      </c>
+      <c r="E55" s="105"/>
+      <c r="F55" s="106"/>
       <c r="G55" s="51" t="s">
         <v>46</v>
       </c>
@@ -8118,16 +8188,16 @@
     </row>
     <row r="56" spans="1:14" ht="88.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="126"/>
+      <c r="B56" s="114"/>
       <c r="C56" s="51" t="str">
         <f>master!C34</f>
         <v>Spring Boot：組込みWebAPサーバ</v>
       </c>
-      <c r="D56" s="116" t="s">
-        <v>136</v>
-      </c>
-      <c r="E56" s="117"/>
-      <c r="F56" s="118"/>
+      <c r="D56" s="104" t="s">
+        <v>135</v>
+      </c>
+      <c r="E56" s="105"/>
+      <c r="F56" s="106"/>
       <c r="G56" s="51" t="s">
         <v>49</v>
       </c>
@@ -8145,14 +8215,14 @@
     </row>
     <row r="57" spans="1:14" ht="25.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="127"/>
+      <c r="B57" s="115"/>
       <c r="C57" s="51" t="str">
         <f>master!C35</f>
         <v>おすすめ書籍：『プロになるためのSpring入門』</v>
       </c>
-      <c r="D57" s="116"/>
-      <c r="E57" s="117"/>
-      <c r="F57" s="118"/>
+      <c r="D57" s="104"/>
+      <c r="E57" s="105"/>
+      <c r="F57" s="106"/>
       <c r="G57" s="51" t="s">
         <v>50</v>
       </c>
@@ -8170,1217 +8240,1217 @@
     </row>
     <row r="58" spans="1:14" ht="37.799999999999997">
       <c r="A58" s="11"/>
-      <c r="B58" s="128" t="str">
+      <c r="B58" s="110" t="str">
         <f>master!B37</f>
         <v>課題1の導入</v>
       </c>
-      <c r="C58" s="62" t="str">
+      <c r="C58" s="61" t="str">
         <f>master!C37</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D58" s="112" t="s">
-        <v>178</v>
-      </c>
-      <c r="E58" s="113"/>
-      <c r="F58" s="114"/>
-      <c r="G58" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H58" s="63"/>
-      <c r="I58" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" s="65">
+      <c r="D58" s="107" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" s="108"/>
+      <c r="F58" s="109"/>
+      <c r="G58" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H58" s="62"/>
+      <c r="I58" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K58" s="66"/>
+      <c r="K58" s="65"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
     <row r="59" spans="1:14" ht="37.799999999999997">
       <c r="A59" s="11"/>
-      <c r="B59" s="129"/>
-      <c r="C59" s="62" t="str">
+      <c r="B59" s="111"/>
+      <c r="C59" s="61" t="str">
         <f>master!C38</f>
         <v>作成物</v>
       </c>
-      <c r="D59" s="112" t="s">
-        <v>179</v>
-      </c>
-      <c r="E59" s="113"/>
-      <c r="F59" s="114"/>
-      <c r="G59" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H59" s="63"/>
-      <c r="I59" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J59" s="65">
+      <c r="D59" s="107" t="s">
+        <v>178</v>
+      </c>
+      <c r="E59" s="108"/>
+      <c r="F59" s="109"/>
+      <c r="G59" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H59" s="62"/>
+      <c r="I59" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K59" s="66"/>
+      <c r="K59" s="65"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
     <row r="60" spans="1:14" ht="75.599999999999994">
       <c r="A60" s="11"/>
-      <c r="B60" s="130"/>
-      <c r="C60" s="62" t="str">
+      <c r="B60" s="112"/>
+      <c r="C60" s="61" t="str">
         <f>master!C39</f>
         <v>演習課題の進め方</v>
       </c>
-      <c r="D60" s="112" t="s">
-        <v>180</v>
-      </c>
-      <c r="E60" s="113"/>
-      <c r="F60" s="114"/>
-      <c r="G60" s="62" t="s">
-        <v>367</v>
-      </c>
-      <c r="H60" s="63"/>
-      <c r="I60" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J60" s="65">
+      <c r="D60" s="107" t="s">
+        <v>179</v>
+      </c>
+      <c r="E60" s="108"/>
+      <c r="F60" s="109"/>
+      <c r="G60" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="H60" s="62"/>
+      <c r="I60" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="64">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K60" s="66"/>
+      <c r="K60" s="65"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
     <row r="61" spans="1:14" ht="15" customHeight="1">
       <c r="A61" s="11"/>
-      <c r="B61" s="128" t="str">
+      <c r="B61" s="110" t="str">
         <f>master!B40</f>
         <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
       </c>
-      <c r="C61" s="62" t="str">
+      <c r="C61" s="61" t="str">
         <f>master!C40</f>
         <v>前提条件</v>
       </c>
-      <c r="D61" s="112"/>
-      <c r="E61" s="113"/>
-      <c r="F61" s="114"/>
-      <c r="G61" s="62" t="s">
-        <v>368</v>
-      </c>
-      <c r="H61" s="63"/>
-      <c r="I61" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J61" s="65">
+      <c r="D61" s="107"/>
+      <c r="E61" s="108"/>
+      <c r="F61" s="109"/>
+      <c r="G61" s="61" t="s">
+        <v>362</v>
+      </c>
+      <c r="H61" s="62"/>
+      <c r="I61" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J61" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K61" s="66"/>
+      <c r="K61" s="65"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
     <row r="62" spans="1:14" ht="37.799999999999997">
       <c r="A62" s="11"/>
-      <c r="B62" s="129"/>
-      <c r="C62" s="62" t="str">
+      <c r="B62" s="111"/>
+      <c r="C62" s="61" t="str">
         <f>master!C41</f>
         <v>Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D62" s="112" t="s">
-        <v>181</v>
-      </c>
-      <c r="E62" s="113"/>
-      <c r="F62" s="114"/>
-      <c r="G62" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H62" s="63"/>
-      <c r="I62" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" s="65">
+      <c r="D62" s="107" t="s">
+        <v>180</v>
+      </c>
+      <c r="E62" s="108"/>
+      <c r="F62" s="109"/>
+      <c r="G62" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H62" s="62"/>
+      <c r="I62" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K62" s="66"/>
+      <c r="K62" s="65"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
     <row r="63" spans="1:14" ht="25.2">
       <c r="A63" s="11"/>
-      <c r="B63" s="129"/>
-      <c r="C63" s="62" t="str">
+      <c r="B63" s="111"/>
+      <c r="C63" s="61" t="str">
         <f>master!C42</f>
         <v>（補足）Spring Bootプロジェクトの準備</v>
       </c>
-      <c r="D63" s="112" t="s">
-        <v>182</v>
-      </c>
-      <c r="E63" s="113"/>
-      <c r="F63" s="114"/>
-      <c r="G63" s="62" t="s">
-        <v>369</v>
-      </c>
-      <c r="H63" s="63"/>
-      <c r="I63" s="64" t="s">
+      <c r="D63" s="107" t="s">
+        <v>181</v>
+      </c>
+      <c r="E63" s="108"/>
+      <c r="F63" s="109"/>
+      <c r="G63" s="61" t="s">
+        <v>363</v>
+      </c>
+      <c r="H63" s="62"/>
+      <c r="I63" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="J63" s="65">
+      <c r="J63" s="64">
         <v>0</v>
       </c>
-      <c r="K63" s="66"/>
+      <c r="K63" s="65"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
     <row r="64" spans="1:14" ht="88.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="130"/>
-      <c r="C64" s="62" t="str">
+      <c r="B64" s="112"/>
+      <c r="C64" s="61" t="str">
         <f>master!C43</f>
         <v>Spring Bootアプリケーションの起動確認</v>
       </c>
-      <c r="D64" s="112" t="s">
-        <v>204</v>
-      </c>
-      <c r="E64" s="113"/>
-      <c r="F64" s="114"/>
-      <c r="G64" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="H64" s="63"/>
-      <c r="I64" s="64" t="s">
+      <c r="D64" s="107" t="s">
+        <v>203</v>
+      </c>
+      <c r="E64" s="108"/>
+      <c r="F64" s="109"/>
+      <c r="G64" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="H64" s="62"/>
+      <c r="I64" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="J64" s="65">
+      <c r="J64" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K64" s="66"/>
+      <c r="K64" s="65"/>
       <c r="L64" s="6"/>
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
     <row r="65" spans="1:14" ht="190.2" customHeight="1">
       <c r="A65" s="11"/>
-      <c r="B65" s="128" t="str">
+      <c r="B65" s="110" t="str">
         <f>master!B44</f>
         <v>ECサイト Webアプリの要件</v>
       </c>
-      <c r="C65" s="62" t="str">
+      <c r="C65" s="61" t="str">
         <f>master!C44</f>
         <v>ECサイト Webアプリの要件 – はじめに</v>
       </c>
-      <c r="D65" s="112" t="s">
-        <v>183</v>
-      </c>
-      <c r="E65" s="113"/>
-      <c r="F65" s="114"/>
-      <c r="G65" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H65" s="63"/>
-      <c r="I65" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J65" s="65">
+      <c r="D65" s="107" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" s="108"/>
+      <c r="F65" s="109"/>
+      <c r="G65" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H65" s="62"/>
+      <c r="I65" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J65" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K65" s="66"/>
+      <c r="K65" s="65"/>
       <c r="L65" s="6"/>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
     <row r="66" spans="1:14" ht="151.19999999999999">
       <c r="A66" s="11"/>
-      <c r="B66" s="129"/>
-      <c r="C66" s="62" t="str">
+      <c r="B66" s="111"/>
+      <c r="C66" s="61" t="str">
         <f>master!C45</f>
         <v>ECサイト Webアプリの要件➊ 画面</v>
       </c>
-      <c r="D66" s="112" t="s">
-        <v>185</v>
-      </c>
-      <c r="E66" s="113"/>
-      <c r="F66" s="114"/>
-      <c r="G66" s="62" t="s">
-        <v>372</v>
-      </c>
-      <c r="H66" s="63"/>
-      <c r="I66" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J66" s="65">
+      <c r="D66" s="107" t="s">
+        <v>184</v>
+      </c>
+      <c r="E66" s="108"/>
+      <c r="F66" s="109"/>
+      <c r="G66" s="61" t="s">
+        <v>366</v>
+      </c>
+      <c r="H66" s="62"/>
+      <c r="I66" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J66" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K66" s="66"/>
+      <c r="K66" s="65"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
     <row r="67" spans="1:14" ht="214.2">
       <c r="A67" s="11"/>
-      <c r="B67" s="129"/>
-      <c r="C67" s="62" t="str">
+      <c r="B67" s="111"/>
+      <c r="C67" s="61" t="str">
         <f>master!C46</f>
         <v>ECサイト Webアプリの要件➋ 機能</v>
       </c>
-      <c r="D67" s="112" t="s">
-        <v>186</v>
-      </c>
-      <c r="E67" s="113"/>
-      <c r="F67" s="114"/>
-      <c r="G67" s="62" t="s">
-        <v>373</v>
-      </c>
-      <c r="H67" s="63"/>
-      <c r="I67" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" s="65">
+      <c r="D67" s="107" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" s="108"/>
+      <c r="F67" s="109"/>
+      <c r="G67" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="H67" s="62"/>
+      <c r="I67" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K67" s="66"/>
+      <c r="K67" s="65"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
     <row r="68" spans="1:14" ht="63">
       <c r="A68" s="11"/>
-      <c r="B68" s="129"/>
-      <c r="C68" s="62" t="str">
+      <c r="B68" s="111"/>
+      <c r="C68" s="61" t="str">
         <f>master!C47</f>
         <v>ECサイト Webアプリの要件➌ 画面遷移</v>
       </c>
-      <c r="D68" s="112" t="s">
-        <v>187</v>
-      </c>
-      <c r="E68" s="113"/>
-      <c r="F68" s="114"/>
-      <c r="G68" s="62" t="s">
-        <v>374</v>
-      </c>
-      <c r="H68" s="63"/>
-      <c r="I68" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J68" s="65">
+      <c r="D68" s="107" t="s">
+        <v>186</v>
+      </c>
+      <c r="E68" s="108"/>
+      <c r="F68" s="109"/>
+      <c r="G68" s="61" t="s">
+        <v>368</v>
+      </c>
+      <c r="H68" s="62"/>
+      <c r="I68" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J68" s="64">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K68" s="66"/>
+      <c r="K68" s="65"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
     <row r="69" spans="1:14" ht="163.80000000000001">
       <c r="A69" s="11"/>
-      <c r="B69" s="129"/>
-      <c r="C69" s="62" t="str">
+      <c r="B69" s="111"/>
+      <c r="C69" s="61" t="str">
         <f>master!C48</f>
         <v>ECサイト Webアプリの要件❹ データ設計</v>
       </c>
-      <c r="D69" s="112" t="s">
-        <v>189</v>
-      </c>
-      <c r="E69" s="113"/>
-      <c r="F69" s="114"/>
-      <c r="G69" s="62" t="s">
-        <v>375</v>
-      </c>
-      <c r="H69" s="63"/>
-      <c r="I69" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J69" s="65">
+      <c r="D69" s="107" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" s="108"/>
+      <c r="F69" s="109"/>
+      <c r="G69" s="61" t="s">
+        <v>369</v>
+      </c>
+      <c r="H69" s="62"/>
+      <c r="I69" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="64">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K69" s="66"/>
+      <c r="K69" s="65"/>
       <c r="L69" s="6"/>
       <c r="M69" s="6"/>
       <c r="N69" s="6"/>
     </row>
     <row r="70" spans="1:14" ht="50.4">
       <c r="A70" s="11"/>
-      <c r="B70" s="129"/>
-      <c r="C70" s="62" t="str">
+      <c r="B70" s="111"/>
+      <c r="C70" s="61" t="str">
         <f>master!C49</f>
         <v>ECサイト Webアプリの要件❺ 初期データ</v>
       </c>
-      <c r="D70" s="112" t="s">
-        <v>190</v>
-      </c>
-      <c r="E70" s="113"/>
-      <c r="F70" s="114"/>
-      <c r="G70" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H70" s="63"/>
-      <c r="I70" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J70" s="65">
+      <c r="D70" s="107" t="s">
+        <v>189</v>
+      </c>
+      <c r="E70" s="108"/>
+      <c r="F70" s="109"/>
+      <c r="G70" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H70" s="62"/>
+      <c r="I70" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J70" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K70" s="66"/>
+      <c r="K70" s="65"/>
       <c r="L70" s="6"/>
       <c r="M70" s="6"/>
       <c r="N70" s="6"/>
     </row>
     <row r="71" spans="1:14" ht="37.799999999999997">
       <c r="A71" s="11"/>
-      <c r="B71" s="129"/>
-      <c r="C71" s="62" t="str">
+      <c r="B71" s="111"/>
+      <c r="C71" s="61" t="str">
         <f>master!C50</f>
         <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
       </c>
-      <c r="D71" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="E71" s="113"/>
-      <c r="F71" s="114"/>
-      <c r="G71" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H71" s="63"/>
-      <c r="I71" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J71" s="65">
+      <c r="D71" s="107" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" s="108"/>
+      <c r="F71" s="109"/>
+      <c r="G71" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H71" s="62"/>
+      <c r="I71" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J71" s="64">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K71" s="66"/>
+      <c r="K71" s="65"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
     <row r="72" spans="1:14" ht="37.799999999999997">
       <c r="A72" s="11"/>
-      <c r="B72" s="129"/>
-      <c r="C72" s="62" t="str">
+      <c r="B72" s="111"/>
+      <c r="C72" s="61" t="str">
         <f>master!C51</f>
         <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
       </c>
-      <c r="D72" s="112" t="s">
-        <v>193</v>
-      </c>
-      <c r="E72" s="113"/>
-      <c r="F72" s="114"/>
-      <c r="G72" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H72" s="63"/>
-      <c r="I72" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J72" s="65">
+      <c r="D72" s="107" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" s="108"/>
+      <c r="F72" s="109"/>
+      <c r="G72" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H72" s="62"/>
+      <c r="I72" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J72" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K72" s="66"/>
+      <c r="K72" s="65"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
     <row r="73" spans="1:14" ht="37.799999999999997">
       <c r="A73" s="11"/>
-      <c r="B73" s="130"/>
-      <c r="C73" s="62" t="str">
+      <c r="B73" s="112"/>
+      <c r="C73" s="61" t="str">
         <f>master!C52</f>
         <v>ECサイト Webアプリの要件❽ リソース構成</v>
       </c>
-      <c r="D73" s="112" t="s">
-        <v>192</v>
-      </c>
-      <c r="E73" s="113"/>
-      <c r="F73" s="114"/>
-      <c r="G73" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H73" s="63"/>
-      <c r="I73" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J73" s="65">
+      <c r="D73" s="107" t="s">
+        <v>191</v>
+      </c>
+      <c r="E73" s="108"/>
+      <c r="F73" s="109"/>
+      <c r="G73" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H73" s="62"/>
+      <c r="I73" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J73" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K73" s="66"/>
+      <c r="K73" s="65"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
     <row r="74" spans="1:14" ht="25.2">
       <c r="A74" s="11"/>
-      <c r="B74" s="128" t="str">
+      <c r="B74" s="110" t="str">
         <f>master!B53</f>
         <v>ハンズオン</v>
       </c>
-      <c r="C74" s="62" t="str">
+      <c r="C74" s="61" t="str">
         <f>master!C53</f>
         <v>バイブコーディング – はじめに</v>
       </c>
-      <c r="D74" s="112" t="s">
-        <v>194</v>
-      </c>
-      <c r="E74" s="113"/>
-      <c r="F74" s="114"/>
-      <c r="G74" s="62" t="s">
-        <v>369</v>
-      </c>
-      <c r="H74" s="63"/>
-      <c r="I74" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J74" s="65">
+      <c r="D74" s="107" t="s">
+        <v>193</v>
+      </c>
+      <c r="E74" s="108"/>
+      <c r="F74" s="109"/>
+      <c r="G74" s="61" t="s">
+        <v>363</v>
+      </c>
+      <c r="H74" s="62"/>
+      <c r="I74" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" s="64">
         <v>1.0416666666666666E-2</v>
       </c>
-      <c r="K74" s="66"/>
+      <c r="K74" s="65"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
     <row r="75" spans="1:14" ht="138.6">
       <c r="A75" s="11"/>
-      <c r="B75" s="129"/>
-      <c r="C75" s="62" t="str">
+      <c r="B75" s="111"/>
+      <c r="C75" s="61" t="str">
         <f>master!C54</f>
         <v>[構造理解] Webアプリケーションで必要なもの</v>
       </c>
-      <c r="D75" s="112" t="s">
-        <v>195</v>
-      </c>
-      <c r="E75" s="113"/>
-      <c r="F75" s="114"/>
-      <c r="G75" s="62" t="s">
-        <v>376</v>
-      </c>
-      <c r="H75" s="63"/>
-      <c r="I75" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="65">
+      <c r="D75" s="107" t="s">
+        <v>194</v>
+      </c>
+      <c r="E75" s="108"/>
+      <c r="F75" s="109"/>
+      <c r="G75" s="61" t="s">
+        <v>370</v>
+      </c>
+      <c r="H75" s="62"/>
+      <c r="I75" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="64">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K75" s="66"/>
+      <c r="K75" s="65"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
     <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="129"/>
-      <c r="C76" s="81" t="str">
+      <c r="B76" s="111"/>
+      <c r="C76" s="79" t="str">
         <f>master!C55</f>
         <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
       </c>
-      <c r="D76" s="112" t="s">
-        <v>205</v>
-      </c>
-      <c r="E76" s="113"/>
-      <c r="F76" s="114"/>
-      <c r="G76" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H76" s="63"/>
-      <c r="I76" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J76" s="65">
+      <c r="D76" s="107" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" s="108"/>
+      <c r="F76" s="109"/>
+      <c r="G76" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H76" s="62"/>
+      <c r="I76" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="64">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K76" s="66"/>
+      <c r="K76" s="65"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
     <row r="77" spans="1:14" ht="88.2" customHeight="1">
       <c r="A77" s="11"/>
-      <c r="B77" s="129"/>
-      <c r="C77" s="82"/>
-      <c r="D77" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E77" s="113"/>
-      <c r="F77" s="114"/>
-      <c r="G77" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="H77" s="63"/>
-      <c r="I77" s="64"/>
-      <c r="J77" s="65"/>
-      <c r="K77" s="66"/>
+      <c r="B77" s="111"/>
+      <c r="C77" s="80"/>
+      <c r="D77" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E77" s="108"/>
+      <c r="F77" s="109"/>
+      <c r="G77" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="H77" s="62"/>
+      <c r="I77" s="63"/>
+      <c r="J77" s="64"/>
+      <c r="K77" s="65"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
     <row r="78" spans="1:14" ht="50.4">
       <c r="A78" s="11"/>
-      <c r="B78" s="129"/>
-      <c r="C78" s="81" t="str">
+      <c r="B78" s="111"/>
+      <c r="C78" s="79" t="str">
         <f>master!C56</f>
         <v>バイブコーディング➋ データベースのテーブルを準備する</v>
       </c>
-      <c r="D78" s="112" t="s">
-        <v>209</v>
-      </c>
-      <c r="E78" s="113"/>
-      <c r="F78" s="114"/>
-      <c r="G78" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H78" s="63"/>
-      <c r="I78" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J78" s="65">
+      <c r="D78" s="107" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" s="108"/>
+      <c r="F78" s="109"/>
+      <c r="G78" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H78" s="62"/>
+      <c r="I78" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J78" s="64">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K78" s="66"/>
+      <c r="K78" s="65"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
     <row r="79" spans="1:14" ht="88.2">
       <c r="A79" s="11"/>
-      <c r="B79" s="129"/>
-      <c r="C79" s="82"/>
-      <c r="D79" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E79" s="113"/>
-      <c r="F79" s="114"/>
-      <c r="G79" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="H79" s="63"/>
-      <c r="I79" s="64"/>
-      <c r="J79" s="65"/>
-      <c r="K79" s="66"/>
+      <c r="B79" s="111"/>
+      <c r="C79" s="80"/>
+      <c r="D79" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E79" s="108"/>
+      <c r="F79" s="109"/>
+      <c r="G79" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="H79" s="62"/>
+      <c r="I79" s="63"/>
+      <c r="J79" s="64"/>
+      <c r="K79" s="65"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
     <row r="80" spans="1:14" ht="50.4">
       <c r="A80" s="11"/>
-      <c r="B80" s="129"/>
-      <c r="C80" s="81" t="str">
+      <c r="B80" s="111"/>
+      <c r="C80" s="79" t="str">
         <f>master!C57</f>
         <v>バイブコーディング➌ データベースのデータを準備する</v>
       </c>
-      <c r="D80" s="112" t="s">
-        <v>208</v>
-      </c>
-      <c r="E80" s="113"/>
-      <c r="F80" s="114"/>
-      <c r="G80" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H80" s="63"/>
-      <c r="I80" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J80" s="65">
+      <c r="D80" s="107" t="s">
+        <v>207</v>
+      </c>
+      <c r="E80" s="108"/>
+      <c r="F80" s="109"/>
+      <c r="G80" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H80" s="62"/>
+      <c r="I80" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J80" s="64">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K80" s="66"/>
+      <c r="K80" s="65"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
     <row r="81" spans="1:14" ht="88.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="129"/>
-      <c r="C81" s="82"/>
-      <c r="D81" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E81" s="113"/>
-      <c r="F81" s="114"/>
-      <c r="G81" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="H81" s="63"/>
-      <c r="I81" s="64"/>
-      <c r="J81" s="65"/>
-      <c r="K81" s="66"/>
+      <c r="B81" s="111"/>
+      <c r="C81" s="80"/>
+      <c r="D81" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E81" s="108"/>
+      <c r="F81" s="109"/>
+      <c r="G81" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="H81" s="62"/>
+      <c r="I81" s="63"/>
+      <c r="J81" s="64"/>
+      <c r="K81" s="65"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
     </row>
     <row r="82" spans="1:14" ht="63">
       <c r="A82" s="11"/>
-      <c r="B82" s="129"/>
-      <c r="C82" s="81" t="str">
+      <c r="B82" s="111"/>
+      <c r="C82" s="79" t="str">
         <f>master!C58</f>
         <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
       </c>
-      <c r="D82" s="112" t="s">
-        <v>207</v>
-      </c>
-      <c r="E82" s="113"/>
-      <c r="F82" s="114"/>
-      <c r="G82" s="62" t="s">
-        <v>374</v>
-      </c>
-      <c r="H82" s="63"/>
-      <c r="I82" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J82" s="65">
+      <c r="D82" s="107" t="s">
+        <v>206</v>
+      </c>
+      <c r="E82" s="108"/>
+      <c r="F82" s="109"/>
+      <c r="G82" s="61" t="s">
+        <v>368</v>
+      </c>
+      <c r="H82" s="62"/>
+      <c r="I82" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K82" s="66"/>
+      <c r="K82" s="65"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
       <c r="N82" s="6"/>
     </row>
     <row r="83" spans="1:14" ht="88.2">
       <c r="A83" s="11"/>
-      <c r="B83" s="129"/>
-      <c r="C83" s="82"/>
-      <c r="D83" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E83" s="113"/>
-      <c r="F83" s="114"/>
-      <c r="G83" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="H83" s="63"/>
-      <c r="I83" s="64"/>
-      <c r="J83" s="65"/>
-      <c r="K83" s="66"/>
+      <c r="B83" s="111"/>
+      <c r="C83" s="80"/>
+      <c r="D83" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E83" s="108"/>
+      <c r="F83" s="109"/>
+      <c r="G83" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="H83" s="62"/>
+      <c r="I83" s="63"/>
+      <c r="J83" s="64"/>
+      <c r="K83" s="65"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
     <row r="84" spans="1:14" ht="50.4">
       <c r="A84" s="11"/>
-      <c r="B84" s="129"/>
-      <c r="C84" s="62" t="str">
+      <c r="B84" s="111"/>
+      <c r="C84" s="61" t="str">
         <f>master!C59</f>
         <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
       </c>
-      <c r="D84" s="112" t="s">
-        <v>197</v>
-      </c>
-      <c r="E84" s="113"/>
-      <c r="F84" s="114"/>
-      <c r="G84" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H84" s="63"/>
-      <c r="I84" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J84" s="65">
+      <c r="D84" s="107" t="s">
+        <v>196</v>
+      </c>
+      <c r="E84" s="108"/>
+      <c r="F84" s="109"/>
+      <c r="G84" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H84" s="62"/>
+      <c r="I84" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J84" s="64">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K84" s="66"/>
+      <c r="K84" s="65"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
     <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="129"/>
-      <c r="C85" s="62" t="str">
+      <c r="B85" s="111"/>
+      <c r="C85" s="61" t="str">
         <f>master!C60</f>
         <v>[解説] Entity/Modelクラスの例（抜粋）</v>
       </c>
-      <c r="D85" s="112" t="s">
-        <v>198</v>
-      </c>
-      <c r="E85" s="113"/>
-      <c r="F85" s="114"/>
-      <c r="G85" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H85" s="63"/>
-      <c r="I85" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J85" s="65">
+      <c r="D85" s="107" t="s">
+        <v>197</v>
+      </c>
+      <c r="E85" s="108"/>
+      <c r="F85" s="109"/>
+      <c r="G85" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H85" s="62"/>
+      <c r="I85" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J85" s="64">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K85" s="66"/>
+      <c r="K85" s="65"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
     <row r="86" spans="1:14" ht="37.799999999999997">
       <c r="A86" s="11"/>
-      <c r="B86" s="129"/>
-      <c r="C86" s="62" t="str">
+      <c r="B86" s="111"/>
+      <c r="C86" s="61" t="str">
         <f>master!C61</f>
         <v>[解説] Serviceクラスの例（抜粋）</v>
       </c>
-      <c r="D86" s="112" t="s">
-        <v>199</v>
-      </c>
-      <c r="E86" s="113"/>
-      <c r="F86" s="114"/>
-      <c r="G86" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H86" s="63"/>
-      <c r="I86" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J86" s="65">
+      <c r="D86" s="107" t="s">
+        <v>198</v>
+      </c>
+      <c r="E86" s="108"/>
+      <c r="F86" s="109"/>
+      <c r="G86" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H86" s="62"/>
+      <c r="I86" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J86" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K86" s="66"/>
+      <c r="K86" s="65"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
     <row r="87" spans="1:14" ht="50.4">
       <c r="A87" s="11"/>
-      <c r="B87" s="129"/>
-      <c r="C87" s="81" t="str">
+      <c r="B87" s="111"/>
+      <c r="C87" s="79" t="str">
         <f>master!C62</f>
         <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
       </c>
-      <c r="D87" s="112" t="s">
-        <v>206</v>
-      </c>
-      <c r="E87" s="113"/>
-      <c r="F87" s="114"/>
-      <c r="G87" s="62" t="s">
-        <v>371</v>
-      </c>
-      <c r="H87" s="63"/>
-      <c r="I87" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J87" s="65">
+      <c r="D87" s="107" t="s">
+        <v>205</v>
+      </c>
+      <c r="E87" s="108"/>
+      <c r="F87" s="109"/>
+      <c r="G87" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="H87" s="62"/>
+      <c r="I87" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J87" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K87" s="66"/>
+      <c r="K87" s="65"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
       <c r="N87" s="6"/>
     </row>
     <row r="88" spans="1:14" ht="88.2">
       <c r="A88" s="11"/>
-      <c r="B88" s="129"/>
-      <c r="C88" s="82"/>
-      <c r="D88" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E88" s="113"/>
-      <c r="F88" s="114"/>
-      <c r="G88" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="H88" s="63"/>
-      <c r="I88" s="64"/>
-      <c r="J88" s="65"/>
-      <c r="K88" s="66"/>
+      <c r="B88" s="111"/>
+      <c r="C88" s="80"/>
+      <c r="D88" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E88" s="108"/>
+      <c r="F88" s="109"/>
+      <c r="G88" s="61" t="s">
+        <v>364</v>
+      </c>
+      <c r="H88" s="62"/>
+      <c r="I88" s="63"/>
+      <c r="J88" s="64"/>
+      <c r="K88" s="65"/>
       <c r="L88" s="6"/>
       <c r="M88" s="6"/>
       <c r="N88" s="6"/>
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="129"/>
-      <c r="C89" s="62" t="str">
+      <c r="B89" s="111"/>
+      <c r="C89" s="61" t="str">
         <f>master!C63</f>
         <v>[解説] Controllerクラスの例（抜粋）</v>
       </c>
-      <c r="D89" s="112" t="s">
-        <v>200</v>
-      </c>
-      <c r="E89" s="113"/>
-      <c r="F89" s="114"/>
-      <c r="G89" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H89" s="63"/>
-      <c r="I89" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J89" s="65">
+      <c r="D89" s="107" t="s">
+        <v>199</v>
+      </c>
+      <c r="E89" s="108"/>
+      <c r="F89" s="109"/>
+      <c r="G89" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H89" s="62"/>
+      <c r="I89" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J89" s="64">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K89" s="66"/>
+      <c r="K89" s="65"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
     <row r="90" spans="1:14" ht="37.799999999999997">
       <c r="A90" s="11"/>
-      <c r="B90" s="129"/>
-      <c r="C90" s="62" t="str">
+      <c r="B90" s="111"/>
+      <c r="C90" s="61" t="str">
         <f>master!C64</f>
         <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
       </c>
-      <c r="D90" s="112" t="s">
-        <v>201</v>
-      </c>
-      <c r="E90" s="113"/>
-      <c r="F90" s="114"/>
-      <c r="G90" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H90" s="63"/>
-      <c r="I90" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J90" s="65">
+      <c r="D90" s="107" t="s">
+        <v>200</v>
+      </c>
+      <c r="E90" s="108"/>
+      <c r="F90" s="109"/>
+      <c r="G90" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H90" s="62"/>
+      <c r="I90" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" s="64">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K90" s="66"/>
+      <c r="K90" s="65"/>
       <c r="L90" s="6"/>
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
     <row r="91" spans="1:14" ht="37.799999999999997">
       <c r="A91" s="11"/>
-      <c r="B91" s="129"/>
-      <c r="C91" s="62" t="str">
+      <c r="B91" s="111"/>
+      <c r="C91" s="61" t="str">
         <f>master!C65</f>
         <v>[解説] Formクラスの例（抜粋）</v>
       </c>
-      <c r="D91" s="112" t="s">
-        <v>202</v>
-      </c>
-      <c r="E91" s="113"/>
-      <c r="F91" s="114"/>
-      <c r="G91" s="62" t="s">
-        <v>366</v>
-      </c>
-      <c r="H91" s="63"/>
-      <c r="I91" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J91" s="65">
+      <c r="D91" s="107" t="s">
+        <v>201</v>
+      </c>
+      <c r="E91" s="108"/>
+      <c r="F91" s="109"/>
+      <c r="G91" s="61" t="s">
+        <v>360</v>
+      </c>
+      <c r="H91" s="62"/>
+      <c r="I91" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J91" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K91" s="66"/>
+      <c r="K91" s="65"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
     <row r="92" spans="1:14" ht="75.599999999999994">
       <c r="A92" s="11"/>
-      <c r="B92" s="129"/>
-      <c r="C92" s="81" t="str">
+      <c r="B92" s="111"/>
+      <c r="C92" s="79" t="str">
         <f>master!C66</f>
         <v>バイブコーディング❻ 動作を確認する</v>
       </c>
-      <c r="D92" s="112" t="s">
-        <v>203</v>
-      </c>
-      <c r="E92" s="113"/>
-      <c r="F92" s="114"/>
-      <c r="G92" s="62" t="s">
-        <v>367</v>
-      </c>
-      <c r="H92" s="63"/>
-      <c r="I92" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J92" s="65">
+      <c r="D92" s="107" t="s">
+        <v>202</v>
+      </c>
+      <c r="E92" s="108"/>
+      <c r="F92" s="109"/>
+      <c r="G92" s="61" t="s">
+        <v>361</v>
+      </c>
+      <c r="H92" s="62"/>
+      <c r="I92" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J92" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K92" s="66"/>
+      <c r="K92" s="65"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
     <row r="93" spans="1:14" ht="63">
       <c r="A93" s="11"/>
-      <c r="B93" s="130"/>
-      <c r="C93" s="82"/>
-      <c r="D93" s="112" t="s">
-        <v>210</v>
-      </c>
-      <c r="E93" s="113"/>
-      <c r="F93" s="114"/>
-      <c r="G93" s="62" t="s">
-        <v>374</v>
-      </c>
-      <c r="H93" s="63"/>
-      <c r="I93" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J93" s="65">
+      <c r="B93" s="112"/>
+      <c r="C93" s="80"/>
+      <c r="D93" s="107" t="s">
+        <v>209</v>
+      </c>
+      <c r="E93" s="108"/>
+      <c r="F93" s="109"/>
+      <c r="G93" s="61" t="s">
+        <v>368</v>
+      </c>
+      <c r="H93" s="62"/>
+      <c r="I93" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J93" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K93" s="66"/>
+      <c r="K93" s="65"/>
       <c r="L93" s="6"/>
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
     <row r="94" spans="1:14" ht="100.8">
       <c r="A94" s="11"/>
-      <c r="B94" s="128" t="str">
+      <c r="B94" s="110" t="str">
         <f>master!B69</f>
         <v>Gitとは</v>
       </c>
-      <c r="C94" s="62" t="str">
+      <c r="C94" s="61" t="str">
         <f>master!C69</f>
         <v>Gitとは</v>
       </c>
-      <c r="D94" s="112" t="s">
-        <v>212</v>
-      </c>
-      <c r="E94" s="113"/>
-      <c r="F94" s="114"/>
-      <c r="G94" s="62" t="s">
-        <v>410</v>
-      </c>
-      <c r="H94" s="63"/>
-      <c r="I94" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J94" s="65">
+      <c r="D94" s="107" t="s">
+        <v>211</v>
+      </c>
+      <c r="E94" s="108"/>
+      <c r="F94" s="109"/>
+      <c r="G94" s="61" t="s">
+        <v>421</v>
+      </c>
+      <c r="H94" s="62"/>
+      <c r="I94" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J94" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K94" s="66"/>
+      <c r="K94" s="65"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
     <row r="95" spans="1:14" ht="189">
       <c r="A95" s="11"/>
-      <c r="B95" s="130"/>
-      <c r="C95" s="62" t="str">
+      <c r="B95" s="112"/>
+      <c r="C95" s="61" t="str">
         <f>master!C70</f>
         <v>Gitの基本的な流れ</v>
       </c>
-      <c r="D95" s="112" t="s">
-        <v>218</v>
-      </c>
-      <c r="E95" s="113"/>
-      <c r="F95" s="114"/>
-      <c r="G95" s="62" t="s">
-        <v>411</v>
-      </c>
-      <c r="H95" s="63"/>
-      <c r="I95" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J95" s="65">
+      <c r="D95" s="107" t="s">
+        <v>216</v>
+      </c>
+      <c r="E95" s="108"/>
+      <c r="F95" s="109"/>
+      <c r="G95" s="61" t="s">
+        <v>422</v>
+      </c>
+      <c r="H95" s="62"/>
+      <c r="I95" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J95" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K95" s="66"/>
+      <c r="K95" s="65"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
     <row r="96" spans="1:14" ht="126">
       <c r="A96" s="11"/>
-      <c r="B96" s="128" t="str">
+      <c r="B96" s="110" t="str">
         <f>master!B71</f>
         <v>VS Code上でGitを使う手順</v>
       </c>
-      <c r="C96" s="62" t="str">
+      <c r="C96" s="61" t="str">
         <f>master!C71</f>
         <v>VS Code上でGitを使う手順-1 【ユーザ名等の登録】</v>
       </c>
-      <c r="D96" s="112" t="s">
-        <v>213</v>
-      </c>
-      <c r="E96" s="113"/>
-      <c r="F96" s="114"/>
-      <c r="G96" s="62" t="s">
-        <v>412</v>
-      </c>
-      <c r="H96" s="63"/>
-      <c r="I96" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J96" s="65">
+      <c r="D96" s="107" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" s="108"/>
+      <c r="F96" s="109"/>
+      <c r="G96" s="61" t="s">
+        <v>423</v>
+      </c>
+      <c r="H96" s="62"/>
+      <c r="I96" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K96" s="66"/>
+      <c r="K96" s="65"/>
       <c r="L96" s="6"/>
       <c r="M96" s="6"/>
       <c r="N96" s="6"/>
     </row>
     <row r="97" spans="1:14" ht="37.799999999999997">
       <c r="A97" s="11"/>
-      <c r="B97" s="129"/>
-      <c r="C97" s="62" t="str">
+      <c r="B97" s="111"/>
+      <c r="C97" s="61" t="str">
         <f>master!C72</f>
         <v>VS Code上でGitを使う手順-2 【リポジトリの初期化】</v>
       </c>
-      <c r="D97" s="112" t="s">
-        <v>214</v>
-      </c>
-      <c r="E97" s="113"/>
-      <c r="F97" s="114"/>
-      <c r="G97" s="62" t="s">
-        <v>413</v>
-      </c>
-      <c r="H97" s="63"/>
-      <c r="I97" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J97" s="65">
+      <c r="D97" s="107" t="s">
+        <v>213</v>
+      </c>
+      <c r="E97" s="108"/>
+      <c r="F97" s="109"/>
+      <c r="G97" s="61" t="s">
+        <v>424</v>
+      </c>
+      <c r="H97" s="62"/>
+      <c r="I97" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J97" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K97" s="66"/>
+      <c r="K97" s="65"/>
       <c r="L97" s="6"/>
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
     <row r="98" spans="1:14" ht="50.4">
       <c r="A98" s="11"/>
-      <c r="B98" s="129"/>
-      <c r="C98" s="62" t="str">
+      <c r="B98" s="111"/>
+      <c r="C98" s="61" t="str">
         <f>master!C73</f>
         <v>VS Code上でGitを使う手順-3 【最初のcommit】</v>
       </c>
-      <c r="D98" s="112" t="s">
-        <v>215</v>
-      </c>
-      <c r="E98" s="113"/>
-      <c r="F98" s="114"/>
-      <c r="G98" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="H98" s="63"/>
-      <c r="I98" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J98" s="65">
+      <c r="D98" s="107" t="s">
+        <v>214</v>
+      </c>
+      <c r="E98" s="108"/>
+      <c r="F98" s="109"/>
+      <c r="G98" s="61" t="s">
+        <v>425</v>
+      </c>
+      <c r="H98" s="62"/>
+      <c r="I98" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J98" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K98" s="66"/>
+      <c r="K98" s="65"/>
       <c r="L98" s="6"/>
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
     <row r="99" spans="1:14" ht="50.4">
       <c r="A99" s="11"/>
-      <c r="B99" s="129"/>
-      <c r="C99" s="62" t="str">
+      <c r="B99" s="111"/>
+      <c r="C99" s="61" t="str">
         <f>master!C74</f>
         <v>VS Code上でGitを使う手順-4 【2回目以降のコミット】</v>
       </c>
-      <c r="D99" s="112" t="s">
-        <v>216</v>
-      </c>
-      <c r="E99" s="113"/>
-      <c r="F99" s="114"/>
-      <c r="G99" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="H99" s="63"/>
-      <c r="I99" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J99" s="65">
+      <c r="D99" s="107" t="s">
+        <v>420</v>
+      </c>
+      <c r="E99" s="108"/>
+      <c r="F99" s="109"/>
+      <c r="G99" s="61" t="s">
+        <v>425</v>
+      </c>
+      <c r="H99" s="62"/>
+      <c r="I99" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J99" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K99" s="66"/>
+      <c r="K99" s="65"/>
       <c r="L99" s="6"/>
       <c r="M99" s="6"/>
       <c r="N99" s="6"/>
     </row>
     <row r="100" spans="1:14" ht="37.799999999999997">
       <c r="A100" s="11"/>
-      <c r="B100" s="129"/>
-      <c r="C100" s="62" t="str">
+      <c r="B100" s="111"/>
+      <c r="C100" s="61" t="str">
         <f>master!C75</f>
         <v>VS Code上でGitを使う手順-5 【過去のcommitの確認】</v>
       </c>
-      <c r="D100" s="112" t="s">
-        <v>217</v>
-      </c>
-      <c r="E100" s="113"/>
-      <c r="F100" s="114"/>
-      <c r="G100" s="62" t="s">
-        <v>413</v>
-      </c>
-      <c r="H100" s="63"/>
-      <c r="I100" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J100" s="65">
+      <c r="D100" s="107" t="s">
+        <v>215</v>
+      </c>
+      <c r="E100" s="108"/>
+      <c r="F100" s="109"/>
+      <c r="G100" s="61" t="s">
+        <v>424</v>
+      </c>
+      <c r="H100" s="62"/>
+      <c r="I100" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J100" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K100" s="66"/>
+      <c r="K100" s="65"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
       <c r="N100" s="6"/>
     </row>
     <row r="101" spans="1:14" ht="63">
       <c r="A101" s="11"/>
-      <c r="B101" s="130"/>
-      <c r="C101" s="62" t="str">
+      <c r="B101" s="112"/>
+      <c r="C101" s="61" t="str">
         <f>master!C76</f>
         <v>VS Code上でGitを使う手順-6 【過去の状態に戻す】</v>
       </c>
-      <c r="D101" s="112" t="s">
-        <v>219</v>
-      </c>
-      <c r="E101" s="113"/>
-      <c r="F101" s="114"/>
-      <c r="G101" s="62" t="s">
-        <v>415</v>
-      </c>
-      <c r="H101" s="63"/>
-      <c r="I101" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J101" s="65">
+      <c r="D101" s="107" t="s">
+        <v>217</v>
+      </c>
+      <c r="E101" s="108"/>
+      <c r="F101" s="109"/>
+      <c r="G101" s="61" t="s">
+        <v>426</v>
+      </c>
+      <c r="H101" s="62"/>
+      <c r="I101" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J101" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K101" s="66"/>
+      <c r="K101" s="65"/>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
       <c r="N101" s="6"/>
     </row>
     <row r="102" spans="1:14" ht="214.2">
       <c r="A102" s="11"/>
-      <c r="B102" s="80" t="str">
+      <c r="B102" s="90" t="str">
         <f>master!B67</f>
         <v>課題1の実施</v>
       </c>
-      <c r="C102" s="62" t="str">
+      <c r="C102" s="61" t="str">
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D102" s="112" t="s">
-        <v>211</v>
-      </c>
-      <c r="E102" s="113"/>
-      <c r="F102" s="114"/>
-      <c r="G102" s="62" t="s">
-        <v>373</v>
-      </c>
-      <c r="H102" s="63"/>
-      <c r="I102" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J102" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K102" s="66"/>
+      <c r="D102" s="107" t="s">
+        <v>210</v>
+      </c>
+      <c r="E102" s="108"/>
+      <c r="F102" s="109"/>
+      <c r="G102" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="H102" s="62"/>
+      <c r="I102" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J102" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K102" s="65"/>
       <c r="L102" s="6"/>
       <c r="M102" s="6"/>
       <c r="N102" s="6"/>
     </row>
-    <row r="103" spans="1:14" ht="88.2">
+    <row r="103" spans="1:14" ht="89.4">
       <c r="A103" s="11"/>
-      <c r="B103" s="84" t="str">
+      <c r="B103" s="127" t="str">
         <f>master!B78</f>
         <v>システム開発プロセスの導入</v>
       </c>
-      <c r="C103" s="83" t="str">
+      <c r="C103" s="81" t="str">
         <f>master!C78</f>
         <v>講義の目的</v>
       </c>
-      <c r="D103" s="116" t="s">
-        <v>254</v>
-      </c>
-      <c r="E103" s="117"/>
-      <c r="F103" s="118"/>
+      <c r="D103" s="104" t="s">
+        <v>251</v>
+      </c>
+      <c r="E103" s="105"/>
+      <c r="F103" s="106"/>
       <c r="G103" s="51" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="49" t="s">
@@ -9396,21 +9466,21 @@
     </row>
     <row r="104" spans="1:14" ht="37.799999999999997">
       <c r="A104" s="11"/>
-      <c r="B104" s="119" t="str">
+      <c r="B104" s="124" t="str">
         <f>master!B79</f>
         <v>システム開発におけるソフトウェア開発ライフサイクル</v>
       </c>
-      <c r="C104" s="83" t="str">
+      <c r="C104" s="81" t="str">
         <f>master!C79</f>
         <v>ソフトウェア開発ライフサイクル</v>
       </c>
-      <c r="D104" s="116" t="s">
-        <v>255</v>
-      </c>
-      <c r="E104" s="117"/>
-      <c r="F104" s="118"/>
+      <c r="D104" s="104" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" s="105"/>
+      <c r="F104" s="106"/>
       <c r="G104" s="51" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="49" t="s">
@@ -9426,18 +9496,18 @@
     </row>
     <row r="105" spans="1:14" ht="277.2">
       <c r="A105" s="11"/>
-      <c r="B105" s="120"/>
-      <c r="C105" s="83" t="str">
+      <c r="B105" s="125"/>
+      <c r="C105" s="81" t="str">
         <f>master!C80</f>
         <v>ソフトウェア開発ライフサイクルの種類</v>
       </c>
-      <c r="D105" s="116" t="s">
-        <v>256</v>
-      </c>
-      <c r="E105" s="117"/>
-      <c r="F105" s="118"/>
+      <c r="D105" s="104" t="s">
+        <v>253</v>
+      </c>
+      <c r="E105" s="105"/>
+      <c r="F105" s="106"/>
       <c r="G105" s="51" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="49" t="s">
@@ -9453,20 +9523,20 @@
     </row>
     <row r="106" spans="1:14" ht="151.19999999999999">
       <c r="A106" s="11"/>
-      <c r="B106" s="119" t="str">
+      <c r="B106" s="124" t="str">
         <f>master!B81</f>
         <v>TERASOLUNAとは</v>
       </c>
-      <c r="C106" s="83" t="s">
-        <v>232</v>
-      </c>
-      <c r="D106" s="116" t="s">
-        <v>257</v>
-      </c>
-      <c r="E106" s="117"/>
-      <c r="F106" s="118"/>
+      <c r="C106" s="81" t="s">
+        <v>229</v>
+      </c>
+      <c r="D106" s="104" t="s">
+        <v>254</v>
+      </c>
+      <c r="E106" s="105"/>
+      <c r="F106" s="106"/>
       <c r="G106" s="51" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="49" t="s">
@@ -9482,17 +9552,17 @@
     </row>
     <row r="107" spans="1:14" ht="138.6">
       <c r="A107" s="11"/>
-      <c r="B107" s="120"/>
-      <c r="C107" s="83" t="s">
-        <v>233</v>
-      </c>
-      <c r="D107" s="116" t="s">
-        <v>258</v>
-      </c>
-      <c r="E107" s="117"/>
-      <c r="F107" s="118"/>
+      <c r="B107" s="125"/>
+      <c r="C107" s="81" t="s">
+        <v>230</v>
+      </c>
+      <c r="D107" s="104" t="s">
+        <v>255</v>
+      </c>
+      <c r="E107" s="105"/>
+      <c r="F107" s="106"/>
       <c r="G107" s="51" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="49" t="s">
@@ -9508,20 +9578,20 @@
     </row>
     <row r="108" spans="1:14" ht="189">
       <c r="A108" s="11"/>
-      <c r="B108" s="119" t="str">
+      <c r="B108" s="124" t="str">
         <f>master!B83</f>
         <v>V字モデルとは</v>
       </c>
-      <c r="C108" s="83" t="s">
-        <v>236</v>
-      </c>
-      <c r="D108" s="116" t="s">
-        <v>259</v>
-      </c>
-      <c r="E108" s="117"/>
-      <c r="F108" s="118"/>
+      <c r="C108" s="81" t="s">
+        <v>233</v>
+      </c>
+      <c r="D108" s="104" t="s">
+        <v>256</v>
+      </c>
+      <c r="E108" s="105"/>
+      <c r="F108" s="106"/>
       <c r="G108" s="51" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="49" t="s">
@@ -9537,17 +9607,17 @@
     </row>
     <row r="109" spans="1:14" ht="100.8">
       <c r="A109" s="11"/>
-      <c r="B109" s="121"/>
-      <c r="C109" s="83" t="s">
-        <v>234</v>
-      </c>
-      <c r="D109" s="116" t="s">
-        <v>260</v>
-      </c>
-      <c r="E109" s="117"/>
-      <c r="F109" s="118"/>
+      <c r="B109" s="126"/>
+      <c r="C109" s="81" t="s">
+        <v>231</v>
+      </c>
+      <c r="D109" s="104" t="s">
+        <v>257</v>
+      </c>
+      <c r="E109" s="105"/>
+      <c r="F109" s="106"/>
       <c r="G109" s="51" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="49" t="s">
@@ -9563,17 +9633,17 @@
     </row>
     <row r="110" spans="1:14" ht="113.4">
       <c r="A110" s="11"/>
-      <c r="B110" s="121"/>
-      <c r="C110" s="83" t="s">
-        <v>238</v>
-      </c>
-      <c r="D110" s="116" t="s">
-        <v>261</v>
-      </c>
-      <c r="E110" s="117"/>
-      <c r="F110" s="118"/>
+      <c r="B110" s="126"/>
+      <c r="C110" s="81" t="s">
+        <v>235</v>
+      </c>
+      <c r="D110" s="104" t="s">
+        <v>258</v>
+      </c>
+      <c r="E110" s="105"/>
+      <c r="F110" s="106"/>
       <c r="G110" s="51" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="49" t="s">
@@ -9589,17 +9659,17 @@
     </row>
     <row r="111" spans="1:14" ht="302.39999999999998">
       <c r="A111" s="11"/>
-      <c r="B111" s="121"/>
-      <c r="C111" s="83" t="s">
-        <v>240</v>
-      </c>
-      <c r="D111" s="116" t="s">
-        <v>262</v>
-      </c>
-      <c r="E111" s="117"/>
-      <c r="F111" s="118"/>
+      <c r="B111" s="126"/>
+      <c r="C111" s="81" t="s">
+        <v>237</v>
+      </c>
+      <c r="D111" s="104" t="s">
+        <v>259</v>
+      </c>
+      <c r="E111" s="105"/>
+      <c r="F111" s="106"/>
       <c r="G111" s="51" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="49" t="s">
@@ -9615,17 +9685,17 @@
     </row>
     <row r="112" spans="1:14" ht="138.6">
       <c r="A112" s="11"/>
-      <c r="B112" s="121"/>
-      <c r="C112" s="83" t="s">
-        <v>242</v>
-      </c>
-      <c r="D112" s="116" t="s">
-        <v>263</v>
-      </c>
-      <c r="E112" s="117"/>
-      <c r="F112" s="118"/>
+      <c r="B112" s="126"/>
+      <c r="C112" s="81" t="s">
+        <v>239</v>
+      </c>
+      <c r="D112" s="104" t="s">
+        <v>260</v>
+      </c>
+      <c r="E112" s="105"/>
+      <c r="F112" s="106"/>
       <c r="G112" s="51" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="49" t="s">
@@ -9641,17 +9711,17 @@
     </row>
     <row r="113" spans="1:14" ht="88.2">
       <c r="A113" s="11"/>
-      <c r="B113" s="121"/>
-      <c r="C113" s="83" t="s">
-        <v>244</v>
-      </c>
-      <c r="D113" s="116" t="s">
-        <v>264</v>
-      </c>
-      <c r="E113" s="117"/>
-      <c r="F113" s="118"/>
+      <c r="B113" s="126"/>
+      <c r="C113" s="81" t="s">
+        <v>241</v>
+      </c>
+      <c r="D113" s="104" t="s">
+        <v>261</v>
+      </c>
+      <c r="E113" s="105"/>
+      <c r="F113" s="106"/>
       <c r="G113" s="51" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="49" t="s">
@@ -9667,17 +9737,17 @@
     </row>
     <row r="114" spans="1:14" ht="75.599999999999994">
       <c r="A114" s="11"/>
-      <c r="B114" s="121"/>
-      <c r="C114" s="83" t="s">
-        <v>246</v>
-      </c>
-      <c r="D114" s="116" t="s">
-        <v>265</v>
-      </c>
-      <c r="E114" s="117"/>
-      <c r="F114" s="118"/>
+      <c r="B114" s="126"/>
+      <c r="C114" s="81" t="s">
+        <v>243</v>
+      </c>
+      <c r="D114" s="104" t="s">
+        <v>262</v>
+      </c>
+      <c r="E114" s="105"/>
+      <c r="F114" s="106"/>
       <c r="G114" s="51" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="49" t="s">
@@ -9693,17 +9763,17 @@
     </row>
     <row r="115" spans="1:14" ht="113.4">
       <c r="A115" s="11"/>
-      <c r="B115" s="121"/>
-      <c r="C115" s="83" t="s">
-        <v>248</v>
-      </c>
-      <c r="D115" s="116" t="s">
-        <v>266</v>
-      </c>
-      <c r="E115" s="117"/>
-      <c r="F115" s="118"/>
+      <c r="B115" s="126"/>
+      <c r="C115" s="81" t="s">
+        <v>245</v>
+      </c>
+      <c r="D115" s="104" t="s">
+        <v>263</v>
+      </c>
+      <c r="E115" s="105"/>
+      <c r="F115" s="106"/>
       <c r="G115" s="51" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="49" t="s">
@@ -9719,17 +9789,17 @@
     </row>
     <row r="116" spans="1:14" ht="126">
       <c r="A116" s="11"/>
-      <c r="B116" s="121"/>
-      <c r="C116" s="83" t="s">
-        <v>267</v>
-      </c>
-      <c r="D116" s="116" t="s">
-        <v>268</v>
-      </c>
-      <c r="E116" s="117"/>
-      <c r="F116" s="118"/>
+      <c r="B116" s="126"/>
+      <c r="C116" s="81" t="s">
+        <v>264</v>
+      </c>
+      <c r="D116" s="104" t="s">
+        <v>265</v>
+      </c>
+      <c r="E116" s="105"/>
+      <c r="F116" s="106"/>
       <c r="G116" s="51" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="49" t="s">
@@ -9745,17 +9815,17 @@
     </row>
     <row r="117" spans="1:14" ht="88.2">
       <c r="A117" s="11"/>
-      <c r="B117" s="121"/>
-      <c r="C117" s="83" t="s">
-        <v>251</v>
-      </c>
-      <c r="D117" s="116" t="s">
-        <v>269</v>
-      </c>
-      <c r="E117" s="117"/>
-      <c r="F117" s="118"/>
+      <c r="B117" s="126"/>
+      <c r="C117" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="D117" s="104" t="s">
+        <v>266</v>
+      </c>
+      <c r="E117" s="105"/>
+      <c r="F117" s="106"/>
       <c r="G117" s="51" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="H117" s="12"/>
       <c r="I117" s="49" t="s">
@@ -9771,17 +9841,17 @@
     </row>
     <row r="118" spans="1:14" ht="138.6">
       <c r="A118" s="11"/>
-      <c r="B118" s="121"/>
-      <c r="C118" s="83" t="s">
-        <v>252</v>
-      </c>
-      <c r="D118" s="116" t="s">
-        <v>270</v>
-      </c>
-      <c r="E118" s="117"/>
-      <c r="F118" s="118"/>
+      <c r="B118" s="126"/>
+      <c r="C118" s="81" t="s">
+        <v>249</v>
+      </c>
+      <c r="D118" s="104" t="s">
+        <v>267</v>
+      </c>
+      <c r="E118" s="105"/>
+      <c r="F118" s="106"/>
       <c r="G118" s="51" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="H118" s="12"/>
       <c r="I118" s="49" t="s">
@@ -9797,15 +9867,15 @@
     </row>
     <row r="119" spans="1:14" ht="24" customHeight="1">
       <c r="A119" s="11"/>
-      <c r="B119" s="120"/>
-      <c r="C119" s="83" t="s">
-        <v>253</v>
-      </c>
-      <c r="D119" s="116"/>
-      <c r="E119" s="117"/>
-      <c r="F119" s="118"/>
+      <c r="B119" s="125"/>
+      <c r="C119" s="81" t="s">
+        <v>250</v>
+      </c>
+      <c r="D119" s="104"/>
+      <c r="E119" s="105"/>
+      <c r="F119" s="106"/>
       <c r="G119" s="51" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="H119" s="12"/>
       <c r="I119" s="49" t="s">
@@ -9821,51 +9891,51 @@
     </row>
     <row r="120" spans="1:14" ht="37.799999999999997">
       <c r="A120" s="11"/>
-      <c r="B120" s="62" t="str">
+      <c r="B120" s="128" t="str">
         <f>master!B67</f>
         <v>課題1の実施</v>
       </c>
-      <c r="C120" s="62" t="str">
+      <c r="C120" s="61" t="str">
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D120" s="112" t="s">
-        <v>323</v>
-      </c>
-      <c r="E120" s="113"/>
-      <c r="F120" s="114"/>
-      <c r="G120" s="62" t="s">
+      <c r="D120" s="107" t="s">
+        <v>320</v>
+      </c>
+      <c r="E120" s="108"/>
+      <c r="F120" s="109"/>
+      <c r="G120" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="H120" s="63"/>
-      <c r="I120" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J120" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K120" s="66"/>
+      <c r="H120" s="62"/>
+      <c r="I120" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J120" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K120" s="65"/>
       <c r="L120" s="6"/>
       <c r="M120" s="6"/>
       <c r="N120" s="6"/>
     </row>
     <row r="121" spans="1:14" ht="50.4">
       <c r="A121" s="11"/>
-      <c r="B121" s="119" t="str">
+      <c r="B121" s="124" t="str">
         <f>master!B96</f>
         <v>単体テストとJunitの導入</v>
       </c>
-      <c r="C121" s="83" t="str">
+      <c r="C121" s="81" t="str">
         <f>master!C96</f>
         <v>講義の目的</v>
       </c>
-      <c r="D121" s="116" t="s">
-        <v>299</v>
-      </c>
-      <c r="E121" s="117"/>
-      <c r="F121" s="118"/>
+      <c r="D121" s="104" t="s">
+        <v>296</v>
+      </c>
+      <c r="E121" s="105"/>
+      <c r="F121" s="106"/>
       <c r="G121" s="51" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="H121" s="12"/>
       <c r="I121" s="49" t="s">
@@ -9881,16 +9951,16 @@
     </row>
     <row r="122" spans="1:14" ht="25.2">
       <c r="A122" s="11"/>
-      <c r="B122" s="121"/>
-      <c r="C122" s="83" t="str">
+      <c r="B122" s="126"/>
+      <c r="C122" s="81" t="str">
         <f>master!C97</f>
         <v>TERASOLUNA 開発手順　 ※再掲</v>
       </c>
-      <c r="D122" s="116"/>
-      <c r="E122" s="117"/>
-      <c r="F122" s="118"/>
+      <c r="D122" s="104"/>
+      <c r="E122" s="105"/>
+      <c r="F122" s="106"/>
       <c r="G122" s="51" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H122" s="12"/>
       <c r="I122" s="49" t="s">
@@ -9906,18 +9976,18 @@
     </row>
     <row r="123" spans="1:14" ht="25.2">
       <c r="A123" s="11"/>
-      <c r="B123" s="120"/>
-      <c r="C123" s="83" t="str">
+      <c r="B123" s="125"/>
+      <c r="C123" s="81" t="str">
         <f>master!C98</f>
         <v>V字モデル　 ※再掲</v>
       </c>
-      <c r="D123" s="116" t="s">
-        <v>300</v>
-      </c>
-      <c r="E123" s="117"/>
-      <c r="F123" s="118"/>
+      <c r="D123" s="104" t="s">
+        <v>297</v>
+      </c>
+      <c r="E123" s="105"/>
+      <c r="F123" s="106"/>
       <c r="G123" s="51" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="49" t="s">
@@ -9933,21 +10003,21 @@
     </row>
     <row r="124" spans="1:14" ht="50.4">
       <c r="A124" s="11"/>
-      <c r="B124" s="119" t="str">
+      <c r="B124" s="124" t="str">
         <f>master!B99</f>
         <v>テストとは</v>
       </c>
-      <c r="C124" s="83" t="str">
+      <c r="C124" s="81" t="str">
         <f>master!C99</f>
         <v>テストとは</v>
       </c>
-      <c r="D124" s="116" t="s">
-        <v>301</v>
-      </c>
-      <c r="E124" s="117"/>
-      <c r="F124" s="118"/>
+      <c r="D124" s="104" t="s">
+        <v>298</v>
+      </c>
+      <c r="E124" s="105"/>
+      <c r="F124" s="106"/>
       <c r="G124" s="51" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="H124" s="12"/>
       <c r="I124" s="49" t="s">
@@ -9963,18 +10033,18 @@
     </row>
     <row r="125" spans="1:14" ht="315">
       <c r="A125" s="11"/>
-      <c r="B125" s="121"/>
-      <c r="C125" s="83" t="str">
+      <c r="B125" s="126"/>
+      <c r="C125" s="81" t="str">
         <f>master!C100</f>
         <v>テストの目的</v>
       </c>
-      <c r="D125" s="116" t="s">
-        <v>302</v>
-      </c>
-      <c r="E125" s="117"/>
-      <c r="F125" s="118"/>
+      <c r="D125" s="104" t="s">
+        <v>299</v>
+      </c>
+      <c r="E125" s="105"/>
+      <c r="F125" s="106"/>
       <c r="G125" s="51" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="H125" s="12"/>
       <c r="I125" s="49" t="s">
@@ -9990,18 +10060,18 @@
     </row>
     <row r="126" spans="1:14" ht="25.2">
       <c r="A126" s="11"/>
-      <c r="B126" s="121"/>
-      <c r="C126" s="83" t="str">
+      <c r="B126" s="126"/>
+      <c r="C126" s="81" t="str">
         <f>master!C101</f>
         <v>テストを実施しなかった場合…</v>
       </c>
-      <c r="D126" s="116" t="s">
-        <v>303</v>
-      </c>
-      <c r="E126" s="117"/>
-      <c r="F126" s="118"/>
+      <c r="D126" s="104" t="s">
+        <v>300</v>
+      </c>
+      <c r="E126" s="105"/>
+      <c r="F126" s="106"/>
       <c r="G126" s="51" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H126" s="12"/>
       <c r="I126" s="49" t="s">
@@ -10017,18 +10087,18 @@
     </row>
     <row r="127" spans="1:14" ht="100.8">
       <c r="A127" s="11"/>
-      <c r="B127" s="120"/>
-      <c r="C127" s="83" t="str">
+      <c r="B127" s="125"/>
+      <c r="C127" s="81" t="str">
         <f>master!C102</f>
         <v>コラム：テストとデバッグ</v>
       </c>
-      <c r="D127" s="116" t="s">
-        <v>304</v>
-      </c>
-      <c r="E127" s="117"/>
-      <c r="F127" s="118"/>
+      <c r="D127" s="104" t="s">
+        <v>301</v>
+      </c>
+      <c r="E127" s="105"/>
+      <c r="F127" s="106"/>
       <c r="G127" s="51" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="H127" s="12"/>
       <c r="I127" s="49" t="s">
@@ -10044,21 +10114,21 @@
     </row>
     <row r="128" spans="1:14" ht="50.4">
       <c r="A128" s="11"/>
-      <c r="B128" s="119" t="str">
+      <c r="B128" s="124" t="str">
         <f>master!B103</f>
         <v>単体テストとは</v>
       </c>
-      <c r="C128" s="83" t="str">
+      <c r="C128" s="81" t="str">
         <f>master!C103</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D128" s="116" t="s">
-        <v>305</v>
-      </c>
-      <c r="E128" s="117"/>
-      <c r="F128" s="118"/>
+      <c r="D128" s="104" t="s">
+        <v>302</v>
+      </c>
+      <c r="E128" s="105"/>
+      <c r="F128" s="106"/>
       <c r="G128" s="51" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="H128" s="12"/>
       <c r="I128" s="49" t="s">
@@ -10074,16 +10144,16 @@
     </row>
     <row r="129" spans="1:14" ht="25.2">
       <c r="A129" s="11"/>
-      <c r="B129" s="121"/>
-      <c r="C129" s="83" t="str">
+      <c r="B129" s="126"/>
+      <c r="C129" s="81" t="str">
         <f>master!C104</f>
         <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
       </c>
-      <c r="D129" s="116"/>
-      <c r="E129" s="117"/>
-      <c r="F129" s="118"/>
+      <c r="D129" s="104"/>
+      <c r="E129" s="105"/>
+      <c r="F129" s="106"/>
       <c r="G129" s="51" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H129" s="12"/>
       <c r="I129" s="49" t="s">
@@ -10099,18 +10169,18 @@
     </row>
     <row r="130" spans="1:14" ht="302.39999999999998">
       <c r="A130" s="11"/>
-      <c r="B130" s="121"/>
-      <c r="C130" s="83" t="str">
+      <c r="B130" s="126"/>
+      <c r="C130" s="81" t="str">
         <f>master!C105</f>
         <v>テスト設計の流れ</v>
       </c>
-      <c r="D130" s="116" t="s">
-        <v>306</v>
-      </c>
-      <c r="E130" s="117"/>
-      <c r="F130" s="118"/>
+      <c r="D130" s="104" t="s">
+        <v>303</v>
+      </c>
+      <c r="E130" s="105"/>
+      <c r="F130" s="106"/>
       <c r="G130" s="51" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="H130" s="12"/>
       <c r="I130" s="49" t="s">
@@ -10126,18 +10196,18 @@
     </row>
     <row r="131" spans="1:14" ht="37.799999999999997">
       <c r="A131" s="11"/>
-      <c r="B131" s="121"/>
-      <c r="C131" s="83" t="str">
+      <c r="B131" s="126"/>
+      <c r="C131" s="81" t="str">
         <f>master!C106</f>
         <v>テスト設計の例</v>
       </c>
-      <c r="D131" s="116" t="s">
-        <v>307</v>
-      </c>
-      <c r="E131" s="117"/>
-      <c r="F131" s="118"/>
+      <c r="D131" s="104" t="s">
+        <v>304</v>
+      </c>
+      <c r="E131" s="105"/>
+      <c r="F131" s="106"/>
       <c r="G131" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H131" s="12"/>
       <c r="I131" s="49" t="s">
@@ -10153,18 +10223,18 @@
     </row>
     <row r="132" spans="1:14" ht="75.599999999999994">
       <c r="A132" s="11"/>
-      <c r="B132" s="121"/>
-      <c r="C132" s="83" t="str">
+      <c r="B132" s="126"/>
+      <c r="C132" s="81" t="str">
         <f>master!C107</f>
         <v>単体テスト（Unit Test）とは</v>
       </c>
-      <c r="D132" s="116" t="s">
-        <v>308</v>
-      </c>
-      <c r="E132" s="117"/>
-      <c r="F132" s="118"/>
+      <c r="D132" s="104" t="s">
+        <v>305</v>
+      </c>
+      <c r="E132" s="105"/>
+      <c r="F132" s="106"/>
       <c r="G132" s="51" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="H132" s="12"/>
       <c r="I132" s="49" t="s">
@@ -10180,18 +10250,18 @@
     </row>
     <row r="133" spans="1:14" ht="113.4">
       <c r="A133" s="11"/>
-      <c r="B133" s="121"/>
-      <c r="C133" s="83" t="str">
+      <c r="B133" s="126"/>
+      <c r="C133" s="81" t="str">
         <f>master!C108</f>
         <v>テスト技法 – ブラックボックステスト技法 –</v>
       </c>
-      <c r="D133" s="116" t="s">
-        <v>309</v>
-      </c>
-      <c r="E133" s="117"/>
-      <c r="F133" s="118"/>
+      <c r="D133" s="104" t="s">
+        <v>306</v>
+      </c>
+      <c r="E133" s="105"/>
+      <c r="F133" s="106"/>
       <c r="G133" s="51" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H133" s="12"/>
       <c r="I133" s="49" t="s">
@@ -10207,18 +10277,18 @@
     </row>
     <row r="134" spans="1:14" ht="201.6">
       <c r="A134" s="11"/>
-      <c r="B134" s="121"/>
-      <c r="C134" s="83" t="str">
+      <c r="B134" s="126"/>
+      <c r="C134" s="81" t="str">
         <f>master!C109</f>
         <v>ブラックボックステスト：同値分割法</v>
       </c>
-      <c r="D134" s="116" t="s">
-        <v>312</v>
-      </c>
-      <c r="E134" s="117"/>
-      <c r="F134" s="118"/>
+      <c r="D134" s="104" t="s">
+        <v>309</v>
+      </c>
+      <c r="E134" s="105"/>
+      <c r="F134" s="106"/>
       <c r="G134" s="51" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="H134" s="12"/>
       <c r="I134" s="49" t="s">
@@ -10234,18 +10304,18 @@
     </row>
     <row r="135" spans="1:14" ht="113.4">
       <c r="A135" s="11"/>
-      <c r="B135" s="121"/>
-      <c r="C135" s="83" t="str">
+      <c r="B135" s="126"/>
+      <c r="C135" s="81" t="str">
         <f>master!C110</f>
         <v>ブラックボックステスト：境界値分析</v>
       </c>
-      <c r="D135" s="116" t="s">
-        <v>311</v>
-      </c>
-      <c r="E135" s="117"/>
-      <c r="F135" s="118"/>
+      <c r="D135" s="104" t="s">
+        <v>308</v>
+      </c>
+      <c r="E135" s="105"/>
+      <c r="F135" s="106"/>
       <c r="G135" s="51" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H135" s="12"/>
       <c r="I135" s="49" t="s">
@@ -10261,18 +10331,18 @@
     </row>
     <row r="136" spans="1:14" ht="176.4">
       <c r="A136" s="11"/>
-      <c r="B136" s="121"/>
-      <c r="C136" s="83" t="str">
+      <c r="B136" s="126"/>
+      <c r="C136" s="81" t="str">
         <f>master!C111</f>
         <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
       </c>
-      <c r="D136" s="116" t="s">
-        <v>310</v>
-      </c>
-      <c r="E136" s="117"/>
-      <c r="F136" s="118"/>
+      <c r="D136" s="104" t="s">
+        <v>307</v>
+      </c>
+      <c r="E136" s="105"/>
+      <c r="F136" s="106"/>
       <c r="G136" s="51" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="H136" s="12"/>
       <c r="I136" s="49" t="s">
@@ -10288,18 +10358,18 @@
     </row>
     <row r="137" spans="1:14" ht="37.799999999999997">
       <c r="A137" s="11"/>
-      <c r="B137" s="121"/>
-      <c r="C137" s="83" t="str">
+      <c r="B137" s="126"/>
+      <c r="C137" s="81" t="str">
         <f>master!C112</f>
         <v>ブラックボックステスト：状態遷移テスト</v>
       </c>
-      <c r="D137" s="116" t="s">
-        <v>313</v>
-      </c>
-      <c r="E137" s="117"/>
-      <c r="F137" s="118"/>
+      <c r="D137" s="104" t="s">
+        <v>310</v>
+      </c>
+      <c r="E137" s="105"/>
+      <c r="F137" s="106"/>
       <c r="G137" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H137" s="12"/>
       <c r="I137" s="49" t="s">
@@ -10315,18 +10385,18 @@
     </row>
     <row r="138" spans="1:14" ht="88.2">
       <c r="A138" s="11"/>
-      <c r="B138" s="121"/>
-      <c r="C138" s="83" t="str">
+      <c r="B138" s="126"/>
+      <c r="C138" s="81" t="str">
         <f>master!C113</f>
         <v>テスト技法 – ホワイトボックステスト技法 –</v>
       </c>
-      <c r="D138" s="116" t="s">
-        <v>314</v>
-      </c>
-      <c r="E138" s="117"/>
-      <c r="F138" s="118"/>
+      <c r="D138" s="104" t="s">
+        <v>311</v>
+      </c>
+      <c r="E138" s="105"/>
+      <c r="F138" s="106"/>
       <c r="G138" s="51" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="H138" s="12"/>
       <c r="I138" s="49" t="s">
@@ -10342,18 +10412,18 @@
     </row>
     <row r="139" spans="1:14" ht="151.19999999999999">
       <c r="A139" s="11"/>
-      <c r="B139" s="121"/>
-      <c r="C139" s="83" t="str">
+      <c r="B139" s="126"/>
+      <c r="C139" s="81" t="str">
         <f>master!C114</f>
         <v>ホワイトボックステストの評価基準</v>
       </c>
-      <c r="D139" s="116" t="s">
-        <v>315</v>
-      </c>
-      <c r="E139" s="117"/>
-      <c r="F139" s="118"/>
+      <c r="D139" s="104" t="s">
+        <v>312</v>
+      </c>
+      <c r="E139" s="105"/>
+      <c r="F139" s="106"/>
       <c r="G139" s="51" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="H139" s="12"/>
       <c r="I139" s="49" t="s">
@@ -10369,18 +10439,18 @@
     </row>
     <row r="140" spans="1:14" ht="37.799999999999997">
       <c r="A140" s="11"/>
-      <c r="B140" s="121"/>
-      <c r="C140" s="83" t="str">
+      <c r="B140" s="126"/>
+      <c r="C140" s="81" t="str">
         <f>master!C115</f>
         <v>ホワイトボックステスト：ステートメントテスト</v>
       </c>
-      <c r="D140" s="116" t="s">
-        <v>316</v>
-      </c>
-      <c r="E140" s="117"/>
-      <c r="F140" s="118"/>
+      <c r="D140" s="104" t="s">
+        <v>313</v>
+      </c>
+      <c r="E140" s="105"/>
+      <c r="F140" s="106"/>
       <c r="G140" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H140" s="12"/>
       <c r="I140" s="49" t="s">
@@ -10396,18 +10466,18 @@
     </row>
     <row r="141" spans="1:14" ht="37.799999999999997">
       <c r="A141" s="11"/>
-      <c r="B141" s="121"/>
-      <c r="C141" s="83" t="str">
+      <c r="B141" s="126"/>
+      <c r="C141" s="81" t="str">
         <f>master!C116</f>
         <v>ホワイトボックステスト：ブランチテスト</v>
       </c>
-      <c r="D141" s="116" t="s">
-        <v>317</v>
-      </c>
-      <c r="E141" s="117"/>
-      <c r="F141" s="118"/>
+      <c r="D141" s="104" t="s">
+        <v>314</v>
+      </c>
+      <c r="E141" s="105"/>
+      <c r="F141" s="106"/>
       <c r="G141" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H141" s="12"/>
       <c r="I141" s="49" t="s">
@@ -10423,18 +10493,18 @@
     </row>
     <row r="142" spans="1:14" ht="37.799999999999997">
       <c r="A142" s="11"/>
-      <c r="B142" s="121"/>
-      <c r="C142" s="83" t="str">
+      <c r="B142" s="126"/>
+      <c r="C142" s="81" t="str">
         <f>master!C117</f>
         <v>ホワイトボックステスト：コンディションテスト</v>
       </c>
-      <c r="D142" s="116" t="s">
-        <v>318</v>
-      </c>
-      <c r="E142" s="117"/>
-      <c r="F142" s="118"/>
+      <c r="D142" s="104" t="s">
+        <v>315</v>
+      </c>
+      <c r="E142" s="105"/>
+      <c r="F142" s="106"/>
       <c r="G142" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H142" s="12"/>
       <c r="I142" s="49" t="s">
@@ -10450,18 +10520,18 @@
     </row>
     <row r="143" spans="1:14" ht="37.799999999999997">
       <c r="A143" s="11"/>
-      <c r="B143" s="121"/>
-      <c r="C143" s="83" t="str">
+      <c r="B143" s="126"/>
+      <c r="C143" s="81" t="str">
         <f>master!C118</f>
         <v>テスト技法 – 経験ベースの技法 –</v>
       </c>
-      <c r="D143" s="116" t="s">
-        <v>319</v>
-      </c>
-      <c r="E143" s="117"/>
-      <c r="F143" s="118"/>
+      <c r="D143" s="104" t="s">
+        <v>316</v>
+      </c>
+      <c r="E143" s="105"/>
+      <c r="F143" s="106"/>
       <c r="G143" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H143" s="12"/>
       <c r="I143" s="49" t="s">
@@ -10477,18 +10547,18 @@
     </row>
     <row r="144" spans="1:14" ht="100.8">
       <c r="A144" s="11"/>
-      <c r="B144" s="121"/>
-      <c r="C144" s="83" t="str">
+      <c r="B144" s="126"/>
+      <c r="C144" s="81" t="str">
         <f>master!C119</f>
         <v>スタブとドライバ</v>
       </c>
-      <c r="D144" s="116" t="s">
-        <v>320</v>
-      </c>
-      <c r="E144" s="117"/>
-      <c r="F144" s="118"/>
+      <c r="D144" s="104" t="s">
+        <v>317</v>
+      </c>
+      <c r="E144" s="105"/>
+      <c r="F144" s="106"/>
       <c r="G144" s="51" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="H144" s="12"/>
       <c r="I144" s="49" t="s">
@@ -10504,18 +10574,18 @@
     </row>
     <row r="145" spans="1:14" ht="75.599999999999994">
       <c r="A145" s="11"/>
-      <c r="B145" s="120"/>
-      <c r="C145" s="83" t="str">
+      <c r="B145" s="125"/>
+      <c r="C145" s="81" t="str">
         <f>master!C120</f>
         <v>スタブとモック</v>
       </c>
-      <c r="D145" s="116" t="s">
-        <v>321</v>
-      </c>
-      <c r="E145" s="117"/>
-      <c r="F145" s="118"/>
+      <c r="D145" s="104" t="s">
+        <v>318</v>
+      </c>
+      <c r="E145" s="105"/>
+      <c r="F145" s="106"/>
       <c r="G145" s="51" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="H145" s="12"/>
       <c r="I145" s="49" t="s">
@@ -10531,21 +10601,21 @@
     </row>
     <row r="146" spans="1:14" ht="37.799999999999997">
       <c r="A146" s="11"/>
-      <c r="B146" s="119" t="str">
+      <c r="B146" s="124" t="str">
         <f>master!B121</f>
         <v>JUnit</v>
       </c>
-      <c r="C146" s="83" t="str">
+      <c r="C146" s="81" t="str">
         <f>master!C121</f>
         <v>JUnitとは</v>
       </c>
-      <c r="D146" s="116" t="s">
-        <v>322</v>
-      </c>
-      <c r="E146" s="117"/>
-      <c r="F146" s="118"/>
+      <c r="D146" s="104" t="s">
+        <v>319</v>
+      </c>
+      <c r="E146" s="105"/>
+      <c r="F146" s="106"/>
       <c r="G146" s="51" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="H146" s="12"/>
       <c r="I146" s="49" t="s">
@@ -10561,16 +10631,16 @@
     </row>
     <row r="147" spans="1:14" ht="25.2">
       <c r="A147" s="11"/>
-      <c r="B147" s="120"/>
-      <c r="C147" s="83" t="str">
+      <c r="B147" s="125"/>
+      <c r="C147" s="81" t="str">
         <f>master!C122</f>
         <v>参考文献</v>
       </c>
-      <c r="D147" s="116"/>
-      <c r="E147" s="117"/>
-      <c r="F147" s="118"/>
+      <c r="D147" s="104"/>
+      <c r="E147" s="105"/>
+      <c r="F147" s="106"/>
       <c r="G147" s="51" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="H147" s="12"/>
       <c r="I147" s="49" t="s">
@@ -10586,734 +10656,846 @@
     </row>
     <row r="148" spans="1:14" ht="37.799999999999997">
       <c r="A148" s="11"/>
-      <c r="B148" s="62" t="str">
+      <c r="B148" s="128" t="str">
         <f>master!B67</f>
         <v>課題1の実施</v>
       </c>
-      <c r="C148" s="62" t="str">
+      <c r="C148" s="61" t="str">
         <f>master!C67</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D148" s="112" t="s">
-        <v>323</v>
-      </c>
-      <c r="E148" s="113"/>
-      <c r="F148" s="114"/>
-      <c r="G148" s="62" t="s">
+      <c r="D148" s="107" t="s">
+        <v>320</v>
+      </c>
+      <c r="E148" s="108"/>
+      <c r="F148" s="109"/>
+      <c r="G148" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="H148" s="63"/>
-      <c r="I148" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J148" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K148" s="66"/>
+      <c r="H148" s="62"/>
+      <c r="I148" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J148" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K148" s="65"/>
       <c r="L148" s="6"/>
       <c r="M148" s="6"/>
       <c r="N148" s="6"/>
     </row>
     <row r="149" spans="1:14" ht="25.2">
       <c r="A149" s="11"/>
-      <c r="B149" s="110" t="str">
+      <c r="B149" s="121" t="str">
         <f>master!B124</f>
         <v>課題2の導入</v>
       </c>
-      <c r="C149" s="62" t="str">
+      <c r="C149" s="61" t="str">
         <f>master!C124</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D149" s="112" t="s">
-        <v>339</v>
-      </c>
-      <c r="E149" s="113"/>
-      <c r="F149" s="114"/>
-      <c r="G149" s="62" t="s">
-        <v>401</v>
-      </c>
-      <c r="H149" s="63"/>
-      <c r="I149" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J149" s="65">
+      <c r="D149" s="107" t="s">
+        <v>336</v>
+      </c>
+      <c r="E149" s="108"/>
+      <c r="F149" s="109"/>
+      <c r="G149" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="H149" s="62"/>
+      <c r="I149" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J149" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K149" s="66"/>
+      <c r="K149" s="65"/>
       <c r="L149" s="6"/>
       <c r="M149" s="6"/>
       <c r="N149" s="6"/>
     </row>
     <row r="150" spans="1:14" ht="138.6">
       <c r="A150" s="11"/>
-      <c r="B150" s="115"/>
-      <c r="C150" s="62" t="str">
+      <c r="B150" s="122"/>
+      <c r="C150" s="61" t="str">
         <f>master!C125</f>
         <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
       </c>
-      <c r="D150" s="112" t="s">
-        <v>340</v>
-      </c>
-      <c r="E150" s="113"/>
-      <c r="F150" s="114"/>
-      <c r="G150" s="62" t="s">
-        <v>402</v>
-      </c>
-      <c r="H150" s="63"/>
-      <c r="I150" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J150" s="65">
+      <c r="D150" s="107" t="s">
+        <v>337</v>
+      </c>
+      <c r="E150" s="108"/>
+      <c r="F150" s="109"/>
+      <c r="G150" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="H150" s="62"/>
+      <c r="I150" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J150" s="64">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K150" s="66"/>
+      <c r="K150" s="65"/>
       <c r="L150" s="6"/>
       <c r="M150" s="6"/>
       <c r="N150" s="6"/>
     </row>
     <row r="151" spans="1:14" ht="50.4">
       <c r="A151" s="11"/>
-      <c r="B151" s="115"/>
-      <c r="C151" s="62" t="str">
+      <c r="B151" s="122"/>
+      <c r="C151" s="61" t="str">
         <f>master!C126</f>
         <v>テストクラスを作成する単位</v>
       </c>
-      <c r="D151" s="112" t="s">
-        <v>341</v>
-      </c>
-      <c r="E151" s="113"/>
-      <c r="F151" s="114"/>
-      <c r="G151" s="62" t="s">
-        <v>403</v>
-      </c>
-      <c r="H151" s="63"/>
-      <c r="I151" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J151" s="65">
+      <c r="D151" s="107" t="s">
+        <v>338</v>
+      </c>
+      <c r="E151" s="108"/>
+      <c r="F151" s="109"/>
+      <c r="G151" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="H151" s="62"/>
+      <c r="I151" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J151" s="64">
         <v>2.0833333333333333E-3</v>
       </c>
-      <c r="K151" s="66"/>
+      <c r="K151" s="65"/>
       <c r="L151" s="6"/>
       <c r="M151" s="6"/>
       <c r="N151" s="6"/>
     </row>
     <row r="152" spans="1:14" ht="113.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="111"/>
-      <c r="C152" s="62" t="str">
+      <c r="B152" s="123"/>
+      <c r="C152" s="61" t="str">
         <f>master!C127</f>
         <v>JUnitで単体テスト</v>
       </c>
-      <c r="D152" s="112" t="s">
-        <v>342</v>
-      </c>
-      <c r="E152" s="113"/>
-      <c r="F152" s="114"/>
-      <c r="G152" s="62" t="s">
-        <v>404</v>
-      </c>
-      <c r="H152" s="63"/>
-      <c r="I152" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J152" s="65">
+      <c r="D152" s="107" t="s">
+        <v>339</v>
+      </c>
+      <c r="E152" s="108"/>
+      <c r="F152" s="109"/>
+      <c r="G152" s="61" t="s">
+        <v>398</v>
+      </c>
+      <c r="H152" s="62"/>
+      <c r="I152" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J152" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K152" s="66"/>
+      <c r="K152" s="65"/>
       <c r="L152" s="6"/>
       <c r="M152" s="6"/>
       <c r="N152" s="6"/>
     </row>
     <row r="153" spans="1:14" ht="25.2">
       <c r="A153" s="11"/>
-      <c r="B153" s="110" t="str">
+      <c r="B153" s="121" t="str">
         <f>master!B128</f>
         <v>ハンズオン</v>
       </c>
-      <c r="C153" s="62" t="str">
+      <c r="C153" s="61" t="str">
         <f>master!C128</f>
         <v>バイブコーディングで単体テスト – はじめに</v>
       </c>
-      <c r="D153" s="112" t="s">
-        <v>343</v>
-      </c>
-      <c r="E153" s="113"/>
-      <c r="F153" s="114"/>
-      <c r="G153" s="62" t="s">
-        <v>401</v>
-      </c>
-      <c r="H153" s="63"/>
-      <c r="I153" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J153" s="65">
+      <c r="D153" s="107" t="s">
+        <v>340</v>
+      </c>
+      <c r="E153" s="108"/>
+      <c r="F153" s="109"/>
+      <c r="G153" s="61" t="s">
+        <v>395</v>
+      </c>
+      <c r="H153" s="62"/>
+      <c r="I153" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J153" s="64">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K153" s="66"/>
+      <c r="K153" s="65"/>
       <c r="L153" s="6"/>
       <c r="M153" s="6"/>
       <c r="N153" s="6"/>
     </row>
     <row r="154" spans="1:14" ht="50.4">
       <c r="A154" s="11"/>
-      <c r="B154" s="115"/>
-      <c r="C154" s="62" t="str">
+      <c r="B154" s="122"/>
+      <c r="C154" s="61" t="str">
         <f>master!C129</f>
         <v>バイブコーディング単体テスト①テスト項目表を作る</v>
       </c>
-      <c r="D154" s="112" t="s">
-        <v>344</v>
-      </c>
-      <c r="E154" s="113"/>
-      <c r="F154" s="114"/>
-      <c r="G154" s="62" t="s">
-        <v>403</v>
-      </c>
-      <c r="H154" s="63"/>
-      <c r="I154" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J154" s="65">
+      <c r="D154" s="107" t="s">
+        <v>341</v>
+      </c>
+      <c r="E154" s="108"/>
+      <c r="F154" s="109"/>
+      <c r="G154" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="H154" s="62"/>
+      <c r="I154" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J154" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K154" s="66"/>
+      <c r="K154" s="65"/>
       <c r="L154" s="6"/>
       <c r="M154" s="6"/>
       <c r="N154" s="6"/>
     </row>
     <row r="155" spans="1:14" ht="88.2">
       <c r="A155" s="11"/>
-      <c r="B155" s="115"/>
-      <c r="C155" s="62"/>
-      <c r="D155" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E155" s="113"/>
-      <c r="F155" s="114"/>
-      <c r="G155" s="62" t="s">
-        <v>405</v>
-      </c>
-      <c r="H155" s="63"/>
-      <c r="I155" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J155" s="65">
+      <c r="B155" s="122"/>
+      <c r="C155" s="61"/>
+      <c r="D155" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E155" s="108"/>
+      <c r="F155" s="109"/>
+      <c r="G155" s="61" t="s">
+        <v>399</v>
+      </c>
+      <c r="H155" s="62"/>
+      <c r="I155" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J155" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K155" s="66"/>
+      <c r="K155" s="65"/>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
       <c r="N155" s="6"/>
     </row>
     <row r="156" spans="1:14" ht="50.4">
       <c r="A156" s="11"/>
-      <c r="B156" s="115"/>
-      <c r="C156" s="81" t="str">
+      <c r="B156" s="122"/>
+      <c r="C156" s="79" t="str">
         <f>master!C130</f>
         <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
       </c>
-      <c r="D156" s="112" t="s">
-        <v>345</v>
-      </c>
-      <c r="E156" s="113"/>
-      <c r="F156" s="114"/>
-      <c r="G156" s="62" t="s">
-        <v>403</v>
-      </c>
-      <c r="H156" s="63"/>
-      <c r="I156" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J156" s="65">
+      <c r="D156" s="107" t="s">
+        <v>342</v>
+      </c>
+      <c r="E156" s="108"/>
+      <c r="F156" s="109"/>
+      <c r="G156" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="H156" s="62"/>
+      <c r="I156" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J156" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K156" s="66"/>
+      <c r="K156" s="65"/>
       <c r="L156" s="6"/>
       <c r="M156" s="6"/>
       <c r="N156" s="6"/>
     </row>
     <row r="157" spans="1:14" ht="88.2">
       <c r="A157" s="11"/>
-      <c r="B157" s="115"/>
-      <c r="C157" s="82"/>
-      <c r="D157" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E157" s="113"/>
-      <c r="F157" s="114"/>
-      <c r="G157" s="62" t="s">
-        <v>405</v>
-      </c>
-      <c r="H157" s="63"/>
-      <c r="I157" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J157" s="65">
+      <c r="B157" s="122"/>
+      <c r="C157" s="80"/>
+      <c r="D157" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E157" s="108"/>
+      <c r="F157" s="109"/>
+      <c r="G157" s="61" t="s">
+        <v>399</v>
+      </c>
+      <c r="H157" s="62"/>
+      <c r="I157" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J157" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K157" s="66"/>
+      <c r="K157" s="65"/>
       <c r="L157" s="6"/>
       <c r="M157" s="6"/>
       <c r="N157" s="6"/>
     </row>
     <row r="158" spans="1:14" ht="138.6">
       <c r="A158" s="11"/>
-      <c r="B158" s="115"/>
-      <c r="C158" s="62" t="str">
+      <c r="B158" s="122"/>
+      <c r="C158" s="61" t="str">
         <f>master!C131</f>
         <v>[解説] Repositoryのテストクラス（抜粋）</v>
       </c>
-      <c r="D158" s="112" t="s">
-        <v>347</v>
-      </c>
-      <c r="E158" s="113"/>
-      <c r="F158" s="114"/>
-      <c r="G158" s="62" t="s">
-        <v>402</v>
-      </c>
-      <c r="H158" s="63"/>
-      <c r="I158" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J158" s="65">
+      <c r="D158" s="107" t="s">
+        <v>344</v>
+      </c>
+      <c r="E158" s="108"/>
+      <c r="F158" s="109"/>
+      <c r="G158" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="H158" s="62"/>
+      <c r="I158" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J158" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K158" s="66"/>
+      <c r="K158" s="65"/>
       <c r="L158" s="6"/>
       <c r="M158" s="6"/>
       <c r="N158" s="6"/>
     </row>
     <row r="159" spans="1:14" ht="50.4">
       <c r="A159" s="11"/>
-      <c r="B159" s="115"/>
-      <c r="C159" s="81" t="str">
+      <c r="B159" s="122"/>
+      <c r="C159" s="79" t="str">
         <f>master!C132</f>
         <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
       </c>
-      <c r="D159" s="112" t="s">
-        <v>345</v>
-      </c>
-      <c r="E159" s="113"/>
-      <c r="F159" s="114"/>
-      <c r="G159" s="62" t="s">
-        <v>403</v>
-      </c>
-      <c r="H159" s="63"/>
-      <c r="I159" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J159" s="65">
+      <c r="D159" s="107" t="s">
+        <v>342</v>
+      </c>
+      <c r="E159" s="108"/>
+      <c r="F159" s="109"/>
+      <c r="G159" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="H159" s="62"/>
+      <c r="I159" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J159" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K159" s="66"/>
+      <c r="K159" s="65"/>
       <c r="L159" s="6"/>
       <c r="M159" s="6"/>
       <c r="N159" s="6"/>
     </row>
     <row r="160" spans="1:14" ht="88.2">
       <c r="A160" s="11"/>
-      <c r="B160" s="115"/>
-      <c r="C160" s="82"/>
-      <c r="D160" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E160" s="113"/>
-      <c r="F160" s="114"/>
-      <c r="G160" s="62" t="s">
-        <v>405</v>
-      </c>
-      <c r="H160" s="63"/>
-      <c r="I160" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J160" s="65">
+      <c r="B160" s="122"/>
+      <c r="C160" s="80"/>
+      <c r="D160" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E160" s="108"/>
+      <c r="F160" s="109"/>
+      <c r="G160" s="61" t="s">
+        <v>399</v>
+      </c>
+      <c r="H160" s="62"/>
+      <c r="I160" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J160" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K160" s="66"/>
+      <c r="K160" s="65"/>
       <c r="L160" s="6"/>
       <c r="M160" s="6"/>
       <c r="N160" s="6"/>
     </row>
     <row r="161" spans="1:14" ht="138.6">
       <c r="A161" s="11"/>
-      <c r="B161" s="115"/>
-      <c r="C161" s="62" t="str">
+      <c r="B161" s="122"/>
+      <c r="C161" s="61" t="str">
         <f>master!C133</f>
         <v>[解説] Serviceのテストクラス（抜粋）</v>
       </c>
-      <c r="D161" s="112" t="s">
-        <v>346</v>
-      </c>
-      <c r="E161" s="113"/>
-      <c r="F161" s="114"/>
-      <c r="G161" s="62" t="s">
-        <v>402</v>
-      </c>
-      <c r="H161" s="63"/>
-      <c r="I161" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J161" s="65">
+      <c r="D161" s="107" t="s">
+        <v>343</v>
+      </c>
+      <c r="E161" s="108"/>
+      <c r="F161" s="109"/>
+      <c r="G161" s="61" t="s">
+        <v>396</v>
+      </c>
+      <c r="H161" s="62"/>
+      <c r="I161" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J161" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K161" s="66"/>
+      <c r="K161" s="65"/>
       <c r="L161" s="6"/>
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
     </row>
     <row r="162" spans="1:14" ht="50.4">
       <c r="A162" s="11"/>
-      <c r="B162" s="115"/>
-      <c r="C162" s="81" t="str">
+      <c r="B162" s="122"/>
+      <c r="C162" s="79" t="str">
         <f>master!C134</f>
         <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
       </c>
-      <c r="D162" s="112" t="s">
-        <v>345</v>
-      </c>
-      <c r="E162" s="113"/>
-      <c r="F162" s="114"/>
-      <c r="G162" s="62" t="s">
-        <v>403</v>
-      </c>
-      <c r="H162" s="63"/>
-      <c r="I162" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J162" s="65">
+      <c r="D162" s="107" t="s">
+        <v>342</v>
+      </c>
+      <c r="E162" s="108"/>
+      <c r="F162" s="109"/>
+      <c r="G162" s="61" t="s">
+        <v>397</v>
+      </c>
+      <c r="H162" s="62"/>
+      <c r="I162" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J162" s="64">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K162" s="66"/>
+      <c r="K162" s="65"/>
       <c r="L162" s="6"/>
       <c r="M162" s="6"/>
       <c r="N162" s="6"/>
     </row>
     <row r="163" spans="1:14" ht="88.2">
       <c r="A163" s="11"/>
-      <c r="B163" s="115"/>
-      <c r="C163" s="82"/>
-      <c r="D163" s="112" t="s">
-        <v>196</v>
-      </c>
-      <c r="E163" s="113"/>
-      <c r="F163" s="114"/>
-      <c r="G163" s="62" t="s">
-        <v>405</v>
-      </c>
-      <c r="H163" s="63"/>
-      <c r="I163" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J163" s="65">
+      <c r="B163" s="122"/>
+      <c r="C163" s="80"/>
+      <c r="D163" s="107" t="s">
+        <v>195</v>
+      </c>
+      <c r="E163" s="108"/>
+      <c r="F163" s="109"/>
+      <c r="G163" s="61" t="s">
+        <v>399</v>
+      </c>
+      <c r="H163" s="62"/>
+      <c r="I163" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J163" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K163" s="66"/>
+      <c r="K163" s="65"/>
       <c r="L163" s="6"/>
       <c r="M163" s="6"/>
       <c r="N163" s="6"/>
     </row>
     <row r="164" spans="1:14" ht="163.80000000000001">
       <c r="A164" s="11"/>
-      <c r="B164" s="111"/>
-      <c r="C164" s="62" t="str">
+      <c r="B164" s="123"/>
+      <c r="C164" s="61" t="str">
         <f>master!C135</f>
         <v>[解説] Controllerのテストクラス（抜粋）</v>
       </c>
-      <c r="D164" s="112" t="s">
-        <v>348</v>
-      </c>
-      <c r="E164" s="113"/>
-      <c r="F164" s="114"/>
-      <c r="G164" s="62" t="s">
-        <v>406</v>
-      </c>
-      <c r="H164" s="63"/>
-      <c r="I164" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J164" s="65">
+      <c r="D164" s="107" t="s">
+        <v>345</v>
+      </c>
+      <c r="E164" s="108"/>
+      <c r="F164" s="109"/>
+      <c r="G164" s="61" t="s">
+        <v>400</v>
+      </c>
+      <c r="H164" s="62"/>
+      <c r="I164" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J164" s="64">
         <v>6.9444444444444441E-3</v>
       </c>
-      <c r="K164" s="66"/>
+      <c r="K164" s="65"/>
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
       <c r="N164" s="6"/>
     </row>
     <row r="165" spans="1:14" ht="165" customHeight="1">
       <c r="A165" s="11"/>
-      <c r="B165" s="110" t="str">
+      <c r="B165" s="121" t="str">
         <f>master!B136</f>
         <v>課題2の実施</v>
       </c>
-      <c r="C165" s="62" t="str">
+      <c r="C165" s="61" t="str">
         <f>master!C136</f>
         <v>ここから各自で演習を始めましょう。</v>
       </c>
-      <c r="D165" s="112" t="s">
-        <v>349</v>
-      </c>
-      <c r="E165" s="113"/>
-      <c r="F165" s="114"/>
-      <c r="G165" s="62" t="s">
-        <v>406</v>
-      </c>
-      <c r="H165" s="63"/>
-      <c r="I165" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J165" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K165" s="66"/>
+      <c r="D165" s="107" t="s">
+        <v>346</v>
+      </c>
+      <c r="E165" s="108"/>
+      <c r="F165" s="109"/>
+      <c r="G165" s="61" t="s">
+        <v>400</v>
+      </c>
+      <c r="H165" s="62"/>
+      <c r="I165" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J165" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K165" s="65"/>
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
       <c r="N165" s="6"/>
     </row>
     <row r="166" spans="1:14" ht="151.19999999999999">
       <c r="A166" s="11"/>
-      <c r="B166" s="111"/>
-      <c r="C166" s="62" t="str">
+      <c r="B166" s="123"/>
+      <c r="C166" s="61" t="str">
         <f>master!C137</f>
         <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
       </c>
-      <c r="D166" s="112" t="s">
-        <v>351</v>
-      </c>
-      <c r="E166" s="113"/>
-      <c r="F166" s="114"/>
-      <c r="G166" s="62" t="s">
-        <v>407</v>
-      </c>
-      <c r="H166" s="63"/>
-      <c r="I166" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J166" s="65">
+      <c r="D166" s="107" t="s">
+        <v>434</v>
+      </c>
+      <c r="E166" s="108"/>
+      <c r="F166" s="109"/>
+      <c r="G166" s="61" t="s">
+        <v>433</v>
+      </c>
+      <c r="H166" s="62"/>
+      <c r="I166" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J166" s="64">
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="K166" s="66"/>
+      <c r="K166" s="65"/>
       <c r="L166" s="6"/>
       <c r="M166" s="6"/>
       <c r="N166" s="6"/>
     </row>
     <row r="167" spans="1:14" ht="163.80000000000001">
       <c r="A167" s="11"/>
-      <c r="B167" s="90" t="str">
+      <c r="B167" s="121" t="str">
         <f>master!B139</f>
-        <v>その他の導入</v>
-      </c>
-      <c r="C167" s="62" t="str">
+        <v>追加課題</v>
+      </c>
+      <c r="C167" s="61" t="str">
         <f>master!C139</f>
         <v>演習課題の概要</v>
       </c>
-      <c r="D167" s="112" t="s">
-        <v>352</v>
-      </c>
-      <c r="E167" s="113"/>
-      <c r="F167" s="114"/>
-      <c r="G167" s="62" t="s">
-        <v>406</v>
-      </c>
-      <c r="H167" s="63"/>
-      <c r="I167" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J167" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K167" s="66"/>
+      <c r="D167" s="107" t="s">
+        <v>348</v>
+      </c>
+      <c r="E167" s="108"/>
+      <c r="F167" s="109"/>
+      <c r="G167" s="61" t="s">
+        <v>427</v>
+      </c>
+      <c r="H167" s="62"/>
+      <c r="I167" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J167" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K167" s="65"/>
       <c r="L167" s="6"/>
       <c r="M167" s="6"/>
       <c r="N167" s="6"/>
     </row>
     <row r="168" spans="1:14" ht="25.2">
       <c r="A168" s="11"/>
-      <c r="B168" s="110" t="str">
-        <f>master!B140</f>
-        <v>追加課題</v>
-      </c>
-      <c r="C168" s="62" t="str">
+      <c r="B168" s="122"/>
+      <c r="C168" s="61" t="str">
         <f>master!C140</f>
         <v>追加課題①：送料の表示機能</v>
       </c>
-      <c r="D168" s="112" t="s">
-        <v>354</v>
-      </c>
-      <c r="E168" s="113"/>
-      <c r="F168" s="114"/>
-      <c r="G168" s="62" t="s">
-        <v>401</v>
-      </c>
-      <c r="H168" s="63"/>
-      <c r="I168" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J168" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K168" s="66"/>
+      <c r="D168" s="107" t="s">
+        <v>350</v>
+      </c>
+      <c r="E168" s="108"/>
+      <c r="F168" s="109"/>
+      <c r="G168" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="H168" s="62"/>
+      <c r="I168" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J168" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K168" s="65"/>
       <c r="L168" s="6"/>
       <c r="M168" s="6"/>
       <c r="N168" s="6"/>
     </row>
     <row r="169" spans="1:14" ht="25.2">
       <c r="A169" s="11"/>
-      <c r="B169" s="115"/>
-      <c r="C169" s="62" t="str">
+      <c r="B169" s="122"/>
+      <c r="C169" s="61" t="str">
         <f>master!C141</f>
         <v>追加課題②：クーポン機能</v>
       </c>
-      <c r="D169" s="112" t="s">
-        <v>354</v>
-      </c>
-      <c r="E169" s="113"/>
-      <c r="F169" s="114"/>
-      <c r="G169" s="62" t="s">
-        <v>401</v>
-      </c>
-      <c r="H169" s="63"/>
-      <c r="I169" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J169" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K169" s="66"/>
+      <c r="D169" s="107" t="s">
+        <v>350</v>
+      </c>
+      <c r="E169" s="108"/>
+      <c r="F169" s="109"/>
+      <c r="G169" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="H169" s="62"/>
+      <c r="I169" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J169" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K169" s="65"/>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
       <c r="N169" s="6"/>
     </row>
     <row r="170" spans="1:14" ht="25.2">
       <c r="A170" s="11"/>
-      <c r="B170" s="111"/>
-      <c r="C170" s="62" t="str">
+      <c r="B170" s="123"/>
+      <c r="C170" s="61" t="str">
         <f>master!C142</f>
         <v>追加課題③：ユーザーアカウント機能</v>
       </c>
-      <c r="D170" s="112" t="s">
-        <v>354</v>
-      </c>
-      <c r="E170" s="113"/>
-      <c r="F170" s="114"/>
-      <c r="G170" s="62" t="s">
-        <v>401</v>
-      </c>
-      <c r="H170" s="63"/>
-      <c r="I170" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J170" s="65" t="s">
-        <v>220</v>
-      </c>
-      <c r="K170" s="66"/>
+      <c r="D170" s="107" t="s">
+        <v>350</v>
+      </c>
+      <c r="E170" s="108"/>
+      <c r="F170" s="109"/>
+      <c r="G170" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="H170" s="62"/>
+      <c r="I170" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J170" s="64" t="s">
+        <v>435</v>
+      </c>
+      <c r="K170" s="65"/>
       <c r="L170" s="6"/>
       <c r="M170" s="6"/>
       <c r="N170" s="6"/>
     </row>
     <row r="171" spans="1:14" ht="176.4">
       <c r="A171" s="11"/>
-      <c r="B171" s="110" t="str">
-        <f>master!B143</f>
+      <c r="B171" s="121" t="str">
+        <f>master!B144</f>
         <v>課題の振り返り</v>
       </c>
-      <c r="C171" s="62" t="str">
-        <f>master!C143</f>
+      <c r="C171" s="61" t="str">
+        <f>master!C144</f>
         <v>サンプルのAPとの自分のAPとの比較</v>
       </c>
-      <c r="D171" s="112" t="s">
-        <v>358</v>
-      </c>
-      <c r="E171" s="113"/>
-      <c r="F171" s="114"/>
-      <c r="G171" s="62" t="s">
-        <v>408</v>
-      </c>
-      <c r="H171" s="63"/>
-      <c r="I171" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J171" s="65">
+      <c r="D171" s="107" t="s">
+        <v>430</v>
+      </c>
+      <c r="E171" s="108"/>
+      <c r="F171" s="109"/>
+      <c r="G171" s="61" t="s">
+        <v>431</v>
+      </c>
+      <c r="H171" s="62"/>
+      <c r="I171" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J171" s="64">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K171" s="66"/>
+      <c r="K171" s="65"/>
       <c r="L171" s="6"/>
       <c r="M171" s="6"/>
       <c r="N171" s="6"/>
     </row>
     <row r="172" spans="1:14" ht="63">
       <c r="A172" s="11"/>
-      <c r="B172" s="111"/>
-      <c r="C172" s="62" t="str">
-        <f>master!C144</f>
+      <c r="B172" s="123"/>
+      <c r="C172" s="61" t="str">
+        <f>master!C145</f>
         <v>レポートの作成</v>
       </c>
-      <c r="D172" s="112" t="s">
-        <v>356</v>
-      </c>
-      <c r="E172" s="113"/>
-      <c r="F172" s="114"/>
-      <c r="G172" s="62" t="s">
-        <v>409</v>
-      </c>
-      <c r="H172" s="63"/>
-      <c r="I172" s="64" t="s">
-        <v>24</v>
-      </c>
-      <c r="J172" s="65">
+      <c r="D172" s="107" t="s">
+        <v>432</v>
+      </c>
+      <c r="E172" s="108"/>
+      <c r="F172" s="109"/>
+      <c r="G172" s="61" t="s">
+        <v>429</v>
+      </c>
+      <c r="H172" s="62"/>
+      <c r="I172" s="63" t="s">
+        <v>24</v>
+      </c>
+      <c r="J172" s="64">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K172" s="66"/>
+      <c r="K172" s="65"/>
       <c r="L172" s="6"/>
       <c r="M172" s="6"/>
       <c r="N172" s="6"/>
     </row>
-    <row r="173" spans="1:14" ht="24" customHeight="1">
-      <c r="A173" s="11"/>
-      <c r="B173" s="84"/>
-      <c r="C173" s="83"/>
-      <c r="D173" s="116"/>
-      <c r="E173" s="117"/>
-      <c r="F173" s="118"/>
-      <c r="G173" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="H173" s="12"/>
-      <c r="I173" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="J173" s="47"/>
-      <c r="K173" s="43"/>
-      <c r="L173" s="6"/>
-      <c r="M173" s="6"/>
-      <c r="N173" s="6"/>
-    </row>
-    <row r="174" spans="1:14" ht="24" customHeight="1">
-      <c r="A174" s="11"/>
-      <c r="B174" s="84"/>
-      <c r="C174" s="83"/>
-      <c r="D174" s="116"/>
-      <c r="E174" s="117"/>
-      <c r="F174" s="118"/>
-      <c r="G174" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="H174" s="12"/>
-      <c r="I174" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="J174" s="47"/>
-      <c r="K174" s="43"/>
-      <c r="L174" s="6"/>
-      <c r="M174" s="6"/>
-      <c r="N174" s="6"/>
-    </row>
-    <row r="175" spans="1:14" ht="15" customHeight="1">
-      <c r="J175" s="46"/>
-    </row>
-    <row r="176" spans="1:14" ht="15" customHeight="1"/>
+    <row r="173" spans="1:14" ht="15" customHeight="1">
+      <c r="J173" s="46"/>
+    </row>
+    <row r="174" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
-  <mergeCells count="181">
+  <mergeCells count="179">
+    <mergeCell ref="B165:B166"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="B171:B172"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="B167:B170"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B106:B107"/>
+    <mergeCell ref="B108:B119"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="D22:F23"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="K22:K23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="B25:B30"/>
+    <mergeCell ref="B31:B38"/>
+    <mergeCell ref="B39:B57"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="B65:B73"/>
+    <mergeCell ref="B61:B64"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="B74:B93"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="B96:B101"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="B124:B127"/>
+    <mergeCell ref="B128:B145"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
     <mergeCell ref="B146:B147"/>
     <mergeCell ref="D119:F119"/>
     <mergeCell ref="D148:F148"/>
@@ -11338,163 +11520,6 @@
     <mergeCell ref="D135:F135"/>
     <mergeCell ref="D136:F136"/>
     <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="B124:B127"/>
-    <mergeCell ref="B128:B145"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="B96:B101"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="B74:B93"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="B65:B73"/>
-    <mergeCell ref="B61:B64"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="B25:B30"/>
-    <mergeCell ref="B31:B38"/>
-    <mergeCell ref="B39:B57"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D22:F23"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="K22:K23"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B106:B107"/>
-    <mergeCell ref="B108:B119"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="B165:B166"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="B168:B170"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="B171:B172"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11507,7 +11532,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H24:H174</xm:sqref>
+          <xm:sqref>H24:H172</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11517,7 +11542,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C145"/>
+  <dimension ref="B1:C146"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -11531,16 +11556,16 @@
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="83" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="C3" t="s">
         <v>57</v>
@@ -11716,610 +11741,612 @@
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="B36" s="87"/>
-      <c r="C36" s="87"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="84"/>
     </row>
     <row r="37" spans="2:3">
       <c r="B37" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="C37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="41" spans="2:3">
       <c r="C41" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="2:3">
       <c r="C42" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="2:3">
       <c r="C43" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="2:3">
       <c r="B44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" t="s">
         <v>143</v>
-      </c>
-      <c r="C44" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="45" spans="2:3">
       <c r="C45" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="2:3">
       <c r="C46" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="2:3">
       <c r="C47" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="2:3">
       <c r="C48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="C49" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="C50" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="C51" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="C52" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="C53" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="C54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="55" spans="2:3">
       <c r="C55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="2:3">
       <c r="C56" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" spans="2:3">
       <c r="C57" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="2:3">
       <c r="C58" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="2:3">
       <c r="C59" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="2:3">
       <c r="C60" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="61" spans="2:3">
       <c r="C61" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="62" spans="2:3">
       <c r="C62" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="2:3">
       <c r="C63" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" spans="2:3">
       <c r="C64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="2:3">
       <c r="C65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="2:3">
       <c r="C66" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="2:3">
       <c r="B67" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="C67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="68" spans="2:3">
-      <c r="B68" s="87"/>
-      <c r="C68" s="87"/>
+      <c r="B68" s="84"/>
+      <c r="C68" s="84"/>
     </row>
     <row r="69" spans="2:3">
       <c r="B69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C69" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="70" spans="2:3">
       <c r="C70" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="71" spans="2:3">
       <c r="B71" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C71" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="72" spans="2:3">
       <c r="C72" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="2:3">
       <c r="C73" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="74" spans="2:3">
       <c r="C74" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="75" spans="2:3">
       <c r="C75" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="2:3">
       <c r="C76" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="2:3">
-      <c r="B77" s="87"/>
-      <c r="C77" s="87"/>
+      <c r="B77" s="84"/>
+      <c r="C77" s="84"/>
     </row>
     <row r="78" spans="2:3">
       <c r="B78" t="s">
-        <v>427</v>
-      </c>
-      <c r="C78" s="88" t="s">
-        <v>230</v>
+        <v>411</v>
+      </c>
+      <c r="C78" s="85" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="2:3">
       <c r="B79" t="s">
-        <v>231</v>
-      </c>
-      <c r="C79" s="88" t="s">
-        <v>221</v>
+        <v>228</v>
+      </c>
+      <c r="C79" s="85" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="2:3">
-      <c r="C80" s="88" t="s">
-        <v>222</v>
+      <c r="C80" s="85" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="81" spans="2:3">
       <c r="B81" t="s">
-        <v>235</v>
-      </c>
-      <c r="C81" s="89" t="s">
-        <v>223</v>
+        <v>232</v>
+      </c>
+      <c r="C81" s="86" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="82" spans="2:3">
-      <c r="C82" s="85" t="s">
-        <v>224</v>
+      <c r="C82" s="82" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="2:3">
       <c r="B83" t="s">
-        <v>237</v>
-      </c>
-      <c r="C83" s="85" t="s">
-        <v>239</v>
+        <v>234</v>
+      </c>
+      <c r="C83" s="82" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="84" spans="2:3">
-      <c r="C84" s="85" t="s">
+      <c r="C84" s="82" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3">
+      <c r="C85" s="82" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3">
+      <c r="C86" s="82" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3">
+      <c r="C87" s="82" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3">
+      <c r="C88" s="82" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3">
+      <c r="C89" s="82" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="90" spans="2:3">
+      <c r="C90" s="82" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="91" spans="2:3">
+      <c r="C91" s="82" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3">
+      <c r="C92" s="82" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3">
+      <c r="C93" s="82" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="85" spans="2:3">
-      <c r="C85" s="85" t="s">
+    <row r="94" spans="2:3">
+      <c r="C94" s="82" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="86" spans="2:3">
-      <c r="C86" s="85" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3">
-      <c r="C87" s="85" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3">
-      <c r="C88" s="85" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3">
-      <c r="C89" s="85" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3">
-      <c r="C90" s="85" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3">
-      <c r="C91" s="85" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3">
-      <c r="C92" s="85" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3">
-      <c r="C93" s="85" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3">
-      <c r="C94" s="85" t="s">
-        <v>229</v>
-      </c>
-    </row>
     <row r="95" spans="2:3">
-      <c r="B95" s="87"/>
-      <c r="C95" s="87"/>
+      <c r="B95" s="84"/>
+      <c r="C95" s="84"/>
     </row>
     <row r="96" spans="2:3">
       <c r="B96" t="s">
-        <v>428</v>
-      </c>
-      <c r="C96" s="85" t="s">
+        <v>412</v>
+      </c>
+      <c r="C96" s="82" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="97" spans="2:3">
-      <c r="C97" s="88" t="s">
-        <v>271</v>
+      <c r="C97" s="85" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="98" spans="2:3">
-      <c r="C98" s="88" t="s">
-        <v>272</v>
+      <c r="C98" s="85" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="2:3">
       <c r="B99" t="s">
-        <v>290</v>
-      </c>
-      <c r="C99" s="88" t="s">
+        <v>287</v>
+      </c>
+      <c r="C99" s="85" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3">
+      <c r="C100" s="85" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3">
+      <c r="C101" s="86" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3">
+      <c r="C102" s="82" t="s">
         <v>273</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3">
-      <c r="C100" s="88" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3">
-      <c r="C101" s="89" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3">
-      <c r="C102" s="85" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="103" spans="2:3">
       <c r="B103" t="s">
-        <v>291</v>
-      </c>
-      <c r="C103" s="85" t="s">
-        <v>286</v>
+        <v>288</v>
+      </c>
+      <c r="C103" s="82" t="s">
+        <v>283</v>
       </c>
     </row>
     <row r="104" spans="2:3">
-      <c r="C104" s="85" t="s">
-        <v>277</v>
+      <c r="C104" s="82" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="105" spans="2:3">
-      <c r="C105" s="85" t="s">
-        <v>292</v>
+      <c r="C105" s="82" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="106" spans="2:3">
-      <c r="C106" s="85" t="s">
-        <v>293</v>
+      <c r="C106" s="82" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="107" spans="2:3">
       <c r="C107" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="108" spans="2:3">
+      <c r="C108" s="82" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="109" spans="2:3">
+      <c r="C109" s="82" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="110" spans="2:3">
+      <c r="C110" s="82" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="111" spans="2:3">
+      <c r="C111" s="82" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="108" spans="2:3">
-      <c r="C108" s="85" t="s">
+    <row r="112" spans="2:3">
+      <c r="C112" s="82" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="113" spans="2:3">
+      <c r="C113" s="82" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="114" spans="2:3">
+      <c r="C114" s="82" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="109" spans="2:3">
-      <c r="C109" s="85" t="s">
+    <row r="115" spans="2:3">
+      <c r="C115" s="82" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="116" spans="2:3">
+      <c r="C116" s="82" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="117" spans="2:3">
+      <c r="C117" s="82" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="118" spans="2:3">
+      <c r="C118" s="82" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="119" spans="2:3">
+      <c r="C119" s="82" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="120" spans="2:3">
+      <c r="C120" s="82" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="121" spans="2:3">
+      <c r="B121" s="82" t="s">
+        <v>404</v>
+      </c>
+      <c r="C121" s="82" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="122" spans="2:3">
+      <c r="C122" s="82" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="110" spans="2:3">
-      <c r="C110" s="85" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3">
-      <c r="C111" s="85" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="112" spans="2:3">
-      <c r="C112" s="85" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3">
-      <c r="C113" s="85" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="114" spans="2:3">
-      <c r="C114" s="85" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3">
-      <c r="C115" s="85" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3">
-      <c r="C116" s="85" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3">
-      <c r="C117" s="85" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3">
-      <c r="C118" s="85" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3">
-      <c r="C119" s="85" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="120" spans="2:3">
-      <c r="C120" s="85" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="121" spans="2:3">
-      <c r="B121" s="85" t="s">
-        <v>419</v>
-      </c>
-      <c r="C121" s="85" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="122" spans="2:3">
-      <c r="C122" s="85" t="s">
-        <v>298</v>
-      </c>
-    </row>
     <row r="123" spans="2:3">
-      <c r="B123" s="87"/>
-      <c r="C123" s="87"/>
+      <c r="B123" s="84"/>
+      <c r="C123" s="84"/>
     </row>
     <row r="124" spans="2:3">
       <c r="B124" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C124" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="125" spans="2:3">
       <c r="C125" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="126" spans="2:3">
-      <c r="C126" s="85" t="s">
-        <v>325</v>
+      <c r="C126" s="82" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="127" spans="2:3">
-      <c r="C127" s="85" t="s">
-        <v>326</v>
+      <c r="C127" s="82" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="128" spans="2:3">
       <c r="B128" t="s">
-        <v>424</v>
-      </c>
-      <c r="C128" s="85" t="s">
+        <v>408</v>
+      </c>
+      <c r="C128" s="82" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="129" spans="2:3">
+      <c r="C129" s="82" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="130" spans="2:3">
+      <c r="C130" s="82" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="131" spans="2:3">
+      <c r="C131" s="82" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="132" spans="2:3">
+      <c r="C132" s="82" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="133" spans="2:3">
+      <c r="C133" s="82" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="134" spans="2:3">
+      <c r="C134" s="82" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="135" spans="2:3">
+      <c r="C135" s="82" t="s">
         <v>327</v>
-      </c>
-    </row>
-    <row r="129" spans="2:3">
-      <c r="C129" s="85" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="130" spans="2:3">
-      <c r="C130" s="85" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="131" spans="2:3">
-      <c r="C131" s="85" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="132" spans="2:3">
-      <c r="C132" s="85" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="133" spans="2:3">
-      <c r="C133" s="85" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="134" spans="2:3">
-      <c r="C134" s="85" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="135" spans="2:3">
-      <c r="C135" s="85" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="136" spans="2:3">
       <c r="B136" t="s">
-        <v>421</v>
-      </c>
-      <c r="C136" s="85" t="s">
-        <v>331</v>
+        <v>405</v>
+      </c>
+      <c r="C136" s="82" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="137" spans="2:3">
-      <c r="C137" s="85" t="s">
-        <v>350</v>
+      <c r="C137" s="82" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="138" spans="2:3">
-      <c r="B138" s="87"/>
-      <c r="C138" s="87"/>
+      <c r="B138" s="84"/>
+      <c r="C138" s="84"/>
     </row>
     <row r="139" spans="2:3">
       <c r="B139" t="s">
-        <v>430</v>
+        <v>330</v>
       </c>
       <c r="C139" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="140" spans="2:3">
-      <c r="B140" s="85" t="s">
-        <v>333</v>
-      </c>
-      <c r="C140" s="85" t="s">
-        <v>353</v>
+      <c r="B140" s="82"/>
+      <c r="C140" s="82" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="141" spans="2:3">
-      <c r="C141" s="85" t="s">
-        <v>332</v>
+      <c r="C141" s="82" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="142" spans="2:3">
-      <c r="C142" s="85" t="s">
-        <v>334</v>
+      <c r="C142" s="82" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="2:3">
-      <c r="B143" t="s">
-        <v>423</v>
-      </c>
-      <c r="C143" s="85" t="s">
-        <v>357</v>
-      </c>
+      <c r="B143" s="84"/>
+      <c r="C143" s="84"/>
     </row>
     <row r="144" spans="2:3">
-      <c r="C144" s="85" t="s">
-        <v>355</v>
+      <c r="B144" t="s">
+        <v>407</v>
+      </c>
+      <c r="C144" s="82" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="145" spans="2:3">
-      <c r="B145" s="87"/>
-      <c r="C145" s="87"/>
+      <c r="C145" s="82" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="146" spans="2:3">
+      <c r="B146" s="84"/>
+      <c r="C146" s="84"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/IG/AI Native-バイブコーディング_IG.xlsx
+++ b/IG/AI Native-バイブコーディング_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB24DB2-78C9-4380-A86D-62A26F6B5CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{081703D8-1AC5-460E-B7C2-7D9A98F7524D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（4日）'!$A$1:$J$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$172</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$171</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -63,7 +63,7 @@
     <author>ishida</author>
   </authors>
   <commentList>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{64B0F3D5-EE14-4570-A1F7-7C1C72F43D2E}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{64B0F3D5-EE14-4570-A1F7-7C1C72F43D2E}">
       <text>
         <r>
           <rPr>
@@ -5431,12 +5431,33 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -5446,26 +5467,23 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
@@ -5475,24 +5493,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -6839,7 +6839,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N173"/>
+  <dimension ref="A2:N172"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -6905,61 +6905,69 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="2:14" ht="36" customHeight="1">
-      <c r="B5" s="125"/>
-      <c r="C5" s="125"/>
-      <c r="D5" s="125"/>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="125"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="125"/>
-      <c r="J5" s="125"/>
-      <c r="K5" s="125"/>
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="119"/>
+      <c r="J5" s="119"/>
+      <c r="K5" s="119"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
-    <row r="6" spans="2:14" ht="32.4" customHeight="1">
-      <c r="B6" s="125"/>
-      <c r="C6" s="125"/>
-      <c r="D6" s="125"/>
-      <c r="E6" s="125"/>
-      <c r="F6" s="125"/>
-      <c r="G6" s="125"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="125"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="125"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="27"/>
+    <row r="6" spans="2:14">
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
+      <c r="B7" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="102" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="102"/>
+      <c r="F7" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="45"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="102" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="102"/>
-      <c r="F8" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="45"/>
-      <c r="J8" s="6"/>
+      <c r="B8" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="41"/>
+      <c r="F8" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>18</v>
+      </c>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
       <c r="M8" s="6"/>
@@ -6967,10 +6975,10 @@
     </row>
     <row r="9" spans="2:14">
       <c r="B9" s="31" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" s="57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" s="42" t="s">
         <v>19</v>
@@ -6989,10 +6997,10 @@
     </row>
     <row r="10" spans="2:14">
       <c r="B10" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="57" t="s">
-        <v>36</v>
+        <v>91</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>35</v>
       </c>
       <c r="D10" s="42" t="s">
         <v>19</v>
@@ -7011,10 +7019,10 @@
     </row>
     <row r="11" spans="2:14">
       <c r="B11" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>35</v>
+        <v>92</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>89</v>
       </c>
       <c r="D11" s="42" t="s">
         <v>19</v>
@@ -7033,10 +7041,10 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" s="31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="57" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>90</v>
       </c>
       <c r="D12" s="42" t="s">
         <v>19</v>
@@ -7055,10 +7063,10 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="33" t="s">
-        <v>90</v>
+        <v>417</v>
+      </c>
+      <c r="C13" s="57" t="s">
+        <v>37</v>
       </c>
       <c r="D13" s="42" t="s">
         <v>19</v>
@@ -7077,10 +7085,10 @@
     </row>
     <row r="14" spans="2:14">
       <c r="B14" s="31" t="s">
-        <v>417</v>
+        <v>94</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D14" s="42" t="s">
         <v>19</v>
@@ -7099,10 +7107,10 @@
     </row>
     <row r="15" spans="2:14">
       <c r="B15" s="31" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C15" s="57" t="s">
-        <v>38</v>
+        <v>355</v>
       </c>
       <c r="D15" s="42" t="s">
         <v>19</v>
@@ -7121,10 +7129,10 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C16" s="57" t="s">
-        <v>355</v>
+        <v>351</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>354</v>
       </c>
       <c r="D16" s="42" t="s">
         <v>19</v>
@@ -7143,10 +7151,10 @@
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
+      </c>
+      <c r="C17" s="57" t="s">
+        <v>352</v>
       </c>
       <c r="D17" s="42" t="s">
         <v>19</v>
@@ -7165,10 +7173,10 @@
     </row>
     <row r="18" spans="1:14">
       <c r="B18" s="31" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C18" s="57" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D18" s="42" t="s">
         <v>19</v>
@@ -7185,125 +7193,130 @@
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14">
-      <c r="B19" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="C19" s="57" t="s">
-        <v>353</v>
-      </c>
-      <c r="D19" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="41"/>
-      <c r="F19" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="21" spans="1:14" ht="24" customHeight="1">
+    <row r="20" spans="1:14" ht="24" customHeight="1">
+      <c r="A20" s="10"/>
+      <c r="B20" s="98" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="98" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="97" t="s">
+        <v>23</v>
+      </c>
+      <c r="I20" s="117" t="s">
+        <v>31</v>
+      </c>
+      <c r="J20" s="118"/>
+      <c r="K20" s="97" t="s">
+        <v>32</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="10"/>
-      <c r="B21" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="98" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="98" t="s">
-        <v>8</v>
-      </c>
+      <c r="B21" s="98"/>
+      <c r="C21" s="98"/>
+      <c r="D21" s="98"/>
       <c r="E21" s="98"/>
       <c r="F21" s="98"/>
-      <c r="G21" s="98" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="97" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21" s="123" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="124"/>
-      <c r="K21" s="97" t="s">
-        <v>32</v>
-      </c>
+      <c r="G21" s="98"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="K21" s="98"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" ht="151.19999999999999">
       <c r="A22" s="10"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J22" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="K22" s="98"/>
+      <c r="B22" s="75" t="str">
+        <f>master!B3</f>
+        <v>バイブコーディングの導入</v>
+      </c>
+      <c r="C22" s="48" t="str">
+        <f>master!C3</f>
+        <v>講義の目的</v>
+      </c>
+      <c r="D22" s="114" t="s">
+        <v>96</v>
+      </c>
+      <c r="E22" s="115"/>
+      <c r="F22" s="116"/>
+      <c r="G22" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="H22" s="12"/>
+      <c r="I22" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J22" s="44">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K22" s="40"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
       <c r="N22" s="6"/>
     </row>
-    <row r="23" spans="1:14" ht="151.19999999999999">
+    <row r="23" spans="1:14" ht="138.6" customHeight="1">
       <c r="A23" s="10"/>
-      <c r="B23" s="75" t="str">
-        <f>master!B3</f>
-        <v>バイブコーディングの導入</v>
+      <c r="B23" s="120" t="str">
+        <f>master!B4</f>
+        <v>Webアプリケーションとは</v>
       </c>
       <c r="C23" s="48" t="str">
-        <f>master!C3</f>
-        <v>講義の目的</v>
-      </c>
-      <c r="D23" s="107" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="108"/>
-      <c r="F23" s="109"/>
+        <f>master!C4</f>
+        <v>Webアプリケーションとは</v>
+      </c>
+      <c r="D23" s="114" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="115"/>
+      <c r="F23" s="116"/>
       <c r="G23" s="48" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J23" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K23" s="40"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="138.6" customHeight="1">
-      <c r="A24" s="10"/>
-      <c r="B24" s="120" t="str">
-        <f>master!B4</f>
-        <v>Webアプリケーションとは</v>
-      </c>
+    <row r="24" spans="1:14" ht="75.599999999999994">
+      <c r="A24" s="11"/>
+      <c r="B24" s="121"/>
       <c r="C24" s="48" t="str">
-        <f>master!C4</f>
-        <v>Webアプリケーションとは</v>
-      </c>
-      <c r="D24" s="107" t="s">
-        <v>98</v>
-      </c>
-      <c r="E24" s="108"/>
-      <c r="F24" s="109"/>
+        <f>master!C5</f>
+        <v>Webアプリケーションの種類</v>
+      </c>
+      <c r="D24" s="114" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="115"/>
+      <c r="F24" s="116"/>
       <c r="G24" s="48" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="46" t="s">
@@ -7317,47 +7330,47 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="75.599999999999994">
+    <row r="25" spans="1:14" ht="37.799999999999997">
       <c r="A25" s="11"/>
       <c r="B25" s="121"/>
       <c r="C25" s="48" t="str">
-        <f>master!C5</f>
-        <v>Webアプリケーションの種類</v>
-      </c>
-      <c r="D25" s="107" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="108"/>
-      <c r="F25" s="109"/>
+        <f>master!C6</f>
+        <v>アプリケーションとは</v>
+      </c>
+      <c r="D25" s="114" t="s">
+        <v>100</v>
+      </c>
+      <c r="E25" s="115"/>
+      <c r="F25" s="116"/>
       <c r="G25" s="48" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J25" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K25" s="40"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="37.799999999999997">
+    <row r="26" spans="1:14" ht="63">
       <c r="A26" s="11"/>
       <c r="B26" s="121"/>
       <c r="C26" s="48" t="str">
-        <f>master!C6</f>
-        <v>アプリケーションとは</v>
-      </c>
-      <c r="D26" s="107" t="s">
-        <v>100</v>
-      </c>
-      <c r="E26" s="108"/>
-      <c r="F26" s="109"/>
+        <f>master!C7</f>
+        <v>Web画面アプリケーション</v>
+      </c>
+      <c r="D26" s="114" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" s="115"/>
+      <c r="F26" s="116"/>
       <c r="G26" s="48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="46" t="s">
@@ -7374,15 +7387,12 @@
     <row r="27" spans="1:14" ht="63">
       <c r="A27" s="11"/>
       <c r="B27" s="121"/>
-      <c r="C27" s="48" t="str">
-        <f>master!C7</f>
-        <v>Web画面アプリケーション</v>
-      </c>
-      <c r="D27" s="107" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="108"/>
-      <c r="F27" s="109"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="114" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="115"/>
+      <c r="F27" s="116"/>
       <c r="G27" s="48" t="s">
         <v>42</v>
       </c>
@@ -7391,51 +7401,57 @@
         <v>24</v>
       </c>
       <c r="J27" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K27" s="40"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="63">
+    <row r="28" spans="1:14" ht="113.4">
       <c r="A28" s="11"/>
-      <c r="B28" s="121"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="107" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="108"/>
-      <c r="F28" s="109"/>
+      <c r="B28" s="122"/>
+      <c r="C28" s="48" t="str">
+        <f>master!C8</f>
+        <v>ブラウザからのリクエスト種類</v>
+      </c>
+      <c r="D28" s="114" t="s">
+        <v>103</v>
+      </c>
+      <c r="E28" s="115"/>
+      <c r="F28" s="116"/>
       <c r="G28" s="48" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J28" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K28" s="40"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
       <c r="N28" s="6"/>
     </row>
-    <row r="29" spans="1:14" ht="113.4">
+    <row r="29" spans="1:14" ht="102" customHeight="1">
       <c r="A29" s="11"/>
-      <c r="B29" s="122"/>
+      <c r="B29" s="120" t="str">
+        <f>master!B9</f>
+        <v>データベースとは</v>
+      </c>
       <c r="C29" s="48" t="str">
-        <f>master!C8</f>
-        <v>ブラウザからのリクエスト種類</v>
-      </c>
-      <c r="D29" s="107" t="s">
-        <v>103</v>
-      </c>
-      <c r="E29" s="108"/>
-      <c r="F29" s="109"/>
+        <f>master!C9</f>
+        <v>データベースとは</v>
+      </c>
+      <c r="D29" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="115"/>
+      <c r="F29" s="116"/>
       <c r="G29" s="48" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="46" t="s">
@@ -7449,50 +7465,47 @@
       <c r="M29" s="6"/>
       <c r="N29" s="6"/>
     </row>
-    <row r="30" spans="1:14" ht="102" customHeight="1">
+    <row r="30" spans="1:14" ht="88.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="120" t="str">
-        <f>master!B9</f>
-        <v>データベースとは</v>
-      </c>
+      <c r="B30" s="121"/>
       <c r="C30" s="48" t="str">
-        <f>master!C9</f>
-        <v>データベースとは</v>
-      </c>
-      <c r="D30" s="107" t="s">
-        <v>104</v>
-      </c>
-      <c r="E30" s="108"/>
-      <c r="F30" s="109"/>
+        <f>master!C10</f>
+        <v>リレーショナルデータベース</v>
+      </c>
+      <c r="D30" s="114" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="115"/>
+      <c r="F30" s="116"/>
       <c r="G30" s="48" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J30" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K30" s="40"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="88.2">
+    <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
       <c r="B31" s="121"/>
       <c r="C31" s="48" t="str">
-        <f>master!C10</f>
-        <v>リレーショナルデータベース</v>
-      </c>
-      <c r="D31" s="107" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" s="108"/>
-      <c r="F31" s="109"/>
+        <f>master!C11</f>
+        <v>データベースの役割</v>
+      </c>
+      <c r="D31" s="114" t="s">
+        <v>106</v>
+      </c>
+      <c r="E31" s="115"/>
+      <c r="F31" s="116"/>
       <c r="G31" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="46" t="s">
@@ -7501,54 +7514,54 @@
       <c r="J31" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K31" s="40"/>
+      <c r="K31" s="40" t="s">
+        <v>116</v>
+      </c>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="25.2">
+    <row r="32" spans="1:14" ht="75.599999999999994">
       <c r="A32" s="11"/>
       <c r="B32" s="121"/>
       <c r="C32" s="48" t="str">
-        <f>master!C11</f>
-        <v>データベースの役割</v>
-      </c>
-      <c r="D32" s="107" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="108"/>
-      <c r="F32" s="109"/>
+        <f>master!C12</f>
+        <v>2.1.テーブル</v>
+      </c>
+      <c r="D32" s="114" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="115"/>
+      <c r="F32" s="116"/>
       <c r="G32" s="48" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J32" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K32" s="40" t="s">
-        <v>116</v>
-      </c>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K32" s="40"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
       <c r="N32" s="6"/>
     </row>
-    <row r="33" spans="1:14" ht="75.599999999999994">
+    <row r="33" spans="1:14" ht="100.8">
       <c r="A33" s="11"/>
       <c r="B33" s="121"/>
       <c r="C33" s="48" t="str">
-        <f>master!C12</f>
-        <v>2.1.テーブル</v>
-      </c>
-      <c r="D33" s="107" t="s">
-        <v>107</v>
-      </c>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
+        <f>master!C13</f>
+        <v>2.2.データ型１</v>
+      </c>
+      <c r="D33" s="114" t="s">
+        <v>108</v>
+      </c>
+      <c r="E33" s="115"/>
+      <c r="F33" s="116"/>
       <c r="G33" s="48" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="46" t="s">
@@ -7562,20 +7575,20 @@
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" ht="100.8">
+    <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
       <c r="B34" s="121"/>
       <c r="C34" s="48" t="str">
-        <f>master!C13</f>
-        <v>2.2.データ型１</v>
-      </c>
-      <c r="D34" s="107" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="108"/>
-      <c r="F34" s="109"/>
+        <f>master!C14</f>
+        <v>2.2.データ型２</v>
+      </c>
+      <c r="D34" s="114" t="s">
+        <v>109</v>
+      </c>
+      <c r="E34" s="115"/>
+      <c r="F34" s="116"/>
       <c r="G34" s="48" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="46" t="s">
@@ -7593,14 +7606,14 @@
       <c r="A35" s="11"/>
       <c r="B35" s="121"/>
       <c r="C35" s="48" t="str">
-        <f>master!C14</f>
-        <v>2.2.データ型２</v>
-      </c>
-      <c r="D35" s="107" t="s">
-        <v>109</v>
-      </c>
-      <c r="E35" s="108"/>
-      <c r="F35" s="109"/>
+        <f>master!C15</f>
+        <v>2.3.リレーション</v>
+      </c>
+      <c r="D35" s="114" t="s">
+        <v>110</v>
+      </c>
+      <c r="E35" s="115"/>
+      <c r="F35" s="116"/>
       <c r="G35" s="48" t="s">
         <v>43</v>
       </c>
@@ -7609,7 +7622,7 @@
         <v>24</v>
       </c>
       <c r="J35" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K35" s="40"/>
       <c r="L35" s="6"/>
@@ -7618,16 +7631,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="121"/>
+      <c r="B36" s="122"/>
       <c r="C36" s="48" t="str">
-        <f>master!C15</f>
-        <v>2.3.リレーション</v>
-      </c>
-      <c r="D36" s="107" t="s">
-        <v>110</v>
-      </c>
-      <c r="E36" s="108"/>
-      <c r="F36" s="109"/>
+        <f>master!C16</f>
+        <v>2.4.データを結合して取得（Join）</v>
+      </c>
+      <c r="D36" s="114" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="115"/>
+      <c r="F36" s="116"/>
       <c r="G36" s="48" t="s">
         <v>43</v>
       </c>
@@ -7636,27 +7649,30 @@
         <v>24</v>
       </c>
       <c r="J36" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K36" s="40"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="37.799999999999997">
+    <row r="37" spans="1:14" ht="88.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="122"/>
+      <c r="B37" s="120" t="str">
+        <f>master!B17</f>
+        <v>Java言語、Springフレームワークとは</v>
+      </c>
       <c r="C37" s="48" t="str">
-        <f>master!C16</f>
-        <v>2.4.データを結合して取得（Join）</v>
-      </c>
-      <c r="D37" s="107" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="108"/>
-      <c r="F37" s="109"/>
+        <f>master!C17</f>
+        <v>Webアプリケーションを作成するためのプログラミング言語</v>
+      </c>
+      <c r="D37" s="114" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" s="115"/>
+      <c r="F37" s="116"/>
       <c r="G37" s="48" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="46" t="s">
@@ -7670,30 +7686,27 @@
       <c r="M37" s="6"/>
       <c r="N37" s="6"/>
     </row>
-    <row r="38" spans="1:14" ht="88.2">
+    <row r="38" spans="1:14" ht="75.599999999999994">
       <c r="A38" s="11"/>
-      <c r="B38" s="120" t="str">
-        <f>master!B17</f>
-        <v>Java言語、Springフレームワークとは</v>
-      </c>
+      <c r="B38" s="121"/>
       <c r="C38" s="48" t="str">
-        <f>master!C17</f>
-        <v>Webアプリケーションを作成するためのプログラミング言語</v>
-      </c>
-      <c r="D38" s="107" t="s">
-        <v>112</v>
-      </c>
-      <c r="E38" s="108"/>
-      <c r="F38" s="109"/>
+        <f>master!C18</f>
+        <v>Java</v>
+      </c>
+      <c r="D38" s="114" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" s="115"/>
+      <c r="F38" s="116"/>
       <c r="G38" s="48" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J38" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K38" s="40"/>
       <c r="L38" s="6"/>
@@ -7704,14 +7717,14 @@
       <c r="A39" s="11"/>
       <c r="B39" s="121"/>
       <c r="C39" s="48" t="str">
-        <f>master!C18</f>
-        <v>Java</v>
-      </c>
-      <c r="D39" s="107" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="108"/>
-      <c r="F39" s="109"/>
+        <f>master!C19</f>
+        <v>Java言語の構成要素</v>
+      </c>
+      <c r="D39" s="114" t="s">
+        <v>114</v>
+      </c>
+      <c r="E39" s="115"/>
+      <c r="F39" s="116"/>
       <c r="G39" s="48" t="s">
         <v>45</v>
       </c>
@@ -7720,54 +7733,54 @@
         <v>24</v>
       </c>
       <c r="J39" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K39" s="40"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="75.599999999999994">
+    <row r="40" spans="1:14" ht="50.4">
       <c r="A40" s="11"/>
       <c r="B40" s="121"/>
       <c r="C40" s="48" t="str">
-        <f>master!C19</f>
-        <v>Java言語の構成要素</v>
-      </c>
-      <c r="D40" s="107" t="s">
-        <v>114</v>
-      </c>
-      <c r="E40" s="108"/>
-      <c r="F40" s="109"/>
+        <f>master!C20</f>
+        <v>Webアプリケーションを構成するクラス</v>
+      </c>
+      <c r="D40" s="114" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" s="115"/>
+      <c r="F40" s="116"/>
       <c r="G40" s="48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J40" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K40" s="40"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="50.4">
+    <row r="41" spans="1:14" ht="88.2">
       <c r="A41" s="11"/>
       <c r="B41" s="121"/>
       <c r="C41" s="48" t="str">
-        <f>master!C20</f>
-        <v>Webアプリケーションを構成するクラス</v>
-      </c>
-      <c r="D41" s="107" t="s">
-        <v>115</v>
-      </c>
-      <c r="E41" s="108"/>
-      <c r="F41" s="109"/>
+        <f>master!C21</f>
+        <v>Nレイヤーアーキテクチャ</v>
+      </c>
+      <c r="D41" s="114" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" s="115"/>
+      <c r="F41" s="116"/>
       <c r="G41" s="48" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H41" s="12"/>
       <c r="I41" s="46" t="s">
@@ -7776,162 +7789,162 @@
       <c r="J41" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K41" s="40"/>
+      <c r="K41" s="40" t="s">
+        <v>116</v>
+      </c>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="88.2">
+    <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
       <c r="B42" s="121"/>
       <c r="C42" s="48" t="str">
-        <f>master!C21</f>
-        <v>Nレイヤーアーキテクチャ</v>
-      </c>
-      <c r="D42" s="107" t="s">
-        <v>117</v>
-      </c>
-      <c r="E42" s="108"/>
-      <c r="F42" s="109"/>
+        <f>master!C22</f>
+        <v>View と Controller と Service と Repository</v>
+      </c>
+      <c r="D42" s="114" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="115"/>
+      <c r="F42" s="116"/>
       <c r="G42" s="48" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="H42" s="12"/>
       <c r="I42" s="46" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J42" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K42" s="40" t="s">
-        <v>116</v>
-      </c>
+      <c r="K42" s="40"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="201.6">
+    <row r="43" spans="1:14" ht="37.799999999999997">
       <c r="A43" s="11"/>
       <c r="B43" s="121"/>
       <c r="C43" s="48" t="str">
-        <f>master!C22</f>
-        <v>View と Controller と Service と Repository</v>
-      </c>
-      <c r="D43" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="108"/>
-      <c r="F43" s="109"/>
+        <f>master!C23</f>
+        <v>Nレイヤーアーキテクチャ</v>
+      </c>
+      <c r="D43" s="114" t="s">
+        <v>120</v>
+      </c>
+      <c r="E43" s="115"/>
+      <c r="F43" s="116"/>
       <c r="G43" s="48" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="H43" s="12"/>
       <c r="I43" s="46" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J43" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K43" s="40"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="37.799999999999997">
+    <row r="44" spans="1:14" ht="163.80000000000001">
       <c r="A44" s="11"/>
       <c r="B44" s="121"/>
       <c r="C44" s="48" t="str">
-        <f>master!C23</f>
-        <v>Nレイヤーアーキテクチャ</v>
-      </c>
-      <c r="D44" s="107" t="s">
-        <v>120</v>
-      </c>
-      <c r="E44" s="108"/>
-      <c r="F44" s="109"/>
+        <f>master!C24</f>
+        <v>Webアプリケーション フレームワーク</v>
+      </c>
+      <c r="D44" s="114" t="s">
+        <v>121</v>
+      </c>
+      <c r="E44" s="115"/>
+      <c r="F44" s="116"/>
       <c r="G44" s="48" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
       <c r="H44" s="12"/>
       <c r="I44" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J44" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K44" s="40"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="163.80000000000001">
+    <row r="45" spans="1:14" ht="25.2">
       <c r="A45" s="11"/>
       <c r="B45" s="121"/>
       <c r="C45" s="48" t="str">
-        <f>master!C24</f>
-        <v>Webアプリケーション フレームワーク</v>
-      </c>
-      <c r="D45" s="107" t="s">
-        <v>121</v>
-      </c>
-      <c r="E45" s="108"/>
-      <c r="F45" s="109"/>
+        <f>master!C25</f>
+        <v>Java向けWebアプリケーションフレームワーク</v>
+      </c>
+      <c r="D45" s="114" t="s">
+        <v>123</v>
+      </c>
+      <c r="E45" s="115"/>
+      <c r="F45" s="116"/>
       <c r="G45" s="48" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J45" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K45" s="40"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="25.2">
+    <row r="46" spans="1:14" ht="189">
       <c r="A46" s="11"/>
       <c r="B46" s="121"/>
       <c r="C46" s="48" t="str">
-        <f>master!C25</f>
-        <v>Java向けWebアプリケーションフレームワーク</v>
-      </c>
-      <c r="D46" s="107" t="s">
-        <v>123</v>
-      </c>
-      <c r="E46" s="108"/>
-      <c r="F46" s="109"/>
+        <f>master!C26</f>
+        <v>Springフレームワーク</v>
+      </c>
+      <c r="D46" s="114" t="s">
+        <v>124</v>
+      </c>
+      <c r="E46" s="115"/>
+      <c r="F46" s="116"/>
       <c r="G46" s="48" t="s">
-        <v>48</v>
+        <v>125</v>
       </c>
       <c r="H46" s="12"/>
       <c r="I46" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J46" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K46" s="40"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
-    <row r="47" spans="1:14" ht="189">
+    <row r="47" spans="1:14" ht="88.2">
       <c r="A47" s="11"/>
       <c r="B47" s="121"/>
       <c r="C47" s="48" t="str">
-        <f>master!C26</f>
-        <v>Springフレームワーク</v>
-      </c>
-      <c r="D47" s="107" t="s">
-        <v>124</v>
-      </c>
-      <c r="E47" s="108"/>
-      <c r="F47" s="109"/>
+        <f>master!C27</f>
+        <v>Springフレームワーク：DIコンテナとは</v>
+      </c>
+      <c r="D47" s="114" t="s">
+        <v>126</v>
+      </c>
+      <c r="E47" s="115"/>
+      <c r="F47" s="116"/>
       <c r="G47" s="48" t="s">
-        <v>125</v>
+        <v>47</v>
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="46" t="s">
@@ -7940,54 +7953,54 @@
       <c r="J47" s="44">
         <v>3.472222222222222E-3</v>
       </c>
-      <c r="K47" s="40"/>
+      <c r="K47" s="40" t="s">
+        <v>116</v>
+      </c>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="88.2">
+    <row r="48" spans="1:14" ht="63">
       <c r="A48" s="11"/>
       <c r="B48" s="121"/>
       <c r="C48" s="48" t="str">
-        <f>master!C27</f>
-        <v>Springフレームワーク：DIコンテナとは</v>
-      </c>
-      <c r="D48" s="107" t="s">
-        <v>126</v>
-      </c>
-      <c r="E48" s="108"/>
-      <c r="F48" s="109"/>
+        <f>master!C28</f>
+        <v>DIコンテナ：DIコンテナが部品を注入する</v>
+      </c>
+      <c r="D48" s="114" t="s">
+        <v>127</v>
+      </c>
+      <c r="E48" s="115"/>
+      <c r="F48" s="116"/>
       <c r="G48" s="48" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H48" s="12"/>
       <c r="I48" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J48" s="44">
-        <v>3.472222222222222E-3</v>
-      </c>
-      <c r="K48" s="40" t="s">
-        <v>116</v>
-      </c>
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K48" s="40"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="63">
+    <row r="49" spans="1:14" ht="100.8">
       <c r="A49" s="11"/>
       <c r="B49" s="121"/>
       <c r="C49" s="48" t="str">
-        <f>master!C28</f>
-        <v>DIコンテナ：DIコンテナが部品を注入する</v>
-      </c>
-      <c r="D49" s="107" t="s">
-        <v>127</v>
-      </c>
-      <c r="E49" s="108"/>
-      <c r="F49" s="109"/>
+        <f>master!C29</f>
+        <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
+      </c>
+      <c r="D49" s="114" t="s">
+        <v>128</v>
+      </c>
+      <c r="E49" s="115"/>
+      <c r="F49" s="116"/>
       <c r="G49" s="48" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H49" s="12"/>
       <c r="I49" s="46" t="s">
@@ -8005,14 +8018,14 @@
       <c r="A50" s="11"/>
       <c r="B50" s="121"/>
       <c r="C50" s="48" t="str">
-        <f>master!C29</f>
-        <v>DIコンテナ：DIコンテナによる部品と注入対象になるための目印</v>
-      </c>
-      <c r="D50" s="107" t="s">
-        <v>128</v>
-      </c>
-      <c r="E50" s="108"/>
-      <c r="F50" s="109"/>
+        <f>master!C30</f>
+        <v>Springフレームワークにおける部品の設定</v>
+      </c>
+      <c r="D50" s="114" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" s="115"/>
+      <c r="F50" s="116"/>
       <c r="G50" s="48" t="s">
         <v>49</v>
       </c>
@@ -8028,20 +8041,20 @@
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="100.8">
+    <row r="51" spans="1:14" ht="88.2">
       <c r="A51" s="11"/>
       <c r="B51" s="121"/>
       <c r="C51" s="48" t="str">
-        <f>master!C30</f>
-        <v>Springフレームワークにおける部品の設定</v>
-      </c>
-      <c r="D51" s="107" t="s">
-        <v>129</v>
-      </c>
-      <c r="E51" s="108"/>
-      <c r="F51" s="109"/>
+        <f>master!C31</f>
+        <v>Spring Boot</v>
+      </c>
+      <c r="D51" s="114" t="s">
+        <v>130</v>
+      </c>
+      <c r="E51" s="115"/>
+      <c r="F51" s="116"/>
       <c r="G51" s="48" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H51" s="12"/>
       <c r="I51" s="46" t="s">
@@ -8055,20 +8068,20 @@
       <c r="M51" s="6"/>
       <c r="N51" s="6"/>
     </row>
-    <row r="52" spans="1:14" ht="88.2">
+    <row r="52" spans="1:14" ht="63">
       <c r="A52" s="11"/>
       <c r="B52" s="121"/>
       <c r="C52" s="48" t="str">
-        <f>master!C31</f>
-        <v>Spring Boot</v>
-      </c>
-      <c r="D52" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" s="108"/>
-      <c r="F52" s="109"/>
+        <f>master!C32</f>
+        <v>Spring Boot：オートコンフィグレーション</v>
+      </c>
+      <c r="D52" s="114" t="s">
+        <v>131</v>
+      </c>
+      <c r="E52" s="115"/>
+      <c r="F52" s="116"/>
       <c r="G52" s="48" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H52" s="12"/>
       <c r="I52" s="46" t="s">
@@ -8082,47 +8095,47 @@
       <c r="M52" s="6"/>
       <c r="N52" s="6"/>
     </row>
-    <row r="53" spans="1:14" ht="63">
+    <row r="53" spans="1:14" ht="50.4">
       <c r="A53" s="11"/>
       <c r="B53" s="121"/>
       <c r="C53" s="48" t="str">
-        <f>master!C32</f>
-        <v>Spring Boot：オートコンフィグレーション</v>
-      </c>
-      <c r="D53" s="107" t="s">
-        <v>131</v>
-      </c>
-      <c r="E53" s="108"/>
-      <c r="F53" s="109"/>
+        <f>master!C33</f>
+        <v>Spring Boot：Starters</v>
+      </c>
+      <c r="D53" s="114" t="s">
+        <v>132</v>
+      </c>
+      <c r="E53" s="115"/>
+      <c r="F53" s="116"/>
       <c r="G53" s="48" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H53" s="12"/>
       <c r="I53" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J53" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K53" s="40"/>
       <c r="L53" s="6"/>
       <c r="M53" s="6"/>
       <c r="N53" s="6"/>
     </row>
-    <row r="54" spans="1:14" ht="50.4">
+    <row r="54" spans="1:14" ht="88.2">
       <c r="A54" s="11"/>
       <c r="B54" s="121"/>
       <c r="C54" s="48" t="str">
-        <f>master!C33</f>
-        <v>Spring Boot：Starters</v>
-      </c>
-      <c r="D54" s="107" t="s">
-        <v>132</v>
-      </c>
-      <c r="E54" s="108"/>
-      <c r="F54" s="109"/>
+        <f>master!C34</f>
+        <v>Spring Boot：組込みWebAPサーバ</v>
+      </c>
+      <c r="D54" s="114" t="s">
+        <v>133</v>
+      </c>
+      <c r="E54" s="115"/>
+      <c r="F54" s="116"/>
       <c r="G54" s="48" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H54" s="12"/>
       <c r="I54" s="46" t="s">
@@ -8136,73 +8149,73 @@
       <c r="M54" s="6"/>
       <c r="N54" s="6"/>
     </row>
-    <row r="55" spans="1:14" ht="88.2">
+    <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="121"/>
+      <c r="B55" s="122"/>
       <c r="C55" s="48" t="str">
-        <f>master!C34</f>
-        <v>Spring Boot：組込みWebAPサーバ</v>
-      </c>
-      <c r="D55" s="107" t="s">
-        <v>133</v>
-      </c>
-      <c r="E55" s="108"/>
-      <c r="F55" s="109"/>
+        <f>master!C35</f>
+        <v>おすすめ書籍：『プロになるためのSpring入門』</v>
+      </c>
+      <c r="D55" s="114"/>
+      <c r="E55" s="115"/>
+      <c r="F55" s="116"/>
       <c r="G55" s="48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H55" s="12"/>
       <c r="I55" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J55" s="44">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K55" s="40"/>
       <c r="L55" s="6"/>
       <c r="M55" s="6"/>
       <c r="N55" s="6"/>
     </row>
-    <row r="56" spans="1:14" ht="25.2">
+    <row r="56" spans="1:14" ht="37.799999999999997">
       <c r="A56" s="11"/>
-      <c r="B56" s="122"/>
-      <c r="C56" s="48" t="str">
-        <f>master!C35</f>
-        <v>おすすめ書籍：『プロになるためのSpring入門』</v>
-      </c>
-      <c r="D56" s="107"/>
-      <c r="E56" s="108"/>
-      <c r="F56" s="109"/>
-      <c r="G56" s="48" t="s">
-        <v>48</v>
-      </c>
-      <c r="H56" s="12"/>
-      <c r="I56" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J56" s="44">
+      <c r="B56" s="123" t="str">
+        <f>master!B37</f>
+        <v>課題1の導入</v>
+      </c>
+      <c r="C56" s="58" t="str">
+        <f>master!C37</f>
+        <v>演習課題の概要</v>
+      </c>
+      <c r="D56" s="105" t="s">
+        <v>175</v>
+      </c>
+      <c r="E56" s="106"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="58" t="s">
+        <v>358</v>
+      </c>
+      <c r="H56" s="59"/>
+      <c r="I56" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" s="61">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K56" s="40"/>
+      <c r="K56" s="62"/>
       <c r="L56" s="6"/>
       <c r="M56" s="6"/>
       <c r="N56" s="6"/>
     </row>
     <row r="57" spans="1:14" ht="37.799999999999997">
       <c r="A57" s="11"/>
-      <c r="B57" s="117" t="str">
-        <f>master!B37</f>
-        <v>課題1の導入</v>
-      </c>
+      <c r="B57" s="124"/>
       <c r="C57" s="58" t="str">
-        <f>master!C37</f>
-        <v>演習課題の概要</v>
-      </c>
-      <c r="D57" s="110" t="s">
-        <v>175</v>
-      </c>
-      <c r="E57" s="111"/>
-      <c r="F57" s="112"/>
+        <f>master!C38</f>
+        <v>作成物</v>
+      </c>
+      <c r="D57" s="105" t="s">
+        <v>176</v>
+      </c>
+      <c r="E57" s="106"/>
+      <c r="F57" s="107"/>
       <c r="G57" s="58" t="s">
         <v>358</v>
       </c>
@@ -8218,186 +8231,186 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="37.799999999999997">
+    <row r="58" spans="1:14" ht="75.599999999999994">
       <c r="A58" s="11"/>
-      <c r="B58" s="118"/>
+      <c r="B58" s="125"/>
       <c r="C58" s="58" t="str">
-        <f>master!C38</f>
-        <v>作成物</v>
-      </c>
-      <c r="D58" s="110" t="s">
-        <v>176</v>
-      </c>
-      <c r="E58" s="111"/>
-      <c r="F58" s="112"/>
+        <f>master!C39</f>
+        <v>演習課題の進め方</v>
+      </c>
+      <c r="D58" s="105" t="s">
+        <v>177</v>
+      </c>
+      <c r="E58" s="106"/>
+      <c r="F58" s="107"/>
       <c r="G58" s="58" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H58" s="59"/>
       <c r="I58" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J58" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="K58" s="62"/>
       <c r="L58" s="6"/>
       <c r="M58" s="6"/>
       <c r="N58" s="6"/>
     </row>
-    <row r="59" spans="1:14" ht="75.599999999999994">
+    <row r="59" spans="1:14" ht="15" customHeight="1">
       <c r="A59" s="11"/>
-      <c r="B59" s="119"/>
+      <c r="B59" s="123" t="str">
+        <f>master!B40</f>
+        <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
+      </c>
       <c r="C59" s="58" t="str">
-        <f>master!C39</f>
-        <v>演習課題の進め方</v>
-      </c>
-      <c r="D59" s="110" t="s">
-        <v>177</v>
-      </c>
-      <c r="E59" s="111"/>
-      <c r="F59" s="112"/>
+        <f>master!C40</f>
+        <v>前提条件</v>
+      </c>
+      <c r="D59" s="105"/>
+      <c r="E59" s="106"/>
+      <c r="F59" s="107"/>
       <c r="G59" s="58" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H59" s="59"/>
       <c r="I59" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J59" s="61">
-        <v>1.3888888888888888E-2</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K59" s="62"/>
       <c r="L59" s="6"/>
       <c r="M59" s="6"/>
       <c r="N59" s="6"/>
     </row>
-    <row r="60" spans="1:14" ht="15" customHeight="1">
+    <row r="60" spans="1:14" ht="37.799999999999997">
       <c r="A60" s="11"/>
-      <c r="B60" s="117" t="str">
-        <f>master!B40</f>
-        <v>Spring Bootプロジェクトの_x000B_準備、起動確認</v>
-      </c>
+      <c r="B60" s="124"/>
       <c r="C60" s="58" t="str">
-        <f>master!C40</f>
-        <v>前提条件</v>
-      </c>
-      <c r="D60" s="110"/>
-      <c r="E60" s="111"/>
-      <c r="F60" s="112"/>
+        <f>master!C41</f>
+        <v>Spring Bootプロジェクトの準備</v>
+      </c>
+      <c r="D60" s="105" t="s">
+        <v>178</v>
+      </c>
+      <c r="E60" s="106"/>
+      <c r="F60" s="107"/>
       <c r="G60" s="58" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="H60" s="59"/>
       <c r="I60" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J60" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K60" s="62"/>
       <c r="L60" s="6"/>
       <c r="M60" s="6"/>
       <c r="N60" s="6"/>
     </row>
-    <row r="61" spans="1:14" ht="37.799999999999997">
+    <row r="61" spans="1:14" ht="25.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="118"/>
+      <c r="B61" s="124"/>
       <c r="C61" s="58" t="str">
-        <f>master!C41</f>
-        <v>Spring Bootプロジェクトの準備</v>
-      </c>
-      <c r="D61" s="110" t="s">
-        <v>178</v>
-      </c>
-      <c r="E61" s="111"/>
-      <c r="F61" s="112"/>
+        <f>master!C42</f>
+        <v>（補足）Spring Bootプロジェクトの準備</v>
+      </c>
+      <c r="D61" s="105" t="s">
+        <v>179</v>
+      </c>
+      <c r="E61" s="106"/>
+      <c r="F61" s="107"/>
       <c r="G61" s="58" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H61" s="59"/>
       <c r="I61" s="60" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J61" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>0</v>
       </c>
       <c r="K61" s="62"/>
       <c r="L61" s="6"/>
       <c r="M61" s="6"/>
       <c r="N61" s="6"/>
     </row>
-    <row r="62" spans="1:14" ht="25.2">
+    <row r="62" spans="1:14" ht="88.2">
       <c r="A62" s="11"/>
-      <c r="B62" s="118"/>
+      <c r="B62" s="125"/>
       <c r="C62" s="58" t="str">
-        <f>master!C42</f>
-        <v>（補足）Spring Bootプロジェクトの準備</v>
-      </c>
-      <c r="D62" s="110" t="s">
-        <v>179</v>
-      </c>
-      <c r="E62" s="111"/>
-      <c r="F62" s="112"/>
+        <f>master!C43</f>
+        <v>Spring Bootアプリケーションの起動確認</v>
+      </c>
+      <c r="D62" s="105" t="s">
+        <v>201</v>
+      </c>
+      <c r="E62" s="106"/>
+      <c r="F62" s="107"/>
       <c r="G62" s="58" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H62" s="59"/>
       <c r="I62" s="60" t="s">
         <v>50</v>
       </c>
       <c r="J62" s="61">
-        <v>0</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K62" s="62"/>
       <c r="L62" s="6"/>
       <c r="M62" s="6"/>
       <c r="N62" s="6"/>
     </row>
-    <row r="63" spans="1:14" ht="88.2">
+    <row r="63" spans="1:14" ht="190.2" customHeight="1">
       <c r="A63" s="11"/>
-      <c r="B63" s="119"/>
+      <c r="B63" s="123" t="str">
+        <f>master!B44</f>
+        <v>ECサイト Webアプリの要件</v>
+      </c>
       <c r="C63" s="58" t="str">
-        <f>master!C43</f>
-        <v>Spring Bootアプリケーションの起動確認</v>
-      </c>
-      <c r="D63" s="110" t="s">
-        <v>201</v>
-      </c>
-      <c r="E63" s="111"/>
-      <c r="F63" s="112"/>
+        <f>master!C44</f>
+        <v>ECサイト Webアプリの要件 – はじめに</v>
+      </c>
+      <c r="D63" s="105" t="s">
+        <v>180</v>
+      </c>
+      <c r="E63" s="106"/>
+      <c r="F63" s="107"/>
       <c r="G63" s="58" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H63" s="59"/>
       <c r="I63" s="60" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="J63" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K63" s="62"/>
       <c r="L63" s="6"/>
       <c r="M63" s="6"/>
       <c r="N63" s="6"/>
     </row>
-    <row r="64" spans="1:14" ht="190.2" customHeight="1">
+    <row r="64" spans="1:14" ht="151.19999999999999">
       <c r="A64" s="11"/>
-      <c r="B64" s="117" t="str">
-        <f>master!B44</f>
-        <v>ECサイト Webアプリの要件</v>
-      </c>
+      <c r="B64" s="124"/>
       <c r="C64" s="58" t="str">
-        <f>master!C44</f>
-        <v>ECサイト Webアプリの要件 – はじめに</v>
-      </c>
-      <c r="D64" s="110" t="s">
-        <v>180</v>
-      </c>
-      <c r="E64" s="111"/>
-      <c r="F64" s="112"/>
+        <f>master!C45</f>
+        <v>ECサイト Webアプリの要件➊ 画面</v>
+      </c>
+      <c r="D64" s="105" t="s">
+        <v>182</v>
+      </c>
+      <c r="E64" s="106"/>
+      <c r="F64" s="107"/>
       <c r="G64" s="58" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H64" s="59"/>
       <c r="I64" s="60" t="s">
@@ -8411,20 +8424,20 @@
       <c r="M64" s="6"/>
       <c r="N64" s="6"/>
     </row>
-    <row r="65" spans="1:14" ht="151.19999999999999">
+    <row r="65" spans="1:14" ht="214.2">
       <c r="A65" s="11"/>
-      <c r="B65" s="118"/>
+      <c r="B65" s="124"/>
       <c r="C65" s="58" t="str">
-        <f>master!C45</f>
-        <v>ECサイト Webアプリの要件➊ 画面</v>
-      </c>
-      <c r="D65" s="110" t="s">
-        <v>182</v>
-      </c>
-      <c r="E65" s="111"/>
-      <c r="F65" s="112"/>
+        <f>master!C46</f>
+        <v>ECサイト Webアプリの要件➋ 機能</v>
+      </c>
+      <c r="D65" s="105" t="s">
+        <v>183</v>
+      </c>
+      <c r="E65" s="106"/>
+      <c r="F65" s="107"/>
       <c r="G65" s="58" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H65" s="59"/>
       <c r="I65" s="60" t="s">
@@ -8438,108 +8451,108 @@
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
     </row>
-    <row r="66" spans="1:14" ht="214.2">
+    <row r="66" spans="1:14" ht="63">
       <c r="A66" s="11"/>
-      <c r="B66" s="118"/>
+      <c r="B66" s="124"/>
       <c r="C66" s="58" t="str">
-        <f>master!C46</f>
-        <v>ECサイト Webアプリの要件➋ 機能</v>
-      </c>
-      <c r="D66" s="110" t="s">
-        <v>183</v>
-      </c>
-      <c r="E66" s="111"/>
-      <c r="F66" s="112"/>
+        <f>master!C47</f>
+        <v>ECサイト Webアプリの要件➌ 画面遷移</v>
+      </c>
+      <c r="D66" s="105" t="s">
+        <v>184</v>
+      </c>
+      <c r="E66" s="106"/>
+      <c r="F66" s="107"/>
       <c r="G66" s="58" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H66" s="59"/>
       <c r="I66" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J66" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K66" s="62"/>
       <c r="L66" s="6"/>
       <c r="M66" s="6"/>
       <c r="N66" s="6"/>
     </row>
-    <row r="67" spans="1:14" ht="63">
+    <row r="67" spans="1:14" ht="163.80000000000001">
       <c r="A67" s="11"/>
-      <c r="B67" s="118"/>
+      <c r="B67" s="124"/>
       <c r="C67" s="58" t="str">
-        <f>master!C47</f>
-        <v>ECサイト Webアプリの要件➌ 画面遷移</v>
-      </c>
-      <c r="D67" s="110" t="s">
-        <v>184</v>
-      </c>
-      <c r="E67" s="111"/>
-      <c r="F67" s="112"/>
+        <f>master!C48</f>
+        <v>ECサイト Webアプリの要件❹ データ設計</v>
+      </c>
+      <c r="D67" s="105" t="s">
+        <v>186</v>
+      </c>
+      <c r="E67" s="106"/>
+      <c r="F67" s="107"/>
       <c r="G67" s="58" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H67" s="59"/>
       <c r="I67" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J67" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K67" s="62"/>
       <c r="L67" s="6"/>
       <c r="M67" s="6"/>
       <c r="N67" s="6"/>
     </row>
-    <row r="68" spans="1:14" ht="163.80000000000001">
+    <row r="68" spans="1:14" ht="50.4">
       <c r="A68" s="11"/>
-      <c r="B68" s="118"/>
+      <c r="B68" s="124"/>
       <c r="C68" s="58" t="str">
-        <f>master!C48</f>
-        <v>ECサイト Webアプリの要件❹ データ設計</v>
-      </c>
-      <c r="D68" s="110" t="s">
-        <v>186</v>
-      </c>
-      <c r="E68" s="111"/>
-      <c r="F68" s="112"/>
+        <f>master!C49</f>
+        <v>ECサイト Webアプリの要件❺ 初期データ</v>
+      </c>
+      <c r="D68" s="105" t="s">
+        <v>187</v>
+      </c>
+      <c r="E68" s="106"/>
+      <c r="F68" s="107"/>
       <c r="G68" s="58" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="H68" s="59"/>
       <c r="I68" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J68" s="61">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K68" s="62"/>
       <c r="L68" s="6"/>
       <c r="M68" s="6"/>
       <c r="N68" s="6"/>
     </row>
-    <row r="69" spans="1:14" ht="50.4">
+    <row r="69" spans="1:14" ht="37.799999999999997">
       <c r="A69" s="11"/>
-      <c r="B69" s="118"/>
+      <c r="B69" s="124"/>
       <c r="C69" s="58" t="str">
-        <f>master!C49</f>
-        <v>ECサイト Webアプリの要件❺ 初期データ</v>
-      </c>
-      <c r="D69" s="110" t="s">
-        <v>187</v>
-      </c>
-      <c r="E69" s="111"/>
-      <c r="F69" s="112"/>
+        <f>master!C50</f>
+        <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
+      </c>
+      <c r="D69" s="105" t="s">
+        <v>188</v>
+      </c>
+      <c r="E69" s="106"/>
+      <c r="F69" s="107"/>
       <c r="G69" s="58" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="H69" s="59"/>
       <c r="I69" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J69" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.0416666666666666E-2</v>
       </c>
       <c r="K69" s="62"/>
       <c r="L69" s="6"/>
@@ -8548,16 +8561,16 @@
     </row>
     <row r="70" spans="1:14" ht="37.799999999999997">
       <c r="A70" s="11"/>
-      <c r="B70" s="118"/>
+      <c r="B70" s="124"/>
       <c r="C70" s="58" t="str">
-        <f>master!C50</f>
-        <v>ECサイト Webアプリの要件❻ ディレクトリ構成</v>
-      </c>
-      <c r="D70" s="110" t="s">
-        <v>188</v>
-      </c>
-      <c r="E70" s="111"/>
-      <c r="F70" s="112"/>
+        <f>master!C51</f>
+        <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
+      </c>
+      <c r="D70" s="105" t="s">
+        <v>190</v>
+      </c>
+      <c r="E70" s="106"/>
+      <c r="F70" s="107"/>
       <c r="G70" s="58" t="s">
         <v>358</v>
       </c>
@@ -8566,7 +8579,7 @@
         <v>24</v>
       </c>
       <c r="J70" s="61">
-        <v>1.0416666666666666E-2</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K70" s="62"/>
       <c r="L70" s="6"/>
@@ -8575,16 +8588,16 @@
     </row>
     <row r="71" spans="1:14" ht="37.799999999999997">
       <c r="A71" s="11"/>
-      <c r="B71" s="118"/>
+      <c r="B71" s="125"/>
       <c r="C71" s="58" t="str">
-        <f>master!C51</f>
-        <v>ECサイト Webアプリの要件❼ パッケージ構成</v>
-      </c>
-      <c r="D71" s="110" t="s">
-        <v>190</v>
-      </c>
-      <c r="E71" s="111"/>
-      <c r="F71" s="112"/>
+        <f>master!C52</f>
+        <v>ECサイト Webアプリの要件❽ リソース構成</v>
+      </c>
+      <c r="D71" s="105" t="s">
+        <v>189</v>
+      </c>
+      <c r="E71" s="106"/>
+      <c r="F71" s="107"/>
       <c r="G71" s="58" t="s">
         <v>358</v>
       </c>
@@ -8593,280 +8606,280 @@
         <v>24</v>
       </c>
       <c r="J71" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K71" s="62"/>
       <c r="L71" s="6"/>
       <c r="M71" s="6"/>
       <c r="N71" s="6"/>
     </row>
-    <row r="72" spans="1:14" ht="37.799999999999997">
+    <row r="72" spans="1:14" ht="25.2">
       <c r="A72" s="11"/>
-      <c r="B72" s="119"/>
+      <c r="B72" s="123" t="str">
+        <f>master!B53</f>
+        <v>ハンズオン</v>
+      </c>
       <c r="C72" s="58" t="str">
-        <f>master!C52</f>
-        <v>ECサイト Webアプリの要件❽ リソース構成</v>
-      </c>
-      <c r="D72" s="110" t="s">
-        <v>189</v>
-      </c>
-      <c r="E72" s="111"/>
-      <c r="F72" s="112"/>
+        <f>master!C53</f>
+        <v>バイブコーディング – はじめに</v>
+      </c>
+      <c r="D72" s="105" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" s="106"/>
+      <c r="F72" s="107"/>
       <c r="G72" s="58" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="H72" s="59"/>
       <c r="I72" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J72" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>1.0416666666666666E-2</v>
       </c>
       <c r="K72" s="62"/>
       <c r="L72" s="6"/>
       <c r="M72" s="6"/>
       <c r="N72" s="6"/>
     </row>
-    <row r="73" spans="1:14" ht="25.2">
+    <row r="73" spans="1:14" ht="138.6">
       <c r="A73" s="11"/>
-      <c r="B73" s="117" t="str">
-        <f>master!B53</f>
-        <v>ハンズオン</v>
-      </c>
+      <c r="B73" s="124"/>
       <c r="C73" s="58" t="str">
-        <f>master!C53</f>
-        <v>バイブコーディング – はじめに</v>
-      </c>
-      <c r="D73" s="110" t="s">
-        <v>191</v>
-      </c>
-      <c r="E73" s="111"/>
-      <c r="F73" s="112"/>
+        <f>master!C54</f>
+        <v>[構造理解] Webアプリケーションで必要なもの</v>
+      </c>
+      <c r="D73" s="105" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" s="106"/>
+      <c r="F73" s="107"/>
       <c r="G73" s="58" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="H73" s="59"/>
       <c r="I73" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J73" s="61">
-        <v>1.0416666666666666E-2</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K73" s="62"/>
       <c r="L73" s="6"/>
       <c r="M73" s="6"/>
       <c r="N73" s="6"/>
     </row>
-    <row r="74" spans="1:14" ht="138.6">
+    <row r="74" spans="1:14" ht="50.4">
       <c r="A74" s="11"/>
-      <c r="B74" s="118"/>
-      <c r="C74" s="58" t="str">
-        <f>master!C54</f>
-        <v>[構造理解] Webアプリケーションで必要なもの</v>
-      </c>
-      <c r="D74" s="110" t="s">
-        <v>192</v>
-      </c>
-      <c r="E74" s="111"/>
-      <c r="F74" s="112"/>
+      <c r="B74" s="124"/>
+      <c r="C74" s="76" t="str">
+        <f>master!C55</f>
+        <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
+      </c>
+      <c r="D74" s="105" t="s">
+        <v>202</v>
+      </c>
+      <c r="E74" s="106"/>
+      <c r="F74" s="107"/>
       <c r="G74" s="58" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="H74" s="59"/>
       <c r="I74" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J74" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>1.3888888888888888E-2</v>
       </c>
       <c r="K74" s="62"/>
       <c r="L74" s="6"/>
       <c r="M74" s="6"/>
       <c r="N74" s="6"/>
     </row>
-    <row r="75" spans="1:14" ht="50.4">
+    <row r="75" spans="1:14" ht="88.2" customHeight="1">
       <c r="A75" s="11"/>
-      <c r="B75" s="118"/>
-      <c r="C75" s="76" t="str">
-        <f>master!C55</f>
-        <v>バイブコーディング➊ 画面モックアップを作ってデザインを決める</v>
-      </c>
-      <c r="D75" s="110" t="s">
-        <v>202</v>
-      </c>
-      <c r="E75" s="111"/>
-      <c r="F75" s="112"/>
+      <c r="B75" s="124"/>
+      <c r="C75" s="77"/>
+      <c r="D75" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E75" s="106"/>
+      <c r="F75" s="107"/>
       <c r="G75" s="58" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H75" s="59"/>
-      <c r="I75" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J75" s="61">
-        <v>1.3888888888888888E-2</v>
-      </c>
+      <c r="I75" s="60"/>
+      <c r="J75" s="61"/>
       <c r="K75" s="62"/>
       <c r="L75" s="6"/>
       <c r="M75" s="6"/>
       <c r="N75" s="6"/>
     </row>
-    <row r="76" spans="1:14" ht="88.2" customHeight="1">
+    <row r="76" spans="1:14" ht="50.4">
       <c r="A76" s="11"/>
-      <c r="B76" s="118"/>
-      <c r="C76" s="77"/>
-      <c r="D76" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E76" s="111"/>
-      <c r="F76" s="112"/>
+      <c r="B76" s="124"/>
+      <c r="C76" s="76" t="str">
+        <f>master!C56</f>
+        <v>バイブコーディング➋ データベースのテーブルを準備する</v>
+      </c>
+      <c r="D76" s="105" t="s">
+        <v>206</v>
+      </c>
+      <c r="E76" s="106"/>
+      <c r="F76" s="107"/>
       <c r="G76" s="58" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H76" s="59"/>
-      <c r="I76" s="60"/>
-      <c r="J76" s="61"/>
+      <c r="I76" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="61">
+        <v>1.3888888888888889E-3</v>
+      </c>
       <c r="K76" s="62"/>
       <c r="L76" s="6"/>
       <c r="M76" s="6"/>
       <c r="N76" s="6"/>
     </row>
-    <row r="77" spans="1:14" ht="50.4">
+    <row r="77" spans="1:14" ht="88.2">
       <c r="A77" s="11"/>
-      <c r="B77" s="118"/>
-      <c r="C77" s="76" t="str">
-        <f>master!C56</f>
-        <v>バイブコーディング➋ データベースのテーブルを準備する</v>
-      </c>
-      <c r="D77" s="110" t="s">
-        <v>206</v>
-      </c>
-      <c r="E77" s="111"/>
-      <c r="F77" s="112"/>
+      <c r="B77" s="124"/>
+      <c r="C77" s="77"/>
+      <c r="D77" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E77" s="106"/>
+      <c r="F77" s="107"/>
       <c r="G77" s="58" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H77" s="59"/>
-      <c r="I77" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J77" s="61">
-        <v>1.3888888888888889E-3</v>
-      </c>
+      <c r="I77" s="60"/>
+      <c r="J77" s="61"/>
       <c r="K77" s="62"/>
       <c r="L77" s="6"/>
       <c r="M77" s="6"/>
       <c r="N77" s="6"/>
     </row>
-    <row r="78" spans="1:14" ht="88.2">
+    <row r="78" spans="1:14" ht="50.4">
       <c r="A78" s="11"/>
-      <c r="B78" s="118"/>
-      <c r="C78" s="77"/>
-      <c r="D78" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E78" s="111"/>
-      <c r="F78" s="112"/>
+      <c r="B78" s="124"/>
+      <c r="C78" s="76" t="str">
+        <f>master!C57</f>
+        <v>バイブコーディング➌ データベースのデータを準備する</v>
+      </c>
+      <c r="D78" s="105" t="s">
+        <v>205</v>
+      </c>
+      <c r="E78" s="106"/>
+      <c r="F78" s="107"/>
       <c r="G78" s="58" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H78" s="59"/>
-      <c r="I78" s="60"/>
-      <c r="J78" s="61"/>
+      <c r="I78" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J78" s="61">
+        <v>1.3888888888888889E-3</v>
+      </c>
       <c r="K78" s="62"/>
       <c r="L78" s="6"/>
       <c r="M78" s="6"/>
       <c r="N78" s="6"/>
     </row>
-    <row r="79" spans="1:14" ht="50.4">
+    <row r="79" spans="1:14" ht="88.2">
       <c r="A79" s="11"/>
-      <c r="B79" s="118"/>
-      <c r="C79" s="76" t="str">
-        <f>master!C57</f>
-        <v>バイブコーディング➌ データベースのデータを準備する</v>
-      </c>
-      <c r="D79" s="110" t="s">
-        <v>205</v>
-      </c>
-      <c r="E79" s="111"/>
-      <c r="F79" s="112"/>
+      <c r="B79" s="124"/>
+      <c r="C79" s="77"/>
+      <c r="D79" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E79" s="106"/>
+      <c r="F79" s="107"/>
       <c r="G79" s="58" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H79" s="59"/>
-      <c r="I79" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J79" s="61">
-        <v>1.3888888888888889E-3</v>
-      </c>
+      <c r="I79" s="60"/>
+      <c r="J79" s="61"/>
       <c r="K79" s="62"/>
       <c r="L79" s="6"/>
       <c r="M79" s="6"/>
       <c r="N79" s="6"/>
     </row>
-    <row r="80" spans="1:14" ht="88.2">
+    <row r="80" spans="1:14" ht="63">
       <c r="A80" s="11"/>
-      <c r="B80" s="118"/>
-      <c r="C80" s="77"/>
-      <c r="D80" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E80" s="111"/>
-      <c r="F80" s="112"/>
+      <c r="B80" s="124"/>
+      <c r="C80" s="76" t="str">
+        <f>master!C58</f>
+        <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
+      </c>
+      <c r="D80" s="105" t="s">
+        <v>204</v>
+      </c>
+      <c r="E80" s="106"/>
+      <c r="F80" s="107"/>
       <c r="G80" s="58" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H80" s="59"/>
-      <c r="I80" s="60"/>
-      <c r="J80" s="61"/>
+      <c r="I80" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J80" s="61">
+        <v>3.472222222222222E-3</v>
+      </c>
       <c r="K80" s="62"/>
       <c r="L80" s="6"/>
       <c r="M80" s="6"/>
       <c r="N80" s="6"/>
     </row>
-    <row r="81" spans="1:14" ht="63">
+    <row r="81" spans="1:14" ht="88.2">
       <c r="A81" s="11"/>
-      <c r="B81" s="118"/>
-      <c r="C81" s="76" t="str">
-        <f>master!C58</f>
-        <v>バイブコーディング❹ データベース処理とビジネスロジックを作る</v>
-      </c>
-      <c r="D81" s="110" t="s">
-        <v>204</v>
-      </c>
-      <c r="E81" s="111"/>
-      <c r="F81" s="112"/>
+      <c r="B81" s="124"/>
+      <c r="C81" s="77"/>
+      <c r="D81" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E81" s="106"/>
+      <c r="F81" s="107"/>
       <c r="G81" s="58" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="H81" s="59"/>
-      <c r="I81" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J81" s="61">
-        <v>3.472222222222222E-3</v>
-      </c>
+      <c r="I81" s="60"/>
+      <c r="J81" s="61"/>
       <c r="K81" s="62"/>
       <c r="L81" s="6"/>
       <c r="M81" s="6"/>
       <c r="N81" s="6"/>
     </row>
-    <row r="82" spans="1:14" ht="88.2">
+    <row r="82" spans="1:14" ht="50.4">
       <c r="A82" s="11"/>
-      <c r="B82" s="118"/>
-      <c r="C82" s="77"/>
-      <c r="D82" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E82" s="111"/>
-      <c r="F82" s="112"/>
+      <c r="B82" s="124"/>
+      <c r="C82" s="58" t="str">
+        <f>master!C59</f>
+        <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
+      </c>
+      <c r="D82" s="105" t="s">
+        <v>194</v>
+      </c>
+      <c r="E82" s="106"/>
+      <c r="F82" s="107"/>
       <c r="G82" s="58" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H82" s="59"/>
-      <c r="I82" s="60"/>
-      <c r="J82" s="61"/>
+      <c r="I82" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J82" s="61">
+        <v>2.0833333333333333E-3</v>
+      </c>
       <c r="K82" s="62"/>
       <c r="L82" s="6"/>
       <c r="M82" s="6"/>
@@ -8874,16 +8887,16 @@
     </row>
     <row r="83" spans="1:14" ht="50.4">
       <c r="A83" s="11"/>
-      <c r="B83" s="118"/>
+      <c r="B83" s="124"/>
       <c r="C83" s="58" t="str">
-        <f>master!C59</f>
-        <v>[解説] RepositoryクラスとSQLの例（抜粋）</v>
-      </c>
-      <c r="D83" s="110" t="s">
-        <v>194</v>
-      </c>
-      <c r="E83" s="111"/>
-      <c r="F83" s="112"/>
+        <f>master!C60</f>
+        <v>[解説] Entity/Modelクラスの例（抜粋）</v>
+      </c>
+      <c r="D83" s="105" t="s">
+        <v>195</v>
+      </c>
+      <c r="E83" s="106"/>
+      <c r="F83" s="107"/>
       <c r="G83" s="58" t="s">
         <v>363</v>
       </c>
@@ -8892,109 +8905,109 @@
         <v>24</v>
       </c>
       <c r="J83" s="61">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K83" s="62"/>
       <c r="L83" s="6"/>
       <c r="M83" s="6"/>
       <c r="N83" s="6"/>
     </row>
-    <row r="84" spans="1:14" ht="50.4">
+    <row r="84" spans="1:14" ht="37.799999999999997">
       <c r="A84" s="11"/>
-      <c r="B84" s="118"/>
+      <c r="B84" s="124"/>
       <c r="C84" s="58" t="str">
-        <f>master!C60</f>
-        <v>[解説] Entity/Modelクラスの例（抜粋）</v>
-      </c>
-      <c r="D84" s="110" t="s">
-        <v>195</v>
-      </c>
-      <c r="E84" s="111"/>
-      <c r="F84" s="112"/>
+        <f>master!C61</f>
+        <v>[解説] Serviceクラスの例（抜粋）</v>
+      </c>
+      <c r="D84" s="105" t="s">
+        <v>196</v>
+      </c>
+      <c r="E84" s="106"/>
+      <c r="F84" s="107"/>
       <c r="G84" s="58" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="H84" s="59"/>
       <c r="I84" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J84" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K84" s="62"/>
       <c r="L84" s="6"/>
       <c r="M84" s="6"/>
       <c r="N84" s="6"/>
     </row>
-    <row r="85" spans="1:14" ht="37.799999999999997">
+    <row r="85" spans="1:14" ht="50.4">
       <c r="A85" s="11"/>
-      <c r="B85" s="118"/>
-      <c r="C85" s="58" t="str">
-        <f>master!C61</f>
-        <v>[解説] Serviceクラスの例（抜粋）</v>
-      </c>
-      <c r="D85" s="110" t="s">
-        <v>196</v>
-      </c>
-      <c r="E85" s="111"/>
-      <c r="F85" s="112"/>
+      <c r="B85" s="124"/>
+      <c r="C85" s="76" t="str">
+        <f>master!C62</f>
+        <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
+      </c>
+      <c r="D85" s="105" t="s">
+        <v>203</v>
+      </c>
+      <c r="E85" s="106"/>
+      <c r="F85" s="107"/>
       <c r="G85" s="58" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="H85" s="59"/>
       <c r="I85" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J85" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K85" s="62"/>
       <c r="L85" s="6"/>
       <c r="M85" s="6"/>
       <c r="N85" s="6"/>
     </row>
-    <row r="86" spans="1:14" ht="50.4">
+    <row r="86" spans="1:14" ht="88.2">
       <c r="A86" s="11"/>
-      <c r="B86" s="118"/>
-      <c r="C86" s="76" t="str">
-        <f>master!C62</f>
-        <v>バイブコーディング❺ モックアップをもとに画面表示/処理を作る</v>
-      </c>
-      <c r="D86" s="110" t="s">
-        <v>203</v>
-      </c>
-      <c r="E86" s="111"/>
-      <c r="F86" s="112"/>
+      <c r="B86" s="124"/>
+      <c r="C86" s="77"/>
+      <c r="D86" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E86" s="106"/>
+      <c r="F86" s="107"/>
       <c r="G86" s="58" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H86" s="59"/>
-      <c r="I86" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J86" s="61">
-        <v>6.9444444444444441E-3</v>
-      </c>
+      <c r="I86" s="60"/>
+      <c r="J86" s="61"/>
       <c r="K86" s="62"/>
       <c r="L86" s="6"/>
       <c r="M86" s="6"/>
       <c r="N86" s="6"/>
     </row>
-    <row r="87" spans="1:14" ht="88.2">
+    <row r="87" spans="1:14" ht="37.799999999999997">
       <c r="A87" s="11"/>
-      <c r="B87" s="118"/>
-      <c r="C87" s="77"/>
-      <c r="D87" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E87" s="111"/>
-      <c r="F87" s="112"/>
+      <c r="B87" s="124"/>
+      <c r="C87" s="58" t="str">
+        <f>master!C63</f>
+        <v>[解説] Controllerクラスの例（抜粋）</v>
+      </c>
+      <c r="D87" s="105" t="s">
+        <v>197</v>
+      </c>
+      <c r="E87" s="106"/>
+      <c r="F87" s="107"/>
       <c r="G87" s="58" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="H87" s="59"/>
-      <c r="I87" s="60"/>
-      <c r="J87" s="61"/>
+      <c r="I87" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J87" s="61">
+        <v>1.3888888888888889E-3</v>
+      </c>
       <c r="K87" s="62"/>
       <c r="L87" s="6"/>
       <c r="M87" s="6"/>
@@ -9002,16 +9015,16 @@
     </row>
     <row r="88" spans="1:14" ht="37.799999999999997">
       <c r="A88" s="11"/>
-      <c r="B88" s="118"/>
+      <c r="B88" s="124"/>
       <c r="C88" s="58" t="str">
-        <f>master!C63</f>
-        <v>[解説] Controllerクラスの例（抜粋）</v>
-      </c>
-      <c r="D88" s="110" t="s">
-        <v>197</v>
-      </c>
-      <c r="E88" s="111"/>
-      <c r="F88" s="112"/>
+        <f>master!C64</f>
+        <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
+      </c>
+      <c r="D88" s="105" t="s">
+        <v>198</v>
+      </c>
+      <c r="E88" s="106"/>
+      <c r="F88" s="107"/>
       <c r="G88" s="58" t="s">
         <v>358</v>
       </c>
@@ -9029,16 +9042,16 @@
     </row>
     <row r="89" spans="1:14" ht="37.799999999999997">
       <c r="A89" s="11"/>
-      <c r="B89" s="118"/>
+      <c r="B89" s="124"/>
       <c r="C89" s="58" t="str">
-        <f>master!C64</f>
-        <v>[解説] Thymeleafテンプレートの例（抜粋）</v>
-      </c>
-      <c r="D89" s="110" t="s">
-        <v>198</v>
-      </c>
-      <c r="E89" s="111"/>
-      <c r="F89" s="112"/>
+        <f>master!C65</f>
+        <v>[解説] Formクラスの例（抜粋）</v>
+      </c>
+      <c r="D89" s="105" t="s">
+        <v>199</v>
+      </c>
+      <c r="E89" s="106"/>
+      <c r="F89" s="107"/>
       <c r="G89" s="58" t="s">
         <v>358</v>
       </c>
@@ -9047,27 +9060,27 @@
         <v>24</v>
       </c>
       <c r="J89" s="61">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K89" s="62"/>
       <c r="L89" s="6"/>
       <c r="M89" s="6"/>
       <c r="N89" s="6"/>
     </row>
-    <row r="90" spans="1:14" ht="37.799999999999997">
+    <row r="90" spans="1:14" ht="75.599999999999994">
       <c r="A90" s="11"/>
-      <c r="B90" s="118"/>
-      <c r="C90" s="58" t="str">
-        <f>master!C65</f>
-        <v>[解説] Formクラスの例（抜粋）</v>
-      </c>
-      <c r="D90" s="110" t="s">
-        <v>199</v>
-      </c>
-      <c r="E90" s="111"/>
-      <c r="F90" s="112"/>
+      <c r="B90" s="124"/>
+      <c r="C90" s="76" t="str">
+        <f>master!C66</f>
+        <v>バイブコーディング❻ 動作を確認する</v>
+      </c>
+      <c r="D90" s="105" t="s">
+        <v>200</v>
+      </c>
+      <c r="E90" s="106"/>
+      <c r="F90" s="107"/>
       <c r="G90" s="58" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H90" s="59"/>
       <c r="I90" s="60" t="s">
@@ -9081,74 +9094,74 @@
       <c r="M90" s="6"/>
       <c r="N90" s="6"/>
     </row>
-    <row r="91" spans="1:14" ht="75.599999999999994">
+    <row r="91" spans="1:14" ht="63">
       <c r="A91" s="11"/>
-      <c r="B91" s="118"/>
-      <c r="C91" s="76" t="str">
-        <f>master!C66</f>
-        <v>バイブコーディング❻ 動作を確認する</v>
-      </c>
-      <c r="D91" s="110" t="s">
-        <v>200</v>
-      </c>
-      <c r="E91" s="111"/>
-      <c r="F91" s="112"/>
+      <c r="B91" s="125"/>
+      <c r="C91" s="77"/>
+      <c r="D91" s="105" t="s">
+        <v>207</v>
+      </c>
+      <c r="E91" s="106"/>
+      <c r="F91" s="107"/>
       <c r="G91" s="58" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="H91" s="59"/>
       <c r="I91" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J91" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K91" s="62"/>
       <c r="L91" s="6"/>
       <c r="M91" s="6"/>
       <c r="N91" s="6"/>
     </row>
-    <row r="92" spans="1:14" ht="63">
+    <row r="92" spans="1:14" ht="100.8">
       <c r="A92" s="11"/>
-      <c r="B92" s="119"/>
-      <c r="C92" s="77"/>
-      <c r="D92" s="110" t="s">
-        <v>207</v>
-      </c>
-      <c r="E92" s="111"/>
-      <c r="F92" s="112"/>
+      <c r="B92" s="123" t="str">
+        <f>master!B69</f>
+        <v>Gitとは</v>
+      </c>
+      <c r="C92" s="58" t="str">
+        <f>master!C69</f>
+        <v>Gitとは</v>
+      </c>
+      <c r="D92" s="105" t="s">
+        <v>209</v>
+      </c>
+      <c r="E92" s="106"/>
+      <c r="F92" s="107"/>
       <c r="G92" s="58" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
       <c r="H92" s="59"/>
       <c r="I92" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J92" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K92" s="62"/>
       <c r="L92" s="6"/>
       <c r="M92" s="6"/>
       <c r="N92" s="6"/>
     </row>
-    <row r="93" spans="1:14" ht="100.8">
+    <row r="93" spans="1:14" ht="189">
       <c r="A93" s="11"/>
-      <c r="B93" s="117" t="str">
-        <f>master!B69</f>
-        <v>Gitとは</v>
-      </c>
+      <c r="B93" s="125"/>
       <c r="C93" s="58" t="str">
-        <f>master!C69</f>
-        <v>Gitとは</v>
-      </c>
-      <c r="D93" s="110" t="s">
-        <v>209</v>
-      </c>
-      <c r="E93" s="111"/>
-      <c r="F93" s="112"/>
+        <f>master!C70</f>
+        <v>Gitの基本的な流れ</v>
+      </c>
+      <c r="D93" s="105" t="s">
+        <v>214</v>
+      </c>
+      <c r="E93" s="106"/>
+      <c r="F93" s="107"/>
       <c r="G93" s="58" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H93" s="59"/>
       <c r="I93" s="60" t="s">
@@ -9162,77 +9175,77 @@
       <c r="M93" s="6"/>
       <c r="N93" s="6"/>
     </row>
-    <row r="94" spans="1:14" ht="189">
+    <row r="94" spans="1:14" ht="126">
       <c r="A94" s="11"/>
-      <c r="B94" s="119"/>
+      <c r="B94" s="123" t="str">
+        <f>master!B71</f>
+        <v>VS Code上でGitを使う手順</v>
+      </c>
       <c r="C94" s="58" t="str">
-        <f>master!C70</f>
-        <v>Gitの基本的な流れ</v>
-      </c>
-      <c r="D94" s="110" t="s">
-        <v>214</v>
-      </c>
-      <c r="E94" s="111"/>
-      <c r="F94" s="112"/>
+        <f>master!C71</f>
+        <v>VS Code上でGitを使う手順-1 【ユーザ名等の登録】</v>
+      </c>
+      <c r="D94" s="105" t="s">
+        <v>210</v>
+      </c>
+      <c r="E94" s="106"/>
+      <c r="F94" s="107"/>
       <c r="G94" s="58" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H94" s="59"/>
       <c r="I94" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J94" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K94" s="62"/>
       <c r="L94" s="6"/>
       <c r="M94" s="6"/>
       <c r="N94" s="6"/>
     </row>
-    <row r="95" spans="1:14" ht="126">
+    <row r="95" spans="1:14" ht="37.799999999999997">
       <c r="A95" s="11"/>
-      <c r="B95" s="117" t="str">
-        <f>master!B71</f>
-        <v>VS Code上でGitを使う手順</v>
-      </c>
+      <c r="B95" s="124"/>
       <c r="C95" s="58" t="str">
-        <f>master!C71</f>
-        <v>VS Code上でGitを使う手順-1 【ユーザ名等の登録】</v>
-      </c>
-      <c r="D95" s="110" t="s">
-        <v>210</v>
-      </c>
-      <c r="E95" s="111"/>
-      <c r="F95" s="112"/>
+        <f>master!C72</f>
+        <v>VS Code上でGitを使う手順-2 【リポジトリの初期化】</v>
+      </c>
+      <c r="D95" s="105" t="s">
+        <v>211</v>
+      </c>
+      <c r="E95" s="106"/>
+      <c r="F95" s="107"/>
       <c r="G95" s="58" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H95" s="59"/>
       <c r="I95" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J95" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K95" s="62"/>
       <c r="L95" s="6"/>
       <c r="M95" s="6"/>
       <c r="N95" s="6"/>
     </row>
-    <row r="96" spans="1:14" ht="37.799999999999997">
+    <row r="96" spans="1:14" ht="50.4">
       <c r="A96" s="11"/>
-      <c r="B96" s="118"/>
+      <c r="B96" s="124"/>
       <c r="C96" s="58" t="str">
-        <f>master!C72</f>
-        <v>VS Code上でGitを使う手順-2 【リポジトリの初期化】</v>
-      </c>
-      <c r="D96" s="110" t="s">
-        <v>211</v>
-      </c>
-      <c r="E96" s="111"/>
-      <c r="F96" s="112"/>
+        <f>master!C73</f>
+        <v>VS Code上でGitを使う手順-3 【最初のcommit】</v>
+      </c>
+      <c r="D96" s="105" t="s">
+        <v>212</v>
+      </c>
+      <c r="E96" s="106"/>
+      <c r="F96" s="107"/>
       <c r="G96" s="58" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H96" s="59"/>
       <c r="I96" s="60" t="s">
@@ -9248,16 +9261,16 @@
     </row>
     <row r="97" spans="1:14" ht="50.4">
       <c r="A97" s="11"/>
-      <c r="B97" s="118"/>
+      <c r="B97" s="124"/>
       <c r="C97" s="58" t="str">
-        <f>master!C73</f>
-        <v>VS Code上でGitを使う手順-3 【最初のcommit】</v>
-      </c>
-      <c r="D97" s="110" t="s">
-        <v>212</v>
-      </c>
-      <c r="E97" s="111"/>
-      <c r="F97" s="112"/>
+        <f>master!C74</f>
+        <v>VS Code上でGitを使う手順-4 【2回目以降のコミット】</v>
+      </c>
+      <c r="D97" s="105" t="s">
+        <v>418</v>
+      </c>
+      <c r="E97" s="106"/>
+      <c r="F97" s="107"/>
       <c r="G97" s="58" t="s">
         <v>423</v>
       </c>
@@ -9273,20 +9286,20 @@
       <c r="M97" s="6"/>
       <c r="N97" s="6"/>
     </row>
-    <row r="98" spans="1:14" ht="50.4">
+    <row r="98" spans="1:14" ht="37.799999999999997">
       <c r="A98" s="11"/>
-      <c r="B98" s="118"/>
+      <c r="B98" s="124"/>
       <c r="C98" s="58" t="str">
-        <f>master!C74</f>
-        <v>VS Code上でGitを使う手順-4 【2回目以降のコミット】</v>
-      </c>
-      <c r="D98" s="110" t="s">
-        <v>418</v>
-      </c>
-      <c r="E98" s="111"/>
-      <c r="F98" s="112"/>
+        <f>master!C75</f>
+        <v>VS Code上でGitを使う手順-5 【過去のcommitの確認】</v>
+      </c>
+      <c r="D98" s="105" t="s">
+        <v>213</v>
+      </c>
+      <c r="E98" s="106"/>
+      <c r="F98" s="107"/>
       <c r="G98" s="58" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H98" s="59"/>
       <c r="I98" s="60" t="s">
@@ -9300,20 +9313,20 @@
       <c r="M98" s="6"/>
       <c r="N98" s="6"/>
     </row>
-    <row r="99" spans="1:14" ht="37.799999999999997">
+    <row r="99" spans="1:14" ht="63">
       <c r="A99" s="11"/>
-      <c r="B99" s="118"/>
+      <c r="B99" s="125"/>
       <c r="C99" s="58" t="str">
-        <f>master!C75</f>
-        <v>VS Code上でGitを使う手順-5 【過去のcommitの確認】</v>
-      </c>
-      <c r="D99" s="110" t="s">
-        <v>213</v>
-      </c>
-      <c r="E99" s="111"/>
-      <c r="F99" s="112"/>
+        <f>master!C76</f>
+        <v>VS Code上でGitを使う手順-6 【過去の状態に戻す】</v>
+      </c>
+      <c r="D99" s="105" t="s">
+        <v>215</v>
+      </c>
+      <c r="E99" s="106"/>
+      <c r="F99" s="107"/>
       <c r="G99" s="58" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="H99" s="59"/>
       <c r="I99" s="60" t="s">
@@ -9327,80 +9340,83 @@
       <c r="M99" s="6"/>
       <c r="N99" s="6"/>
     </row>
-    <row r="100" spans="1:14" ht="63">
+    <row r="100" spans="1:14" ht="214.2">
       <c r="A100" s="11"/>
-      <c r="B100" s="119"/>
+      <c r="B100" s="87" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
       <c r="C100" s="58" t="str">
-        <f>master!C76</f>
-        <v>VS Code上でGitを使う手順-6 【過去の状態に戻す】</v>
-      </c>
-      <c r="D100" s="110" t="s">
-        <v>215</v>
-      </c>
-      <c r="E100" s="111"/>
-      <c r="F100" s="112"/>
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D100" s="105" t="s">
+        <v>208</v>
+      </c>
+      <c r="E100" s="106"/>
+      <c r="F100" s="107"/>
       <c r="G100" s="58" t="s">
-        <v>424</v>
+        <v>365</v>
       </c>
       <c r="H100" s="59"/>
       <c r="I100" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J100" s="61">
-        <v>3.472222222222222E-3</v>
+      <c r="J100" s="61" t="s">
+        <v>433</v>
       </c>
       <c r="K100" s="62"/>
       <c r="L100" s="6"/>
       <c r="M100" s="6"/>
       <c r="N100" s="6"/>
     </row>
-    <row r="101" spans="1:14" ht="214.2">
+    <row r="101" spans="1:14" ht="89.4">
       <c r="A101" s="11"/>
-      <c r="B101" s="87" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
-      </c>
-      <c r="C101" s="58" t="str">
-        <f>master!C67</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D101" s="110" t="s">
-        <v>208</v>
-      </c>
-      <c r="E101" s="111"/>
-      <c r="F101" s="112"/>
-      <c r="G101" s="58" t="s">
-        <v>365</v>
-      </c>
-      <c r="H101" s="59"/>
-      <c r="I101" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J101" s="61" t="s">
-        <v>433</v>
-      </c>
-      <c r="K101" s="62"/>
+      <c r="B101" s="89" t="str">
+        <f>master!B78</f>
+        <v>システム開発プロセスの導入</v>
+      </c>
+      <c r="C101" s="78" t="str">
+        <f>master!C78</f>
+        <v>講義の目的</v>
+      </c>
+      <c r="D101" s="114" t="s">
+        <v>249</v>
+      </c>
+      <c r="E101" s="115"/>
+      <c r="F101" s="116"/>
+      <c r="G101" s="48" t="s">
+        <v>369</v>
+      </c>
+      <c r="H101" s="12"/>
+      <c r="I101" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J101" s="44">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K101" s="40"/>
       <c r="L101" s="6"/>
       <c r="M101" s="6"/>
       <c r="N101" s="6"/>
     </row>
-    <row r="102" spans="1:14" ht="89.4">
+    <row r="102" spans="1:14" ht="37.799999999999997">
       <c r="A102" s="11"/>
-      <c r="B102" s="89" t="str">
-        <f>master!B78</f>
-        <v>システム開発プロセスの導入</v>
+      <c r="B102" s="111" t="str">
+        <f>master!B79</f>
+        <v>システム開発におけるソフトウェア開発ライフサイクル</v>
       </c>
       <c r="C102" s="78" t="str">
-        <f>master!C78</f>
-        <v>講義の目的</v>
-      </c>
-      <c r="D102" s="107" t="s">
-        <v>249</v>
-      </c>
-      <c r="E102" s="108"/>
-      <c r="F102" s="109"/>
+        <f>master!C79</f>
+        <v>ソフトウェア開発ライフサイクル</v>
+      </c>
+      <c r="D102" s="114" t="s">
+        <v>250</v>
+      </c>
+      <c r="E102" s="115"/>
+      <c r="F102" s="116"/>
       <c r="G102" s="48" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H102" s="12"/>
       <c r="I102" s="46" t="s">
@@ -9414,79 +9430,75 @@
       <c r="M102" s="6"/>
       <c r="N102" s="6"/>
     </row>
-    <row r="103" spans="1:14" ht="37.799999999999997">
+    <row r="103" spans="1:14" ht="277.2">
       <c r="A103" s="11"/>
-      <c r="B103" s="105" t="str">
-        <f>master!B79</f>
-        <v>システム開発におけるソフトウェア開発ライフサイクル</v>
-      </c>
+      <c r="B103" s="112"/>
       <c r="C103" s="78" t="str">
-        <f>master!C79</f>
-        <v>ソフトウェア開発ライフサイクル</v>
-      </c>
-      <c r="D103" s="107" t="s">
-        <v>250</v>
-      </c>
-      <c r="E103" s="108"/>
-      <c r="F103" s="109"/>
+        <f>master!C80</f>
+        <v>ソフトウェア開発ライフサイクルの種類</v>
+      </c>
+      <c r="D103" s="114" t="s">
+        <v>251</v>
+      </c>
+      <c r="E103" s="115"/>
+      <c r="F103" s="116"/>
       <c r="G103" s="48" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H103" s="12"/>
       <c r="I103" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J103" s="44">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K103" s="40"/>
       <c r="L103" s="6"/>
       <c r="M103" s="6"/>
       <c r="N103" s="6"/>
     </row>
-    <row r="104" spans="1:14" ht="277.2">
+    <row r="104" spans="1:14" ht="151.19999999999999">
       <c r="A104" s="11"/>
-      <c r="B104" s="106"/>
-      <c r="C104" s="78" t="str">
-        <f>master!C80</f>
-        <v>ソフトウェア開発ライフサイクルの種類</v>
-      </c>
-      <c r="D104" s="107" t="s">
-        <v>251</v>
-      </c>
-      <c r="E104" s="108"/>
-      <c r="F104" s="109"/>
+      <c r="B104" s="111" t="str">
+        <f>master!B81</f>
+        <v>TERASOLUNAとは</v>
+      </c>
+      <c r="C104" s="78" t="s">
+        <v>227</v>
+      </c>
+      <c r="D104" s="114" t="s">
+        <v>252</v>
+      </c>
+      <c r="E104" s="115"/>
+      <c r="F104" s="116"/>
       <c r="G104" s="48" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H104" s="12"/>
       <c r="I104" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J104" s="44">
-        <v>6.9444444444444441E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K104" s="40"/>
       <c r="L104" s="6"/>
       <c r="M104" s="6"/>
       <c r="N104" s="6"/>
     </row>
-    <row r="105" spans="1:14" ht="151.19999999999999">
+    <row r="105" spans="1:14" ht="138.6">
       <c r="A105" s="11"/>
-      <c r="B105" s="105" t="str">
-        <f>master!B81</f>
-        <v>TERASOLUNAとは</v>
-      </c>
+      <c r="B105" s="112"/>
       <c r="C105" s="78" t="s">
-        <v>227</v>
-      </c>
-      <c r="D105" s="107" t="s">
-        <v>252</v>
-      </c>
-      <c r="E105" s="108"/>
-      <c r="F105" s="109"/>
+        <v>228</v>
+      </c>
+      <c r="D105" s="114" t="s">
+        <v>253</v>
+      </c>
+      <c r="E105" s="115"/>
+      <c r="F105" s="116"/>
       <c r="G105" s="48" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H105" s="12"/>
       <c r="I105" s="46" t="s">
@@ -9500,48 +9512,48 @@
       <c r="M105" s="6"/>
       <c r="N105" s="6"/>
     </row>
-    <row r="106" spans="1:14" ht="138.6">
+    <row r="106" spans="1:14" ht="189">
       <c r="A106" s="11"/>
-      <c r="B106" s="106"/>
+      <c r="B106" s="111" t="str">
+        <f>master!B83</f>
+        <v>V字モデルとは</v>
+      </c>
       <c r="C106" s="78" t="s">
-        <v>228</v>
-      </c>
-      <c r="D106" s="107" t="s">
-        <v>253</v>
-      </c>
-      <c r="E106" s="108"/>
-      <c r="F106" s="109"/>
+        <v>231</v>
+      </c>
+      <c r="D106" s="114" t="s">
+        <v>254</v>
+      </c>
+      <c r="E106" s="115"/>
+      <c r="F106" s="116"/>
       <c r="G106" s="48" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H106" s="12"/>
       <c r="I106" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J106" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K106" s="40"/>
       <c r="L106" s="6"/>
       <c r="M106" s="6"/>
       <c r="N106" s="6"/>
     </row>
-    <row r="107" spans="1:14" ht="189">
+    <row r="107" spans="1:14" ht="100.8">
       <c r="A107" s="11"/>
-      <c r="B107" s="105" t="str">
-        <f>master!B83</f>
-        <v>V字モデルとは</v>
-      </c>
+      <c r="B107" s="113"/>
       <c r="C107" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="D107" s="107" t="s">
-        <v>254</v>
-      </c>
-      <c r="E107" s="108"/>
-      <c r="F107" s="109"/>
+        <v>229</v>
+      </c>
+      <c r="D107" s="114" t="s">
+        <v>255</v>
+      </c>
+      <c r="E107" s="115"/>
+      <c r="F107" s="116"/>
       <c r="G107" s="48" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H107" s="12"/>
       <c r="I107" s="46" t="s">
@@ -9555,19 +9567,19 @@
       <c r="M107" s="6"/>
       <c r="N107" s="6"/>
     </row>
-    <row r="108" spans="1:14" ht="100.8">
+    <row r="108" spans="1:14" ht="113.4">
       <c r="A108" s="11"/>
-      <c r="B108" s="116"/>
+      <c r="B108" s="113"/>
       <c r="C108" s="78" t="s">
-        <v>229</v>
-      </c>
-      <c r="D108" s="107" t="s">
-        <v>255</v>
-      </c>
-      <c r="E108" s="108"/>
-      <c r="F108" s="109"/>
+        <v>233</v>
+      </c>
+      <c r="D108" s="114" t="s">
+        <v>256</v>
+      </c>
+      <c r="E108" s="115"/>
+      <c r="F108" s="116"/>
       <c r="G108" s="48" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H108" s="12"/>
       <c r="I108" s="46" t="s">
@@ -9581,97 +9593,97 @@
       <c r="M108" s="6"/>
       <c r="N108" s="6"/>
     </row>
-    <row r="109" spans="1:14" ht="113.4">
+    <row r="109" spans="1:14" ht="302.39999999999998">
       <c r="A109" s="11"/>
-      <c r="B109" s="116"/>
+      <c r="B109" s="113"/>
       <c r="C109" s="78" t="s">
-        <v>233</v>
-      </c>
-      <c r="D109" s="107" t="s">
-        <v>256</v>
-      </c>
-      <c r="E109" s="108"/>
-      <c r="F109" s="109"/>
+        <v>235</v>
+      </c>
+      <c r="D109" s="114" t="s">
+        <v>257</v>
+      </c>
+      <c r="E109" s="115"/>
+      <c r="F109" s="116"/>
       <c r="G109" s="48" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H109" s="12"/>
       <c r="I109" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J109" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>1.0416666666666666E-2</v>
       </c>
       <c r="K109" s="40"/>
       <c r="L109" s="6"/>
       <c r="M109" s="6"/>
       <c r="N109" s="6"/>
     </row>
-    <row r="110" spans="1:14" ht="302.39999999999998">
+    <row r="110" spans="1:14" ht="138.6">
       <c r="A110" s="11"/>
-      <c r="B110" s="116"/>
+      <c r="B110" s="113"/>
       <c r="C110" s="78" t="s">
-        <v>235</v>
-      </c>
-      <c r="D110" s="107" t="s">
-        <v>257</v>
-      </c>
-      <c r="E110" s="108"/>
-      <c r="F110" s="109"/>
+        <v>237</v>
+      </c>
+      <c r="D110" s="114" t="s">
+        <v>258</v>
+      </c>
+      <c r="E110" s="115"/>
+      <c r="F110" s="116"/>
       <c r="G110" s="48" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="H110" s="12"/>
       <c r="I110" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J110" s="44">
-        <v>1.0416666666666666E-2</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K110" s="40"/>
       <c r="L110" s="6"/>
       <c r="M110" s="6"/>
       <c r="N110" s="6"/>
     </row>
-    <row r="111" spans="1:14" ht="138.6">
+    <row r="111" spans="1:14" ht="88.2">
       <c r="A111" s="11"/>
-      <c r="B111" s="116"/>
+      <c r="B111" s="113"/>
       <c r="C111" s="78" t="s">
-        <v>237</v>
-      </c>
-      <c r="D111" s="107" t="s">
-        <v>258</v>
-      </c>
-      <c r="E111" s="108"/>
-      <c r="F111" s="109"/>
+        <v>239</v>
+      </c>
+      <c r="D111" s="114" t="s">
+        <v>259</v>
+      </c>
+      <c r="E111" s="115"/>
+      <c r="F111" s="116"/>
       <c r="G111" s="48" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="H111" s="12"/>
       <c r="I111" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J111" s="44">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K111" s="40"/>
       <c r="L111" s="6"/>
       <c r="M111" s="6"/>
       <c r="N111" s="6"/>
     </row>
-    <row r="112" spans="1:14" ht="88.2">
+    <row r="112" spans="1:14" ht="75.599999999999994">
       <c r="A112" s="11"/>
-      <c r="B112" s="116"/>
+      <c r="B112" s="113"/>
       <c r="C112" s="78" t="s">
-        <v>239</v>
-      </c>
-      <c r="D112" s="107" t="s">
-        <v>259</v>
-      </c>
-      <c r="E112" s="108"/>
-      <c r="F112" s="109"/>
+        <v>241</v>
+      </c>
+      <c r="D112" s="114" t="s">
+        <v>260</v>
+      </c>
+      <c r="E112" s="115"/>
+      <c r="F112" s="116"/>
       <c r="G112" s="48" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="H112" s="12"/>
       <c r="I112" s="46" t="s">
@@ -9685,19 +9697,19 @@
       <c r="M112" s="6"/>
       <c r="N112" s="6"/>
     </row>
-    <row r="113" spans="1:14" ht="75.599999999999994">
+    <row r="113" spans="1:14" ht="113.4">
       <c r="A113" s="11"/>
-      <c r="B113" s="116"/>
+      <c r="B113" s="113"/>
       <c r="C113" s="78" t="s">
-        <v>241</v>
-      </c>
-      <c r="D113" s="107" t="s">
-        <v>260</v>
-      </c>
-      <c r="E113" s="108"/>
-      <c r="F113" s="109"/>
+        <v>243</v>
+      </c>
+      <c r="D113" s="114" t="s">
+        <v>261</v>
+      </c>
+      <c r="E113" s="115"/>
+      <c r="F113" s="116"/>
       <c r="G113" s="48" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H113" s="12"/>
       <c r="I113" s="46" t="s">
@@ -9711,45 +9723,45 @@
       <c r="M113" s="6"/>
       <c r="N113" s="6"/>
     </row>
-    <row r="114" spans="1:14" ht="113.4">
+    <row r="114" spans="1:14" ht="126">
       <c r="A114" s="11"/>
-      <c r="B114" s="116"/>
+      <c r="B114" s="113"/>
       <c r="C114" s="78" t="s">
-        <v>243</v>
-      </c>
-      <c r="D114" s="107" t="s">
-        <v>261</v>
-      </c>
-      <c r="E114" s="108"/>
-      <c r="F114" s="109"/>
+        <v>262</v>
+      </c>
+      <c r="D114" s="114" t="s">
+        <v>263</v>
+      </c>
+      <c r="E114" s="115"/>
+      <c r="F114" s="116"/>
       <c r="G114" s="48" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H114" s="12"/>
       <c r="I114" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J114" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K114" s="40"/>
       <c r="L114" s="6"/>
       <c r="M114" s="6"/>
       <c r="N114" s="6"/>
     </row>
-    <row r="115" spans="1:14" ht="126">
+    <row r="115" spans="1:14" ht="88.2">
       <c r="A115" s="11"/>
-      <c r="B115" s="116"/>
+      <c r="B115" s="113"/>
       <c r="C115" s="78" t="s">
-        <v>262</v>
-      </c>
-      <c r="D115" s="107" t="s">
-        <v>263</v>
-      </c>
-      <c r="E115" s="108"/>
-      <c r="F115" s="109"/>
+        <v>246</v>
+      </c>
+      <c r="D115" s="114" t="s">
+        <v>264</v>
+      </c>
+      <c r="E115" s="115"/>
+      <c r="F115" s="116"/>
       <c r="G115" s="48" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="H115" s="12"/>
       <c r="I115" s="46" t="s">
@@ -9763,19 +9775,19 @@
       <c r="M115" s="6"/>
       <c r="N115" s="6"/>
     </row>
-    <row r="116" spans="1:14" ht="88.2">
+    <row r="116" spans="1:14" ht="138.6">
       <c r="A116" s="11"/>
-      <c r="B116" s="116"/>
+      <c r="B116" s="113"/>
       <c r="C116" s="78" t="s">
-        <v>246</v>
-      </c>
-      <c r="D116" s="107" t="s">
-        <v>264</v>
-      </c>
-      <c r="E116" s="108"/>
-      <c r="F116" s="109"/>
+        <v>247</v>
+      </c>
+      <c r="D116" s="114" t="s">
+        <v>265</v>
+      </c>
+      <c r="E116" s="115"/>
+      <c r="F116" s="116"/>
       <c r="G116" s="48" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="H116" s="12"/>
       <c r="I116" s="46" t="s">
@@ -9789,103 +9801,102 @@
       <c r="M116" s="6"/>
       <c r="N116" s="6"/>
     </row>
-    <row r="117" spans="1:14" ht="138.6">
+    <row r="117" spans="1:14" ht="24" customHeight="1">
       <c r="A117" s="11"/>
-      <c r="B117" s="116"/>
+      <c r="B117" s="112"/>
       <c r="C117" s="78" t="s">
-        <v>247</v>
-      </c>
-      <c r="D117" s="107" t="s">
-        <v>265</v>
-      </c>
-      <c r="E117" s="108"/>
-      <c r="F117" s="109"/>
+        <v>248</v>
+      </c>
+      <c r="D117" s="114"/>
+      <c r="E117" s="115"/>
+      <c r="F117" s="116"/>
       <c r="G117" s="48" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="H117" s="12"/>
       <c r="I117" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J117" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K117" s="40"/>
       <c r="L117" s="6"/>
       <c r="M117" s="6"/>
       <c r="N117" s="6"/>
     </row>
-    <row r="118" spans="1:14" ht="24" customHeight="1">
+    <row r="118" spans="1:14" ht="37.799999999999997">
       <c r="A118" s="11"/>
-      <c r="B118" s="106"/>
-      <c r="C118" s="78" t="s">
-        <v>248</v>
-      </c>
-      <c r="D118" s="107"/>
-      <c r="E118" s="108"/>
-      <c r="F118" s="109"/>
-      <c r="G118" s="48" t="s">
-        <v>380</v>
-      </c>
-      <c r="H118" s="12"/>
-      <c r="I118" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J118" s="44">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K118" s="40"/>
+      <c r="B118" s="90" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
+      <c r="C118" s="58" t="str">
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D118" s="105" t="s">
+        <v>318</v>
+      </c>
+      <c r="E118" s="106"/>
+      <c r="F118" s="107"/>
+      <c r="G118" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="H118" s="59"/>
+      <c r="I118" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J118" s="61" t="s">
+        <v>433</v>
+      </c>
+      <c r="K118" s="62"/>
       <c r="L118" s="6"/>
       <c r="M118" s="6"/>
       <c r="N118" s="6"/>
     </row>
-    <row r="119" spans="1:14" ht="37.799999999999997">
+    <row r="119" spans="1:14" ht="50.4">
       <c r="A119" s="11"/>
-      <c r="B119" s="90" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
-      </c>
-      <c r="C119" s="58" t="str">
-        <f>master!C67</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D119" s="110" t="s">
-        <v>318</v>
-      </c>
-      <c r="E119" s="111"/>
-      <c r="F119" s="112"/>
-      <c r="G119" s="58" t="s">
-        <v>43</v>
-      </c>
-      <c r="H119" s="59"/>
-      <c r="I119" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J119" s="61" t="s">
-        <v>433</v>
-      </c>
-      <c r="K119" s="62"/>
+      <c r="B119" s="111" t="str">
+        <f>master!B96</f>
+        <v>単体テストとJunitの導入</v>
+      </c>
+      <c r="C119" s="78" t="str">
+        <f>master!C96</f>
+        <v>講義の目的</v>
+      </c>
+      <c r="D119" s="114" t="s">
+        <v>294</v>
+      </c>
+      <c r="E119" s="115"/>
+      <c r="F119" s="116"/>
+      <c r="G119" s="48" t="s">
+        <v>381</v>
+      </c>
+      <c r="H119" s="12"/>
+      <c r="I119" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J119" s="44">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K119" s="40"/>
       <c r="L119" s="6"/>
       <c r="M119" s="6"/>
       <c r="N119" s="6"/>
     </row>
-    <row r="120" spans="1:14" ht="50.4">
+    <row r="120" spans="1:14" ht="25.2">
       <c r="A120" s="11"/>
-      <c r="B120" s="105" t="str">
-        <f>master!B96</f>
-        <v>単体テストとJunitの導入</v>
-      </c>
+      <c r="B120" s="113"/>
       <c r="C120" s="78" t="str">
-        <f>master!C96</f>
-        <v>講義の目的</v>
-      </c>
-      <c r="D120" s="107" t="s">
-        <v>294</v>
-      </c>
-      <c r="E120" s="108"/>
-      <c r="F120" s="109"/>
+        <f>master!C97</f>
+        <v>TERASOLUNA 開発手順　 ※再掲</v>
+      </c>
+      <c r="D120" s="114"/>
+      <c r="E120" s="115"/>
+      <c r="F120" s="116"/>
       <c r="G120" s="48" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H120" s="12"/>
       <c r="I120" s="46" t="s">
@@ -9901,14 +9912,16 @@
     </row>
     <row r="121" spans="1:14" ht="25.2">
       <c r="A121" s="11"/>
-      <c r="B121" s="116"/>
+      <c r="B121" s="112"/>
       <c r="C121" s="78" t="str">
-        <f>master!C97</f>
-        <v>TERASOLUNA 開発手順　 ※再掲</v>
-      </c>
-      <c r="D121" s="107"/>
-      <c r="E121" s="108"/>
-      <c r="F121" s="109"/>
+        <f>master!C98</f>
+        <v>V字モデル　 ※再掲</v>
+      </c>
+      <c r="D121" s="114" t="s">
+        <v>295</v>
+      </c>
+      <c r="E121" s="115"/>
+      <c r="F121" s="116"/>
       <c r="G121" s="48" t="s">
         <v>382</v>
       </c>
@@ -9924,104 +9937,104 @@
       <c r="M121" s="6"/>
       <c r="N121" s="6"/>
     </row>
-    <row r="122" spans="1:14" ht="25.2">
+    <row r="122" spans="1:14" ht="50.4">
       <c r="A122" s="11"/>
-      <c r="B122" s="106"/>
+      <c r="B122" s="111" t="str">
+        <f>master!B99</f>
+        <v>テストとは</v>
+      </c>
       <c r="C122" s="78" t="str">
-        <f>master!C98</f>
-        <v>V字モデル　 ※再掲</v>
-      </c>
-      <c r="D122" s="107" t="s">
-        <v>295</v>
-      </c>
-      <c r="E122" s="108"/>
-      <c r="F122" s="109"/>
+        <f>master!C99</f>
+        <v>テストとは</v>
+      </c>
+      <c r="D122" s="114" t="s">
+        <v>296</v>
+      </c>
+      <c r="E122" s="115"/>
+      <c r="F122" s="116"/>
       <c r="G122" s="48" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H122" s="12"/>
       <c r="I122" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J122" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K122" s="40"/>
       <c r="L122" s="6"/>
       <c r="M122" s="6"/>
       <c r="N122" s="6"/>
     </row>
-    <row r="123" spans="1:14" ht="50.4">
+    <row r="123" spans="1:14" ht="315">
       <c r="A123" s="11"/>
-      <c r="B123" s="105" t="str">
-        <f>master!B99</f>
-        <v>テストとは</v>
-      </c>
+      <c r="B123" s="113"/>
       <c r="C123" s="78" t="str">
-        <f>master!C99</f>
-        <v>テストとは</v>
-      </c>
-      <c r="D123" s="107" t="s">
-        <v>296</v>
-      </c>
-      <c r="E123" s="108"/>
-      <c r="F123" s="109"/>
+        <f>master!C100</f>
+        <v>テストの目的</v>
+      </c>
+      <c r="D123" s="114" t="s">
+        <v>297</v>
+      </c>
+      <c r="E123" s="115"/>
+      <c r="F123" s="116"/>
       <c r="G123" s="48" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="H123" s="12"/>
       <c r="I123" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J123" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K123" s="40"/>
       <c r="L123" s="6"/>
       <c r="M123" s="6"/>
       <c r="N123" s="6"/>
     </row>
-    <row r="124" spans="1:14" ht="315">
+    <row r="124" spans="1:14" ht="25.2">
       <c r="A124" s="11"/>
-      <c r="B124" s="116"/>
+      <c r="B124" s="113"/>
       <c r="C124" s="78" t="str">
-        <f>master!C100</f>
-        <v>テストの目的</v>
-      </c>
-      <c r="D124" s="107" t="s">
-        <v>297</v>
-      </c>
-      <c r="E124" s="108"/>
-      <c r="F124" s="109"/>
+        <f>master!C101</f>
+        <v>テストを実施しなかった場合…</v>
+      </c>
+      <c r="D124" s="114" t="s">
+        <v>298</v>
+      </c>
+      <c r="E124" s="115"/>
+      <c r="F124" s="116"/>
       <c r="G124" s="48" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H124" s="12"/>
       <c r="I124" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J124" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K124" s="40"/>
       <c r="L124" s="6"/>
       <c r="M124" s="6"/>
       <c r="N124" s="6"/>
     </row>
-    <row r="125" spans="1:14" ht="25.2">
+    <row r="125" spans="1:14" ht="100.8">
       <c r="A125" s="11"/>
-      <c r="B125" s="116"/>
+      <c r="B125" s="112"/>
       <c r="C125" s="78" t="str">
-        <f>master!C101</f>
-        <v>テストを実施しなかった場合…</v>
-      </c>
-      <c r="D125" s="107" t="s">
-        <v>298</v>
-      </c>
-      <c r="E125" s="108"/>
-      <c r="F125" s="109"/>
+        <f>master!C102</f>
+        <v>コラム：テストとデバッグ</v>
+      </c>
+      <c r="D125" s="114" t="s">
+        <v>299</v>
+      </c>
+      <c r="E125" s="115"/>
+      <c r="F125" s="116"/>
       <c r="G125" s="48" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H125" s="12"/>
       <c r="I125" s="46" t="s">
@@ -10035,50 +10048,48 @@
       <c r="M125" s="6"/>
       <c r="N125" s="6"/>
     </row>
-    <row r="126" spans="1:14" ht="100.8">
+    <row r="126" spans="1:14" ht="50.4">
       <c r="A126" s="11"/>
-      <c r="B126" s="106"/>
+      <c r="B126" s="111" t="str">
+        <f>master!B103</f>
+        <v>単体テストとは</v>
+      </c>
       <c r="C126" s="78" t="str">
-        <f>master!C102</f>
-        <v>コラム：テストとデバッグ</v>
-      </c>
-      <c r="D126" s="107" t="s">
-        <v>299</v>
-      </c>
-      <c r="E126" s="108"/>
-      <c r="F126" s="109"/>
+        <f>master!C103</f>
+        <v>単体テスト（Unit Test）とは</v>
+      </c>
+      <c r="D126" s="114" t="s">
+        <v>300</v>
+      </c>
+      <c r="E126" s="115"/>
+      <c r="F126" s="116"/>
       <c r="G126" s="48" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="H126" s="12"/>
       <c r="I126" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J126" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K126" s="40"/>
       <c r="L126" s="6"/>
       <c r="M126" s="6"/>
       <c r="N126" s="6"/>
     </row>
-    <row r="127" spans="1:14" ht="50.4">
+    <row r="127" spans="1:14" ht="25.2">
       <c r="A127" s="11"/>
-      <c r="B127" s="105" t="str">
-        <f>master!B103</f>
-        <v>単体テストとは</v>
-      </c>
+      <c r="B127" s="113"/>
       <c r="C127" s="78" t="str">
-        <f>master!C103</f>
-        <v>単体テスト（Unit Test）とは</v>
-      </c>
-      <c r="D127" s="107" t="s">
-        <v>300</v>
-      </c>
-      <c r="E127" s="108"/>
-      <c r="F127" s="109"/>
+        <f>master!C104</f>
+        <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
+      </c>
+      <c r="D127" s="114"/>
+      <c r="E127" s="115"/>
+      <c r="F127" s="116"/>
       <c r="G127" s="48" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H127" s="12"/>
       <c r="I127" s="46" t="s">
@@ -10092,45 +10103,47 @@
       <c r="M127" s="6"/>
       <c r="N127" s="6"/>
     </row>
-    <row r="128" spans="1:14" ht="25.2">
+    <row r="128" spans="1:14" ht="302.39999999999998">
       <c r="A128" s="11"/>
-      <c r="B128" s="116"/>
+      <c r="B128" s="113"/>
       <c r="C128" s="78" t="str">
-        <f>master!C104</f>
-        <v xml:space="preserve">V字モデル　– 製造/単体テスト –　※再掲 </v>
-      </c>
-      <c r="D128" s="107"/>
-      <c r="E128" s="108"/>
-      <c r="F128" s="109"/>
+        <f>master!C105</f>
+        <v>テスト設計の流れ</v>
+      </c>
+      <c r="D128" s="114" t="s">
+        <v>301</v>
+      </c>
+      <c r="E128" s="115"/>
+      <c r="F128" s="116"/>
       <c r="G128" s="48" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H128" s="12"/>
       <c r="I128" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J128" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K128" s="40"/>
       <c r="L128" s="6"/>
       <c r="M128" s="6"/>
       <c r="N128" s="6"/>
     </row>
-    <row r="129" spans="1:14" ht="302.39999999999998">
+    <row r="129" spans="1:14" ht="37.799999999999997">
       <c r="A129" s="11"/>
-      <c r="B129" s="116"/>
+      <c r="B129" s="113"/>
       <c r="C129" s="78" t="str">
-        <f>master!C105</f>
-        <v>テスト設計の流れ</v>
-      </c>
-      <c r="D129" s="107" t="s">
-        <v>301</v>
-      </c>
-      <c r="E129" s="108"/>
-      <c r="F129" s="109"/>
+        <f>master!C106</f>
+        <v>テスト設計の例</v>
+      </c>
+      <c r="D129" s="114" t="s">
+        <v>302</v>
+      </c>
+      <c r="E129" s="115"/>
+      <c r="F129" s="116"/>
       <c r="G129" s="48" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H129" s="12"/>
       <c r="I129" s="46" t="s">
@@ -10144,155 +10157,155 @@
       <c r="M129" s="6"/>
       <c r="N129" s="6"/>
     </row>
-    <row r="130" spans="1:14" ht="37.799999999999997">
+    <row r="130" spans="1:14" ht="75.599999999999994">
       <c r="A130" s="11"/>
-      <c r="B130" s="116"/>
+      <c r="B130" s="113"/>
       <c r="C130" s="78" t="str">
-        <f>master!C106</f>
-        <v>テスト設計の例</v>
-      </c>
-      <c r="D130" s="107" t="s">
-        <v>302</v>
-      </c>
-      <c r="E130" s="108"/>
-      <c r="F130" s="109"/>
+        <f>master!C107</f>
+        <v>単体テスト（Unit Test）とは</v>
+      </c>
+      <c r="D130" s="114" t="s">
+        <v>303</v>
+      </c>
+      <c r="E130" s="115"/>
+      <c r="F130" s="116"/>
       <c r="G130" s="48" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H130" s="12"/>
       <c r="I130" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J130" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K130" s="40"/>
       <c r="L130" s="6"/>
       <c r="M130" s="6"/>
       <c r="N130" s="6"/>
     </row>
-    <row r="131" spans="1:14" ht="75.599999999999994">
+    <row r="131" spans="1:14" ht="113.4">
       <c r="A131" s="11"/>
-      <c r="B131" s="116"/>
+      <c r="B131" s="113"/>
       <c r="C131" s="78" t="str">
-        <f>master!C107</f>
-        <v>単体テスト（Unit Test）とは</v>
-      </c>
-      <c r="D131" s="107" t="s">
-        <v>303</v>
-      </c>
-      <c r="E131" s="108"/>
-      <c r="F131" s="109"/>
+        <f>master!C108</f>
+        <v>テスト技法 – ブラックボックステスト技法 –</v>
+      </c>
+      <c r="D131" s="114" t="s">
+        <v>304</v>
+      </c>
+      <c r="E131" s="115"/>
+      <c r="F131" s="116"/>
       <c r="G131" s="48" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H131" s="12"/>
       <c r="I131" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J131" s="44">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K131" s="40"/>
       <c r="L131" s="6"/>
       <c r="M131" s="6"/>
       <c r="N131" s="6"/>
     </row>
-    <row r="132" spans="1:14" ht="113.4">
+    <row r="132" spans="1:14" ht="201.6">
       <c r="A132" s="11"/>
-      <c r="B132" s="116"/>
+      <c r="B132" s="113"/>
       <c r="C132" s="78" t="str">
-        <f>master!C108</f>
-        <v>テスト技法 – ブラックボックステスト技法 –</v>
-      </c>
-      <c r="D132" s="107" t="s">
-        <v>304</v>
-      </c>
-      <c r="E132" s="108"/>
-      <c r="F132" s="109"/>
+        <f>master!C109</f>
+        <v>ブラックボックステスト：同値分割法</v>
+      </c>
+      <c r="D132" s="114" t="s">
+        <v>307</v>
+      </c>
+      <c r="E132" s="115"/>
+      <c r="F132" s="116"/>
       <c r="G132" s="48" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H132" s="12"/>
       <c r="I132" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J132" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K132" s="40"/>
       <c r="L132" s="6"/>
       <c r="M132" s="6"/>
       <c r="N132" s="6"/>
     </row>
-    <row r="133" spans="1:14" ht="201.6">
+    <row r="133" spans="1:14" ht="113.4">
       <c r="A133" s="11"/>
-      <c r="B133" s="116"/>
+      <c r="B133" s="113"/>
       <c r="C133" s="78" t="str">
-        <f>master!C109</f>
-        <v>ブラックボックステスト：同値分割法</v>
-      </c>
-      <c r="D133" s="107" t="s">
-        <v>307</v>
-      </c>
-      <c r="E133" s="108"/>
-      <c r="F133" s="109"/>
+        <f>master!C110</f>
+        <v>ブラックボックステスト：境界値分析</v>
+      </c>
+      <c r="D133" s="114" t="s">
+        <v>306</v>
+      </c>
+      <c r="E133" s="115"/>
+      <c r="F133" s="116"/>
       <c r="G133" s="48" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H133" s="12"/>
       <c r="I133" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J133" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K133" s="40"/>
       <c r="L133" s="6"/>
       <c r="M133" s="6"/>
       <c r="N133" s="6"/>
     </row>
-    <row r="134" spans="1:14" ht="113.4">
+    <row r="134" spans="1:14" ht="176.4">
       <c r="A134" s="11"/>
-      <c r="B134" s="116"/>
+      <c r="B134" s="113"/>
       <c r="C134" s="78" t="str">
-        <f>master!C110</f>
-        <v>ブラックボックステスト：境界値分析</v>
-      </c>
-      <c r="D134" s="107" t="s">
-        <v>306</v>
-      </c>
-      <c r="E134" s="108"/>
-      <c r="F134" s="109"/>
+        <f>master!C111</f>
+        <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
+      </c>
+      <c r="D134" s="114" t="s">
+        <v>305</v>
+      </c>
+      <c r="E134" s="115"/>
+      <c r="F134" s="116"/>
       <c r="G134" s="48" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H134" s="12"/>
       <c r="I134" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J134" s="44">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K134" s="40"/>
       <c r="L134" s="6"/>
       <c r="M134" s="6"/>
       <c r="N134" s="6"/>
     </row>
-    <row r="135" spans="1:14" ht="176.4">
+    <row r="135" spans="1:14" ht="37.799999999999997">
       <c r="A135" s="11"/>
-      <c r="B135" s="116"/>
+      <c r="B135" s="113"/>
       <c r="C135" s="78" t="str">
-        <f>master!C111</f>
-        <v>ブラックボックステスト：ディシジョンテーブルテスト</v>
-      </c>
-      <c r="D135" s="107" t="s">
-        <v>305</v>
-      </c>
-      <c r="E135" s="108"/>
-      <c r="F135" s="109"/>
+        <f>master!C112</f>
+        <v>ブラックボックステスト：状態遷移テスト</v>
+      </c>
+      <c r="D135" s="114" t="s">
+        <v>308</v>
+      </c>
+      <c r="E135" s="115"/>
+      <c r="F135" s="116"/>
       <c r="G135" s="48" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H135" s="12"/>
       <c r="I135" s="46" t="s">
@@ -10306,74 +10319,74 @@
       <c r="M135" s="6"/>
       <c r="N135" s="6"/>
     </row>
-    <row r="136" spans="1:14" ht="37.799999999999997">
+    <row r="136" spans="1:14" ht="88.2">
       <c r="A136" s="11"/>
-      <c r="B136" s="116"/>
+      <c r="B136" s="113"/>
       <c r="C136" s="78" t="str">
-        <f>master!C112</f>
-        <v>ブラックボックステスト：状態遷移テスト</v>
-      </c>
-      <c r="D136" s="107" t="s">
-        <v>308</v>
-      </c>
-      <c r="E136" s="108"/>
-      <c r="F136" s="109"/>
+        <f>master!C113</f>
+        <v>テスト技法 – ホワイトボックステスト技法 –</v>
+      </c>
+      <c r="D136" s="114" t="s">
+        <v>309</v>
+      </c>
+      <c r="E136" s="115"/>
+      <c r="F136" s="116"/>
       <c r="G136" s="48" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="H136" s="12"/>
       <c r="I136" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J136" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K136" s="40"/>
       <c r="L136" s="6"/>
       <c r="M136" s="6"/>
       <c r="N136" s="6"/>
     </row>
-    <row r="137" spans="1:14" ht="88.2">
+    <row r="137" spans="1:14" ht="151.19999999999999">
       <c r="A137" s="11"/>
-      <c r="B137" s="116"/>
+      <c r="B137" s="113"/>
       <c r="C137" s="78" t="str">
-        <f>master!C113</f>
-        <v>テスト技法 – ホワイトボックステスト技法 –</v>
-      </c>
-      <c r="D137" s="107" t="s">
-        <v>309</v>
-      </c>
-      <c r="E137" s="108"/>
-      <c r="F137" s="109"/>
+        <f>master!C114</f>
+        <v>ホワイトボックステストの評価基準</v>
+      </c>
+      <c r="D137" s="114" t="s">
+        <v>310</v>
+      </c>
+      <c r="E137" s="115"/>
+      <c r="F137" s="116"/>
       <c r="G137" s="48" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H137" s="12"/>
       <c r="I137" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J137" s="44">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K137" s="40"/>
       <c r="L137" s="6"/>
       <c r="M137" s="6"/>
       <c r="N137" s="6"/>
     </row>
-    <row r="138" spans="1:14" ht="151.19999999999999">
+    <row r="138" spans="1:14" ht="37.799999999999997">
       <c r="A138" s="11"/>
-      <c r="B138" s="116"/>
+      <c r="B138" s="113"/>
       <c r="C138" s="78" t="str">
-        <f>master!C114</f>
-        <v>ホワイトボックステストの評価基準</v>
-      </c>
-      <c r="D138" s="107" t="s">
-        <v>310</v>
-      </c>
-      <c r="E138" s="108"/>
-      <c r="F138" s="109"/>
+        <f>master!C115</f>
+        <v>ホワイトボックステスト：ステートメントテスト</v>
+      </c>
+      <c r="D138" s="114" t="s">
+        <v>311</v>
+      </c>
+      <c r="E138" s="115"/>
+      <c r="F138" s="116"/>
       <c r="G138" s="48" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="H138" s="12"/>
       <c r="I138" s="46" t="s">
@@ -10389,16 +10402,16 @@
     </row>
     <row r="139" spans="1:14" ht="37.799999999999997">
       <c r="A139" s="11"/>
-      <c r="B139" s="116"/>
+      <c r="B139" s="113"/>
       <c r="C139" s="78" t="str">
-        <f>master!C115</f>
-        <v>ホワイトボックステスト：ステートメントテスト</v>
-      </c>
-      <c r="D139" s="107" t="s">
-        <v>311</v>
-      </c>
-      <c r="E139" s="108"/>
-      <c r="F139" s="109"/>
+        <f>master!C116</f>
+        <v>ホワイトボックステスト：ブランチテスト</v>
+      </c>
+      <c r="D139" s="114" t="s">
+        <v>312</v>
+      </c>
+      <c r="E139" s="115"/>
+      <c r="F139" s="116"/>
       <c r="G139" s="48" t="s">
         <v>386</v>
       </c>
@@ -10416,16 +10429,16 @@
     </row>
     <row r="140" spans="1:14" ht="37.799999999999997">
       <c r="A140" s="11"/>
-      <c r="B140" s="116"/>
+      <c r="B140" s="113"/>
       <c r="C140" s="78" t="str">
-        <f>master!C116</f>
-        <v>ホワイトボックステスト：ブランチテスト</v>
-      </c>
-      <c r="D140" s="107" t="s">
-        <v>312</v>
-      </c>
-      <c r="E140" s="108"/>
-      <c r="F140" s="109"/>
+        <f>master!C117</f>
+        <v>ホワイトボックステスト：コンディションテスト</v>
+      </c>
+      <c r="D140" s="114" t="s">
+        <v>313</v>
+      </c>
+      <c r="E140" s="115"/>
+      <c r="F140" s="116"/>
       <c r="G140" s="48" t="s">
         <v>386</v>
       </c>
@@ -10443,16 +10456,16 @@
     </row>
     <row r="141" spans="1:14" ht="37.799999999999997">
       <c r="A141" s="11"/>
-      <c r="B141" s="116"/>
+      <c r="B141" s="113"/>
       <c r="C141" s="78" t="str">
-        <f>master!C117</f>
-        <v>ホワイトボックステスト：コンディションテスト</v>
-      </c>
-      <c r="D141" s="107" t="s">
-        <v>313</v>
-      </c>
-      <c r="E141" s="108"/>
-      <c r="F141" s="109"/>
+        <f>master!C118</f>
+        <v>テスト技法 – 経験ベースの技法 –</v>
+      </c>
+      <c r="D141" s="114" t="s">
+        <v>314</v>
+      </c>
+      <c r="E141" s="115"/>
+      <c r="F141" s="116"/>
       <c r="G141" s="48" t="s">
         <v>386</v>
       </c>
@@ -10468,20 +10481,20 @@
       <c r="M141" s="6"/>
       <c r="N141" s="6"/>
     </row>
-    <row r="142" spans="1:14" ht="37.799999999999997">
+    <row r="142" spans="1:14" ht="100.8">
       <c r="A142" s="11"/>
-      <c r="B142" s="116"/>
+      <c r="B142" s="113"/>
       <c r="C142" s="78" t="str">
-        <f>master!C118</f>
-        <v>テスト技法 – 経験ベースの技法 –</v>
-      </c>
-      <c r="D142" s="107" t="s">
-        <v>314</v>
-      </c>
-      <c r="E142" s="108"/>
-      <c r="F142" s="109"/>
+        <f>master!C119</f>
+        <v>スタブとドライバ</v>
+      </c>
+      <c r="D142" s="114" t="s">
+        <v>315</v>
+      </c>
+      <c r="E142" s="115"/>
+      <c r="F142" s="116"/>
       <c r="G142" s="48" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H142" s="12"/>
       <c r="I142" s="46" t="s">
@@ -10495,20 +10508,20 @@
       <c r="M142" s="6"/>
       <c r="N142" s="6"/>
     </row>
-    <row r="143" spans="1:14" ht="100.8">
+    <row r="143" spans="1:14" ht="75.599999999999994">
       <c r="A143" s="11"/>
-      <c r="B143" s="116"/>
+      <c r="B143" s="112"/>
       <c r="C143" s="78" t="str">
-        <f>master!C119</f>
-        <v>スタブとドライバ</v>
-      </c>
-      <c r="D143" s="107" t="s">
-        <v>315</v>
-      </c>
-      <c r="E143" s="108"/>
-      <c r="F143" s="109"/>
+        <f>master!C120</f>
+        <v>スタブとモック</v>
+      </c>
+      <c r="D143" s="114" t="s">
+        <v>316</v>
+      </c>
+      <c r="E143" s="115"/>
+      <c r="F143" s="116"/>
       <c r="G143" s="48" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="H143" s="12"/>
       <c r="I143" s="46" t="s">
@@ -10522,162 +10535,162 @@
       <c r="M143" s="6"/>
       <c r="N143" s="6"/>
     </row>
-    <row r="144" spans="1:14" ht="75.599999999999994">
+    <row r="144" spans="1:14" ht="37.799999999999997">
       <c r="A144" s="11"/>
-      <c r="B144" s="106"/>
+      <c r="B144" s="111" t="str">
+        <f>master!B121</f>
+        <v>JUnit</v>
+      </c>
       <c r="C144" s="78" t="str">
-        <f>master!C120</f>
-        <v>スタブとモック</v>
-      </c>
-      <c r="D144" s="107" t="s">
-        <v>316</v>
-      </c>
-      <c r="E144" s="108"/>
-      <c r="F144" s="109"/>
+        <f>master!C121</f>
+        <v>JUnitとは</v>
+      </c>
+      <c r="D144" s="114" t="s">
+        <v>317</v>
+      </c>
+      <c r="E144" s="115"/>
+      <c r="F144" s="116"/>
       <c r="G144" s="48" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H144" s="12"/>
       <c r="I144" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J144" s="44">
-        <v>3.472222222222222E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K144" s="40"/>
       <c r="L144" s="6"/>
       <c r="M144" s="6"/>
       <c r="N144" s="6"/>
     </row>
-    <row r="145" spans="1:14" ht="37.799999999999997">
+    <row r="145" spans="1:14" ht="25.2">
       <c r="A145" s="11"/>
-      <c r="B145" s="105" t="str">
-        <f>master!B121</f>
-        <v>JUnit</v>
-      </c>
+      <c r="B145" s="112"/>
       <c r="C145" s="78" t="str">
-        <f>master!C121</f>
-        <v>JUnitとは</v>
-      </c>
-      <c r="D145" s="107" t="s">
-        <v>317</v>
-      </c>
-      <c r="E145" s="108"/>
-      <c r="F145" s="109"/>
+        <f>master!C122</f>
+        <v>参考文献</v>
+      </c>
+      <c r="D145" s="114"/>
+      <c r="E145" s="115"/>
+      <c r="F145" s="116"/>
       <c r="G145" s="48" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H145" s="12"/>
       <c r="I145" s="46" t="s">
         <v>24</v>
       </c>
       <c r="J145" s="44">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K145" s="40"/>
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
       <c r="N145" s="6"/>
     </row>
-    <row r="146" spans="1:14" ht="25.2">
+    <row r="146" spans="1:14" ht="37.799999999999997">
       <c r="A146" s="11"/>
-      <c r="B146" s="106"/>
-      <c r="C146" s="78" t="str">
-        <f>master!C122</f>
-        <v>参考文献</v>
-      </c>
-      <c r="D146" s="107"/>
-      <c r="E146" s="108"/>
-      <c r="F146" s="109"/>
-      <c r="G146" s="48" t="s">
-        <v>382</v>
-      </c>
-      <c r="H146" s="12"/>
-      <c r="I146" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="J146" s="44">
-        <v>6.9444444444444447E-4</v>
-      </c>
-      <c r="K146" s="40"/>
+      <c r="B146" s="90" t="str">
+        <f>master!B67</f>
+        <v>課題1の実施</v>
+      </c>
+      <c r="C146" s="58" t="str">
+        <f>master!C67</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D146" s="105" t="s">
+        <v>318</v>
+      </c>
+      <c r="E146" s="106"/>
+      <c r="F146" s="107"/>
+      <c r="G146" s="58" t="s">
+        <v>43</v>
+      </c>
+      <c r="H146" s="59"/>
+      <c r="I146" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J146" s="61" t="s">
+        <v>433</v>
+      </c>
+      <c r="K146" s="62"/>
       <c r="L146" s="6"/>
       <c r="M146" s="6"/>
       <c r="N146" s="6"/>
     </row>
-    <row r="147" spans="1:14" ht="37.799999999999997">
+    <row r="147" spans="1:14" ht="25.2">
       <c r="A147" s="11"/>
-      <c r="B147" s="90" t="str">
-        <f>master!B67</f>
-        <v>課題1の実施</v>
+      <c r="B147" s="108" t="str">
+        <f>master!B124</f>
+        <v>課題2の導入</v>
       </c>
       <c r="C147" s="58" t="str">
-        <f>master!C67</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D147" s="110" t="s">
-        <v>318</v>
-      </c>
-      <c r="E147" s="111"/>
-      <c r="F147" s="112"/>
+        <f>master!C124</f>
+        <v>演習課題の概要</v>
+      </c>
+      <c r="D147" s="105" t="s">
+        <v>334</v>
+      </c>
+      <c r="E147" s="106"/>
+      <c r="F147" s="107"/>
       <c r="G147" s="58" t="s">
-        <v>43</v>
+        <v>393</v>
       </c>
       <c r="H147" s="59"/>
       <c r="I147" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J147" s="61" t="s">
-        <v>433</v>
+      <c r="J147" s="61">
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K147" s="62"/>
       <c r="L147" s="6"/>
       <c r="M147" s="6"/>
       <c r="N147" s="6"/>
     </row>
-    <row r="148" spans="1:14" ht="25.2">
+    <row r="148" spans="1:14" ht="138.6">
       <c r="A148" s="11"/>
-      <c r="B148" s="113" t="str">
-        <f>master!B124</f>
-        <v>課題2の導入</v>
-      </c>
+      <c r="B148" s="110"/>
       <c r="C148" s="58" t="str">
-        <f>master!C124</f>
-        <v>演習課題の概要</v>
-      </c>
-      <c r="D148" s="110" t="s">
-        <v>334</v>
-      </c>
-      <c r="E148" s="111"/>
-      <c r="F148" s="112"/>
+        <f>master!C125</f>
+        <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
+      </c>
+      <c r="D148" s="105" t="s">
+        <v>335</v>
+      </c>
+      <c r="E148" s="106"/>
+      <c r="F148" s="107"/>
       <c r="G148" s="58" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H148" s="59"/>
       <c r="I148" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J148" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K148" s="62"/>
       <c r="L148" s="6"/>
       <c r="M148" s="6"/>
       <c r="N148" s="6"/>
     </row>
-    <row r="149" spans="1:14" ht="138.6">
+    <row r="149" spans="1:14" ht="50.4">
       <c r="A149" s="11"/>
-      <c r="B149" s="114"/>
+      <c r="B149" s="110"/>
       <c r="C149" s="58" t="str">
-        <f>master!C125</f>
-        <v>[構造理解] Webアプリケーションで必要なもの  ※再掲</v>
-      </c>
-      <c r="D149" s="110" t="s">
-        <v>335</v>
-      </c>
-      <c r="E149" s="111"/>
-      <c r="F149" s="112"/>
+        <f>master!C126</f>
+        <v>テストクラスを作成する単位</v>
+      </c>
+      <c r="D149" s="105" t="s">
+        <v>336</v>
+      </c>
+      <c r="E149" s="106"/>
+      <c r="F149" s="107"/>
       <c r="G149" s="58" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H149" s="59"/>
       <c r="I149" s="60" t="s">
@@ -10691,179 +10704,179 @@
       <c r="M149" s="6"/>
       <c r="N149" s="6"/>
     </row>
-    <row r="150" spans="1:14" ht="50.4">
+    <row r="150" spans="1:14" ht="113.4">
       <c r="A150" s="11"/>
-      <c r="B150" s="114"/>
+      <c r="B150" s="109"/>
       <c r="C150" s="58" t="str">
-        <f>master!C126</f>
-        <v>テストクラスを作成する単位</v>
-      </c>
-      <c r="D150" s="110" t="s">
-        <v>336</v>
-      </c>
-      <c r="E150" s="111"/>
-      <c r="F150" s="112"/>
+        <f>master!C127</f>
+        <v>JUnitで単体テスト</v>
+      </c>
+      <c r="D150" s="105" t="s">
+        <v>337</v>
+      </c>
+      <c r="E150" s="106"/>
+      <c r="F150" s="107"/>
       <c r="G150" s="58" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H150" s="59"/>
       <c r="I150" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J150" s="61">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K150" s="62"/>
       <c r="L150" s="6"/>
       <c r="M150" s="6"/>
       <c r="N150" s="6"/>
     </row>
-    <row r="151" spans="1:14" ht="113.4">
+    <row r="151" spans="1:14" ht="25.2">
       <c r="A151" s="11"/>
-      <c r="B151" s="115"/>
+      <c r="B151" s="108" t="str">
+        <f>master!B128</f>
+        <v>ハンズオン</v>
+      </c>
       <c r="C151" s="58" t="str">
-        <f>master!C127</f>
-        <v>JUnitで単体テスト</v>
-      </c>
-      <c r="D151" s="110" t="s">
-        <v>337</v>
-      </c>
-      <c r="E151" s="111"/>
-      <c r="F151" s="112"/>
+        <f>master!C128</f>
+        <v>バイブコーディングで単体テスト – はじめに</v>
+      </c>
+      <c r="D151" s="105" t="s">
+        <v>338</v>
+      </c>
+      <c r="E151" s="106"/>
+      <c r="F151" s="107"/>
       <c r="G151" s="58" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H151" s="59"/>
       <c r="I151" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J151" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K151" s="62"/>
       <c r="L151" s="6"/>
       <c r="M151" s="6"/>
       <c r="N151" s="6"/>
     </row>
-    <row r="152" spans="1:14" ht="25.2">
+    <row r="152" spans="1:14" ht="50.4">
       <c r="A152" s="11"/>
-      <c r="B152" s="113" t="str">
-        <f>master!B128</f>
-        <v>ハンズオン</v>
-      </c>
+      <c r="B152" s="110"/>
       <c r="C152" s="58" t="str">
-        <f>master!C128</f>
-        <v>バイブコーディングで単体テスト – はじめに</v>
-      </c>
-      <c r="D152" s="110" t="s">
-        <v>338</v>
-      </c>
-      <c r="E152" s="111"/>
-      <c r="F152" s="112"/>
+        <f>master!C129</f>
+        <v>バイブコーディング単体テスト①テスト項目表を作る</v>
+      </c>
+      <c r="D152" s="105" t="s">
+        <v>339</v>
+      </c>
+      <c r="E152" s="106"/>
+      <c r="F152" s="107"/>
       <c r="G152" s="58" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="H152" s="59"/>
       <c r="I152" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J152" s="61">
-        <v>6.9444444444444447E-4</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K152" s="62"/>
       <c r="L152" s="6"/>
       <c r="M152" s="6"/>
       <c r="N152" s="6"/>
     </row>
-    <row r="153" spans="1:14" ht="50.4">
+    <row r="153" spans="1:14" ht="88.2">
       <c r="A153" s="11"/>
-      <c r="B153" s="114"/>
-      <c r="C153" s="58" t="str">
-        <f>master!C129</f>
-        <v>バイブコーディング単体テスト①テスト項目表を作る</v>
-      </c>
-      <c r="D153" s="110" t="s">
-        <v>339</v>
-      </c>
-      <c r="E153" s="111"/>
-      <c r="F153" s="112"/>
+      <c r="B153" s="110"/>
+      <c r="C153" s="58"/>
+      <c r="D153" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E153" s="106"/>
+      <c r="F153" s="107"/>
       <c r="G153" s="58" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H153" s="59"/>
       <c r="I153" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J153" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K153" s="62"/>
       <c r="L153" s="6"/>
       <c r="M153" s="6"/>
       <c r="N153" s="6"/>
     </row>
-    <row r="154" spans="1:14" ht="88.2">
+    <row r="154" spans="1:14" ht="50.4">
       <c r="A154" s="11"/>
-      <c r="B154" s="114"/>
-      <c r="C154" s="58"/>
-      <c r="D154" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E154" s="111"/>
-      <c r="F154" s="112"/>
+      <c r="B154" s="110"/>
+      <c r="C154" s="76" t="str">
+        <f>master!C130</f>
+        <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
+      </c>
+      <c r="D154" s="105" t="s">
+        <v>340</v>
+      </c>
+      <c r="E154" s="106"/>
+      <c r="F154" s="107"/>
       <c r="G154" s="58" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="H154" s="59"/>
       <c r="I154" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J154" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K154" s="62"/>
       <c r="L154" s="6"/>
       <c r="M154" s="6"/>
       <c r="N154" s="6"/>
     </row>
-    <row r="155" spans="1:14" ht="50.4">
+    <row r="155" spans="1:14" ht="88.2">
       <c r="A155" s="11"/>
-      <c r="B155" s="114"/>
-      <c r="C155" s="76" t="str">
-        <f>master!C130</f>
-        <v>バイブコーディング単体テスト②Repositoryのテストを作る</v>
-      </c>
-      <c r="D155" s="110" t="s">
-        <v>340</v>
-      </c>
-      <c r="E155" s="111"/>
-      <c r="F155" s="112"/>
+      <c r="B155" s="110"/>
+      <c r="C155" s="77"/>
+      <c r="D155" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E155" s="106"/>
+      <c r="F155" s="107"/>
       <c r="G155" s="58" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H155" s="59"/>
       <c r="I155" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J155" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K155" s="62"/>
       <c r="L155" s="6"/>
       <c r="M155" s="6"/>
       <c r="N155" s="6"/>
     </row>
-    <row r="156" spans="1:14" ht="88.2">
+    <row r="156" spans="1:14" ht="138.6">
       <c r="A156" s="11"/>
-      <c r="B156" s="114"/>
-      <c r="C156" s="77"/>
-      <c r="D156" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E156" s="111"/>
-      <c r="F156" s="112"/>
+      <c r="B156" s="110"/>
+      <c r="C156" s="58" t="str">
+        <f>master!C131</f>
+        <v>[解説] Repositoryのテストクラス（抜粋）</v>
+      </c>
+      <c r="D156" s="105" t="s">
+        <v>342</v>
+      </c>
+      <c r="E156" s="106"/>
+      <c r="F156" s="107"/>
       <c r="G156" s="58" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H156" s="59"/>
       <c r="I156" s="60" t="s">
@@ -10877,71 +10890,71 @@
       <c r="M156" s="6"/>
       <c r="N156" s="6"/>
     </row>
-    <row r="157" spans="1:14" ht="138.6">
+    <row r="157" spans="1:14" ht="50.4">
       <c r="A157" s="11"/>
-      <c r="B157" s="114"/>
-      <c r="C157" s="58" t="str">
-        <f>master!C131</f>
-        <v>[解説] Repositoryのテストクラス（抜粋）</v>
-      </c>
-      <c r="D157" s="110" t="s">
-        <v>342</v>
-      </c>
-      <c r="E157" s="111"/>
-      <c r="F157" s="112"/>
+      <c r="B157" s="110"/>
+      <c r="C157" s="76" t="str">
+        <f>master!C132</f>
+        <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
+      </c>
+      <c r="D157" s="105" t="s">
+        <v>340</v>
+      </c>
+      <c r="E157" s="106"/>
+      <c r="F157" s="107"/>
       <c r="G157" s="58" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H157" s="59"/>
       <c r="I157" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J157" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K157" s="62"/>
       <c r="L157" s="6"/>
       <c r="M157" s="6"/>
       <c r="N157" s="6"/>
     </row>
-    <row r="158" spans="1:14" ht="50.4">
+    <row r="158" spans="1:14" ht="88.2">
       <c r="A158" s="11"/>
-      <c r="B158" s="114"/>
-      <c r="C158" s="76" t="str">
-        <f>master!C132</f>
-        <v>バイブコーディング単体テスト③Serviceのテストを作る</v>
-      </c>
-      <c r="D158" s="110" t="s">
-        <v>340</v>
-      </c>
-      <c r="E158" s="111"/>
-      <c r="F158" s="112"/>
+      <c r="B158" s="110"/>
+      <c r="C158" s="77"/>
+      <c r="D158" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E158" s="106"/>
+      <c r="F158" s="107"/>
       <c r="G158" s="58" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H158" s="59"/>
       <c r="I158" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J158" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K158" s="62"/>
       <c r="L158" s="6"/>
       <c r="M158" s="6"/>
       <c r="N158" s="6"/>
     </row>
-    <row r="159" spans="1:14" ht="88.2">
+    <row r="159" spans="1:14" ht="138.6">
       <c r="A159" s="11"/>
-      <c r="B159" s="114"/>
-      <c r="C159" s="77"/>
-      <c r="D159" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E159" s="111"/>
-      <c r="F159" s="112"/>
+      <c r="B159" s="110"/>
+      <c r="C159" s="58" t="str">
+        <f>master!C133</f>
+        <v>[解説] Serviceのテストクラス（抜粋）</v>
+      </c>
+      <c r="D159" s="105" t="s">
+        <v>341</v>
+      </c>
+      <c r="E159" s="106"/>
+      <c r="F159" s="107"/>
       <c r="G159" s="58" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="H159" s="59"/>
       <c r="I159" s="60" t="s">
@@ -10955,71 +10968,71 @@
       <c r="M159" s="6"/>
       <c r="N159" s="6"/>
     </row>
-    <row r="160" spans="1:14" ht="138.6">
+    <row r="160" spans="1:14" ht="50.4">
       <c r="A160" s="11"/>
-      <c r="B160" s="114"/>
-      <c r="C160" s="58" t="str">
-        <f>master!C133</f>
-        <v>[解説] Serviceのテストクラス（抜粋）</v>
-      </c>
-      <c r="D160" s="110" t="s">
-        <v>341</v>
-      </c>
-      <c r="E160" s="111"/>
-      <c r="F160" s="112"/>
+      <c r="B160" s="110"/>
+      <c r="C160" s="76" t="str">
+        <f>master!C134</f>
+        <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
+      </c>
+      <c r="D160" s="105" t="s">
+        <v>340</v>
+      </c>
+      <c r="E160" s="106"/>
+      <c r="F160" s="107"/>
       <c r="G160" s="58" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H160" s="59"/>
       <c r="I160" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J160" s="61">
-        <v>6.9444444444444441E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K160" s="62"/>
       <c r="L160" s="6"/>
       <c r="M160" s="6"/>
       <c r="N160" s="6"/>
     </row>
-    <row r="161" spans="1:14" ht="50.4">
+    <row r="161" spans="1:14" ht="88.2">
       <c r="A161" s="11"/>
-      <c r="B161" s="114"/>
-      <c r="C161" s="76" t="str">
-        <f>master!C134</f>
-        <v>バイブコーディング単体テスト④Controllerのテストを作る</v>
-      </c>
-      <c r="D161" s="110" t="s">
-        <v>340</v>
-      </c>
-      <c r="E161" s="111"/>
-      <c r="F161" s="112"/>
+      <c r="B161" s="110"/>
+      <c r="C161" s="77"/>
+      <c r="D161" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="E161" s="106"/>
+      <c r="F161" s="107"/>
       <c r="G161" s="58" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="H161" s="59"/>
       <c r="I161" s="60" t="s">
         <v>24</v>
       </c>
       <c r="J161" s="61">
-        <v>3.472222222222222E-3</v>
+        <v>6.9444444444444441E-3</v>
       </c>
       <c r="K161" s="62"/>
       <c r="L161" s="6"/>
       <c r="M161" s="6"/>
       <c r="N161" s="6"/>
     </row>
-    <row r="162" spans="1:14" ht="88.2">
+    <row r="162" spans="1:14" ht="163.80000000000001">
       <c r="A162" s="11"/>
-      <c r="B162" s="114"/>
-      <c r="C162" s="77"/>
-      <c r="D162" s="110" t="s">
-        <v>193</v>
-      </c>
-      <c r="E162" s="111"/>
-      <c r="F162" s="112"/>
+      <c r="B162" s="109"/>
+      <c r="C162" s="58" t="str">
+        <f>master!C135</f>
+        <v>[解説] Controllerのテストクラス（抜粋）</v>
+      </c>
+      <c r="D162" s="105" t="s">
+        <v>343</v>
+      </c>
+      <c r="E162" s="106"/>
+      <c r="F162" s="107"/>
       <c r="G162" s="58" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H162" s="59"/>
       <c r="I162" s="60" t="s">
@@ -11033,18 +11046,21 @@
       <c r="M162" s="6"/>
       <c r="N162" s="6"/>
     </row>
-    <row r="163" spans="1:14" ht="163.80000000000001">
+    <row r="163" spans="1:14" ht="165" customHeight="1">
       <c r="A163" s="11"/>
-      <c r="B163" s="115"/>
+      <c r="B163" s="108" t="str">
+        <f>master!B136</f>
+        <v>課題2の実施</v>
+      </c>
       <c r="C163" s="58" t="str">
-        <f>master!C135</f>
-        <v>[解説] Controllerのテストクラス（抜粋）</v>
-      </c>
-      <c r="D163" s="110" t="s">
-        <v>343</v>
-      </c>
-      <c r="E163" s="111"/>
-      <c r="F163" s="112"/>
+        <f>master!C136</f>
+        <v>ここから各自で演習を始めましょう。</v>
+      </c>
+      <c r="D163" s="105" t="s">
+        <v>344</v>
+      </c>
+      <c r="E163" s="106"/>
+      <c r="F163" s="107"/>
       <c r="G163" s="58" t="s">
         <v>398</v>
       </c>
@@ -11052,88 +11068,85 @@
       <c r="I163" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J163" s="61">
-        <v>6.9444444444444441E-3</v>
+      <c r="J163" s="61" t="s">
+        <v>433</v>
       </c>
       <c r="K163" s="62"/>
       <c r="L163" s="6"/>
       <c r="M163" s="6"/>
       <c r="N163" s="6"/>
     </row>
-    <row r="164" spans="1:14" ht="165" customHeight="1">
+    <row r="164" spans="1:14" ht="151.19999999999999">
       <c r="A164" s="11"/>
-      <c r="B164" s="113" t="str">
-        <f>master!B136</f>
-        <v>課題2の実施</v>
-      </c>
+      <c r="B164" s="109"/>
       <c r="C164" s="58" t="str">
-        <f>master!C136</f>
-        <v>ここから各自で演習を始めましょう。</v>
-      </c>
-      <c r="D164" s="110" t="s">
-        <v>344</v>
-      </c>
-      <c r="E164" s="111"/>
-      <c r="F164" s="112"/>
+        <f>master!C137</f>
+        <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
+      </c>
+      <c r="D164" s="105" t="s">
+        <v>432</v>
+      </c>
+      <c r="E164" s="106"/>
+      <c r="F164" s="107"/>
       <c r="G164" s="58" t="s">
-        <v>398</v>
+        <v>431</v>
       </c>
       <c r="H164" s="59"/>
       <c r="I164" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J164" s="61" t="s">
-        <v>433</v>
+      <c r="J164" s="61">
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="K164" s="62"/>
       <c r="L164" s="6"/>
       <c r="M164" s="6"/>
       <c r="N164" s="6"/>
     </row>
-    <row r="165" spans="1:14" ht="151.19999999999999">
+    <row r="165" spans="1:14" ht="163.80000000000001">
       <c r="A165" s="11"/>
-      <c r="B165" s="115"/>
+      <c r="B165" s="108" t="str">
+        <f>master!B139</f>
+        <v>追加課題</v>
+      </c>
       <c r="C165" s="58" t="str">
-        <f>master!C137</f>
-        <v>[終了条件] 講師配布のテストプログラム(JUnit)が成功すること</v>
-      </c>
-      <c r="D165" s="110" t="s">
-        <v>432</v>
-      </c>
-      <c r="E165" s="111"/>
-      <c r="F165" s="112"/>
+        <f>master!C139</f>
+        <v>演習課題の概要</v>
+      </c>
+      <c r="D165" s="105" t="s">
+        <v>346</v>
+      </c>
+      <c r="E165" s="106"/>
+      <c r="F165" s="107"/>
       <c r="G165" s="58" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="H165" s="59"/>
       <c r="I165" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J165" s="61">
-        <v>8.3333333333333329E-2</v>
+      <c r="J165" s="61" t="s">
+        <v>433</v>
       </c>
       <c r="K165" s="62"/>
       <c r="L165" s="6"/>
       <c r="M165" s="6"/>
       <c r="N165" s="6"/>
     </row>
-    <row r="166" spans="1:14" ht="163.80000000000001">
+    <row r="166" spans="1:14" ht="25.2">
       <c r="A166" s="11"/>
-      <c r="B166" s="113" t="str">
-        <f>master!B139</f>
-        <v>追加課題</v>
-      </c>
+      <c r="B166" s="110"/>
       <c r="C166" s="58" t="str">
-        <f>master!C139</f>
-        <v>演習課題の概要</v>
-      </c>
-      <c r="D166" s="110" t="s">
-        <v>346</v>
-      </c>
-      <c r="E166" s="111"/>
-      <c r="F166" s="112"/>
+        <f>master!C140</f>
+        <v>追加課題①：送料の表示機能</v>
+      </c>
+      <c r="D166" s="105" t="s">
+        <v>348</v>
+      </c>
+      <c r="E166" s="106"/>
+      <c r="F166" s="107"/>
       <c r="G166" s="58" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H166" s="59"/>
       <c r="I166" s="60" t="s">
@@ -11149,16 +11162,16 @@
     </row>
     <row r="167" spans="1:14" ht="25.2">
       <c r="A167" s="11"/>
-      <c r="B167" s="114"/>
+      <c r="B167" s="110"/>
       <c r="C167" s="58" t="str">
-        <f>master!C140</f>
-        <v>追加課題①：送料の表示機能</v>
-      </c>
-      <c r="D167" s="110" t="s">
+        <f>master!C141</f>
+        <v>追加課題②：クーポン機能</v>
+      </c>
+      <c r="D167" s="105" t="s">
         <v>348</v>
       </c>
-      <c r="E167" s="111"/>
-      <c r="F167" s="112"/>
+      <c r="E167" s="106"/>
+      <c r="F167" s="107"/>
       <c r="G167" s="58" t="s">
         <v>426</v>
       </c>
@@ -11176,16 +11189,16 @@
     </row>
     <row r="168" spans="1:14" ht="25.2">
       <c r="A168" s="11"/>
-      <c r="B168" s="114"/>
+      <c r="B168" s="109"/>
       <c r="C168" s="58" t="str">
-        <f>master!C141</f>
-        <v>追加課題②：クーポン機能</v>
-      </c>
-      <c r="D168" s="110" t="s">
+        <f>master!C142</f>
+        <v>追加課題③：ユーザーアカウント機能</v>
+      </c>
+      <c r="D168" s="105" t="s">
         <v>348</v>
       </c>
-      <c r="E168" s="111"/>
-      <c r="F168" s="112"/>
+      <c r="E168" s="106"/>
+      <c r="F168" s="107"/>
       <c r="G168" s="58" t="s">
         <v>426</v>
       </c>
@@ -11201,50 +11214,50 @@
       <c r="M168" s="6"/>
       <c r="N168" s="6"/>
     </row>
-    <row r="169" spans="1:14" ht="25.2">
+    <row r="169" spans="1:14" ht="176.4">
       <c r="A169" s="11"/>
-      <c r="B169" s="115"/>
+      <c r="B169" s="108" t="str">
+        <f>master!B144</f>
+        <v>課題の振り返り</v>
+      </c>
       <c r="C169" s="58" t="str">
-        <f>master!C142</f>
-        <v>追加課題③：ユーザーアカウント機能</v>
-      </c>
-      <c r="D169" s="110" t="s">
-        <v>348</v>
-      </c>
-      <c r="E169" s="111"/>
-      <c r="F169" s="112"/>
+        <f>master!C144</f>
+        <v>サンプルのAPとの自分のAPとの比較</v>
+      </c>
+      <c r="D169" s="105" t="s">
+        <v>428</v>
+      </c>
+      <c r="E169" s="106"/>
+      <c r="F169" s="107"/>
       <c r="G169" s="58" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="H169" s="59"/>
       <c r="I169" s="60" t="s">
         <v>24</v>
       </c>
-      <c r="J169" s="61" t="s">
-        <v>433</v>
+      <c r="J169" s="61">
+        <v>2.0833333333333332E-2</v>
       </c>
       <c r="K169" s="62"/>
       <c r="L169" s="6"/>
       <c r="M169" s="6"/>
       <c r="N169" s="6"/>
     </row>
-    <row r="170" spans="1:14" ht="176.4">
+    <row r="170" spans="1:14" ht="63">
       <c r="A170" s="11"/>
-      <c r="B170" s="113" t="str">
-        <f>master!B144</f>
-        <v>課題の振り返り</v>
-      </c>
+      <c r="B170" s="109"/>
       <c r="C170" s="58" t="str">
-        <f>master!C144</f>
-        <v>サンプルのAPとの自分のAPとの比較</v>
-      </c>
-      <c r="D170" s="110" t="s">
-        <v>428</v>
-      </c>
-      <c r="E170" s="111"/>
-      <c r="F170" s="112"/>
+        <f>master!C145</f>
+        <v>レポートの作成</v>
+      </c>
+      <c r="D170" s="105" t="s">
+        <v>430</v>
+      </c>
+      <c r="E170" s="106"/>
+      <c r="F170" s="107"/>
       <c r="G170" s="58" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="H170" s="59"/>
       <c r="I170" s="60" t="s">
@@ -11258,121 +11271,113 @@
       <c r="M170" s="6"/>
       <c r="N170" s="6"/>
     </row>
-    <row r="171" spans="1:14" ht="63">
-      <c r="A171" s="11"/>
-      <c r="B171" s="115"/>
-      <c r="C171" s="58" t="str">
-        <f>master!C145</f>
-        <v>レポートの作成</v>
-      </c>
-      <c r="D171" s="110" t="s">
-        <v>430</v>
-      </c>
-      <c r="E171" s="111"/>
-      <c r="F171" s="112"/>
-      <c r="G171" s="58" t="s">
-        <v>427</v>
-      </c>
-      <c r="H171" s="59"/>
-      <c r="I171" s="60" t="s">
-        <v>24</v>
-      </c>
-      <c r="J171" s="61">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K171" s="62"/>
-      <c r="L171" s="6"/>
-      <c r="M171" s="6"/>
-      <c r="N171" s="6"/>
-    </row>
-    <row r="172" spans="1:14" ht="15" customHeight="1">
-      <c r="J172" s="43"/>
-    </row>
-    <row r="173" spans="1:14" ht="15" customHeight="1"/>
+    <row r="171" spans="1:14" ht="15" customHeight="1">
+      <c r="J171" s="43"/>
+    </row>
+    <row r="172" spans="1:14" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="180">
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="D146:F146"/>
     <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="B170:B171"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D159:F159"/>
     <mergeCell ref="D153:F153"/>
     <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="B166:B169"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="B107:B118"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D156:F156"/>
+    <mergeCell ref="B151:B162"/>
+    <mergeCell ref="B147:B150"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="B126:B143"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D120:F120"/>
     <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D126:F126"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="D21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="K21:K22"/>
-    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="B94:B99"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="B72:B91"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="B56:B58"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="B63:B71"/>
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="D47:F47"/>
     <mergeCell ref="D48:F48"/>
     <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="B29:B36"/>
+    <mergeCell ref="B37:B55"/>
     <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="B24:B29"/>
-    <mergeCell ref="B30:B37"/>
-    <mergeCell ref="B38:B56"/>
     <mergeCell ref="D51:F51"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="D53:F53"/>
     <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D40:F40"/>
     <mergeCell ref="D41:F41"/>
@@ -11381,96 +11386,77 @@
     <mergeCell ref="D44:F44"/>
     <mergeCell ref="D45:F45"/>
     <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="B57:B59"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="B64:B72"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="B73:B92"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="B95:B100"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D20:F21"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B106:B117"/>
     <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="B93:B94"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="B120:B122"/>
-    <mergeCell ref="B123:B126"/>
-    <mergeCell ref="B127:B144"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="B163:B164"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
     <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D167:F167"/>
     <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="B169:B170"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D160:F160"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="B165:B168"/>
     <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="B152:B163"/>
-    <mergeCell ref="B148:B151"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="D135:F135"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11483,7 +11469,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H23:H171</xm:sqref>
+          <xm:sqref>H22:H170</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
